--- a/artkal-c197-m221-418-official/colors.xlsx
+++ b/artkal-c197-m221-418-official/colors.xlsx
@@ -4042,7 +4042,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>原始查询名</t>
+          <t>系列短名</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/artkal-c197-m221-418-official/colors.xlsx
+++ b/artkal-c197-m221-418-official/colors.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="信息" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_C" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_CE" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_CG" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_CP" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_CT" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_MA" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_MB" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_MC" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_MD" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_ME" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_MF" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_MG" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_MH" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_MM" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="信息" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="01_C" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="02_CE" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="03_CG" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="04_CP" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="05_CT" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="06_MA" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="07_MB" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="08_MC" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="09_MD" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="10_ME" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="11_MF" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="12_MG" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="13_MH" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="14_MM" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/artkal-c197-m221-418-official/colors.xlsx
+++ b/artkal-c197-m221-418-official/colors.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="信息" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="01_C" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="02_CE" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="03_CG" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="04_CP" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="05_CT" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="06_MA" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="07_MB" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="08_MC" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="09_MD" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="10_ME" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="11_MF" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="12_MG" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="13_MH" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="14_MM" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="信息" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_C" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_CE" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_CG" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_CP" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_CT" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_MA" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_MB" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_MC" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_MD" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_ME" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_MF" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_MG" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_MH" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_MM" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -64,7 +64,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="395">
+  <fills count="417">
     <fill>
       <patternFill/>
     </fill>
@@ -943,7 +943,117 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
+        <fgColor rgb="FFB2B9BF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBEA6BA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF62B6D8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8985C1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB9D96"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ABA96"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94637F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ECAB2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD8F75"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBA16C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC8DA4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8A506A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3063A3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3E5694"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6C6D2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE664A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6875C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4C764"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF32B195"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF757DD1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB1DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5688A0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6B849D"/>
       </patternFill>
     </fill>
     <fill>
@@ -2063,7 +2173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="794">
+  <cellXfs count="838">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2784,7 +2894,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="178" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="179" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="179" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="179" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2796,7 +2906,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="181" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="182" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="182" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="182" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2816,23 +2926,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="186" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="187" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="187" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="187" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="188" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="188" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="188" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="189" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="189" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="189" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="190" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="190" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="190" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="191" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="191" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="191" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2844,11 +2954,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="193" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="194" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="194" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="194" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="195" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="195" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="195" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2856,11 +2966,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="196" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="197" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="197" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="197" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="198" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="198" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="198" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2904,27 +3014,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="208" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="209" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="209" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="209" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="210" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="210" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="210" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="211" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="211" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="211" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="212" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="212" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="212" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="213" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="213" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="213" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="214" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="214" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="214" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2936,7 +3046,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="216" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="217" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="217" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="217" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2944,7 +3054,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="218" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="219" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="219" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="219" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2960,15 +3070,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="222" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="223" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="223" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="223" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="224" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="224" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="224" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="225" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="225" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="225" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2976,11 +3086,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="226" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="227" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="227" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="227" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="228" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="228" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="228" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2992,15 +3102,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="230" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="231" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="231" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="231" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="232" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="232" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="232" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="233" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="233" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="233" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3008,11 +3118,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="234" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="235" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="235" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="235" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="236" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="236" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="236" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3020,7 +3130,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="237" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="238" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="238" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="238" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3028,7 +3138,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="239" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="240" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="240" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="240" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3036,11 +3146,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="241" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="242" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="242" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="242" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="243" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="243" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="243" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3056,7 +3166,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="246" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="247" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="247" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="247" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3076,15 +3186,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="251" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="252" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="252" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="252" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="253" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="253" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="253" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="254" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="254" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="254" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3112,11 +3222,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="260" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="261" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="261" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="261" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="262" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="262" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="262" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3132,7 +3242,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="265" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="266" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="266" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="266" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3148,27 +3258,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="269" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="270" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="270" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="270" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="271" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="271" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="271" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="272" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="272" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="272" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="273" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="273" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="273" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="274" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="274" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="274" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="275" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="275" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="275" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3176,11 +3286,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="276" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="277" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="277" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="277" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="278" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="278" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="278" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3196,15 +3306,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="281" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="282" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="282" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="282" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="283" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="283" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="283" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="284" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="284" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="284" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3212,7 +3322,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="285" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="286" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="286" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="286" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3224,11 +3334,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="288" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="289" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="289" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="289" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="290" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="290" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="290" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3236,7 +3346,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="291" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="292" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="292" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="292" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3244,7 +3354,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="293" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="294" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="294" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="294" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3252,7 +3362,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="295" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="296" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="296" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="296" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3260,7 +3370,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="297" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="298" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="298" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="298" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3268,7 +3378,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="299" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="300" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="300" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="300" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3276,7 +3386,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="301" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="302" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="302" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="302" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3288,15 +3398,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="304" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="305" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="305" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="305" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="306" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="306" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="306" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="307" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="307" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="307" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3304,19 +3414,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="308" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="309" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="309" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="309" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="310" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="310" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="310" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="311" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="311" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="311" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="312" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="312" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="312" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3328,7 +3438,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="314" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="315" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="315" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="315" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3344,11 +3454,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="318" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="319" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="319" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="319" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="320" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="320" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="320" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3360,7 +3470,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="322" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="323" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="323" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="323" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3368,11 +3478,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="324" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="325" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="325" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="325" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="326" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="326" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="326" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3380,7 +3490,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="327" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="328" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="328" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="328" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3392,19 +3502,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="330" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="331" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="331" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="331" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="332" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="332" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="332" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="333" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="333" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="333" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="334" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="334" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="334" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3416,7 +3526,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="336" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="337" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="337" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="337" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3424,23 +3534,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="338" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="339" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="339" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="339" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="340" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="340" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="340" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="341" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="341" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="341" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="342" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="342" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="342" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="343" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="343" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="343" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3456,7 +3566,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="346" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="347" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="347" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="347" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3468,27 +3578,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="349" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="350" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="350" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="350" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="351" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="351" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="351" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="352" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="352" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="352" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="353" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="353" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="353" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="354" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="354" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="354" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="355" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="355" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="355" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3500,7 +3610,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="357" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="358" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="358" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="358" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3508,19 +3618,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="359" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="360" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="360" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="360" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="361" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="361" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="361" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="362" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="362" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="362" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="363" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="363" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="363" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3536,11 +3646,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="366" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="367" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="367" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="367" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="368" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="368" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="368" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3548,7 +3658,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="369" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="370" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="370" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="370" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3556,15 +3666,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="371" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="372" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="372" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="372" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="373" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="373" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="373" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="374" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="374" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="374" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3576,7 +3686,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="376" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="377" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="377" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="377" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3588,27 +3698,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="379" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="380" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="380" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="380" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="381" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="381" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="381" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="382" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="382" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="382" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="383" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="383" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="383" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="384" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="384" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="384" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="385" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="385" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="385" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3616,7 +3726,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="386" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="387" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="387" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="387" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3632,7 +3742,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="390" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="391" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="391" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="391" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3640,14 +3750,102 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="392" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="393" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="393" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="393" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="394" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="394" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="394" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="395" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="395" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="396" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="396" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="397" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="397" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="398" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="398" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="399" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="399" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="400" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="400" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="401" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="401" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="402" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="402" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="403" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="403" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="404" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="404" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="405" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="405" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="406" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="406" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="407" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="407" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="408" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="408" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="409" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="409" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="410" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="410" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="411" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="411" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="412" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="412" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="413" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="413" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="414" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="414" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="415" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="415" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="416" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="416" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4080,17 +4278,17 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>394</v>
+        <v>418</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>无 RGB / 透明或未公开</t>
+          <t>无 RGB / 未填数值</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4148,14 +4346,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://artkalfusebeads.com/pages/c-color-chart</t>
+          <t>https://cdn.shopify.com/s/files/1/1323/8195/files/M_MINI_Beads_RGB_Color_Chart_2025.pdf?v=1760661747</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/1323/8195/files/M_MINI_Beads_RGB_Color_Chart_2025.pdf?v=1760661747</t>
+          <t>https://bitbead.pomodiary.com/zh/colors/artkal-mini/MH1</t>
         </is>
       </c>
     </row>
@@ -4209,56 +4407,56 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="532" t="inlineStr">
+      <c r="A4" s="576" t="inlineStr">
         <is>
           <t>MD1</t>
         </is>
       </c>
-      <c r="B4" s="533" t="n"/>
-      <c r="C4" s="533" t="n"/>
-      <c r="D4" s="533" t="n"/>
-      <c r="F4" s="534" t="inlineStr">
+      <c r="B4" s="577" t="n"/>
+      <c r="C4" s="577" t="n"/>
+      <c r="D4" s="577" t="n"/>
+      <c r="F4" s="578" t="inlineStr">
         <is>
           <t>MD2</t>
         </is>
       </c>
-      <c r="G4" s="535" t="n"/>
-      <c r="H4" s="535" t="n"/>
-      <c r="I4" s="535" t="n"/>
-      <c r="K4" s="536" t="inlineStr">
+      <c r="G4" s="579" t="n"/>
+      <c r="H4" s="579" t="n"/>
+      <c r="I4" s="579" t="n"/>
+      <c r="K4" s="580" t="inlineStr">
         <is>
           <t>MD3</t>
         </is>
       </c>
-      <c r="L4" s="537" t="n"/>
-      <c r="M4" s="537" t="n"/>
-      <c r="N4" s="537" t="n"/>
-      <c r="P4" s="538" t="inlineStr">
+      <c r="L4" s="581" t="n"/>
+      <c r="M4" s="581" t="n"/>
+      <c r="N4" s="581" t="n"/>
+      <c r="P4" s="582" t="inlineStr">
         <is>
           <t>MD4</t>
         </is>
       </c>
-      <c r="Q4" s="539" t="n"/>
-      <c r="R4" s="539" t="n"/>
-      <c r="S4" s="539" t="n"/>
+      <c r="Q4" s="583" t="n"/>
+      <c r="R4" s="583" t="n"/>
+      <c r="S4" s="583" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="533" t="n"/>
-      <c r="B5" s="533" t="n"/>
-      <c r="C5" s="533" t="n"/>
-      <c r="D5" s="533" t="n"/>
-      <c r="F5" s="535" t="n"/>
-      <c r="G5" s="535" t="n"/>
-      <c r="H5" s="535" t="n"/>
-      <c r="I5" s="535" t="n"/>
-      <c r="K5" s="537" t="n"/>
-      <c r="L5" s="537" t="n"/>
-      <c r="M5" s="537" t="n"/>
-      <c r="N5" s="537" t="n"/>
-      <c r="P5" s="539" t="n"/>
-      <c r="Q5" s="539" t="n"/>
-      <c r="R5" s="539" t="n"/>
-      <c r="S5" s="539" t="n"/>
+      <c r="A5" s="577" t="n"/>
+      <c r="B5" s="577" t="n"/>
+      <c r="C5" s="577" t="n"/>
+      <c r="D5" s="577" t="n"/>
+      <c r="F5" s="579" t="n"/>
+      <c r="G5" s="579" t="n"/>
+      <c r="H5" s="579" t="n"/>
+      <c r="I5" s="579" t="n"/>
+      <c r="K5" s="581" t="n"/>
+      <c r="L5" s="581" t="n"/>
+      <c r="M5" s="581" t="n"/>
+      <c r="N5" s="581" t="n"/>
+      <c r="P5" s="583" t="n"/>
+      <c r="Q5" s="583" t="n"/>
+      <c r="R5" s="583" t="n"/>
+      <c r="S5" s="583" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -4363,56 +4561,56 @@
       <c r="S8" s="15" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="540" t="inlineStr">
+      <c r="A9" s="584" t="inlineStr">
         <is>
           <t>MD5</t>
         </is>
       </c>
-      <c r="B9" s="541" t="n"/>
-      <c r="C9" s="541" t="n"/>
-      <c r="D9" s="541" t="n"/>
-      <c r="F9" s="542" t="inlineStr">
+      <c r="B9" s="585" t="n"/>
+      <c r="C9" s="585" t="n"/>
+      <c r="D9" s="585" t="n"/>
+      <c r="F9" s="586" t="inlineStr">
         <is>
           <t>MD6</t>
         </is>
       </c>
-      <c r="G9" s="543" t="n"/>
-      <c r="H9" s="543" t="n"/>
-      <c r="I9" s="543" t="n"/>
-      <c r="K9" s="544" t="inlineStr">
+      <c r="G9" s="587" t="n"/>
+      <c r="H9" s="587" t="n"/>
+      <c r="I9" s="587" t="n"/>
+      <c r="K9" s="588" t="inlineStr">
         <is>
           <t>MD7</t>
         </is>
       </c>
-      <c r="L9" s="545" t="n"/>
-      <c r="M9" s="545" t="n"/>
-      <c r="N9" s="545" t="n"/>
-      <c r="P9" s="546" t="inlineStr">
+      <c r="L9" s="589" t="n"/>
+      <c r="M9" s="589" t="n"/>
+      <c r="N9" s="589" t="n"/>
+      <c r="P9" s="590" t="inlineStr">
         <is>
           <t>MD8</t>
         </is>
       </c>
-      <c r="Q9" s="547" t="n"/>
-      <c r="R9" s="547" t="n"/>
-      <c r="S9" s="547" t="n"/>
+      <c r="Q9" s="591" t="n"/>
+      <c r="R9" s="591" t="n"/>
+      <c r="S9" s="591" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="541" t="n"/>
-      <c r="B10" s="541" t="n"/>
-      <c r="C10" s="541" t="n"/>
-      <c r="D10" s="541" t="n"/>
-      <c r="F10" s="543" t="n"/>
-      <c r="G10" s="543" t="n"/>
-      <c r="H10" s="543" t="n"/>
-      <c r="I10" s="543" t="n"/>
-      <c r="K10" s="545" t="n"/>
-      <c r="L10" s="545" t="n"/>
-      <c r="M10" s="545" t="n"/>
-      <c r="N10" s="545" t="n"/>
-      <c r="P10" s="547" t="n"/>
-      <c r="Q10" s="547" t="n"/>
-      <c r="R10" s="547" t="n"/>
-      <c r="S10" s="547" t="n"/>
+      <c r="A10" s="585" t="n"/>
+      <c r="B10" s="585" t="n"/>
+      <c r="C10" s="585" t="n"/>
+      <c r="D10" s="585" t="n"/>
+      <c r="F10" s="587" t="n"/>
+      <c r="G10" s="587" t="n"/>
+      <c r="H10" s="587" t="n"/>
+      <c r="I10" s="587" t="n"/>
+      <c r="K10" s="589" t="n"/>
+      <c r="L10" s="589" t="n"/>
+      <c r="M10" s="589" t="n"/>
+      <c r="N10" s="589" t="n"/>
+      <c r="P10" s="591" t="n"/>
+      <c r="Q10" s="591" t="n"/>
+      <c r="R10" s="591" t="n"/>
+      <c r="S10" s="591" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -4517,56 +4715,56 @@
       <c r="S13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="548" t="inlineStr">
+      <c r="A14" s="592" t="inlineStr">
         <is>
           <t>MD9</t>
         </is>
       </c>
-      <c r="B14" s="549" t="n"/>
-      <c r="C14" s="549" t="n"/>
-      <c r="D14" s="549" t="n"/>
-      <c r="F14" s="550" t="inlineStr">
+      <c r="B14" s="593" t="n"/>
+      <c r="C14" s="593" t="n"/>
+      <c r="D14" s="593" t="n"/>
+      <c r="F14" s="594" t="inlineStr">
         <is>
           <t>MD10</t>
         </is>
       </c>
-      <c r="G14" s="551" t="n"/>
-      <c r="H14" s="551" t="n"/>
-      <c r="I14" s="551" t="n"/>
-      <c r="K14" s="552" t="inlineStr">
+      <c r="G14" s="595" t="n"/>
+      <c r="H14" s="595" t="n"/>
+      <c r="I14" s="595" t="n"/>
+      <c r="K14" s="596" t="inlineStr">
         <is>
           <t>MD11</t>
         </is>
       </c>
-      <c r="L14" s="553" t="n"/>
-      <c r="M14" s="553" t="n"/>
-      <c r="N14" s="553" t="n"/>
-      <c r="P14" s="554" t="inlineStr">
+      <c r="L14" s="597" t="n"/>
+      <c r="M14" s="597" t="n"/>
+      <c r="N14" s="597" t="n"/>
+      <c r="P14" s="598" t="inlineStr">
         <is>
           <t>MD12</t>
         </is>
       </c>
-      <c r="Q14" s="555" t="n"/>
-      <c r="R14" s="555" t="n"/>
-      <c r="S14" s="555" t="n"/>
+      <c r="Q14" s="599" t="n"/>
+      <c r="R14" s="599" t="n"/>
+      <c r="S14" s="599" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="549" t="n"/>
-      <c r="B15" s="549" t="n"/>
-      <c r="C15" s="549" t="n"/>
-      <c r="D15" s="549" t="n"/>
-      <c r="F15" s="551" t="n"/>
-      <c r="G15" s="551" t="n"/>
-      <c r="H15" s="551" t="n"/>
-      <c r="I15" s="551" t="n"/>
-      <c r="K15" s="553" t="n"/>
-      <c r="L15" s="553" t="n"/>
-      <c r="M15" s="553" t="n"/>
-      <c r="N15" s="553" t="n"/>
-      <c r="P15" s="555" t="n"/>
-      <c r="Q15" s="555" t="n"/>
-      <c r="R15" s="555" t="n"/>
-      <c r="S15" s="555" t="n"/>
+      <c r="A15" s="593" t="n"/>
+      <c r="B15" s="593" t="n"/>
+      <c r="C15" s="593" t="n"/>
+      <c r="D15" s="593" t="n"/>
+      <c r="F15" s="595" t="n"/>
+      <c r="G15" s="595" t="n"/>
+      <c r="H15" s="595" t="n"/>
+      <c r="I15" s="595" t="n"/>
+      <c r="K15" s="597" t="n"/>
+      <c r="L15" s="597" t="n"/>
+      <c r="M15" s="597" t="n"/>
+      <c r="N15" s="597" t="n"/>
+      <c r="P15" s="599" t="n"/>
+      <c r="Q15" s="599" t="n"/>
+      <c r="R15" s="599" t="n"/>
+      <c r="S15" s="599" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -4671,56 +4869,56 @@
       <c r="S18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="556" t="inlineStr">
+      <c r="A19" s="600" t="inlineStr">
         <is>
           <t>MD13</t>
         </is>
       </c>
-      <c r="B19" s="557" t="n"/>
-      <c r="C19" s="557" t="n"/>
-      <c r="D19" s="557" t="n"/>
-      <c r="F19" s="558" t="inlineStr">
+      <c r="B19" s="601" t="n"/>
+      <c r="C19" s="601" t="n"/>
+      <c r="D19" s="601" t="n"/>
+      <c r="F19" s="602" t="inlineStr">
         <is>
           <t>MD14</t>
         </is>
       </c>
-      <c r="G19" s="559" t="n"/>
-      <c r="H19" s="559" t="n"/>
-      <c r="I19" s="559" t="n"/>
-      <c r="K19" s="560" t="inlineStr">
+      <c r="G19" s="603" t="n"/>
+      <c r="H19" s="603" t="n"/>
+      <c r="I19" s="603" t="n"/>
+      <c r="K19" s="604" t="inlineStr">
         <is>
           <t>MD15</t>
         </is>
       </c>
-      <c r="L19" s="561" t="n"/>
-      <c r="M19" s="561" t="n"/>
-      <c r="N19" s="561" t="n"/>
-      <c r="P19" s="562" t="inlineStr">
+      <c r="L19" s="605" t="n"/>
+      <c r="M19" s="605" t="n"/>
+      <c r="N19" s="605" t="n"/>
+      <c r="P19" s="606" t="inlineStr">
         <is>
           <t>MD16</t>
         </is>
       </c>
-      <c r="Q19" s="563" t="n"/>
-      <c r="R19" s="563" t="n"/>
-      <c r="S19" s="563" t="n"/>
+      <c r="Q19" s="607" t="n"/>
+      <c r="R19" s="607" t="n"/>
+      <c r="S19" s="607" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="557" t="n"/>
-      <c r="B20" s="557" t="n"/>
-      <c r="C20" s="557" t="n"/>
-      <c r="D20" s="557" t="n"/>
-      <c r="F20" s="559" t="n"/>
-      <c r="G20" s="559" t="n"/>
-      <c r="H20" s="559" t="n"/>
-      <c r="I20" s="559" t="n"/>
-      <c r="K20" s="561" t="n"/>
-      <c r="L20" s="561" t="n"/>
-      <c r="M20" s="561" t="n"/>
-      <c r="N20" s="561" t="n"/>
-      <c r="P20" s="563" t="n"/>
-      <c r="Q20" s="563" t="n"/>
-      <c r="R20" s="563" t="n"/>
-      <c r="S20" s="563" t="n"/>
+      <c r="A20" s="601" t="n"/>
+      <c r="B20" s="601" t="n"/>
+      <c r="C20" s="601" t="n"/>
+      <c r="D20" s="601" t="n"/>
+      <c r="F20" s="603" t="n"/>
+      <c r="G20" s="603" t="n"/>
+      <c r="H20" s="603" t="n"/>
+      <c r="I20" s="603" t="n"/>
+      <c r="K20" s="605" t="n"/>
+      <c r="L20" s="605" t="n"/>
+      <c r="M20" s="605" t="n"/>
+      <c r="N20" s="605" t="n"/>
+      <c r="P20" s="607" t="n"/>
+      <c r="Q20" s="607" t="n"/>
+      <c r="R20" s="607" t="n"/>
+      <c r="S20" s="607" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -4825,56 +5023,56 @@
       <c r="S23" s="15" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="564" t="inlineStr">
+      <c r="A24" s="608" t="inlineStr">
         <is>
           <t>MD17</t>
         </is>
       </c>
-      <c r="B24" s="565" t="n"/>
-      <c r="C24" s="565" t="n"/>
-      <c r="D24" s="565" t="n"/>
-      <c r="F24" s="566" t="inlineStr">
+      <c r="B24" s="609" t="n"/>
+      <c r="C24" s="609" t="n"/>
+      <c r="D24" s="609" t="n"/>
+      <c r="F24" s="610" t="inlineStr">
         <is>
           <t>MD18</t>
         </is>
       </c>
-      <c r="G24" s="567" t="n"/>
-      <c r="H24" s="567" t="n"/>
-      <c r="I24" s="567" t="n"/>
-      <c r="K24" s="568" t="inlineStr">
+      <c r="G24" s="611" t="n"/>
+      <c r="H24" s="611" t="n"/>
+      <c r="I24" s="611" t="n"/>
+      <c r="K24" s="612" t="inlineStr">
         <is>
           <t>MD19</t>
         </is>
       </c>
-      <c r="L24" s="569" t="n"/>
-      <c r="M24" s="569" t="n"/>
-      <c r="N24" s="569" t="n"/>
-      <c r="P24" s="570" t="inlineStr">
+      <c r="L24" s="613" t="n"/>
+      <c r="M24" s="613" t="n"/>
+      <c r="N24" s="613" t="n"/>
+      <c r="P24" s="614" t="inlineStr">
         <is>
           <t>MD20</t>
         </is>
       </c>
-      <c r="Q24" s="571" t="n"/>
-      <c r="R24" s="571" t="n"/>
-      <c r="S24" s="571" t="n"/>
+      <c r="Q24" s="615" t="n"/>
+      <c r="R24" s="615" t="n"/>
+      <c r="S24" s="615" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="565" t="n"/>
-      <c r="B25" s="565" t="n"/>
-      <c r="C25" s="565" t="n"/>
-      <c r="D25" s="565" t="n"/>
-      <c r="F25" s="567" t="n"/>
-      <c r="G25" s="567" t="n"/>
-      <c r="H25" s="567" t="n"/>
-      <c r="I25" s="567" t="n"/>
-      <c r="K25" s="569" t="n"/>
-      <c r="L25" s="569" t="n"/>
-      <c r="M25" s="569" t="n"/>
-      <c r="N25" s="569" t="n"/>
-      <c r="P25" s="571" t="n"/>
-      <c r="Q25" s="571" t="n"/>
-      <c r="R25" s="571" t="n"/>
-      <c r="S25" s="571" t="n"/>
+      <c r="A25" s="609" t="n"/>
+      <c r="B25" s="609" t="n"/>
+      <c r="C25" s="609" t="n"/>
+      <c r="D25" s="609" t="n"/>
+      <c r="F25" s="611" t="n"/>
+      <c r="G25" s="611" t="n"/>
+      <c r="H25" s="611" t="n"/>
+      <c r="I25" s="611" t="n"/>
+      <c r="K25" s="613" t="n"/>
+      <c r="L25" s="613" t="n"/>
+      <c r="M25" s="613" t="n"/>
+      <c r="N25" s="613" t="n"/>
+      <c r="P25" s="615" t="n"/>
+      <c r="Q25" s="615" t="n"/>
+      <c r="R25" s="615" t="n"/>
+      <c r="S25" s="615" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
@@ -4979,56 +5177,56 @@
       <c r="S28" s="15" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="572" t="inlineStr">
+      <c r="A29" s="616" t="inlineStr">
         <is>
           <t>MD21</t>
         </is>
       </c>
-      <c r="B29" s="573" t="n"/>
-      <c r="C29" s="573" t="n"/>
-      <c r="D29" s="573" t="n"/>
-      <c r="F29" s="574" t="inlineStr">
+      <c r="B29" s="617" t="n"/>
+      <c r="C29" s="617" t="n"/>
+      <c r="D29" s="617" t="n"/>
+      <c r="F29" s="618" t="inlineStr">
         <is>
           <t>MD22</t>
         </is>
       </c>
-      <c r="G29" s="575" t="n"/>
-      <c r="H29" s="575" t="n"/>
-      <c r="I29" s="575" t="n"/>
-      <c r="K29" s="576" t="inlineStr">
+      <c r="G29" s="619" t="n"/>
+      <c r="H29" s="619" t="n"/>
+      <c r="I29" s="619" t="n"/>
+      <c r="K29" s="620" t="inlineStr">
         <is>
           <t>MD23</t>
         </is>
       </c>
-      <c r="L29" s="577" t="n"/>
-      <c r="M29" s="577" t="n"/>
-      <c r="N29" s="577" t="n"/>
-      <c r="P29" s="578" t="inlineStr">
+      <c r="L29" s="621" t="n"/>
+      <c r="M29" s="621" t="n"/>
+      <c r="N29" s="621" t="n"/>
+      <c r="P29" s="622" t="inlineStr">
         <is>
           <t>MD24</t>
         </is>
       </c>
-      <c r="Q29" s="579" t="n"/>
-      <c r="R29" s="579" t="n"/>
-      <c r="S29" s="579" t="n"/>
+      <c r="Q29" s="623" t="n"/>
+      <c r="R29" s="623" t="n"/>
+      <c r="S29" s="623" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="573" t="n"/>
-      <c r="B30" s="573" t="n"/>
-      <c r="C30" s="573" t="n"/>
-      <c r="D30" s="573" t="n"/>
-      <c r="F30" s="575" t="n"/>
-      <c r="G30" s="575" t="n"/>
-      <c r="H30" s="575" t="n"/>
-      <c r="I30" s="575" t="n"/>
-      <c r="K30" s="577" t="n"/>
-      <c r="L30" s="577" t="n"/>
-      <c r="M30" s="577" t="n"/>
-      <c r="N30" s="577" t="n"/>
-      <c r="P30" s="579" t="n"/>
-      <c r="Q30" s="579" t="n"/>
-      <c r="R30" s="579" t="n"/>
-      <c r="S30" s="579" t="n"/>
+      <c r="A30" s="617" t="n"/>
+      <c r="B30" s="617" t="n"/>
+      <c r="C30" s="617" t="n"/>
+      <c r="D30" s="617" t="n"/>
+      <c r="F30" s="619" t="n"/>
+      <c r="G30" s="619" t="n"/>
+      <c r="H30" s="619" t="n"/>
+      <c r="I30" s="619" t="n"/>
+      <c r="K30" s="621" t="n"/>
+      <c r="L30" s="621" t="n"/>
+      <c r="M30" s="621" t="n"/>
+      <c r="N30" s="621" t="n"/>
+      <c r="P30" s="623" t="n"/>
+      <c r="Q30" s="623" t="n"/>
+      <c r="R30" s="623" t="n"/>
+      <c r="S30" s="623" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -5133,32 +5331,32 @@
       <c r="S33" s="15" t="n"/>
     </row>
     <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="580" t="inlineStr">
+      <c r="A34" s="624" t="inlineStr">
         <is>
           <t>MD25</t>
         </is>
       </c>
-      <c r="B34" s="581" t="n"/>
-      <c r="C34" s="581" t="n"/>
-      <c r="D34" s="581" t="n"/>
-      <c r="F34" s="582" t="inlineStr">
+      <c r="B34" s="625" t="n"/>
+      <c r="C34" s="625" t="n"/>
+      <c r="D34" s="625" t="n"/>
+      <c r="F34" s="626" t="inlineStr">
         <is>
           <t>MD26</t>
         </is>
       </c>
-      <c r="G34" s="583" t="n"/>
-      <c r="H34" s="583" t="n"/>
-      <c r="I34" s="583" t="n"/>
+      <c r="G34" s="627" t="n"/>
+      <c r="H34" s="627" t="n"/>
+      <c r="I34" s="627" t="n"/>
     </row>
     <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="581" t="n"/>
-      <c r="B35" s="581" t="n"/>
-      <c r="C35" s="581" t="n"/>
-      <c r="D35" s="581" t="n"/>
-      <c r="F35" s="583" t="n"/>
-      <c r="G35" s="583" t="n"/>
-      <c r="H35" s="583" t="n"/>
-      <c r="I35" s="583" t="n"/>
+      <c r="A35" s="625" t="n"/>
+      <c r="B35" s="625" t="n"/>
+      <c r="C35" s="625" t="n"/>
+      <c r="D35" s="625" t="n"/>
+      <c r="F35" s="627" t="n"/>
+      <c r="G35" s="627" t="n"/>
+      <c r="H35" s="627" t="n"/>
+      <c r="I35" s="627" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -5370,56 +5568,56 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="584" t="inlineStr">
+      <c r="A4" s="628" t="inlineStr">
         <is>
           <t>ME1</t>
         </is>
       </c>
-      <c r="B4" s="585" t="n"/>
-      <c r="C4" s="585" t="n"/>
-      <c r="D4" s="585" t="n"/>
-      <c r="F4" s="586" t="inlineStr">
+      <c r="B4" s="629" t="n"/>
+      <c r="C4" s="629" t="n"/>
+      <c r="D4" s="629" t="n"/>
+      <c r="F4" s="630" t="inlineStr">
         <is>
           <t>ME2</t>
         </is>
       </c>
-      <c r="G4" s="587" t="n"/>
-      <c r="H4" s="587" t="n"/>
-      <c r="I4" s="587" t="n"/>
-      <c r="K4" s="588" t="inlineStr">
+      <c r="G4" s="631" t="n"/>
+      <c r="H4" s="631" t="n"/>
+      <c r="I4" s="631" t="n"/>
+      <c r="K4" s="632" t="inlineStr">
         <is>
           <t>ME3</t>
         </is>
       </c>
-      <c r="L4" s="589" t="n"/>
-      <c r="M4" s="589" t="n"/>
-      <c r="N4" s="589" t="n"/>
-      <c r="P4" s="590" t="inlineStr">
+      <c r="L4" s="633" t="n"/>
+      <c r="M4" s="633" t="n"/>
+      <c r="N4" s="633" t="n"/>
+      <c r="P4" s="634" t="inlineStr">
         <is>
           <t>ME4</t>
         </is>
       </c>
-      <c r="Q4" s="591" t="n"/>
-      <c r="R4" s="591" t="n"/>
-      <c r="S4" s="591" t="n"/>
+      <c r="Q4" s="635" t="n"/>
+      <c r="R4" s="635" t="n"/>
+      <c r="S4" s="635" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="585" t="n"/>
-      <c r="B5" s="585" t="n"/>
-      <c r="C5" s="585" t="n"/>
-      <c r="D5" s="585" t="n"/>
-      <c r="F5" s="587" t="n"/>
-      <c r="G5" s="587" t="n"/>
-      <c r="H5" s="587" t="n"/>
-      <c r="I5" s="587" t="n"/>
-      <c r="K5" s="589" t="n"/>
-      <c r="L5" s="589" t="n"/>
-      <c r="M5" s="589" t="n"/>
-      <c r="N5" s="589" t="n"/>
-      <c r="P5" s="591" t="n"/>
-      <c r="Q5" s="591" t="n"/>
-      <c r="R5" s="591" t="n"/>
-      <c r="S5" s="591" t="n"/>
+      <c r="A5" s="629" t="n"/>
+      <c r="B5" s="629" t="n"/>
+      <c r="C5" s="629" t="n"/>
+      <c r="D5" s="629" t="n"/>
+      <c r="F5" s="631" t="n"/>
+      <c r="G5" s="631" t="n"/>
+      <c r="H5" s="631" t="n"/>
+      <c r="I5" s="631" t="n"/>
+      <c r="K5" s="633" t="n"/>
+      <c r="L5" s="633" t="n"/>
+      <c r="M5" s="633" t="n"/>
+      <c r="N5" s="633" t="n"/>
+      <c r="P5" s="635" t="n"/>
+      <c r="Q5" s="635" t="n"/>
+      <c r="R5" s="635" t="n"/>
+      <c r="S5" s="635" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -5524,56 +5722,56 @@
       <c r="S8" s="15" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="592" t="inlineStr">
+      <c r="A9" s="636" t="inlineStr">
         <is>
           <t>ME5</t>
         </is>
       </c>
-      <c r="B9" s="593" t="n"/>
-      <c r="C9" s="593" t="n"/>
-      <c r="D9" s="593" t="n"/>
-      <c r="F9" s="594" t="inlineStr">
+      <c r="B9" s="637" t="n"/>
+      <c r="C9" s="637" t="n"/>
+      <c r="D9" s="637" t="n"/>
+      <c r="F9" s="638" t="inlineStr">
         <is>
           <t>ME6</t>
         </is>
       </c>
-      <c r="G9" s="595" t="n"/>
-      <c r="H9" s="595" t="n"/>
-      <c r="I9" s="595" t="n"/>
-      <c r="K9" s="596" t="inlineStr">
+      <c r="G9" s="639" t="n"/>
+      <c r="H9" s="639" t="n"/>
+      <c r="I9" s="639" t="n"/>
+      <c r="K9" s="640" t="inlineStr">
         <is>
           <t>ME7</t>
         </is>
       </c>
-      <c r="L9" s="597" t="n"/>
-      <c r="M9" s="597" t="n"/>
-      <c r="N9" s="597" t="n"/>
-      <c r="P9" s="598" t="inlineStr">
+      <c r="L9" s="641" t="n"/>
+      <c r="M9" s="641" t="n"/>
+      <c r="N9" s="641" t="n"/>
+      <c r="P9" s="642" t="inlineStr">
         <is>
           <t>ME8</t>
         </is>
       </c>
-      <c r="Q9" s="599" t="n"/>
-      <c r="R9" s="599" t="n"/>
-      <c r="S9" s="599" t="n"/>
+      <c r="Q9" s="643" t="n"/>
+      <c r="R9" s="643" t="n"/>
+      <c r="S9" s="643" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="593" t="n"/>
-      <c r="B10" s="593" t="n"/>
-      <c r="C10" s="593" t="n"/>
-      <c r="D10" s="593" t="n"/>
-      <c r="F10" s="595" t="n"/>
-      <c r="G10" s="595" t="n"/>
-      <c r="H10" s="595" t="n"/>
-      <c r="I10" s="595" t="n"/>
-      <c r="K10" s="597" t="n"/>
-      <c r="L10" s="597" t="n"/>
-      <c r="M10" s="597" t="n"/>
-      <c r="N10" s="597" t="n"/>
-      <c r="P10" s="599" t="n"/>
-      <c r="Q10" s="599" t="n"/>
-      <c r="R10" s="599" t="n"/>
-      <c r="S10" s="599" t="n"/>
+      <c r="A10" s="637" t="n"/>
+      <c r="B10" s="637" t="n"/>
+      <c r="C10" s="637" t="n"/>
+      <c r="D10" s="637" t="n"/>
+      <c r="F10" s="639" t="n"/>
+      <c r="G10" s="639" t="n"/>
+      <c r="H10" s="639" t="n"/>
+      <c r="I10" s="639" t="n"/>
+      <c r="K10" s="641" t="n"/>
+      <c r="L10" s="641" t="n"/>
+      <c r="M10" s="641" t="n"/>
+      <c r="N10" s="641" t="n"/>
+      <c r="P10" s="643" t="n"/>
+      <c r="Q10" s="643" t="n"/>
+      <c r="R10" s="643" t="n"/>
+      <c r="S10" s="643" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -5678,56 +5876,56 @@
       <c r="S13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="600" t="inlineStr">
+      <c r="A14" s="644" t="inlineStr">
         <is>
           <t>ME9</t>
         </is>
       </c>
-      <c r="B14" s="601" t="n"/>
-      <c r="C14" s="601" t="n"/>
-      <c r="D14" s="601" t="n"/>
-      <c r="F14" s="602" t="inlineStr">
+      <c r="B14" s="645" t="n"/>
+      <c r="C14" s="645" t="n"/>
+      <c r="D14" s="645" t="n"/>
+      <c r="F14" s="646" t="inlineStr">
         <is>
           <t>ME10</t>
         </is>
       </c>
-      <c r="G14" s="603" t="n"/>
-      <c r="H14" s="603" t="n"/>
-      <c r="I14" s="603" t="n"/>
-      <c r="K14" s="604" t="inlineStr">
+      <c r="G14" s="647" t="n"/>
+      <c r="H14" s="647" t="n"/>
+      <c r="I14" s="647" t="n"/>
+      <c r="K14" s="648" t="inlineStr">
         <is>
           <t>ME11</t>
         </is>
       </c>
-      <c r="L14" s="605" t="n"/>
-      <c r="M14" s="605" t="n"/>
-      <c r="N14" s="605" t="n"/>
-      <c r="P14" s="606" t="inlineStr">
+      <c r="L14" s="649" t="n"/>
+      <c r="M14" s="649" t="n"/>
+      <c r="N14" s="649" t="n"/>
+      <c r="P14" s="650" t="inlineStr">
         <is>
           <t>ME12</t>
         </is>
       </c>
-      <c r="Q14" s="607" t="n"/>
-      <c r="R14" s="607" t="n"/>
-      <c r="S14" s="607" t="n"/>
+      <c r="Q14" s="651" t="n"/>
+      <c r="R14" s="651" t="n"/>
+      <c r="S14" s="651" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="601" t="n"/>
-      <c r="B15" s="601" t="n"/>
-      <c r="C15" s="601" t="n"/>
-      <c r="D15" s="601" t="n"/>
-      <c r="F15" s="603" t="n"/>
-      <c r="G15" s="603" t="n"/>
-      <c r="H15" s="603" t="n"/>
-      <c r="I15" s="603" t="n"/>
-      <c r="K15" s="605" t="n"/>
-      <c r="L15" s="605" t="n"/>
-      <c r="M15" s="605" t="n"/>
-      <c r="N15" s="605" t="n"/>
-      <c r="P15" s="607" t="n"/>
-      <c r="Q15" s="607" t="n"/>
-      <c r="R15" s="607" t="n"/>
-      <c r="S15" s="607" t="n"/>
+      <c r="A15" s="645" t="n"/>
+      <c r="B15" s="645" t="n"/>
+      <c r="C15" s="645" t="n"/>
+      <c r="D15" s="645" t="n"/>
+      <c r="F15" s="647" t="n"/>
+      <c r="G15" s="647" t="n"/>
+      <c r="H15" s="647" t="n"/>
+      <c r="I15" s="647" t="n"/>
+      <c r="K15" s="649" t="n"/>
+      <c r="L15" s="649" t="n"/>
+      <c r="M15" s="649" t="n"/>
+      <c r="N15" s="649" t="n"/>
+      <c r="P15" s="651" t="n"/>
+      <c r="Q15" s="651" t="n"/>
+      <c r="R15" s="651" t="n"/>
+      <c r="S15" s="651" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -5832,56 +6030,56 @@
       <c r="S18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="608" t="inlineStr">
+      <c r="A19" s="652" t="inlineStr">
         <is>
           <t>ME13</t>
         </is>
       </c>
-      <c r="B19" s="609" t="n"/>
-      <c r="C19" s="609" t="n"/>
-      <c r="D19" s="609" t="n"/>
-      <c r="F19" s="610" t="inlineStr">
+      <c r="B19" s="653" t="n"/>
+      <c r="C19" s="653" t="n"/>
+      <c r="D19" s="653" t="n"/>
+      <c r="F19" s="654" t="inlineStr">
         <is>
           <t>ME14</t>
         </is>
       </c>
-      <c r="G19" s="611" t="n"/>
-      <c r="H19" s="611" t="n"/>
-      <c r="I19" s="611" t="n"/>
-      <c r="K19" s="612" t="inlineStr">
+      <c r="G19" s="655" t="n"/>
+      <c r="H19" s="655" t="n"/>
+      <c r="I19" s="655" t="n"/>
+      <c r="K19" s="656" t="inlineStr">
         <is>
           <t>ME15</t>
         </is>
       </c>
-      <c r="L19" s="613" t="n"/>
-      <c r="M19" s="613" t="n"/>
-      <c r="N19" s="613" t="n"/>
-      <c r="P19" s="614" t="inlineStr">
+      <c r="L19" s="657" t="n"/>
+      <c r="M19" s="657" t="n"/>
+      <c r="N19" s="657" t="n"/>
+      <c r="P19" s="658" t="inlineStr">
         <is>
           <t>ME16</t>
         </is>
       </c>
-      <c r="Q19" s="615" t="n"/>
-      <c r="R19" s="615" t="n"/>
-      <c r="S19" s="615" t="n"/>
+      <c r="Q19" s="659" t="n"/>
+      <c r="R19" s="659" t="n"/>
+      <c r="S19" s="659" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="609" t="n"/>
-      <c r="B20" s="609" t="n"/>
-      <c r="C20" s="609" t="n"/>
-      <c r="D20" s="609" t="n"/>
-      <c r="F20" s="611" t="n"/>
-      <c r="G20" s="611" t="n"/>
-      <c r="H20" s="611" t="n"/>
-      <c r="I20" s="611" t="n"/>
-      <c r="K20" s="613" t="n"/>
-      <c r="L20" s="613" t="n"/>
-      <c r="M20" s="613" t="n"/>
-      <c r="N20" s="613" t="n"/>
-      <c r="P20" s="615" t="n"/>
-      <c r="Q20" s="615" t="n"/>
-      <c r="R20" s="615" t="n"/>
-      <c r="S20" s="615" t="n"/>
+      <c r="A20" s="653" t="n"/>
+      <c r="B20" s="653" t="n"/>
+      <c r="C20" s="653" t="n"/>
+      <c r="D20" s="653" t="n"/>
+      <c r="F20" s="655" t="n"/>
+      <c r="G20" s="655" t="n"/>
+      <c r="H20" s="655" t="n"/>
+      <c r="I20" s="655" t="n"/>
+      <c r="K20" s="657" t="n"/>
+      <c r="L20" s="657" t="n"/>
+      <c r="M20" s="657" t="n"/>
+      <c r="N20" s="657" t="n"/>
+      <c r="P20" s="659" t="n"/>
+      <c r="Q20" s="659" t="n"/>
+      <c r="R20" s="659" t="n"/>
+      <c r="S20" s="659" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -5986,56 +6184,56 @@
       <c r="S23" s="15" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="616" t="inlineStr">
+      <c r="A24" s="660" t="inlineStr">
         <is>
           <t>ME17</t>
         </is>
       </c>
-      <c r="B24" s="617" t="n"/>
-      <c r="C24" s="617" t="n"/>
-      <c r="D24" s="617" t="n"/>
-      <c r="F24" s="618" t="inlineStr">
+      <c r="B24" s="661" t="n"/>
+      <c r="C24" s="661" t="n"/>
+      <c r="D24" s="661" t="n"/>
+      <c r="F24" s="662" t="inlineStr">
         <is>
           <t>ME18</t>
         </is>
       </c>
-      <c r="G24" s="619" t="n"/>
-      <c r="H24" s="619" t="n"/>
-      <c r="I24" s="619" t="n"/>
-      <c r="K24" s="620" t="inlineStr">
+      <c r="G24" s="663" t="n"/>
+      <c r="H24" s="663" t="n"/>
+      <c r="I24" s="663" t="n"/>
+      <c r="K24" s="664" t="inlineStr">
         <is>
           <t>ME19</t>
         </is>
       </c>
-      <c r="L24" s="621" t="n"/>
-      <c r="M24" s="621" t="n"/>
-      <c r="N24" s="621" t="n"/>
-      <c r="P24" s="622" t="inlineStr">
+      <c r="L24" s="665" t="n"/>
+      <c r="M24" s="665" t="n"/>
+      <c r="N24" s="665" t="n"/>
+      <c r="P24" s="666" t="inlineStr">
         <is>
           <t>ME20</t>
         </is>
       </c>
-      <c r="Q24" s="623" t="n"/>
-      <c r="R24" s="623" t="n"/>
-      <c r="S24" s="623" t="n"/>
+      <c r="Q24" s="667" t="n"/>
+      <c r="R24" s="667" t="n"/>
+      <c r="S24" s="667" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="617" t="n"/>
-      <c r="B25" s="617" t="n"/>
-      <c r="C25" s="617" t="n"/>
-      <c r="D25" s="617" t="n"/>
-      <c r="F25" s="619" t="n"/>
-      <c r="G25" s="619" t="n"/>
-      <c r="H25" s="619" t="n"/>
-      <c r="I25" s="619" t="n"/>
-      <c r="K25" s="621" t="n"/>
-      <c r="L25" s="621" t="n"/>
-      <c r="M25" s="621" t="n"/>
-      <c r="N25" s="621" t="n"/>
-      <c r="P25" s="623" t="n"/>
-      <c r="Q25" s="623" t="n"/>
-      <c r="R25" s="623" t="n"/>
-      <c r="S25" s="623" t="n"/>
+      <c r="A25" s="661" t="n"/>
+      <c r="B25" s="661" t="n"/>
+      <c r="C25" s="661" t="n"/>
+      <c r="D25" s="661" t="n"/>
+      <c r="F25" s="663" t="n"/>
+      <c r="G25" s="663" t="n"/>
+      <c r="H25" s="663" t="n"/>
+      <c r="I25" s="663" t="n"/>
+      <c r="K25" s="665" t="n"/>
+      <c r="L25" s="665" t="n"/>
+      <c r="M25" s="665" t="n"/>
+      <c r="N25" s="665" t="n"/>
+      <c r="P25" s="667" t="n"/>
+      <c r="Q25" s="667" t="n"/>
+      <c r="R25" s="667" t="n"/>
+      <c r="S25" s="667" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
@@ -6140,56 +6338,56 @@
       <c r="S28" s="15" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="624" t="inlineStr">
+      <c r="A29" s="668" t="inlineStr">
         <is>
           <t>ME21</t>
         </is>
       </c>
-      <c r="B29" s="625" t="n"/>
-      <c r="C29" s="625" t="n"/>
-      <c r="D29" s="625" t="n"/>
-      <c r="F29" s="626" t="inlineStr">
+      <c r="B29" s="669" t="n"/>
+      <c r="C29" s="669" t="n"/>
+      <c r="D29" s="669" t="n"/>
+      <c r="F29" s="670" t="inlineStr">
         <is>
           <t>ME22</t>
         </is>
       </c>
-      <c r="G29" s="627" t="n"/>
-      <c r="H29" s="627" t="n"/>
-      <c r="I29" s="627" t="n"/>
-      <c r="K29" s="628" t="inlineStr">
+      <c r="G29" s="671" t="n"/>
+      <c r="H29" s="671" t="n"/>
+      <c r="I29" s="671" t="n"/>
+      <c r="K29" s="672" t="inlineStr">
         <is>
           <t>ME23</t>
         </is>
       </c>
-      <c r="L29" s="629" t="n"/>
-      <c r="M29" s="629" t="n"/>
-      <c r="N29" s="629" t="n"/>
-      <c r="P29" s="630" t="inlineStr">
+      <c r="L29" s="673" t="n"/>
+      <c r="M29" s="673" t="n"/>
+      <c r="N29" s="673" t="n"/>
+      <c r="P29" s="674" t="inlineStr">
         <is>
           <t>ME24</t>
         </is>
       </c>
-      <c r="Q29" s="631" t="n"/>
-      <c r="R29" s="631" t="n"/>
-      <c r="S29" s="631" t="n"/>
+      <c r="Q29" s="675" t="n"/>
+      <c r="R29" s="675" t="n"/>
+      <c r="S29" s="675" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="625" t="n"/>
-      <c r="B30" s="625" t="n"/>
-      <c r="C30" s="625" t="n"/>
-      <c r="D30" s="625" t="n"/>
-      <c r="F30" s="627" t="n"/>
-      <c r="G30" s="627" t="n"/>
-      <c r="H30" s="627" t="n"/>
-      <c r="I30" s="627" t="n"/>
-      <c r="K30" s="629" t="n"/>
-      <c r="L30" s="629" t="n"/>
-      <c r="M30" s="629" t="n"/>
-      <c r="N30" s="629" t="n"/>
-      <c r="P30" s="631" t="n"/>
-      <c r="Q30" s="631" t="n"/>
-      <c r="R30" s="631" t="n"/>
-      <c r="S30" s="631" t="n"/>
+      <c r="A30" s="669" t="n"/>
+      <c r="B30" s="669" t="n"/>
+      <c r="C30" s="669" t="n"/>
+      <c r="D30" s="669" t="n"/>
+      <c r="F30" s="671" t="n"/>
+      <c r="G30" s="671" t="n"/>
+      <c r="H30" s="671" t="n"/>
+      <c r="I30" s="671" t="n"/>
+      <c r="K30" s="673" t="n"/>
+      <c r="L30" s="673" t="n"/>
+      <c r="M30" s="673" t="n"/>
+      <c r="N30" s="673" t="n"/>
+      <c r="P30" s="675" t="n"/>
+      <c r="Q30" s="675" t="n"/>
+      <c r="R30" s="675" t="n"/>
+      <c r="S30" s="675" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -6441,56 +6639,56 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="632" t="inlineStr">
+      <c r="A4" s="676" t="inlineStr">
         <is>
           <t>MF1</t>
         </is>
       </c>
-      <c r="B4" s="633" t="n"/>
-      <c r="C4" s="633" t="n"/>
-      <c r="D4" s="633" t="n"/>
-      <c r="F4" s="634" t="inlineStr">
+      <c r="B4" s="677" t="n"/>
+      <c r="C4" s="677" t="n"/>
+      <c r="D4" s="677" t="n"/>
+      <c r="F4" s="678" t="inlineStr">
         <is>
           <t>MF2</t>
         </is>
       </c>
-      <c r="G4" s="635" t="n"/>
-      <c r="H4" s="635" t="n"/>
-      <c r="I4" s="635" t="n"/>
-      <c r="K4" s="636" t="inlineStr">
+      <c r="G4" s="679" t="n"/>
+      <c r="H4" s="679" t="n"/>
+      <c r="I4" s="679" t="n"/>
+      <c r="K4" s="680" t="inlineStr">
         <is>
           <t>MF3</t>
         </is>
       </c>
-      <c r="L4" s="637" t="n"/>
-      <c r="M4" s="637" t="n"/>
-      <c r="N4" s="637" t="n"/>
-      <c r="P4" s="638" t="inlineStr">
+      <c r="L4" s="681" t="n"/>
+      <c r="M4" s="681" t="n"/>
+      <c r="N4" s="681" t="n"/>
+      <c r="P4" s="682" t="inlineStr">
         <is>
           <t>MF4</t>
         </is>
       </c>
-      <c r="Q4" s="639" t="n"/>
-      <c r="R4" s="639" t="n"/>
-      <c r="S4" s="639" t="n"/>
+      <c r="Q4" s="683" t="n"/>
+      <c r="R4" s="683" t="n"/>
+      <c r="S4" s="683" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="633" t="n"/>
-      <c r="B5" s="633" t="n"/>
-      <c r="C5" s="633" t="n"/>
-      <c r="D5" s="633" t="n"/>
-      <c r="F5" s="635" t="n"/>
-      <c r="G5" s="635" t="n"/>
-      <c r="H5" s="635" t="n"/>
-      <c r="I5" s="635" t="n"/>
-      <c r="K5" s="637" t="n"/>
-      <c r="L5" s="637" t="n"/>
-      <c r="M5" s="637" t="n"/>
-      <c r="N5" s="637" t="n"/>
-      <c r="P5" s="639" t="n"/>
-      <c r="Q5" s="639" t="n"/>
-      <c r="R5" s="639" t="n"/>
-      <c r="S5" s="639" t="n"/>
+      <c r="A5" s="677" t="n"/>
+      <c r="B5" s="677" t="n"/>
+      <c r="C5" s="677" t="n"/>
+      <c r="D5" s="677" t="n"/>
+      <c r="F5" s="679" t="n"/>
+      <c r="G5" s="679" t="n"/>
+      <c r="H5" s="679" t="n"/>
+      <c r="I5" s="679" t="n"/>
+      <c r="K5" s="681" t="n"/>
+      <c r="L5" s="681" t="n"/>
+      <c r="M5" s="681" t="n"/>
+      <c r="N5" s="681" t="n"/>
+      <c r="P5" s="683" t="n"/>
+      <c r="Q5" s="683" t="n"/>
+      <c r="R5" s="683" t="n"/>
+      <c r="S5" s="683" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -6595,56 +6793,56 @@
       <c r="S8" s="15" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="640" t="inlineStr">
+      <c r="A9" s="684" t="inlineStr">
         <is>
           <t>MF5</t>
         </is>
       </c>
-      <c r="B9" s="641" t="n"/>
-      <c r="C9" s="641" t="n"/>
-      <c r="D9" s="641" t="n"/>
-      <c r="F9" s="642" t="inlineStr">
+      <c r="B9" s="685" t="n"/>
+      <c r="C9" s="685" t="n"/>
+      <c r="D9" s="685" t="n"/>
+      <c r="F9" s="686" t="inlineStr">
         <is>
           <t>MF6</t>
         </is>
       </c>
-      <c r="G9" s="643" t="n"/>
-      <c r="H9" s="643" t="n"/>
-      <c r="I9" s="643" t="n"/>
-      <c r="K9" s="644" t="inlineStr">
+      <c r="G9" s="687" t="n"/>
+      <c r="H9" s="687" t="n"/>
+      <c r="I9" s="687" t="n"/>
+      <c r="K9" s="688" t="inlineStr">
         <is>
           <t>MF7</t>
         </is>
       </c>
-      <c r="L9" s="645" t="n"/>
-      <c r="M9" s="645" t="n"/>
-      <c r="N9" s="645" t="n"/>
-      <c r="P9" s="646" t="inlineStr">
+      <c r="L9" s="689" t="n"/>
+      <c r="M9" s="689" t="n"/>
+      <c r="N9" s="689" t="n"/>
+      <c r="P9" s="690" t="inlineStr">
         <is>
           <t>MF8</t>
         </is>
       </c>
-      <c r="Q9" s="647" t="n"/>
-      <c r="R9" s="647" t="n"/>
-      <c r="S9" s="647" t="n"/>
+      <c r="Q9" s="691" t="n"/>
+      <c r="R9" s="691" t="n"/>
+      <c r="S9" s="691" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="641" t="n"/>
-      <c r="B10" s="641" t="n"/>
-      <c r="C10" s="641" t="n"/>
-      <c r="D10" s="641" t="n"/>
-      <c r="F10" s="643" t="n"/>
-      <c r="G10" s="643" t="n"/>
-      <c r="H10" s="643" t="n"/>
-      <c r="I10" s="643" t="n"/>
-      <c r="K10" s="645" t="n"/>
-      <c r="L10" s="645" t="n"/>
-      <c r="M10" s="645" t="n"/>
-      <c r="N10" s="645" t="n"/>
-      <c r="P10" s="647" t="n"/>
-      <c r="Q10" s="647" t="n"/>
-      <c r="R10" s="647" t="n"/>
-      <c r="S10" s="647" t="n"/>
+      <c r="A10" s="685" t="n"/>
+      <c r="B10" s="685" t="n"/>
+      <c r="C10" s="685" t="n"/>
+      <c r="D10" s="685" t="n"/>
+      <c r="F10" s="687" t="n"/>
+      <c r="G10" s="687" t="n"/>
+      <c r="H10" s="687" t="n"/>
+      <c r="I10" s="687" t="n"/>
+      <c r="K10" s="689" t="n"/>
+      <c r="L10" s="689" t="n"/>
+      <c r="M10" s="689" t="n"/>
+      <c r="N10" s="689" t="n"/>
+      <c r="P10" s="691" t="n"/>
+      <c r="Q10" s="691" t="n"/>
+      <c r="R10" s="691" t="n"/>
+      <c r="S10" s="691" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -6749,56 +6947,56 @@
       <c r="S13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="648" t="inlineStr">
+      <c r="A14" s="692" t="inlineStr">
         <is>
           <t>MF9</t>
         </is>
       </c>
-      <c r="B14" s="649" t="n"/>
-      <c r="C14" s="649" t="n"/>
-      <c r="D14" s="649" t="n"/>
-      <c r="F14" s="650" t="inlineStr">
+      <c r="B14" s="693" t="n"/>
+      <c r="C14" s="693" t="n"/>
+      <c r="D14" s="693" t="n"/>
+      <c r="F14" s="694" t="inlineStr">
         <is>
           <t>MF10</t>
         </is>
       </c>
-      <c r="G14" s="651" t="n"/>
-      <c r="H14" s="651" t="n"/>
-      <c r="I14" s="651" t="n"/>
-      <c r="K14" s="652" t="inlineStr">
+      <c r="G14" s="695" t="n"/>
+      <c r="H14" s="695" t="n"/>
+      <c r="I14" s="695" t="n"/>
+      <c r="K14" s="696" t="inlineStr">
         <is>
           <t>MF11</t>
         </is>
       </c>
-      <c r="L14" s="653" t="n"/>
-      <c r="M14" s="653" t="n"/>
-      <c r="N14" s="653" t="n"/>
-      <c r="P14" s="654" t="inlineStr">
+      <c r="L14" s="697" t="n"/>
+      <c r="M14" s="697" t="n"/>
+      <c r="N14" s="697" t="n"/>
+      <c r="P14" s="698" t="inlineStr">
         <is>
           <t>MF12</t>
         </is>
       </c>
-      <c r="Q14" s="655" t="n"/>
-      <c r="R14" s="655" t="n"/>
-      <c r="S14" s="655" t="n"/>
+      <c r="Q14" s="699" t="n"/>
+      <c r="R14" s="699" t="n"/>
+      <c r="S14" s="699" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="649" t="n"/>
-      <c r="B15" s="649" t="n"/>
-      <c r="C15" s="649" t="n"/>
-      <c r="D15" s="649" t="n"/>
-      <c r="F15" s="651" t="n"/>
-      <c r="G15" s="651" t="n"/>
-      <c r="H15" s="651" t="n"/>
-      <c r="I15" s="651" t="n"/>
-      <c r="K15" s="653" t="n"/>
-      <c r="L15" s="653" t="n"/>
-      <c r="M15" s="653" t="n"/>
-      <c r="N15" s="653" t="n"/>
-      <c r="P15" s="655" t="n"/>
-      <c r="Q15" s="655" t="n"/>
-      <c r="R15" s="655" t="n"/>
-      <c r="S15" s="655" t="n"/>
+      <c r="A15" s="693" t="n"/>
+      <c r="B15" s="693" t="n"/>
+      <c r="C15" s="693" t="n"/>
+      <c r="D15" s="693" t="n"/>
+      <c r="F15" s="695" t="n"/>
+      <c r="G15" s="695" t="n"/>
+      <c r="H15" s="695" t="n"/>
+      <c r="I15" s="695" t="n"/>
+      <c r="K15" s="697" t="n"/>
+      <c r="L15" s="697" t="n"/>
+      <c r="M15" s="697" t="n"/>
+      <c r="N15" s="697" t="n"/>
+      <c r="P15" s="699" t="n"/>
+      <c r="Q15" s="699" t="n"/>
+      <c r="R15" s="699" t="n"/>
+      <c r="S15" s="699" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -6903,56 +7101,56 @@
       <c r="S18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="656" t="inlineStr">
+      <c r="A19" s="700" t="inlineStr">
         <is>
           <t>MF13</t>
         </is>
       </c>
-      <c r="B19" s="657" t="n"/>
-      <c r="C19" s="657" t="n"/>
-      <c r="D19" s="657" t="n"/>
-      <c r="F19" s="658" t="inlineStr">
+      <c r="B19" s="701" t="n"/>
+      <c r="C19" s="701" t="n"/>
+      <c r="D19" s="701" t="n"/>
+      <c r="F19" s="702" t="inlineStr">
         <is>
           <t>MF14</t>
         </is>
       </c>
-      <c r="G19" s="659" t="n"/>
-      <c r="H19" s="659" t="n"/>
-      <c r="I19" s="659" t="n"/>
-      <c r="K19" s="660" t="inlineStr">
+      <c r="G19" s="703" t="n"/>
+      <c r="H19" s="703" t="n"/>
+      <c r="I19" s="703" t="n"/>
+      <c r="K19" s="704" t="inlineStr">
         <is>
           <t>MF15</t>
         </is>
       </c>
-      <c r="L19" s="661" t="n"/>
-      <c r="M19" s="661" t="n"/>
-      <c r="N19" s="661" t="n"/>
-      <c r="P19" s="662" t="inlineStr">
+      <c r="L19" s="705" t="n"/>
+      <c r="M19" s="705" t="n"/>
+      <c r="N19" s="705" t="n"/>
+      <c r="P19" s="706" t="inlineStr">
         <is>
           <t>MF16</t>
         </is>
       </c>
-      <c r="Q19" s="663" t="n"/>
-      <c r="R19" s="663" t="n"/>
-      <c r="S19" s="663" t="n"/>
+      <c r="Q19" s="707" t="n"/>
+      <c r="R19" s="707" t="n"/>
+      <c r="S19" s="707" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="657" t="n"/>
-      <c r="B20" s="657" t="n"/>
-      <c r="C20" s="657" t="n"/>
-      <c r="D20" s="657" t="n"/>
-      <c r="F20" s="659" t="n"/>
-      <c r="G20" s="659" t="n"/>
-      <c r="H20" s="659" t="n"/>
-      <c r="I20" s="659" t="n"/>
-      <c r="K20" s="661" t="n"/>
-      <c r="L20" s="661" t="n"/>
-      <c r="M20" s="661" t="n"/>
-      <c r="N20" s="661" t="n"/>
-      <c r="P20" s="663" t="n"/>
-      <c r="Q20" s="663" t="n"/>
-      <c r="R20" s="663" t="n"/>
-      <c r="S20" s="663" t="n"/>
+      <c r="A20" s="701" t="n"/>
+      <c r="B20" s="701" t="n"/>
+      <c r="C20" s="701" t="n"/>
+      <c r="D20" s="701" t="n"/>
+      <c r="F20" s="703" t="n"/>
+      <c r="G20" s="703" t="n"/>
+      <c r="H20" s="703" t="n"/>
+      <c r="I20" s="703" t="n"/>
+      <c r="K20" s="705" t="n"/>
+      <c r="L20" s="705" t="n"/>
+      <c r="M20" s="705" t="n"/>
+      <c r="N20" s="705" t="n"/>
+      <c r="P20" s="707" t="n"/>
+      <c r="Q20" s="707" t="n"/>
+      <c r="R20" s="707" t="n"/>
+      <c r="S20" s="707" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -7057,56 +7255,56 @@
       <c r="S23" s="15" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="664" t="inlineStr">
+      <c r="A24" s="708" t="inlineStr">
         <is>
           <t>MF17</t>
         </is>
       </c>
-      <c r="B24" s="665" t="n"/>
-      <c r="C24" s="665" t="n"/>
-      <c r="D24" s="665" t="n"/>
-      <c r="F24" s="666" t="inlineStr">
+      <c r="B24" s="709" t="n"/>
+      <c r="C24" s="709" t="n"/>
+      <c r="D24" s="709" t="n"/>
+      <c r="F24" s="710" t="inlineStr">
         <is>
           <t>MF18</t>
         </is>
       </c>
-      <c r="G24" s="667" t="n"/>
-      <c r="H24" s="667" t="n"/>
-      <c r="I24" s="667" t="n"/>
-      <c r="K24" s="668" t="inlineStr">
+      <c r="G24" s="711" t="n"/>
+      <c r="H24" s="711" t="n"/>
+      <c r="I24" s="711" t="n"/>
+      <c r="K24" s="712" t="inlineStr">
         <is>
           <t>MF19</t>
         </is>
       </c>
-      <c r="L24" s="669" t="n"/>
-      <c r="M24" s="669" t="n"/>
-      <c r="N24" s="669" t="n"/>
-      <c r="P24" s="670" t="inlineStr">
+      <c r="L24" s="713" t="n"/>
+      <c r="M24" s="713" t="n"/>
+      <c r="N24" s="713" t="n"/>
+      <c r="P24" s="714" t="inlineStr">
         <is>
           <t>MF20</t>
         </is>
       </c>
-      <c r="Q24" s="671" t="n"/>
-      <c r="R24" s="671" t="n"/>
-      <c r="S24" s="671" t="n"/>
+      <c r="Q24" s="715" t="n"/>
+      <c r="R24" s="715" t="n"/>
+      <c r="S24" s="715" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="665" t="n"/>
-      <c r="B25" s="665" t="n"/>
-      <c r="C25" s="665" t="n"/>
-      <c r="D25" s="665" t="n"/>
-      <c r="F25" s="667" t="n"/>
-      <c r="G25" s="667" t="n"/>
-      <c r="H25" s="667" t="n"/>
-      <c r="I25" s="667" t="n"/>
-      <c r="K25" s="669" t="n"/>
-      <c r="L25" s="669" t="n"/>
-      <c r="M25" s="669" t="n"/>
-      <c r="N25" s="669" t="n"/>
-      <c r="P25" s="671" t="n"/>
-      <c r="Q25" s="671" t="n"/>
-      <c r="R25" s="671" t="n"/>
-      <c r="S25" s="671" t="n"/>
+      <c r="A25" s="709" t="n"/>
+      <c r="B25" s="709" t="n"/>
+      <c r="C25" s="709" t="n"/>
+      <c r="D25" s="709" t="n"/>
+      <c r="F25" s="711" t="n"/>
+      <c r="G25" s="711" t="n"/>
+      <c r="H25" s="711" t="n"/>
+      <c r="I25" s="711" t="n"/>
+      <c r="K25" s="713" t="n"/>
+      <c r="L25" s="713" t="n"/>
+      <c r="M25" s="713" t="n"/>
+      <c r="N25" s="713" t="n"/>
+      <c r="P25" s="715" t="n"/>
+      <c r="Q25" s="715" t="n"/>
+      <c r="R25" s="715" t="n"/>
+      <c r="S25" s="715" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
@@ -7211,56 +7409,56 @@
       <c r="S28" s="15" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="672" t="inlineStr">
+      <c r="A29" s="716" t="inlineStr">
         <is>
           <t>MF21</t>
         </is>
       </c>
-      <c r="B29" s="673" t="n"/>
-      <c r="C29" s="673" t="n"/>
-      <c r="D29" s="673" t="n"/>
-      <c r="F29" s="674" t="inlineStr">
+      <c r="B29" s="717" t="n"/>
+      <c r="C29" s="717" t="n"/>
+      <c r="D29" s="717" t="n"/>
+      <c r="F29" s="718" t="inlineStr">
         <is>
           <t>MF22</t>
         </is>
       </c>
-      <c r="G29" s="675" t="n"/>
-      <c r="H29" s="675" t="n"/>
-      <c r="I29" s="675" t="n"/>
-      <c r="K29" s="676" t="inlineStr">
+      <c r="G29" s="719" t="n"/>
+      <c r="H29" s="719" t="n"/>
+      <c r="I29" s="719" t="n"/>
+      <c r="K29" s="720" t="inlineStr">
         <is>
           <t>MF23</t>
         </is>
       </c>
-      <c r="L29" s="677" t="n"/>
-      <c r="M29" s="677" t="n"/>
-      <c r="N29" s="677" t="n"/>
-      <c r="P29" s="678" t="inlineStr">
+      <c r="L29" s="721" t="n"/>
+      <c r="M29" s="721" t="n"/>
+      <c r="N29" s="721" t="n"/>
+      <c r="P29" s="722" t="inlineStr">
         <is>
           <t>MF24</t>
         </is>
       </c>
-      <c r="Q29" s="679" t="n"/>
-      <c r="R29" s="679" t="n"/>
-      <c r="S29" s="679" t="n"/>
+      <c r="Q29" s="723" t="n"/>
+      <c r="R29" s="723" t="n"/>
+      <c r="S29" s="723" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="673" t="n"/>
-      <c r="B30" s="673" t="n"/>
-      <c r="C30" s="673" t="n"/>
-      <c r="D30" s="673" t="n"/>
-      <c r="F30" s="675" t="n"/>
-      <c r="G30" s="675" t="n"/>
-      <c r="H30" s="675" t="n"/>
-      <c r="I30" s="675" t="n"/>
-      <c r="K30" s="677" t="n"/>
-      <c r="L30" s="677" t="n"/>
-      <c r="M30" s="677" t="n"/>
-      <c r="N30" s="677" t="n"/>
-      <c r="P30" s="679" t="n"/>
-      <c r="Q30" s="679" t="n"/>
-      <c r="R30" s="679" t="n"/>
-      <c r="S30" s="679" t="n"/>
+      <c r="A30" s="717" t="n"/>
+      <c r="B30" s="717" t="n"/>
+      <c r="C30" s="717" t="n"/>
+      <c r="D30" s="717" t="n"/>
+      <c r="F30" s="719" t="n"/>
+      <c r="G30" s="719" t="n"/>
+      <c r="H30" s="719" t="n"/>
+      <c r="I30" s="719" t="n"/>
+      <c r="K30" s="721" t="n"/>
+      <c r="L30" s="721" t="n"/>
+      <c r="M30" s="721" t="n"/>
+      <c r="N30" s="721" t="n"/>
+      <c r="P30" s="723" t="n"/>
+      <c r="Q30" s="723" t="n"/>
+      <c r="R30" s="723" t="n"/>
+      <c r="S30" s="723" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -7365,20 +7563,20 @@
       <c r="S33" s="15" t="n"/>
     </row>
     <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="680" t="inlineStr">
+      <c r="A34" s="724" t="inlineStr">
         <is>
           <t>MF25</t>
         </is>
       </c>
-      <c r="B34" s="681" t="n"/>
-      <c r="C34" s="681" t="n"/>
-      <c r="D34" s="681" t="n"/>
+      <c r="B34" s="725" t="n"/>
+      <c r="C34" s="725" t="n"/>
+      <c r="D34" s="725" t="n"/>
     </row>
     <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="681" t="n"/>
-      <c r="B35" s="681" t="n"/>
-      <c r="C35" s="681" t="n"/>
-      <c r="D35" s="681" t="n"/>
+      <c r="A35" s="725" t="n"/>
+      <c r="B35" s="725" t="n"/>
+      <c r="C35" s="725" t="n"/>
+      <c r="D35" s="725" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -7562,56 +7760,56 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="682" t="inlineStr">
+      <c r="A4" s="726" t="inlineStr">
         <is>
           <t>MG1</t>
         </is>
       </c>
-      <c r="B4" s="683" t="n"/>
-      <c r="C4" s="683" t="n"/>
-      <c r="D4" s="683" t="n"/>
-      <c r="F4" s="684" t="inlineStr">
+      <c r="B4" s="727" t="n"/>
+      <c r="C4" s="727" t="n"/>
+      <c r="D4" s="727" t="n"/>
+      <c r="F4" s="728" t="inlineStr">
         <is>
           <t>MG2</t>
         </is>
       </c>
-      <c r="G4" s="685" t="n"/>
-      <c r="H4" s="685" t="n"/>
-      <c r="I4" s="685" t="n"/>
-      <c r="K4" s="686" t="inlineStr">
+      <c r="G4" s="729" t="n"/>
+      <c r="H4" s="729" t="n"/>
+      <c r="I4" s="729" t="n"/>
+      <c r="K4" s="730" t="inlineStr">
         <is>
           <t>MG3</t>
         </is>
       </c>
-      <c r="L4" s="687" t="n"/>
-      <c r="M4" s="687" t="n"/>
-      <c r="N4" s="687" t="n"/>
-      <c r="P4" s="688" t="inlineStr">
+      <c r="L4" s="731" t="n"/>
+      <c r="M4" s="731" t="n"/>
+      <c r="N4" s="731" t="n"/>
+      <c r="P4" s="732" t="inlineStr">
         <is>
           <t>MG4</t>
         </is>
       </c>
-      <c r="Q4" s="689" t="n"/>
-      <c r="R4" s="689" t="n"/>
-      <c r="S4" s="689" t="n"/>
+      <c r="Q4" s="733" t="n"/>
+      <c r="R4" s="733" t="n"/>
+      <c r="S4" s="733" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="683" t="n"/>
-      <c r="B5" s="683" t="n"/>
-      <c r="C5" s="683" t="n"/>
-      <c r="D5" s="683" t="n"/>
-      <c r="F5" s="685" t="n"/>
-      <c r="G5" s="685" t="n"/>
-      <c r="H5" s="685" t="n"/>
-      <c r="I5" s="685" t="n"/>
-      <c r="K5" s="687" t="n"/>
-      <c r="L5" s="687" t="n"/>
-      <c r="M5" s="687" t="n"/>
-      <c r="N5" s="687" t="n"/>
-      <c r="P5" s="689" t="n"/>
-      <c r="Q5" s="689" t="n"/>
-      <c r="R5" s="689" t="n"/>
-      <c r="S5" s="689" t="n"/>
+      <c r="A5" s="727" t="n"/>
+      <c r="B5" s="727" t="n"/>
+      <c r="C5" s="727" t="n"/>
+      <c r="D5" s="727" t="n"/>
+      <c r="F5" s="729" t="n"/>
+      <c r="G5" s="729" t="n"/>
+      <c r="H5" s="729" t="n"/>
+      <c r="I5" s="729" t="n"/>
+      <c r="K5" s="731" t="n"/>
+      <c r="L5" s="731" t="n"/>
+      <c r="M5" s="731" t="n"/>
+      <c r="N5" s="731" t="n"/>
+      <c r="P5" s="733" t="n"/>
+      <c r="Q5" s="733" t="n"/>
+      <c r="R5" s="733" t="n"/>
+      <c r="S5" s="733" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -7716,56 +7914,56 @@
       <c r="S8" s="15" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="690" t="inlineStr">
+      <c r="A9" s="734" t="inlineStr">
         <is>
           <t>MG5</t>
         </is>
       </c>
-      <c r="B9" s="691" t="n"/>
-      <c r="C9" s="691" t="n"/>
-      <c r="D9" s="691" t="n"/>
-      <c r="F9" s="692" t="inlineStr">
+      <c r="B9" s="735" t="n"/>
+      <c r="C9" s="735" t="n"/>
+      <c r="D9" s="735" t="n"/>
+      <c r="F9" s="736" t="inlineStr">
         <is>
           <t>MG6</t>
         </is>
       </c>
-      <c r="G9" s="693" t="n"/>
-      <c r="H9" s="693" t="n"/>
-      <c r="I9" s="693" t="n"/>
-      <c r="K9" s="694" t="inlineStr">
+      <c r="G9" s="737" t="n"/>
+      <c r="H9" s="737" t="n"/>
+      <c r="I9" s="737" t="n"/>
+      <c r="K9" s="738" t="inlineStr">
         <is>
           <t>MG7</t>
         </is>
       </c>
-      <c r="L9" s="695" t="n"/>
-      <c r="M9" s="695" t="n"/>
-      <c r="N9" s="695" t="n"/>
-      <c r="P9" s="696" t="inlineStr">
+      <c r="L9" s="739" t="n"/>
+      <c r="M9" s="739" t="n"/>
+      <c r="N9" s="739" t="n"/>
+      <c r="P9" s="740" t="inlineStr">
         <is>
           <t>MG8</t>
         </is>
       </c>
-      <c r="Q9" s="697" t="n"/>
-      <c r="R9" s="697" t="n"/>
-      <c r="S9" s="697" t="n"/>
+      <c r="Q9" s="741" t="n"/>
+      <c r="R9" s="741" t="n"/>
+      <c r="S9" s="741" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="691" t="n"/>
-      <c r="B10" s="691" t="n"/>
-      <c r="C10" s="691" t="n"/>
-      <c r="D10" s="691" t="n"/>
-      <c r="F10" s="693" t="n"/>
-      <c r="G10" s="693" t="n"/>
-      <c r="H10" s="693" t="n"/>
-      <c r="I10" s="693" t="n"/>
-      <c r="K10" s="695" t="n"/>
-      <c r="L10" s="695" t="n"/>
-      <c r="M10" s="695" t="n"/>
-      <c r="N10" s="695" t="n"/>
-      <c r="P10" s="697" t="n"/>
-      <c r="Q10" s="697" t="n"/>
-      <c r="R10" s="697" t="n"/>
-      <c r="S10" s="697" t="n"/>
+      <c r="A10" s="735" t="n"/>
+      <c r="B10" s="735" t="n"/>
+      <c r="C10" s="735" t="n"/>
+      <c r="D10" s="735" t="n"/>
+      <c r="F10" s="737" t="n"/>
+      <c r="G10" s="737" t="n"/>
+      <c r="H10" s="737" t="n"/>
+      <c r="I10" s="737" t="n"/>
+      <c r="K10" s="739" t="n"/>
+      <c r="L10" s="739" t="n"/>
+      <c r="M10" s="739" t="n"/>
+      <c r="N10" s="739" t="n"/>
+      <c r="P10" s="741" t="n"/>
+      <c r="Q10" s="741" t="n"/>
+      <c r="R10" s="741" t="n"/>
+      <c r="S10" s="741" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -7870,56 +8068,56 @@
       <c r="S13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="698" t="inlineStr">
+      <c r="A14" s="742" t="inlineStr">
         <is>
           <t>MG9</t>
         </is>
       </c>
-      <c r="B14" s="699" t="n"/>
-      <c r="C14" s="699" t="n"/>
-      <c r="D14" s="699" t="n"/>
-      <c r="F14" s="700" t="inlineStr">
+      <c r="B14" s="743" t="n"/>
+      <c r="C14" s="743" t="n"/>
+      <c r="D14" s="743" t="n"/>
+      <c r="F14" s="744" t="inlineStr">
         <is>
           <t>MG10</t>
         </is>
       </c>
-      <c r="G14" s="701" t="n"/>
-      <c r="H14" s="701" t="n"/>
-      <c r="I14" s="701" t="n"/>
-      <c r="K14" s="702" t="inlineStr">
+      <c r="G14" s="745" t="n"/>
+      <c r="H14" s="745" t="n"/>
+      <c r="I14" s="745" t="n"/>
+      <c r="K14" s="746" t="inlineStr">
         <is>
           <t>MG11</t>
         </is>
       </c>
-      <c r="L14" s="703" t="n"/>
-      <c r="M14" s="703" t="n"/>
-      <c r="N14" s="703" t="n"/>
-      <c r="P14" s="704" t="inlineStr">
+      <c r="L14" s="747" t="n"/>
+      <c r="M14" s="747" t="n"/>
+      <c r="N14" s="747" t="n"/>
+      <c r="P14" s="748" t="inlineStr">
         <is>
           <t>MG12</t>
         </is>
       </c>
-      <c r="Q14" s="705" t="n"/>
-      <c r="R14" s="705" t="n"/>
-      <c r="S14" s="705" t="n"/>
+      <c r="Q14" s="749" t="n"/>
+      <c r="R14" s="749" t="n"/>
+      <c r="S14" s="749" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="699" t="n"/>
-      <c r="B15" s="699" t="n"/>
-      <c r="C15" s="699" t="n"/>
-      <c r="D15" s="699" t="n"/>
-      <c r="F15" s="701" t="n"/>
-      <c r="G15" s="701" t="n"/>
-      <c r="H15" s="701" t="n"/>
-      <c r="I15" s="701" t="n"/>
-      <c r="K15" s="703" t="n"/>
-      <c r="L15" s="703" t="n"/>
-      <c r="M15" s="703" t="n"/>
-      <c r="N15" s="703" t="n"/>
-      <c r="P15" s="705" t="n"/>
-      <c r="Q15" s="705" t="n"/>
-      <c r="R15" s="705" t="n"/>
-      <c r="S15" s="705" t="n"/>
+      <c r="A15" s="743" t="n"/>
+      <c r="B15" s="743" t="n"/>
+      <c r="C15" s="743" t="n"/>
+      <c r="D15" s="743" t="n"/>
+      <c r="F15" s="745" t="n"/>
+      <c r="G15" s="745" t="n"/>
+      <c r="H15" s="745" t="n"/>
+      <c r="I15" s="745" t="n"/>
+      <c r="K15" s="747" t="n"/>
+      <c r="L15" s="747" t="n"/>
+      <c r="M15" s="747" t="n"/>
+      <c r="N15" s="747" t="n"/>
+      <c r="P15" s="749" t="n"/>
+      <c r="Q15" s="749" t="n"/>
+      <c r="R15" s="749" t="n"/>
+      <c r="S15" s="749" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -8024,56 +8222,56 @@
       <c r="S18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="706" t="inlineStr">
+      <c r="A19" s="750" t="inlineStr">
         <is>
           <t>MG13</t>
         </is>
       </c>
-      <c r="B19" s="707" t="n"/>
-      <c r="C19" s="707" t="n"/>
-      <c r="D19" s="707" t="n"/>
-      <c r="F19" s="708" t="inlineStr">
+      <c r="B19" s="751" t="n"/>
+      <c r="C19" s="751" t="n"/>
+      <c r="D19" s="751" t="n"/>
+      <c r="F19" s="752" t="inlineStr">
         <is>
           <t>MG14</t>
         </is>
       </c>
-      <c r="G19" s="709" t="n"/>
-      <c r="H19" s="709" t="n"/>
-      <c r="I19" s="709" t="n"/>
-      <c r="K19" s="710" t="inlineStr">
+      <c r="G19" s="753" t="n"/>
+      <c r="H19" s="753" t="n"/>
+      <c r="I19" s="753" t="n"/>
+      <c r="K19" s="754" t="inlineStr">
         <is>
           <t>MG15</t>
         </is>
       </c>
-      <c r="L19" s="711" t="n"/>
-      <c r="M19" s="711" t="n"/>
-      <c r="N19" s="711" t="n"/>
-      <c r="P19" s="712" t="inlineStr">
+      <c r="L19" s="755" t="n"/>
+      <c r="M19" s="755" t="n"/>
+      <c r="N19" s="755" t="n"/>
+      <c r="P19" s="756" t="inlineStr">
         <is>
           <t>MG16</t>
         </is>
       </c>
-      <c r="Q19" s="713" t="n"/>
-      <c r="R19" s="713" t="n"/>
-      <c r="S19" s="713" t="n"/>
+      <c r="Q19" s="757" t="n"/>
+      <c r="R19" s="757" t="n"/>
+      <c r="S19" s="757" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="707" t="n"/>
-      <c r="B20" s="707" t="n"/>
-      <c r="C20" s="707" t="n"/>
-      <c r="D20" s="707" t="n"/>
-      <c r="F20" s="709" t="n"/>
-      <c r="G20" s="709" t="n"/>
-      <c r="H20" s="709" t="n"/>
-      <c r="I20" s="709" t="n"/>
-      <c r="K20" s="711" t="n"/>
-      <c r="L20" s="711" t="n"/>
-      <c r="M20" s="711" t="n"/>
-      <c r="N20" s="711" t="n"/>
-      <c r="P20" s="713" t="n"/>
-      <c r="Q20" s="713" t="n"/>
-      <c r="R20" s="713" t="n"/>
-      <c r="S20" s="713" t="n"/>
+      <c r="A20" s="751" t="n"/>
+      <c r="B20" s="751" t="n"/>
+      <c r="C20" s="751" t="n"/>
+      <c r="D20" s="751" t="n"/>
+      <c r="F20" s="753" t="n"/>
+      <c r="G20" s="753" t="n"/>
+      <c r="H20" s="753" t="n"/>
+      <c r="I20" s="753" t="n"/>
+      <c r="K20" s="755" t="n"/>
+      <c r="L20" s="755" t="n"/>
+      <c r="M20" s="755" t="n"/>
+      <c r="N20" s="755" t="n"/>
+      <c r="P20" s="757" t="n"/>
+      <c r="Q20" s="757" t="n"/>
+      <c r="R20" s="757" t="n"/>
+      <c r="S20" s="757" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -8178,56 +8376,56 @@
       <c r="S23" s="15" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="714" t="inlineStr">
+      <c r="A24" s="758" t="inlineStr">
         <is>
           <t>MG17</t>
         </is>
       </c>
-      <c r="B24" s="715" t="n"/>
-      <c r="C24" s="715" t="n"/>
-      <c r="D24" s="715" t="n"/>
-      <c r="F24" s="716" t="inlineStr">
+      <c r="B24" s="759" t="n"/>
+      <c r="C24" s="759" t="n"/>
+      <c r="D24" s="759" t="n"/>
+      <c r="F24" s="760" t="inlineStr">
         <is>
           <t>MG18</t>
         </is>
       </c>
-      <c r="G24" s="717" t="n"/>
-      <c r="H24" s="717" t="n"/>
-      <c r="I24" s="717" t="n"/>
-      <c r="K24" s="718" t="inlineStr">
+      <c r="G24" s="761" t="n"/>
+      <c r="H24" s="761" t="n"/>
+      <c r="I24" s="761" t="n"/>
+      <c r="K24" s="762" t="inlineStr">
         <is>
           <t>MG19</t>
         </is>
       </c>
-      <c r="L24" s="719" t="n"/>
-      <c r="M24" s="719" t="n"/>
-      <c r="N24" s="719" t="n"/>
-      <c r="P24" s="720" t="inlineStr">
+      <c r="L24" s="763" t="n"/>
+      <c r="M24" s="763" t="n"/>
+      <c r="N24" s="763" t="n"/>
+      <c r="P24" s="764" t="inlineStr">
         <is>
           <t>MG20</t>
         </is>
       </c>
-      <c r="Q24" s="721" t="n"/>
-      <c r="R24" s="721" t="n"/>
-      <c r="S24" s="721" t="n"/>
+      <c r="Q24" s="765" t="n"/>
+      <c r="R24" s="765" t="n"/>
+      <c r="S24" s="765" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="715" t="n"/>
-      <c r="B25" s="715" t="n"/>
-      <c r="C25" s="715" t="n"/>
-      <c r="D25" s="715" t="n"/>
-      <c r="F25" s="717" t="n"/>
-      <c r="G25" s="717" t="n"/>
-      <c r="H25" s="717" t="n"/>
-      <c r="I25" s="717" t="n"/>
-      <c r="K25" s="719" t="n"/>
-      <c r="L25" s="719" t="n"/>
-      <c r="M25" s="719" t="n"/>
-      <c r="N25" s="719" t="n"/>
-      <c r="P25" s="721" t="n"/>
-      <c r="Q25" s="721" t="n"/>
-      <c r="R25" s="721" t="n"/>
-      <c r="S25" s="721" t="n"/>
+      <c r="A25" s="759" t="n"/>
+      <c r="B25" s="759" t="n"/>
+      <c r="C25" s="759" t="n"/>
+      <c r="D25" s="759" t="n"/>
+      <c r="F25" s="761" t="n"/>
+      <c r="G25" s="761" t="n"/>
+      <c r="H25" s="761" t="n"/>
+      <c r="I25" s="761" t="n"/>
+      <c r="K25" s="763" t="n"/>
+      <c r="L25" s="763" t="n"/>
+      <c r="M25" s="763" t="n"/>
+      <c r="N25" s="763" t="n"/>
+      <c r="P25" s="765" t="n"/>
+      <c r="Q25" s="765" t="n"/>
+      <c r="R25" s="765" t="n"/>
+      <c r="S25" s="765" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
@@ -8332,20 +8530,20 @@
       <c r="S28" s="15" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="722" t="inlineStr">
+      <c r="A29" s="766" t="inlineStr">
         <is>
           <t>MG21</t>
         </is>
       </c>
-      <c r="B29" s="723" t="n"/>
-      <c r="C29" s="723" t="n"/>
-      <c r="D29" s="723" t="n"/>
+      <c r="B29" s="767" t="n"/>
+      <c r="C29" s="767" t="n"/>
+      <c r="D29" s="767" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="723" t="n"/>
-      <c r="B30" s="723" t="n"/>
-      <c r="C30" s="723" t="n"/>
-      <c r="D30" s="723" t="n"/>
+      <c r="A30" s="767" t="n"/>
+      <c r="B30" s="767" t="n"/>
+      <c r="C30" s="767" t="n"/>
+      <c r="D30" s="767" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -8513,14 +8711,14 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="356" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>MH1</t>
         </is>
       </c>
-      <c r="B4" s="357" t="n"/>
-      <c r="C4" s="357" t="n"/>
-      <c r="D4" s="357" t="n"/>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
       <c r="F4" s="6" t="inlineStr">
         <is>
           <t>MH2</t>
@@ -8529,45 +8727,45 @@
       <c r="G4" s="7" t="n"/>
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
-      <c r="K4" s="724" t="inlineStr">
+      <c r="K4" s="768" t="inlineStr">
         <is>
           <t>MH3</t>
         </is>
       </c>
-      <c r="L4" s="725" t="n"/>
-      <c r="M4" s="725" t="n"/>
-      <c r="N4" s="725" t="n"/>
-      <c r="P4" s="726" t="inlineStr">
+      <c r="L4" s="769" t="n"/>
+      <c r="M4" s="769" t="n"/>
+      <c r="N4" s="769" t="n"/>
+      <c r="P4" s="770" t="inlineStr">
         <is>
           <t>MH4</t>
         </is>
       </c>
-      <c r="Q4" s="727" t="n"/>
-      <c r="R4" s="727" t="n"/>
-      <c r="S4" s="727" t="n"/>
+      <c r="Q4" s="771" t="n"/>
+      <c r="R4" s="771" t="n"/>
+      <c r="S4" s="771" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="357" t="n"/>
-      <c r="B5" s="357" t="n"/>
-      <c r="C5" s="357" t="n"/>
-      <c r="D5" s="357" t="n"/>
+      <c r="A5" s="7" t="n"/>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
       <c r="F5" s="7" t="n"/>
       <c r="G5" s="7" t="n"/>
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
-      <c r="K5" s="725" t="n"/>
-      <c r="L5" s="725" t="n"/>
-      <c r="M5" s="725" t="n"/>
-      <c r="N5" s="725" t="n"/>
-      <c r="P5" s="727" t="n"/>
-      <c r="Q5" s="727" t="n"/>
-      <c r="R5" s="727" t="n"/>
-      <c r="S5" s="727" t="n"/>
+      <c r="K5" s="769" t="n"/>
+      <c r="L5" s="769" t="n"/>
+      <c r="M5" s="769" t="n"/>
+      <c r="N5" s="769" t="n"/>
+      <c r="P5" s="771" t="n"/>
+      <c r="Q5" s="771" t="n"/>
+      <c r="R5" s="771" t="n"/>
+      <c r="S5" s="771" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>HEX: N/A</t>
+          <t>HEX: #FFFFFF</t>
         </is>
       </c>
       <c r="B6" s="15" t="n"/>
@@ -8601,7 +8799,7 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>RGB: N/A</t>
+          <t>RGB: 255, 255, 255</t>
         </is>
       </c>
       <c r="B7" s="15" t="n"/>
@@ -8635,7 +8833,7 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>来源: official_pdf</t>
+          <t>来源: public_tool_display_hex</t>
         </is>
       </c>
       <c r="B8" s="15" t="n"/>
@@ -8667,22 +8865,22 @@
       <c r="S8" s="15" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="728" t="inlineStr">
+      <c r="A9" s="772" t="inlineStr">
         <is>
           <t>MH5</t>
         </is>
       </c>
-      <c r="B9" s="729" t="n"/>
-      <c r="C9" s="729" t="n"/>
-      <c r="D9" s="729" t="n"/>
-      <c r="F9" s="730" t="inlineStr">
+      <c r="B9" s="773" t="n"/>
+      <c r="C9" s="773" t="n"/>
+      <c r="D9" s="773" t="n"/>
+      <c r="F9" s="774" t="inlineStr">
         <is>
           <t>MH6</t>
         </is>
       </c>
-      <c r="G9" s="731" t="n"/>
-      <c r="H9" s="731" t="n"/>
-      <c r="I9" s="731" t="n"/>
+      <c r="G9" s="775" t="n"/>
+      <c r="H9" s="775" t="n"/>
+      <c r="I9" s="775" t="n"/>
       <c r="K9" s="8" t="inlineStr">
         <is>
           <t>MH7</t>
@@ -8691,32 +8889,32 @@
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
       <c r="N9" s="9" t="n"/>
-      <c r="P9" s="732" t="inlineStr">
+      <c r="P9" s="776" t="inlineStr">
         <is>
           <t>MH8</t>
         </is>
       </c>
-      <c r="Q9" s="733" t="n"/>
-      <c r="R9" s="733" t="n"/>
-      <c r="S9" s="733" t="n"/>
+      <c r="Q9" s="777" t="n"/>
+      <c r="R9" s="777" t="n"/>
+      <c r="S9" s="777" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="729" t="n"/>
-      <c r="B10" s="729" t="n"/>
-      <c r="C10" s="729" t="n"/>
-      <c r="D10" s="729" t="n"/>
-      <c r="F10" s="731" t="n"/>
-      <c r="G10" s="731" t="n"/>
-      <c r="H10" s="731" t="n"/>
-      <c r="I10" s="731" t="n"/>
+      <c r="A10" s="773" t="n"/>
+      <c r="B10" s="773" t="n"/>
+      <c r="C10" s="773" t="n"/>
+      <c r="D10" s="773" t="n"/>
+      <c r="F10" s="775" t="n"/>
+      <c r="G10" s="775" t="n"/>
+      <c r="H10" s="775" t="n"/>
+      <c r="I10" s="775" t="n"/>
       <c r="K10" s="9" t="n"/>
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="9" t="n"/>
       <c r="N10" s="9" t="n"/>
-      <c r="P10" s="733" t="n"/>
-      <c r="Q10" s="733" t="n"/>
-      <c r="R10" s="733" t="n"/>
-      <c r="S10" s="733" t="n"/>
+      <c r="P10" s="777" t="n"/>
+      <c r="Q10" s="777" t="n"/>
+      <c r="R10" s="777" t="n"/>
+      <c r="S10" s="777" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -8821,56 +9019,56 @@
       <c r="S13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="734" t="inlineStr">
+      <c r="A14" s="778" t="inlineStr">
         <is>
           <t>MH9</t>
         </is>
       </c>
-      <c r="B14" s="735" t="n"/>
-      <c r="C14" s="735" t="n"/>
-      <c r="D14" s="735" t="n"/>
-      <c r="F14" s="736" t="inlineStr">
+      <c r="B14" s="779" t="n"/>
+      <c r="C14" s="779" t="n"/>
+      <c r="D14" s="779" t="n"/>
+      <c r="F14" s="780" t="inlineStr">
         <is>
           <t>MH10</t>
         </is>
       </c>
-      <c r="G14" s="737" t="n"/>
-      <c r="H14" s="737" t="n"/>
-      <c r="I14" s="737" t="n"/>
-      <c r="K14" s="738" t="inlineStr">
+      <c r="G14" s="781" t="n"/>
+      <c r="H14" s="781" t="n"/>
+      <c r="I14" s="781" t="n"/>
+      <c r="K14" s="782" t="inlineStr">
         <is>
           <t>MH11</t>
         </is>
       </c>
-      <c r="L14" s="739" t="n"/>
-      <c r="M14" s="739" t="n"/>
-      <c r="N14" s="739" t="n"/>
-      <c r="P14" s="740" t="inlineStr">
+      <c r="L14" s="783" t="n"/>
+      <c r="M14" s="783" t="n"/>
+      <c r="N14" s="783" t="n"/>
+      <c r="P14" s="784" t="inlineStr">
         <is>
           <t>MH12</t>
         </is>
       </c>
-      <c r="Q14" s="741" t="n"/>
-      <c r="R14" s="741" t="n"/>
-      <c r="S14" s="741" t="n"/>
+      <c r="Q14" s="785" t="n"/>
+      <c r="R14" s="785" t="n"/>
+      <c r="S14" s="785" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="735" t="n"/>
-      <c r="B15" s="735" t="n"/>
-      <c r="C15" s="735" t="n"/>
-      <c r="D15" s="735" t="n"/>
-      <c r="F15" s="737" t="n"/>
-      <c r="G15" s="737" t="n"/>
-      <c r="H15" s="737" t="n"/>
-      <c r="I15" s="737" t="n"/>
-      <c r="K15" s="739" t="n"/>
-      <c r="L15" s="739" t="n"/>
-      <c r="M15" s="739" t="n"/>
-      <c r="N15" s="739" t="n"/>
-      <c r="P15" s="741" t="n"/>
-      <c r="Q15" s="741" t="n"/>
-      <c r="R15" s="741" t="n"/>
-      <c r="S15" s="741" t="n"/>
+      <c r="A15" s="779" t="n"/>
+      <c r="B15" s="779" t="n"/>
+      <c r="C15" s="779" t="n"/>
+      <c r="D15" s="779" t="n"/>
+      <c r="F15" s="781" t="n"/>
+      <c r="G15" s="781" t="n"/>
+      <c r="H15" s="781" t="n"/>
+      <c r="I15" s="781" t="n"/>
+      <c r="K15" s="783" t="n"/>
+      <c r="L15" s="783" t="n"/>
+      <c r="M15" s="783" t="n"/>
+      <c r="N15" s="783" t="n"/>
+      <c r="P15" s="785" t="n"/>
+      <c r="Q15" s="785" t="n"/>
+      <c r="R15" s="785" t="n"/>
+      <c r="S15" s="785" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -8975,56 +9173,56 @@
       <c r="S18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="742" t="inlineStr">
+      <c r="A19" s="786" t="inlineStr">
         <is>
           <t>MH13</t>
         </is>
       </c>
-      <c r="B19" s="743" t="n"/>
-      <c r="C19" s="743" t="n"/>
-      <c r="D19" s="743" t="n"/>
-      <c r="F19" s="744" t="inlineStr">
+      <c r="B19" s="787" t="n"/>
+      <c r="C19" s="787" t="n"/>
+      <c r="D19" s="787" t="n"/>
+      <c r="F19" s="788" t="inlineStr">
         <is>
           <t>MH14</t>
         </is>
       </c>
-      <c r="G19" s="745" t="n"/>
-      <c r="H19" s="745" t="n"/>
-      <c r="I19" s="745" t="n"/>
-      <c r="K19" s="746" t="inlineStr">
+      <c r="G19" s="789" t="n"/>
+      <c r="H19" s="789" t="n"/>
+      <c r="I19" s="789" t="n"/>
+      <c r="K19" s="790" t="inlineStr">
         <is>
           <t>MH15</t>
         </is>
       </c>
-      <c r="L19" s="747" t="n"/>
-      <c r="M19" s="747" t="n"/>
-      <c r="N19" s="747" t="n"/>
-      <c r="P19" s="748" t="inlineStr">
+      <c r="L19" s="791" t="n"/>
+      <c r="M19" s="791" t="n"/>
+      <c r="N19" s="791" t="n"/>
+      <c r="P19" s="792" t="inlineStr">
         <is>
           <t>MH16</t>
         </is>
       </c>
-      <c r="Q19" s="749" t="n"/>
-      <c r="R19" s="749" t="n"/>
-      <c r="S19" s="749" t="n"/>
+      <c r="Q19" s="793" t="n"/>
+      <c r="R19" s="793" t="n"/>
+      <c r="S19" s="793" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="743" t="n"/>
-      <c r="B20" s="743" t="n"/>
-      <c r="C20" s="743" t="n"/>
-      <c r="D20" s="743" t="n"/>
-      <c r="F20" s="745" t="n"/>
-      <c r="G20" s="745" t="n"/>
-      <c r="H20" s="745" t="n"/>
-      <c r="I20" s="745" t="n"/>
-      <c r="K20" s="747" t="n"/>
-      <c r="L20" s="747" t="n"/>
-      <c r="M20" s="747" t="n"/>
-      <c r="N20" s="747" t="n"/>
-      <c r="P20" s="749" t="n"/>
-      <c r="Q20" s="749" t="n"/>
-      <c r="R20" s="749" t="n"/>
-      <c r="S20" s="749" t="n"/>
+      <c r="A20" s="787" t="n"/>
+      <c r="B20" s="787" t="n"/>
+      <c r="C20" s="787" t="n"/>
+      <c r="D20" s="787" t="n"/>
+      <c r="F20" s="789" t="n"/>
+      <c r="G20" s="789" t="n"/>
+      <c r="H20" s="789" t="n"/>
+      <c r="I20" s="789" t="n"/>
+      <c r="K20" s="791" t="n"/>
+      <c r="L20" s="791" t="n"/>
+      <c r="M20" s="791" t="n"/>
+      <c r="N20" s="791" t="n"/>
+      <c r="P20" s="793" t="n"/>
+      <c r="Q20" s="793" t="n"/>
+      <c r="R20" s="793" t="n"/>
+      <c r="S20" s="793" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -9129,56 +9327,56 @@
       <c r="S23" s="15" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="750" t="inlineStr">
+      <c r="A24" s="794" t="inlineStr">
         <is>
           <t>MH17</t>
         </is>
       </c>
-      <c r="B24" s="751" t="n"/>
-      <c r="C24" s="751" t="n"/>
-      <c r="D24" s="751" t="n"/>
-      <c r="F24" s="752" t="inlineStr">
+      <c r="B24" s="795" t="n"/>
+      <c r="C24" s="795" t="n"/>
+      <c r="D24" s="795" t="n"/>
+      <c r="F24" s="796" t="inlineStr">
         <is>
           <t>MH18</t>
         </is>
       </c>
-      <c r="G24" s="753" t="n"/>
-      <c r="H24" s="753" t="n"/>
-      <c r="I24" s="753" t="n"/>
-      <c r="K24" s="754" t="inlineStr">
+      <c r="G24" s="797" t="n"/>
+      <c r="H24" s="797" t="n"/>
+      <c r="I24" s="797" t="n"/>
+      <c r="K24" s="798" t="inlineStr">
         <is>
           <t>MH19</t>
         </is>
       </c>
-      <c r="L24" s="755" t="n"/>
-      <c r="M24" s="755" t="n"/>
-      <c r="N24" s="755" t="n"/>
-      <c r="P24" s="756" t="inlineStr">
+      <c r="L24" s="799" t="n"/>
+      <c r="M24" s="799" t="n"/>
+      <c r="N24" s="799" t="n"/>
+      <c r="P24" s="800" t="inlineStr">
         <is>
           <t>MH20</t>
         </is>
       </c>
-      <c r="Q24" s="757" t="n"/>
-      <c r="R24" s="757" t="n"/>
-      <c r="S24" s="757" t="n"/>
+      <c r="Q24" s="801" t="n"/>
+      <c r="R24" s="801" t="n"/>
+      <c r="S24" s="801" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="751" t="n"/>
-      <c r="B25" s="751" t="n"/>
-      <c r="C25" s="751" t="n"/>
-      <c r="D25" s="751" t="n"/>
-      <c r="F25" s="753" t="n"/>
-      <c r="G25" s="753" t="n"/>
-      <c r="H25" s="753" t="n"/>
-      <c r="I25" s="753" t="n"/>
-      <c r="K25" s="755" t="n"/>
-      <c r="L25" s="755" t="n"/>
-      <c r="M25" s="755" t="n"/>
-      <c r="N25" s="755" t="n"/>
-      <c r="P25" s="757" t="n"/>
-      <c r="Q25" s="757" t="n"/>
-      <c r="R25" s="757" t="n"/>
-      <c r="S25" s="757" t="n"/>
+      <c r="A25" s="795" t="n"/>
+      <c r="B25" s="795" t="n"/>
+      <c r="C25" s="795" t="n"/>
+      <c r="D25" s="795" t="n"/>
+      <c r="F25" s="797" t="n"/>
+      <c r="G25" s="797" t="n"/>
+      <c r="H25" s="797" t="n"/>
+      <c r="I25" s="797" t="n"/>
+      <c r="K25" s="799" t="n"/>
+      <c r="L25" s="799" t="n"/>
+      <c r="M25" s="799" t="n"/>
+      <c r="N25" s="799" t="n"/>
+      <c r="P25" s="801" t="n"/>
+      <c r="Q25" s="801" t="n"/>
+      <c r="R25" s="801" t="n"/>
+      <c r="S25" s="801" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
@@ -9283,44 +9481,44 @@
       <c r="S28" s="15" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="758" t="inlineStr">
+      <c r="A29" s="802" t="inlineStr">
         <is>
           <t>MH21</t>
         </is>
       </c>
-      <c r="B29" s="759" t="n"/>
-      <c r="C29" s="759" t="n"/>
-      <c r="D29" s="759" t="n"/>
-      <c r="F29" s="760" t="inlineStr">
+      <c r="B29" s="803" t="n"/>
+      <c r="C29" s="803" t="n"/>
+      <c r="D29" s="803" t="n"/>
+      <c r="F29" s="804" t="inlineStr">
         <is>
           <t>MH22</t>
         </is>
       </c>
-      <c r="G29" s="761" t="n"/>
-      <c r="H29" s="761" t="n"/>
-      <c r="I29" s="761" t="n"/>
-      <c r="K29" s="762" t="inlineStr">
+      <c r="G29" s="805" t="n"/>
+      <c r="H29" s="805" t="n"/>
+      <c r="I29" s="805" t="n"/>
+      <c r="K29" s="806" t="inlineStr">
         <is>
           <t>MH23</t>
         </is>
       </c>
-      <c r="L29" s="763" t="n"/>
-      <c r="M29" s="763" t="n"/>
-      <c r="N29" s="763" t="n"/>
+      <c r="L29" s="807" t="n"/>
+      <c r="M29" s="807" t="n"/>
+      <c r="N29" s="807" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="759" t="n"/>
-      <c r="B30" s="759" t="n"/>
-      <c r="C30" s="759" t="n"/>
-      <c r="D30" s="759" t="n"/>
-      <c r="F30" s="761" t="n"/>
-      <c r="G30" s="761" t="n"/>
-      <c r="H30" s="761" t="n"/>
-      <c r="I30" s="761" t="n"/>
-      <c r="K30" s="763" t="n"/>
-      <c r="L30" s="763" t="n"/>
-      <c r="M30" s="763" t="n"/>
-      <c r="N30" s="763" t="n"/>
+      <c r="A30" s="803" t="n"/>
+      <c r="B30" s="803" t="n"/>
+      <c r="C30" s="803" t="n"/>
+      <c r="D30" s="803" t="n"/>
+      <c r="F30" s="805" t="n"/>
+      <c r="G30" s="805" t="n"/>
+      <c r="H30" s="805" t="n"/>
+      <c r="I30" s="805" t="n"/>
+      <c r="K30" s="807" t="n"/>
+      <c r="L30" s="807" t="n"/>
+      <c r="M30" s="807" t="n"/>
+      <c r="N30" s="807" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -9544,56 +9742,56 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="764" t="inlineStr">
+      <c r="A4" s="808" t="inlineStr">
         <is>
           <t>MM1</t>
         </is>
       </c>
-      <c r="B4" s="765" t="n"/>
-      <c r="C4" s="765" t="n"/>
-      <c r="D4" s="765" t="n"/>
-      <c r="F4" s="766" t="inlineStr">
+      <c r="B4" s="809" t="n"/>
+      <c r="C4" s="809" t="n"/>
+      <c r="D4" s="809" t="n"/>
+      <c r="F4" s="810" t="inlineStr">
         <is>
           <t>MM2</t>
         </is>
       </c>
-      <c r="G4" s="767" t="n"/>
-      <c r="H4" s="767" t="n"/>
-      <c r="I4" s="767" t="n"/>
-      <c r="K4" s="768" t="inlineStr">
+      <c r="G4" s="811" t="n"/>
+      <c r="H4" s="811" t="n"/>
+      <c r="I4" s="811" t="n"/>
+      <c r="K4" s="812" t="inlineStr">
         <is>
           <t>MM3</t>
         </is>
       </c>
-      <c r="L4" s="769" t="n"/>
-      <c r="M4" s="769" t="n"/>
-      <c r="N4" s="769" t="n"/>
-      <c r="P4" s="770" t="inlineStr">
+      <c r="L4" s="813" t="n"/>
+      <c r="M4" s="813" t="n"/>
+      <c r="N4" s="813" t="n"/>
+      <c r="P4" s="814" t="inlineStr">
         <is>
           <t>MM4</t>
         </is>
       </c>
-      <c r="Q4" s="771" t="n"/>
-      <c r="R4" s="771" t="n"/>
-      <c r="S4" s="771" t="n"/>
+      <c r="Q4" s="815" t="n"/>
+      <c r="R4" s="815" t="n"/>
+      <c r="S4" s="815" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="765" t="n"/>
-      <c r="B5" s="765" t="n"/>
-      <c r="C5" s="765" t="n"/>
-      <c r="D5" s="765" t="n"/>
-      <c r="F5" s="767" t="n"/>
-      <c r="G5" s="767" t="n"/>
-      <c r="H5" s="767" t="n"/>
-      <c r="I5" s="767" t="n"/>
-      <c r="K5" s="769" t="n"/>
-      <c r="L5" s="769" t="n"/>
-      <c r="M5" s="769" t="n"/>
-      <c r="N5" s="769" t="n"/>
-      <c r="P5" s="771" t="n"/>
-      <c r="Q5" s="771" t="n"/>
-      <c r="R5" s="771" t="n"/>
-      <c r="S5" s="771" t="n"/>
+      <c r="A5" s="809" t="n"/>
+      <c r="B5" s="809" t="n"/>
+      <c r="C5" s="809" t="n"/>
+      <c r="D5" s="809" t="n"/>
+      <c r="F5" s="811" t="n"/>
+      <c r="G5" s="811" t="n"/>
+      <c r="H5" s="811" t="n"/>
+      <c r="I5" s="811" t="n"/>
+      <c r="K5" s="813" t="n"/>
+      <c r="L5" s="813" t="n"/>
+      <c r="M5" s="813" t="n"/>
+      <c r="N5" s="813" t="n"/>
+      <c r="P5" s="815" t="n"/>
+      <c r="Q5" s="815" t="n"/>
+      <c r="R5" s="815" t="n"/>
+      <c r="S5" s="815" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -9698,56 +9896,56 @@
       <c r="S8" s="15" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="772" t="inlineStr">
+      <c r="A9" s="816" t="inlineStr">
         <is>
           <t>MM5</t>
         </is>
       </c>
-      <c r="B9" s="773" t="n"/>
-      <c r="C9" s="773" t="n"/>
-      <c r="D9" s="773" t="n"/>
-      <c r="F9" s="774" t="inlineStr">
+      <c r="B9" s="817" t="n"/>
+      <c r="C9" s="817" t="n"/>
+      <c r="D9" s="817" t="n"/>
+      <c r="F9" s="818" t="inlineStr">
         <is>
           <t>MM6</t>
         </is>
       </c>
-      <c r="G9" s="775" t="n"/>
-      <c r="H9" s="775" t="n"/>
-      <c r="I9" s="775" t="n"/>
-      <c r="K9" s="776" t="inlineStr">
+      <c r="G9" s="819" t="n"/>
+      <c r="H9" s="819" t="n"/>
+      <c r="I9" s="819" t="n"/>
+      <c r="K9" s="820" t="inlineStr">
         <is>
           <t>MM7</t>
         </is>
       </c>
-      <c r="L9" s="777" t="n"/>
-      <c r="M9" s="777" t="n"/>
-      <c r="N9" s="777" t="n"/>
-      <c r="P9" s="778" t="inlineStr">
+      <c r="L9" s="821" t="n"/>
+      <c r="M9" s="821" t="n"/>
+      <c r="N9" s="821" t="n"/>
+      <c r="P9" s="822" t="inlineStr">
         <is>
           <t>MM8</t>
         </is>
       </c>
-      <c r="Q9" s="779" t="n"/>
-      <c r="R9" s="779" t="n"/>
-      <c r="S9" s="779" t="n"/>
+      <c r="Q9" s="823" t="n"/>
+      <c r="R9" s="823" t="n"/>
+      <c r="S9" s="823" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="773" t="n"/>
-      <c r="B10" s="773" t="n"/>
-      <c r="C10" s="773" t="n"/>
-      <c r="D10" s="773" t="n"/>
-      <c r="F10" s="775" t="n"/>
-      <c r="G10" s="775" t="n"/>
-      <c r="H10" s="775" t="n"/>
-      <c r="I10" s="775" t="n"/>
-      <c r="K10" s="777" t="n"/>
-      <c r="L10" s="777" t="n"/>
-      <c r="M10" s="777" t="n"/>
-      <c r="N10" s="777" t="n"/>
-      <c r="P10" s="779" t="n"/>
-      <c r="Q10" s="779" t="n"/>
-      <c r="R10" s="779" t="n"/>
-      <c r="S10" s="779" t="n"/>
+      <c r="A10" s="817" t="n"/>
+      <c r="B10" s="817" t="n"/>
+      <c r="C10" s="817" t="n"/>
+      <c r="D10" s="817" t="n"/>
+      <c r="F10" s="819" t="n"/>
+      <c r="G10" s="819" t="n"/>
+      <c r="H10" s="819" t="n"/>
+      <c r="I10" s="819" t="n"/>
+      <c r="K10" s="821" t="n"/>
+      <c r="L10" s="821" t="n"/>
+      <c r="M10" s="821" t="n"/>
+      <c r="N10" s="821" t="n"/>
+      <c r="P10" s="823" t="n"/>
+      <c r="Q10" s="823" t="n"/>
+      <c r="R10" s="823" t="n"/>
+      <c r="S10" s="823" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -9852,56 +10050,56 @@
       <c r="S13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="780" t="inlineStr">
+      <c r="A14" s="824" t="inlineStr">
         <is>
           <t>MM9</t>
         </is>
       </c>
-      <c r="B14" s="781" t="n"/>
-      <c r="C14" s="781" t="n"/>
-      <c r="D14" s="781" t="n"/>
-      <c r="F14" s="782" t="inlineStr">
+      <c r="B14" s="825" t="n"/>
+      <c r="C14" s="825" t="n"/>
+      <c r="D14" s="825" t="n"/>
+      <c r="F14" s="826" t="inlineStr">
         <is>
           <t>MM10</t>
         </is>
       </c>
-      <c r="G14" s="783" t="n"/>
-      <c r="H14" s="783" t="n"/>
-      <c r="I14" s="783" t="n"/>
-      <c r="K14" s="784" t="inlineStr">
+      <c r="G14" s="827" t="n"/>
+      <c r="H14" s="827" t="n"/>
+      <c r="I14" s="827" t="n"/>
+      <c r="K14" s="828" t="inlineStr">
         <is>
           <t>MM11</t>
         </is>
       </c>
-      <c r="L14" s="785" t="n"/>
-      <c r="M14" s="785" t="n"/>
-      <c r="N14" s="785" t="n"/>
-      <c r="P14" s="786" t="inlineStr">
+      <c r="L14" s="829" t="n"/>
+      <c r="M14" s="829" t="n"/>
+      <c r="N14" s="829" t="n"/>
+      <c r="P14" s="830" t="inlineStr">
         <is>
           <t>MM12</t>
         </is>
       </c>
-      <c r="Q14" s="787" t="n"/>
-      <c r="R14" s="787" t="n"/>
-      <c r="S14" s="787" t="n"/>
+      <c r="Q14" s="831" t="n"/>
+      <c r="R14" s="831" t="n"/>
+      <c r="S14" s="831" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="781" t="n"/>
-      <c r="B15" s="781" t="n"/>
-      <c r="C15" s="781" t="n"/>
-      <c r="D15" s="781" t="n"/>
-      <c r="F15" s="783" t="n"/>
-      <c r="G15" s="783" t="n"/>
-      <c r="H15" s="783" t="n"/>
-      <c r="I15" s="783" t="n"/>
-      <c r="K15" s="785" t="n"/>
-      <c r="L15" s="785" t="n"/>
-      <c r="M15" s="785" t="n"/>
-      <c r="N15" s="785" t="n"/>
-      <c r="P15" s="787" t="n"/>
-      <c r="Q15" s="787" t="n"/>
-      <c r="R15" s="787" t="n"/>
-      <c r="S15" s="787" t="n"/>
+      <c r="A15" s="825" t="n"/>
+      <c r="B15" s="825" t="n"/>
+      <c r="C15" s="825" t="n"/>
+      <c r="D15" s="825" t="n"/>
+      <c r="F15" s="827" t="n"/>
+      <c r="G15" s="827" t="n"/>
+      <c r="H15" s="827" t="n"/>
+      <c r="I15" s="827" t="n"/>
+      <c r="K15" s="829" t="n"/>
+      <c r="L15" s="829" t="n"/>
+      <c r="M15" s="829" t="n"/>
+      <c r="N15" s="829" t="n"/>
+      <c r="P15" s="831" t="n"/>
+      <c r="Q15" s="831" t="n"/>
+      <c r="R15" s="831" t="n"/>
+      <c r="S15" s="831" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -10006,44 +10204,44 @@
       <c r="S18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="788" t="inlineStr">
+      <c r="A19" s="832" t="inlineStr">
         <is>
           <t>MM13</t>
         </is>
       </c>
-      <c r="B19" s="789" t="n"/>
-      <c r="C19" s="789" t="n"/>
-      <c r="D19" s="789" t="n"/>
-      <c r="F19" s="790" t="inlineStr">
+      <c r="B19" s="833" t="n"/>
+      <c r="C19" s="833" t="n"/>
+      <c r="D19" s="833" t="n"/>
+      <c r="F19" s="834" t="inlineStr">
         <is>
           <t>MM14</t>
         </is>
       </c>
-      <c r="G19" s="791" t="n"/>
-      <c r="H19" s="791" t="n"/>
-      <c r="I19" s="791" t="n"/>
-      <c r="K19" s="792" t="inlineStr">
+      <c r="G19" s="835" t="n"/>
+      <c r="H19" s="835" t="n"/>
+      <c r="I19" s="835" t="n"/>
+      <c r="K19" s="836" t="inlineStr">
         <is>
           <t>MM15</t>
         </is>
       </c>
-      <c r="L19" s="793" t="n"/>
-      <c r="M19" s="793" t="n"/>
-      <c r="N19" s="793" t="n"/>
+      <c r="L19" s="837" t="n"/>
+      <c r="M19" s="837" t="n"/>
+      <c r="N19" s="837" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="789" t="n"/>
-      <c r="B20" s="789" t="n"/>
-      <c r="C20" s="789" t="n"/>
-      <c r="D20" s="789" t="n"/>
-      <c r="F20" s="791" t="n"/>
-      <c r="G20" s="791" t="n"/>
-      <c r="H20" s="791" t="n"/>
-      <c r="I20" s="791" t="n"/>
-      <c r="K20" s="793" t="n"/>
-      <c r="L20" s="793" t="n"/>
-      <c r="M20" s="793" t="n"/>
-      <c r="N20" s="793" t="n"/>
+      <c r="A20" s="833" t="n"/>
+      <c r="B20" s="833" t="n"/>
+      <c r="C20" s="833" t="n"/>
+      <c r="D20" s="833" t="n"/>
+      <c r="F20" s="835" t="n"/>
+      <c r="G20" s="835" t="n"/>
+      <c r="H20" s="835" t="n"/>
+      <c r="I20" s="835" t="n"/>
+      <c r="K20" s="837" t="n"/>
+      <c r="L20" s="837" t="n"/>
+      <c r="M20" s="837" t="n"/>
+      <c r="N20" s="837" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -17755,53 +17953,53 @@
       <c r="B4" s="357" t="n"/>
       <c r="C4" s="357" t="n"/>
       <c r="D4" s="357" t="n"/>
-      <c r="F4" s="356" t="inlineStr">
+      <c r="F4" s="358" t="inlineStr">
         <is>
           <t>CG02</t>
         </is>
       </c>
-      <c r="G4" s="357" t="n"/>
-      <c r="H4" s="357" t="n"/>
-      <c r="I4" s="357" t="n"/>
-      <c r="K4" s="356" t="inlineStr">
+      <c r="G4" s="359" t="n"/>
+      <c r="H4" s="359" t="n"/>
+      <c r="I4" s="359" t="n"/>
+      <c r="K4" s="360" t="inlineStr">
         <is>
           <t>CG03</t>
         </is>
       </c>
-      <c r="L4" s="357" t="n"/>
-      <c r="M4" s="357" t="n"/>
-      <c r="N4" s="357" t="n"/>
-      <c r="P4" s="356" t="inlineStr">
+      <c r="L4" s="361" t="n"/>
+      <c r="M4" s="361" t="n"/>
+      <c r="N4" s="361" t="n"/>
+      <c r="P4" s="362" t="inlineStr">
         <is>
           <t>CG04</t>
         </is>
       </c>
-      <c r="Q4" s="357" t="n"/>
-      <c r="R4" s="357" t="n"/>
-      <c r="S4" s="357" t="n"/>
+      <c r="Q4" s="363" t="n"/>
+      <c r="R4" s="363" t="n"/>
+      <c r="S4" s="363" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="357" t="n"/>
       <c r="B5" s="357" t="n"/>
       <c r="C5" s="357" t="n"/>
       <c r="D5" s="357" t="n"/>
-      <c r="F5" s="357" t="n"/>
-      <c r="G5" s="357" t="n"/>
-      <c r="H5" s="357" t="n"/>
-      <c r="I5" s="357" t="n"/>
-      <c r="K5" s="357" t="n"/>
-      <c r="L5" s="357" t="n"/>
-      <c r="M5" s="357" t="n"/>
-      <c r="N5" s="357" t="n"/>
-      <c r="P5" s="357" t="n"/>
-      <c r="Q5" s="357" t="n"/>
-      <c r="R5" s="357" t="n"/>
-      <c r="S5" s="357" t="n"/>
+      <c r="F5" s="359" t="n"/>
+      <c r="G5" s="359" t="n"/>
+      <c r="H5" s="359" t="n"/>
+      <c r="I5" s="359" t="n"/>
+      <c r="K5" s="361" t="n"/>
+      <c r="L5" s="361" t="n"/>
+      <c r="M5" s="361" t="n"/>
+      <c r="N5" s="361" t="n"/>
+      <c r="P5" s="363" t="n"/>
+      <c r="Q5" s="363" t="n"/>
+      <c r="R5" s="363" t="n"/>
+      <c r="S5" s="363" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>HEX: N/A</t>
+          <t>HEX: #B2B9BF</t>
         </is>
       </c>
       <c r="B6" s="15" t="n"/>
@@ -17809,7 +18007,7 @@
       <c r="D6" s="15" t="n"/>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>HEX: N/A</t>
+          <t>HEX: #BEA6BA</t>
         </is>
       </c>
       <c r="G6" s="15" t="n"/>
@@ -17817,7 +18015,7 @@
       <c r="I6" s="15" t="n"/>
       <c r="K6" s="14" t="inlineStr">
         <is>
-          <t>HEX: N/A</t>
+          <t>HEX: #62B6D8</t>
         </is>
       </c>
       <c r="L6" s="15" t="n"/>
@@ -17825,7 +18023,7 @@
       <c r="N6" s="15" t="n"/>
       <c r="P6" s="14" t="inlineStr">
         <is>
-          <t>HEX: N/A</t>
+          <t>HEX: #8985C1</t>
         </is>
       </c>
       <c r="Q6" s="15" t="n"/>
@@ -17835,7 +18033,7 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>RGB: N/A</t>
+          <t>RGB: 178, 185, 191</t>
         </is>
       </c>
       <c r="B7" s="15" t="n"/>
@@ -17843,7 +18041,7 @@
       <c r="D7" s="15" t="n"/>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>RGB: N/A</t>
+          <t>RGB: 190, 166, 186</t>
         </is>
       </c>
       <c r="G7" s="15" t="n"/>
@@ -17851,7 +18049,7 @@
       <c r="I7" s="15" t="n"/>
       <c r="K7" s="14" t="inlineStr">
         <is>
-          <t>RGB: N/A</t>
+          <t>RGB: 98, 182, 216</t>
         </is>
       </c>
       <c r="L7" s="15" t="n"/>
@@ -17859,7 +18057,7 @@
       <c r="N7" s="15" t="n"/>
       <c r="P7" s="14" t="inlineStr">
         <is>
-          <t>RGB: N/A</t>
+          <t>RGB: 137, 133, 193</t>
         </is>
       </c>
       <c r="Q7" s="15" t="n"/>
@@ -17869,7 +18067,7 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>来源: official_chart_code_only</t>
+          <t>来源: official_chart_image_sampled</t>
         </is>
       </c>
       <c r="B8" s="15" t="n"/>
@@ -17877,7 +18075,7 @@
       <c r="D8" s="15" t="n"/>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>来源: official_chart_code_only</t>
+          <t>来源: official_chart_image_sampled</t>
         </is>
       </c>
       <c r="G8" s="15" t="n"/>
@@ -17885,7 +18083,7 @@
       <c r="I8" s="15" t="n"/>
       <c r="K8" s="14" t="inlineStr">
         <is>
-          <t>来源: official_chart_code_only</t>
+          <t>来源: official_chart_image_sampled</t>
         </is>
       </c>
       <c r="L8" s="15" t="n"/>
@@ -17893,7 +18091,7 @@
       <c r="N8" s="15" t="n"/>
       <c r="P8" s="14" t="inlineStr">
         <is>
-          <t>来源: official_chart_code_only</t>
+          <t>来源: official_chart_image_sampled</t>
         </is>
       </c>
       <c r="Q8" s="15" t="n"/>
@@ -17901,49 +18099,49 @@
       <c r="S8" s="15" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="356" t="inlineStr">
+      <c r="A9" s="364" t="inlineStr">
         <is>
           <t>CG05</t>
         </is>
       </c>
-      <c r="B9" s="357" t="n"/>
-      <c r="C9" s="357" t="n"/>
-      <c r="D9" s="357" t="n"/>
-      <c r="F9" s="356" t="inlineStr">
+      <c r="B9" s="365" t="n"/>
+      <c r="C9" s="365" t="n"/>
+      <c r="D9" s="365" t="n"/>
+      <c r="F9" s="366" t="inlineStr">
         <is>
           <t>CG06</t>
         </is>
       </c>
-      <c r="G9" s="357" t="n"/>
-      <c r="H9" s="357" t="n"/>
-      <c r="I9" s="357" t="n"/>
-      <c r="K9" s="356" t="inlineStr">
+      <c r="G9" s="367" t="n"/>
+      <c r="H9" s="367" t="n"/>
+      <c r="I9" s="367" t="n"/>
+      <c r="K9" s="368" t="inlineStr">
         <is>
           <t>CG07</t>
         </is>
       </c>
-      <c r="L9" s="357" t="n"/>
-      <c r="M9" s="357" t="n"/>
-      <c r="N9" s="357" t="n"/>
+      <c r="L9" s="369" t="n"/>
+      <c r="M9" s="369" t="n"/>
+      <c r="N9" s="369" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="357" t="n"/>
-      <c r="B10" s="357" t="n"/>
-      <c r="C10" s="357" t="n"/>
-      <c r="D10" s="357" t="n"/>
-      <c r="F10" s="357" t="n"/>
-      <c r="G10" s="357" t="n"/>
-      <c r="H10" s="357" t="n"/>
-      <c r="I10" s="357" t="n"/>
-      <c r="K10" s="357" t="n"/>
-      <c r="L10" s="357" t="n"/>
-      <c r="M10" s="357" t="n"/>
-      <c r="N10" s="357" t="n"/>
+      <c r="A10" s="365" t="n"/>
+      <c r="B10" s="365" t="n"/>
+      <c r="C10" s="365" t="n"/>
+      <c r="D10" s="365" t="n"/>
+      <c r="F10" s="367" t="n"/>
+      <c r="G10" s="367" t="n"/>
+      <c r="H10" s="367" t="n"/>
+      <c r="I10" s="367" t="n"/>
+      <c r="K10" s="369" t="n"/>
+      <c r="L10" s="369" t="n"/>
+      <c r="M10" s="369" t="n"/>
+      <c r="N10" s="369" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>HEX: N/A</t>
+          <t>HEX: #CB9D96</t>
         </is>
       </c>
       <c r="B11" s="15" t="n"/>
@@ -17951,7 +18149,7 @@
       <c r="D11" s="15" t="n"/>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>HEX: N/A</t>
+          <t>HEX: #8ABA96</t>
         </is>
       </c>
       <c r="G11" s="15" t="n"/>
@@ -17959,7 +18157,7 @@
       <c r="I11" s="15" t="n"/>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>HEX: N/A</t>
+          <t>HEX: #94637F</t>
         </is>
       </c>
       <c r="L11" s="15" t="n"/>
@@ -17969,7 +18167,7 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>RGB: N/A</t>
+          <t>RGB: 203, 157, 150</t>
         </is>
       </c>
       <c r="B12" s="15" t="n"/>
@@ -17977,7 +18175,7 @@
       <c r="D12" s="15" t="n"/>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>RGB: N/A</t>
+          <t>RGB: 138, 186, 150</t>
         </is>
       </c>
       <c r="G12" s="15" t="n"/>
@@ -17985,7 +18183,7 @@
       <c r="I12" s="15" t="n"/>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>RGB: N/A</t>
+          <t>RGB: 148, 99, 127</t>
         </is>
       </c>
       <c r="L12" s="15" t="n"/>
@@ -17995,7 +18193,7 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>来源: official_chart_code_only</t>
+          <t>来源: official_chart_image_sampled</t>
         </is>
       </c>
       <c r="B13" s="15" t="n"/>
@@ -18003,7 +18201,7 @@
       <c r="D13" s="15" t="n"/>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>来源: official_chart_code_only</t>
+          <t>来源: official_chart_image_sampled</t>
         </is>
       </c>
       <c r="G13" s="15" t="n"/>
@@ -18011,7 +18209,7 @@
       <c r="I13" s="15" t="n"/>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>来源: official_chart_code_only</t>
+          <t>来源: official_chart_image_sampled</t>
         </is>
       </c>
       <c r="L13" s="15" t="n"/>
@@ -18098,61 +18296,61 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="356" t="inlineStr">
+      <c r="A4" s="370" t="inlineStr">
         <is>
           <t>CP01</t>
         </is>
       </c>
-      <c r="B4" s="357" t="n"/>
-      <c r="C4" s="357" t="n"/>
-      <c r="D4" s="357" t="n"/>
-      <c r="F4" s="356" t="inlineStr">
+      <c r="B4" s="371" t="n"/>
+      <c r="C4" s="371" t="n"/>
+      <c r="D4" s="371" t="n"/>
+      <c r="F4" s="372" t="inlineStr">
         <is>
           <t>CP02</t>
         </is>
       </c>
-      <c r="G4" s="357" t="n"/>
-      <c r="H4" s="357" t="n"/>
-      <c r="I4" s="357" t="n"/>
-      <c r="K4" s="356" t="inlineStr">
+      <c r="G4" s="373" t="n"/>
+      <c r="H4" s="373" t="n"/>
+      <c r="I4" s="373" t="n"/>
+      <c r="K4" s="374" t="inlineStr">
         <is>
           <t>CP03</t>
         </is>
       </c>
-      <c r="L4" s="357" t="n"/>
-      <c r="M4" s="357" t="n"/>
-      <c r="N4" s="357" t="n"/>
-      <c r="P4" s="356" t="inlineStr">
+      <c r="L4" s="375" t="n"/>
+      <c r="M4" s="375" t="n"/>
+      <c r="N4" s="375" t="n"/>
+      <c r="P4" s="376" t="inlineStr">
         <is>
           <t>CP04</t>
         </is>
       </c>
-      <c r="Q4" s="357" t="n"/>
-      <c r="R4" s="357" t="n"/>
-      <c r="S4" s="357" t="n"/>
+      <c r="Q4" s="377" t="n"/>
+      <c r="R4" s="377" t="n"/>
+      <c r="S4" s="377" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="357" t="n"/>
-      <c r="B5" s="357" t="n"/>
-      <c r="C5" s="357" t="n"/>
-      <c r="D5" s="357" t="n"/>
-      <c r="F5" s="357" t="n"/>
-      <c r="G5" s="357" t="n"/>
-      <c r="H5" s="357" t="n"/>
-      <c r="I5" s="357" t="n"/>
-      <c r="K5" s="357" t="n"/>
-      <c r="L5" s="357" t="n"/>
-      <c r="M5" s="357" t="n"/>
-      <c r="N5" s="357" t="n"/>
-      <c r="P5" s="357" t="n"/>
-      <c r="Q5" s="357" t="n"/>
-      <c r="R5" s="357" t="n"/>
-      <c r="S5" s="357" t="n"/>
+      <c r="A5" s="371" t="n"/>
+      <c r="B5" s="371" t="n"/>
+      <c r="C5" s="371" t="n"/>
+      <c r="D5" s="371" t="n"/>
+      <c r="F5" s="373" t="n"/>
+      <c r="G5" s="373" t="n"/>
+      <c r="H5" s="373" t="n"/>
+      <c r="I5" s="373" t="n"/>
+      <c r="K5" s="375" t="n"/>
+      <c r="L5" s="375" t="n"/>
+      <c r="M5" s="375" t="n"/>
+      <c r="N5" s="375" t="n"/>
+      <c r="P5" s="377" t="n"/>
+      <c r="Q5" s="377" t="n"/>
+      <c r="R5" s="377" t="n"/>
+      <c r="S5" s="377" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>HEX: N/A</t>
+          <t>HEX: #8ECAB2</t>
         </is>
       </c>
       <c r="B6" s="15" t="n"/>
@@ -18160,7 +18358,7 @@
       <c r="D6" s="15" t="n"/>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>HEX: N/A</t>
+          <t>HEX: #CD8F75</t>
         </is>
       </c>
       <c r="G6" s="15" t="n"/>
@@ -18168,7 +18366,7 @@
       <c r="I6" s="15" t="n"/>
       <c r="K6" s="14" t="inlineStr">
         <is>
-          <t>HEX: N/A</t>
+          <t>HEX: #CBA16C</t>
         </is>
       </c>
       <c r="L6" s="15" t="n"/>
@@ -18176,7 +18374,7 @@
       <c r="N6" s="15" t="n"/>
       <c r="P6" s="14" t="inlineStr">
         <is>
-          <t>HEX: N/A</t>
+          <t>HEX: #BC8DA4</t>
         </is>
       </c>
       <c r="Q6" s="15" t="n"/>
@@ -18186,7 +18384,7 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>RGB: N/A</t>
+          <t>RGB: 142, 202, 178</t>
         </is>
       </c>
       <c r="B7" s="15" t="n"/>
@@ -18194,7 +18392,7 @@
       <c r="D7" s="15" t="n"/>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>RGB: N/A</t>
+          <t>RGB: 205, 143, 117</t>
         </is>
       </c>
       <c r="G7" s="15" t="n"/>
@@ -18202,7 +18400,7 @@
       <c r="I7" s="15" t="n"/>
       <c r="K7" s="14" t="inlineStr">
         <is>
-          <t>RGB: N/A</t>
+          <t>RGB: 203, 161, 108</t>
         </is>
       </c>
       <c r="L7" s="15" t="n"/>
@@ -18210,7 +18408,7 @@
       <c r="N7" s="15" t="n"/>
       <c r="P7" s="14" t="inlineStr">
         <is>
-          <t>RGB: N/A</t>
+          <t>RGB: 188, 141, 164</t>
         </is>
       </c>
       <c r="Q7" s="15" t="n"/>
@@ -18220,7 +18418,7 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>来源: official_chart_code_only</t>
+          <t>来源: official_chart_image_sampled</t>
         </is>
       </c>
       <c r="B8" s="15" t="n"/>
@@ -18228,7 +18426,7 @@
       <c r="D8" s="15" t="n"/>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>来源: official_chart_code_only</t>
+          <t>来源: official_chart_image_sampled</t>
         </is>
       </c>
       <c r="G8" s="15" t="n"/>
@@ -18236,7 +18434,7 @@
       <c r="I8" s="15" t="n"/>
       <c r="K8" s="14" t="inlineStr">
         <is>
-          <t>来源: official_chart_code_only</t>
+          <t>来源: official_chart_image_sampled</t>
         </is>
       </c>
       <c r="L8" s="15" t="n"/>
@@ -18244,7 +18442,7 @@
       <c r="N8" s="15" t="n"/>
       <c r="P8" s="14" t="inlineStr">
         <is>
-          <t>来源: official_chart_code_only</t>
+          <t>来源: official_chart_image_sampled</t>
         </is>
       </c>
       <c r="Q8" s="15" t="n"/>
@@ -18252,49 +18450,49 @@
       <c r="S8" s="15" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="356" t="inlineStr">
+      <c r="A9" s="378" t="inlineStr">
         <is>
           <t>CP05</t>
         </is>
       </c>
-      <c r="B9" s="357" t="n"/>
-      <c r="C9" s="357" t="n"/>
-      <c r="D9" s="357" t="n"/>
-      <c r="F9" s="356" t="inlineStr">
+      <c r="B9" s="379" t="n"/>
+      <c r="C9" s="379" t="n"/>
+      <c r="D9" s="379" t="n"/>
+      <c r="F9" s="380" t="inlineStr">
         <is>
           <t>CP06</t>
         </is>
       </c>
-      <c r="G9" s="357" t="n"/>
-      <c r="H9" s="357" t="n"/>
-      <c r="I9" s="357" t="n"/>
-      <c r="K9" s="356" t="inlineStr">
+      <c r="G9" s="381" t="n"/>
+      <c r="H9" s="381" t="n"/>
+      <c r="I9" s="381" t="n"/>
+      <c r="K9" s="382" t="inlineStr">
         <is>
           <t>CP07</t>
         </is>
       </c>
-      <c r="L9" s="357" t="n"/>
-      <c r="M9" s="357" t="n"/>
-      <c r="N9" s="357" t="n"/>
+      <c r="L9" s="383" t="n"/>
+      <c r="M9" s="383" t="n"/>
+      <c r="N9" s="383" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="357" t="n"/>
-      <c r="B10" s="357" t="n"/>
-      <c r="C10" s="357" t="n"/>
-      <c r="D10" s="357" t="n"/>
-      <c r="F10" s="357" t="n"/>
-      <c r="G10" s="357" t="n"/>
-      <c r="H10" s="357" t="n"/>
-      <c r="I10" s="357" t="n"/>
-      <c r="K10" s="357" t="n"/>
-      <c r="L10" s="357" t="n"/>
-      <c r="M10" s="357" t="n"/>
-      <c r="N10" s="357" t="n"/>
+      <c r="A10" s="379" t="n"/>
+      <c r="B10" s="379" t="n"/>
+      <c r="C10" s="379" t="n"/>
+      <c r="D10" s="379" t="n"/>
+      <c r="F10" s="381" t="n"/>
+      <c r="G10" s="381" t="n"/>
+      <c r="H10" s="381" t="n"/>
+      <c r="I10" s="381" t="n"/>
+      <c r="K10" s="383" t="n"/>
+      <c r="L10" s="383" t="n"/>
+      <c r="M10" s="383" t="n"/>
+      <c r="N10" s="383" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>HEX: N/A</t>
+          <t>HEX: #8A506A</t>
         </is>
       </c>
       <c r="B11" s="15" t="n"/>
@@ -18302,7 +18500,7 @@
       <c r="D11" s="15" t="n"/>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>HEX: N/A</t>
+          <t>HEX: #3063A3</t>
         </is>
       </c>
       <c r="G11" s="15" t="n"/>
@@ -18310,7 +18508,7 @@
       <c r="I11" s="15" t="n"/>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>HEX: N/A</t>
+          <t>HEX: #3E5694</t>
         </is>
       </c>
       <c r="L11" s="15" t="n"/>
@@ -18320,7 +18518,7 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>RGB: N/A</t>
+          <t>RGB: 138, 80, 106</t>
         </is>
       </c>
       <c r="B12" s="15" t="n"/>
@@ -18328,7 +18526,7 @@
       <c r="D12" s="15" t="n"/>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>RGB: N/A</t>
+          <t>RGB: 48, 99, 163</t>
         </is>
       </c>
       <c r="G12" s="15" t="n"/>
@@ -18336,7 +18534,7 @@
       <c r="I12" s="15" t="n"/>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>RGB: N/A</t>
+          <t>RGB: 62, 86, 148</t>
         </is>
       </c>
       <c r="L12" s="15" t="n"/>
@@ -18346,7 +18544,7 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>来源: official_chart_code_only</t>
+          <t>来源: official_chart_image_sampled</t>
         </is>
       </c>
       <c r="B13" s="15" t="n"/>
@@ -18354,7 +18552,7 @@
       <c r="D13" s="15" t="n"/>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>来源: official_chart_code_only</t>
+          <t>来源: official_chart_image_sampled</t>
         </is>
       </c>
       <c r="G13" s="15" t="n"/>
@@ -18362,7 +18560,7 @@
       <c r="I13" s="15" t="n"/>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>来源: official_chart_code_only</t>
+          <t>来源: official_chart_image_sampled</t>
         </is>
       </c>
       <c r="L13" s="15" t="n"/>
@@ -18449,61 +18647,61 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="356" t="inlineStr">
+      <c r="A4" s="384" t="inlineStr">
         <is>
           <t>CT01</t>
         </is>
       </c>
-      <c r="B4" s="357" t="n"/>
-      <c r="C4" s="357" t="n"/>
-      <c r="D4" s="357" t="n"/>
-      <c r="F4" s="356" t="inlineStr">
+      <c r="B4" s="385" t="n"/>
+      <c r="C4" s="385" t="n"/>
+      <c r="D4" s="385" t="n"/>
+      <c r="F4" s="386" t="inlineStr">
         <is>
           <t>CT02</t>
         </is>
       </c>
-      <c r="G4" s="357" t="n"/>
-      <c r="H4" s="357" t="n"/>
-      <c r="I4" s="357" t="n"/>
-      <c r="K4" s="356" t="inlineStr">
+      <c r="G4" s="387" t="n"/>
+      <c r="H4" s="387" t="n"/>
+      <c r="I4" s="387" t="n"/>
+      <c r="K4" s="388" t="inlineStr">
         <is>
           <t>CT03</t>
         </is>
       </c>
-      <c r="L4" s="357" t="n"/>
-      <c r="M4" s="357" t="n"/>
-      <c r="N4" s="357" t="n"/>
-      <c r="P4" s="356" t="inlineStr">
+      <c r="L4" s="389" t="n"/>
+      <c r="M4" s="389" t="n"/>
+      <c r="N4" s="389" t="n"/>
+      <c r="P4" s="390" t="inlineStr">
         <is>
           <t>CT04</t>
         </is>
       </c>
-      <c r="Q4" s="357" t="n"/>
-      <c r="R4" s="357" t="n"/>
-      <c r="S4" s="357" t="n"/>
+      <c r="Q4" s="391" t="n"/>
+      <c r="R4" s="391" t="n"/>
+      <c r="S4" s="391" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="357" t="n"/>
-      <c r="B5" s="357" t="n"/>
-      <c r="C5" s="357" t="n"/>
-      <c r="D5" s="357" t="n"/>
-      <c r="F5" s="357" t="n"/>
-      <c r="G5" s="357" t="n"/>
-      <c r="H5" s="357" t="n"/>
-      <c r="I5" s="357" t="n"/>
-      <c r="K5" s="357" t="n"/>
-      <c r="L5" s="357" t="n"/>
-      <c r="M5" s="357" t="n"/>
-      <c r="N5" s="357" t="n"/>
-      <c r="P5" s="357" t="n"/>
-      <c r="Q5" s="357" t="n"/>
-      <c r="R5" s="357" t="n"/>
-      <c r="S5" s="357" t="n"/>
+      <c r="A5" s="385" t="n"/>
+      <c r="B5" s="385" t="n"/>
+      <c r="C5" s="385" t="n"/>
+      <c r="D5" s="385" t="n"/>
+      <c r="F5" s="387" t="n"/>
+      <c r="G5" s="387" t="n"/>
+      <c r="H5" s="387" t="n"/>
+      <c r="I5" s="387" t="n"/>
+      <c r="K5" s="389" t="n"/>
+      <c r="L5" s="389" t="n"/>
+      <c r="M5" s="389" t="n"/>
+      <c r="N5" s="389" t="n"/>
+      <c r="P5" s="391" t="n"/>
+      <c r="Q5" s="391" t="n"/>
+      <c r="R5" s="391" t="n"/>
+      <c r="S5" s="391" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>HEX: N/A</t>
+          <t>HEX: #C6C6D2</t>
         </is>
       </c>
       <c r="B6" s="15" t="n"/>
@@ -18511,7 +18709,7 @@
       <c r="D6" s="15" t="n"/>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>HEX: N/A</t>
+          <t>HEX: #E664A6</t>
         </is>
       </c>
       <c r="G6" s="15" t="n"/>
@@ -18519,7 +18717,7 @@
       <c r="I6" s="15" t="n"/>
       <c r="K6" s="14" t="inlineStr">
         <is>
-          <t>HEX: N/A</t>
+          <t>HEX: #F6875C</t>
         </is>
       </c>
       <c r="L6" s="15" t="n"/>
@@ -18527,7 +18725,7 @@
       <c r="N6" s="15" t="n"/>
       <c r="P6" s="14" t="inlineStr">
         <is>
-          <t>HEX: N/A</t>
+          <t>HEX: #C4C764</t>
         </is>
       </c>
       <c r="Q6" s="15" t="n"/>
@@ -18537,7 +18735,7 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>RGB: N/A</t>
+          <t>RGB: 198, 198, 210</t>
         </is>
       </c>
       <c r="B7" s="15" t="n"/>
@@ -18545,7 +18743,7 @@
       <c r="D7" s="15" t="n"/>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>RGB: N/A</t>
+          <t>RGB: 230, 100, 166</t>
         </is>
       </c>
       <c r="G7" s="15" t="n"/>
@@ -18553,7 +18751,7 @@
       <c r="I7" s="15" t="n"/>
       <c r="K7" s="14" t="inlineStr">
         <is>
-          <t>RGB: N/A</t>
+          <t>RGB: 246, 135, 92</t>
         </is>
       </c>
       <c r="L7" s="15" t="n"/>
@@ -18561,7 +18759,7 @@
       <c r="N7" s="15" t="n"/>
       <c r="P7" s="14" t="inlineStr">
         <is>
-          <t>RGB: N/A</t>
+          <t>RGB: 196, 199, 100</t>
         </is>
       </c>
       <c r="Q7" s="15" t="n"/>
@@ -18571,7 +18769,7 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>来源: official_chart_code_only</t>
+          <t>来源: official_chart_image_sampled</t>
         </is>
       </c>
       <c r="B8" s="15" t="n"/>
@@ -18579,7 +18777,7 @@
       <c r="D8" s="15" t="n"/>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>来源: official_chart_code_only</t>
+          <t>来源: official_chart_image_sampled</t>
         </is>
       </c>
       <c r="G8" s="15" t="n"/>
@@ -18587,7 +18785,7 @@
       <c r="I8" s="15" t="n"/>
       <c r="K8" s="14" t="inlineStr">
         <is>
-          <t>来源: official_chart_code_only</t>
+          <t>来源: official_chart_image_sampled</t>
         </is>
       </c>
       <c r="L8" s="15" t="n"/>
@@ -18595,7 +18793,7 @@
       <c r="N8" s="15" t="n"/>
       <c r="P8" s="14" t="inlineStr">
         <is>
-          <t>来源: official_chart_code_only</t>
+          <t>来源: official_chart_image_sampled</t>
         </is>
       </c>
       <c r="Q8" s="15" t="n"/>
@@ -18603,61 +18801,61 @@
       <c r="S8" s="15" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="356" t="inlineStr">
+      <c r="A9" s="392" t="inlineStr">
         <is>
           <t>CT05</t>
         </is>
       </c>
-      <c r="B9" s="357" t="n"/>
-      <c r="C9" s="357" t="n"/>
-      <c r="D9" s="357" t="n"/>
-      <c r="F9" s="356" t="inlineStr">
+      <c r="B9" s="393" t="n"/>
+      <c r="C9" s="393" t="n"/>
+      <c r="D9" s="393" t="n"/>
+      <c r="F9" s="394" t="inlineStr">
         <is>
           <t>CT06</t>
         </is>
       </c>
-      <c r="G9" s="357" t="n"/>
-      <c r="H9" s="357" t="n"/>
-      <c r="I9" s="357" t="n"/>
-      <c r="K9" s="356" t="inlineStr">
+      <c r="G9" s="395" t="n"/>
+      <c r="H9" s="395" t="n"/>
+      <c r="I9" s="395" t="n"/>
+      <c r="K9" s="396" t="inlineStr">
         <is>
           <t>CT07</t>
         </is>
       </c>
-      <c r="L9" s="357" t="n"/>
-      <c r="M9" s="357" t="n"/>
-      <c r="N9" s="357" t="n"/>
-      <c r="P9" s="356" t="inlineStr">
+      <c r="L9" s="397" t="n"/>
+      <c r="M9" s="397" t="n"/>
+      <c r="N9" s="397" t="n"/>
+      <c r="P9" s="398" t="inlineStr">
         <is>
           <t>CT08</t>
         </is>
       </c>
-      <c r="Q9" s="357" t="n"/>
-      <c r="R9" s="357" t="n"/>
-      <c r="S9" s="357" t="n"/>
+      <c r="Q9" s="399" t="n"/>
+      <c r="R9" s="399" t="n"/>
+      <c r="S9" s="399" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="357" t="n"/>
-      <c r="B10" s="357" t="n"/>
-      <c r="C10" s="357" t="n"/>
-      <c r="D10" s="357" t="n"/>
-      <c r="F10" s="357" t="n"/>
-      <c r="G10" s="357" t="n"/>
-      <c r="H10" s="357" t="n"/>
-      <c r="I10" s="357" t="n"/>
-      <c r="K10" s="357" t="n"/>
-      <c r="L10" s="357" t="n"/>
-      <c r="M10" s="357" t="n"/>
-      <c r="N10" s="357" t="n"/>
-      <c r="P10" s="357" t="n"/>
-      <c r="Q10" s="357" t="n"/>
-      <c r="R10" s="357" t="n"/>
-      <c r="S10" s="357" t="n"/>
+      <c r="A10" s="393" t="n"/>
+      <c r="B10" s="393" t="n"/>
+      <c r="C10" s="393" t="n"/>
+      <c r="D10" s="393" t="n"/>
+      <c r="F10" s="395" t="n"/>
+      <c r="G10" s="395" t="n"/>
+      <c r="H10" s="395" t="n"/>
+      <c r="I10" s="395" t="n"/>
+      <c r="K10" s="397" t="n"/>
+      <c r="L10" s="397" t="n"/>
+      <c r="M10" s="397" t="n"/>
+      <c r="N10" s="397" t="n"/>
+      <c r="P10" s="399" t="n"/>
+      <c r="Q10" s="399" t="n"/>
+      <c r="R10" s="399" t="n"/>
+      <c r="S10" s="399" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>HEX: N/A</t>
+          <t>HEX: #32B195</t>
         </is>
       </c>
       <c r="B11" s="15" t="n"/>
@@ -18665,7 +18863,7 @@
       <c r="D11" s="15" t="n"/>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>HEX: N/A</t>
+          <t>HEX: #757DD1</t>
         </is>
       </c>
       <c r="G11" s="15" t="n"/>
@@ -18673,7 +18871,7 @@
       <c r="I11" s="15" t="n"/>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>HEX: N/A</t>
+          <t>HEX: #4EB1DC</t>
         </is>
       </c>
       <c r="L11" s="15" t="n"/>
@@ -18681,7 +18879,7 @@
       <c r="N11" s="15" t="n"/>
       <c r="P11" s="14" t="inlineStr">
         <is>
-          <t>HEX: N/A</t>
+          <t>HEX: #5688A0</t>
         </is>
       </c>
       <c r="Q11" s="15" t="n"/>
@@ -18691,7 +18889,7 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>RGB: N/A</t>
+          <t>RGB: 50, 177, 149</t>
         </is>
       </c>
       <c r="B12" s="15" t="n"/>
@@ -18699,7 +18897,7 @@
       <c r="D12" s="15" t="n"/>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>RGB: N/A</t>
+          <t>RGB: 117, 125, 209</t>
         </is>
       </c>
       <c r="G12" s="15" t="n"/>
@@ -18707,7 +18905,7 @@
       <c r="I12" s="15" t="n"/>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>RGB: N/A</t>
+          <t>RGB: 78, 177, 220</t>
         </is>
       </c>
       <c r="L12" s="15" t="n"/>
@@ -18715,7 +18913,7 @@
       <c r="N12" s="15" t="n"/>
       <c r="P12" s="14" t="inlineStr">
         <is>
-          <t>RGB: N/A</t>
+          <t>RGB: 86, 136, 160</t>
         </is>
       </c>
       <c r="Q12" s="15" t="n"/>
@@ -18725,7 +18923,7 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>来源: official_chart_code_only</t>
+          <t>来源: official_chart_image_sampled</t>
         </is>
       </c>
       <c r="B13" s="15" t="n"/>
@@ -18733,7 +18931,7 @@
       <c r="D13" s="15" t="n"/>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>来源: official_chart_code_only</t>
+          <t>来源: official_chart_image_sampled</t>
         </is>
       </c>
       <c r="G13" s="15" t="n"/>
@@ -18741,7 +18939,7 @@
       <c r="I13" s="15" t="n"/>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>来源: official_chart_code_only</t>
+          <t>来源: official_chart_image_sampled</t>
         </is>
       </c>
       <c r="L13" s="15" t="n"/>
@@ -18749,7 +18947,7 @@
       <c r="N13" s="15" t="n"/>
       <c r="P13" s="14" t="inlineStr">
         <is>
-          <t>来源: official_chart_code_only</t>
+          <t>来源: official_chart_image_sampled</t>
         </is>
       </c>
       <c r="Q13" s="15" t="n"/>
@@ -18757,25 +18955,25 @@
       <c r="S13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="356" t="inlineStr">
+      <c r="A14" s="400" t="inlineStr">
         <is>
           <t>CT09</t>
         </is>
       </c>
-      <c r="B14" s="357" t="n"/>
-      <c r="C14" s="357" t="n"/>
-      <c r="D14" s="357" t="n"/>
+      <c r="B14" s="401" t="n"/>
+      <c r="C14" s="401" t="n"/>
+      <c r="D14" s="401" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="357" t="n"/>
-      <c r="B15" s="357" t="n"/>
-      <c r="C15" s="357" t="n"/>
-      <c r="D15" s="357" t="n"/>
+      <c r="A15" s="401" t="n"/>
+      <c r="B15" s="401" t="n"/>
+      <c r="C15" s="401" t="n"/>
+      <c r="D15" s="401" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>HEX: N/A</t>
+          <t>HEX: #6B849D</t>
         </is>
       </c>
       <c r="B16" s="15" t="n"/>
@@ -18785,7 +18983,7 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>RGB: N/A</t>
+          <t>RGB: 107, 132, 157</t>
         </is>
       </c>
       <c r="B17" s="15" t="n"/>
@@ -18795,7 +18993,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>来源: official_chart_code_only</t>
+          <t>来源: official_chart_image_sampled</t>
         </is>
       </c>
       <c r="B18" s="15" t="n"/>
@@ -18890,56 +19088,56 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="358" t="inlineStr">
+      <c r="A4" s="402" t="inlineStr">
         <is>
           <t>MA1</t>
         </is>
       </c>
-      <c r="B4" s="359" t="n"/>
-      <c r="C4" s="359" t="n"/>
-      <c r="D4" s="359" t="n"/>
-      <c r="F4" s="360" t="inlineStr">
+      <c r="B4" s="403" t="n"/>
+      <c r="C4" s="403" t="n"/>
+      <c r="D4" s="403" t="n"/>
+      <c r="F4" s="404" t="inlineStr">
         <is>
           <t>MA2</t>
         </is>
       </c>
-      <c r="G4" s="361" t="n"/>
-      <c r="H4" s="361" t="n"/>
-      <c r="I4" s="361" t="n"/>
-      <c r="K4" s="362" t="inlineStr">
+      <c r="G4" s="405" t="n"/>
+      <c r="H4" s="405" t="n"/>
+      <c r="I4" s="405" t="n"/>
+      <c r="K4" s="406" t="inlineStr">
         <is>
           <t>MA3</t>
         </is>
       </c>
-      <c r="L4" s="363" t="n"/>
-      <c r="M4" s="363" t="n"/>
-      <c r="N4" s="363" t="n"/>
-      <c r="P4" s="364" t="inlineStr">
+      <c r="L4" s="407" t="n"/>
+      <c r="M4" s="407" t="n"/>
+      <c r="N4" s="407" t="n"/>
+      <c r="P4" s="408" t="inlineStr">
         <is>
           <t>MA4</t>
         </is>
       </c>
-      <c r="Q4" s="365" t="n"/>
-      <c r="R4" s="365" t="n"/>
-      <c r="S4" s="365" t="n"/>
+      <c r="Q4" s="409" t="n"/>
+      <c r="R4" s="409" t="n"/>
+      <c r="S4" s="409" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="359" t="n"/>
-      <c r="B5" s="359" t="n"/>
-      <c r="C5" s="359" t="n"/>
-      <c r="D5" s="359" t="n"/>
-      <c r="F5" s="361" t="n"/>
-      <c r="G5" s="361" t="n"/>
-      <c r="H5" s="361" t="n"/>
-      <c r="I5" s="361" t="n"/>
-      <c r="K5" s="363" t="n"/>
-      <c r="L5" s="363" t="n"/>
-      <c r="M5" s="363" t="n"/>
-      <c r="N5" s="363" t="n"/>
-      <c r="P5" s="365" t="n"/>
-      <c r="Q5" s="365" t="n"/>
-      <c r="R5" s="365" t="n"/>
-      <c r="S5" s="365" t="n"/>
+      <c r="A5" s="403" t="n"/>
+      <c r="B5" s="403" t="n"/>
+      <c r="C5" s="403" t="n"/>
+      <c r="D5" s="403" t="n"/>
+      <c r="F5" s="405" t="n"/>
+      <c r="G5" s="405" t="n"/>
+      <c r="H5" s="405" t="n"/>
+      <c r="I5" s="405" t="n"/>
+      <c r="K5" s="407" t="n"/>
+      <c r="L5" s="407" t="n"/>
+      <c r="M5" s="407" t="n"/>
+      <c r="N5" s="407" t="n"/>
+      <c r="P5" s="409" t="n"/>
+      <c r="Q5" s="409" t="n"/>
+      <c r="R5" s="409" t="n"/>
+      <c r="S5" s="409" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -19044,56 +19242,56 @@
       <c r="S8" s="15" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="366" t="inlineStr">
+      <c r="A9" s="410" t="inlineStr">
         <is>
           <t>MA5</t>
         </is>
       </c>
-      <c r="B9" s="367" t="n"/>
-      <c r="C9" s="367" t="n"/>
-      <c r="D9" s="367" t="n"/>
-      <c r="F9" s="368" t="inlineStr">
+      <c r="B9" s="411" t="n"/>
+      <c r="C9" s="411" t="n"/>
+      <c r="D9" s="411" t="n"/>
+      <c r="F9" s="412" t="inlineStr">
         <is>
           <t>MA6</t>
         </is>
       </c>
-      <c r="G9" s="369" t="n"/>
-      <c r="H9" s="369" t="n"/>
-      <c r="I9" s="369" t="n"/>
-      <c r="K9" s="370" t="inlineStr">
+      <c r="G9" s="413" t="n"/>
+      <c r="H9" s="413" t="n"/>
+      <c r="I9" s="413" t="n"/>
+      <c r="K9" s="414" t="inlineStr">
         <is>
           <t>MA7</t>
         </is>
       </c>
-      <c r="L9" s="371" t="n"/>
-      <c r="M9" s="371" t="n"/>
-      <c r="N9" s="371" t="n"/>
-      <c r="P9" s="372" t="inlineStr">
+      <c r="L9" s="415" t="n"/>
+      <c r="M9" s="415" t="n"/>
+      <c r="N9" s="415" t="n"/>
+      <c r="P9" s="416" t="inlineStr">
         <is>
           <t>MA8</t>
         </is>
       </c>
-      <c r="Q9" s="373" t="n"/>
-      <c r="R9" s="373" t="n"/>
-      <c r="S9" s="373" t="n"/>
+      <c r="Q9" s="417" t="n"/>
+      <c r="R9" s="417" t="n"/>
+      <c r="S9" s="417" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="367" t="n"/>
-      <c r="B10" s="367" t="n"/>
-      <c r="C10" s="367" t="n"/>
-      <c r="D10" s="367" t="n"/>
-      <c r="F10" s="369" t="n"/>
-      <c r="G10" s="369" t="n"/>
-      <c r="H10" s="369" t="n"/>
-      <c r="I10" s="369" t="n"/>
-      <c r="K10" s="371" t="n"/>
-      <c r="L10" s="371" t="n"/>
-      <c r="M10" s="371" t="n"/>
-      <c r="N10" s="371" t="n"/>
-      <c r="P10" s="373" t="n"/>
-      <c r="Q10" s="373" t="n"/>
-      <c r="R10" s="373" t="n"/>
-      <c r="S10" s="373" t="n"/>
+      <c r="A10" s="411" t="n"/>
+      <c r="B10" s="411" t="n"/>
+      <c r="C10" s="411" t="n"/>
+      <c r="D10" s="411" t="n"/>
+      <c r="F10" s="413" t="n"/>
+      <c r="G10" s="413" t="n"/>
+      <c r="H10" s="413" t="n"/>
+      <c r="I10" s="413" t="n"/>
+      <c r="K10" s="415" t="n"/>
+      <c r="L10" s="415" t="n"/>
+      <c r="M10" s="415" t="n"/>
+      <c r="N10" s="415" t="n"/>
+      <c r="P10" s="417" t="n"/>
+      <c r="Q10" s="417" t="n"/>
+      <c r="R10" s="417" t="n"/>
+      <c r="S10" s="417" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -19198,56 +19396,56 @@
       <c r="S13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="374" t="inlineStr">
+      <c r="A14" s="418" t="inlineStr">
         <is>
           <t>MA9</t>
         </is>
       </c>
-      <c r="B14" s="375" t="n"/>
-      <c r="C14" s="375" t="n"/>
-      <c r="D14" s="375" t="n"/>
-      <c r="F14" s="376" t="inlineStr">
+      <c r="B14" s="419" t="n"/>
+      <c r="C14" s="419" t="n"/>
+      <c r="D14" s="419" t="n"/>
+      <c r="F14" s="420" t="inlineStr">
         <is>
           <t>MA10</t>
         </is>
       </c>
-      <c r="G14" s="377" t="n"/>
-      <c r="H14" s="377" t="n"/>
-      <c r="I14" s="377" t="n"/>
-      <c r="K14" s="378" t="inlineStr">
+      <c r="G14" s="421" t="n"/>
+      <c r="H14" s="421" t="n"/>
+      <c r="I14" s="421" t="n"/>
+      <c r="K14" s="422" t="inlineStr">
         <is>
           <t>MA11</t>
         </is>
       </c>
-      <c r="L14" s="379" t="n"/>
-      <c r="M14" s="379" t="n"/>
-      <c r="N14" s="379" t="n"/>
-      <c r="P14" s="380" t="inlineStr">
+      <c r="L14" s="423" t="n"/>
+      <c r="M14" s="423" t="n"/>
+      <c r="N14" s="423" t="n"/>
+      <c r="P14" s="424" t="inlineStr">
         <is>
           <t>MA12</t>
         </is>
       </c>
-      <c r="Q14" s="381" t="n"/>
-      <c r="R14" s="381" t="n"/>
-      <c r="S14" s="381" t="n"/>
+      <c r="Q14" s="425" t="n"/>
+      <c r="R14" s="425" t="n"/>
+      <c r="S14" s="425" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="375" t="n"/>
-      <c r="B15" s="375" t="n"/>
-      <c r="C15" s="375" t="n"/>
-      <c r="D15" s="375" t="n"/>
-      <c r="F15" s="377" t="n"/>
-      <c r="G15" s="377" t="n"/>
-      <c r="H15" s="377" t="n"/>
-      <c r="I15" s="377" t="n"/>
-      <c r="K15" s="379" t="n"/>
-      <c r="L15" s="379" t="n"/>
-      <c r="M15" s="379" t="n"/>
-      <c r="N15" s="379" t="n"/>
-      <c r="P15" s="381" t="n"/>
-      <c r="Q15" s="381" t="n"/>
-      <c r="R15" s="381" t="n"/>
-      <c r="S15" s="381" t="n"/>
+      <c r="A15" s="419" t="n"/>
+      <c r="B15" s="419" t="n"/>
+      <c r="C15" s="419" t="n"/>
+      <c r="D15" s="419" t="n"/>
+      <c r="F15" s="421" t="n"/>
+      <c r="G15" s="421" t="n"/>
+      <c r="H15" s="421" t="n"/>
+      <c r="I15" s="421" t="n"/>
+      <c r="K15" s="423" t="n"/>
+      <c r="L15" s="423" t="n"/>
+      <c r="M15" s="423" t="n"/>
+      <c r="N15" s="423" t="n"/>
+      <c r="P15" s="425" t="n"/>
+      <c r="Q15" s="425" t="n"/>
+      <c r="R15" s="425" t="n"/>
+      <c r="S15" s="425" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -19352,56 +19550,56 @@
       <c r="S18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="382" t="inlineStr">
+      <c r="A19" s="426" t="inlineStr">
         <is>
           <t>MA13</t>
         </is>
       </c>
-      <c r="B19" s="383" t="n"/>
-      <c r="C19" s="383" t="n"/>
-      <c r="D19" s="383" t="n"/>
-      <c r="F19" s="384" t="inlineStr">
+      <c r="B19" s="427" t="n"/>
+      <c r="C19" s="427" t="n"/>
+      <c r="D19" s="427" t="n"/>
+      <c r="F19" s="428" t="inlineStr">
         <is>
           <t>MA14</t>
         </is>
       </c>
-      <c r="G19" s="385" t="n"/>
-      <c r="H19" s="385" t="n"/>
-      <c r="I19" s="385" t="n"/>
-      <c r="K19" s="386" t="inlineStr">
+      <c r="G19" s="429" t="n"/>
+      <c r="H19" s="429" t="n"/>
+      <c r="I19" s="429" t="n"/>
+      <c r="K19" s="430" t="inlineStr">
         <is>
           <t>MA15</t>
         </is>
       </c>
-      <c r="L19" s="387" t="n"/>
-      <c r="M19" s="387" t="n"/>
-      <c r="N19" s="387" t="n"/>
-      <c r="P19" s="388" t="inlineStr">
+      <c r="L19" s="431" t="n"/>
+      <c r="M19" s="431" t="n"/>
+      <c r="N19" s="431" t="n"/>
+      <c r="P19" s="432" t="inlineStr">
         <is>
           <t>MA16</t>
         </is>
       </c>
-      <c r="Q19" s="389" t="n"/>
-      <c r="R19" s="389" t="n"/>
-      <c r="S19" s="389" t="n"/>
+      <c r="Q19" s="433" t="n"/>
+      <c r="R19" s="433" t="n"/>
+      <c r="S19" s="433" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="383" t="n"/>
-      <c r="B20" s="383" t="n"/>
-      <c r="C20" s="383" t="n"/>
-      <c r="D20" s="383" t="n"/>
-      <c r="F20" s="385" t="n"/>
-      <c r="G20" s="385" t="n"/>
-      <c r="H20" s="385" t="n"/>
-      <c r="I20" s="385" t="n"/>
-      <c r="K20" s="387" t="n"/>
-      <c r="L20" s="387" t="n"/>
-      <c r="M20" s="387" t="n"/>
-      <c r="N20" s="387" t="n"/>
-      <c r="P20" s="389" t="n"/>
-      <c r="Q20" s="389" t="n"/>
-      <c r="R20" s="389" t="n"/>
-      <c r="S20" s="389" t="n"/>
+      <c r="A20" s="427" t="n"/>
+      <c r="B20" s="427" t="n"/>
+      <c r="C20" s="427" t="n"/>
+      <c r="D20" s="427" t="n"/>
+      <c r="F20" s="429" t="n"/>
+      <c r="G20" s="429" t="n"/>
+      <c r="H20" s="429" t="n"/>
+      <c r="I20" s="429" t="n"/>
+      <c r="K20" s="431" t="n"/>
+      <c r="L20" s="431" t="n"/>
+      <c r="M20" s="431" t="n"/>
+      <c r="N20" s="431" t="n"/>
+      <c r="P20" s="433" t="n"/>
+      <c r="Q20" s="433" t="n"/>
+      <c r="R20" s="433" t="n"/>
+      <c r="S20" s="433" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -19506,56 +19704,56 @@
       <c r="S23" s="15" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="390" t="inlineStr">
+      <c r="A24" s="434" t="inlineStr">
         <is>
           <t>MA17</t>
         </is>
       </c>
-      <c r="B24" s="391" t="n"/>
-      <c r="C24" s="391" t="n"/>
-      <c r="D24" s="391" t="n"/>
-      <c r="F24" s="392" t="inlineStr">
+      <c r="B24" s="435" t="n"/>
+      <c r="C24" s="435" t="n"/>
+      <c r="D24" s="435" t="n"/>
+      <c r="F24" s="436" t="inlineStr">
         <is>
           <t>MA18</t>
         </is>
       </c>
-      <c r="G24" s="393" t="n"/>
-      <c r="H24" s="393" t="n"/>
-      <c r="I24" s="393" t="n"/>
-      <c r="K24" s="394" t="inlineStr">
+      <c r="G24" s="437" t="n"/>
+      <c r="H24" s="437" t="n"/>
+      <c r="I24" s="437" t="n"/>
+      <c r="K24" s="438" t="inlineStr">
         <is>
           <t>MA19</t>
         </is>
       </c>
-      <c r="L24" s="395" t="n"/>
-      <c r="M24" s="395" t="n"/>
-      <c r="N24" s="395" t="n"/>
-      <c r="P24" s="396" t="inlineStr">
+      <c r="L24" s="439" t="n"/>
+      <c r="M24" s="439" t="n"/>
+      <c r="N24" s="439" t="n"/>
+      <c r="P24" s="440" t="inlineStr">
         <is>
           <t>MA20</t>
         </is>
       </c>
-      <c r="Q24" s="397" t="n"/>
-      <c r="R24" s="397" t="n"/>
-      <c r="S24" s="397" t="n"/>
+      <c r="Q24" s="441" t="n"/>
+      <c r="R24" s="441" t="n"/>
+      <c r="S24" s="441" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="391" t="n"/>
-      <c r="B25" s="391" t="n"/>
-      <c r="C25" s="391" t="n"/>
-      <c r="D25" s="391" t="n"/>
-      <c r="F25" s="393" t="n"/>
-      <c r="G25" s="393" t="n"/>
-      <c r="H25" s="393" t="n"/>
-      <c r="I25" s="393" t="n"/>
-      <c r="K25" s="395" t="n"/>
-      <c r="L25" s="395" t="n"/>
-      <c r="M25" s="395" t="n"/>
-      <c r="N25" s="395" t="n"/>
-      <c r="P25" s="397" t="n"/>
-      <c r="Q25" s="397" t="n"/>
-      <c r="R25" s="397" t="n"/>
-      <c r="S25" s="397" t="n"/>
+      <c r="A25" s="435" t="n"/>
+      <c r="B25" s="435" t="n"/>
+      <c r="C25" s="435" t="n"/>
+      <c r="D25" s="435" t="n"/>
+      <c r="F25" s="437" t="n"/>
+      <c r="G25" s="437" t="n"/>
+      <c r="H25" s="437" t="n"/>
+      <c r="I25" s="437" t="n"/>
+      <c r="K25" s="439" t="n"/>
+      <c r="L25" s="439" t="n"/>
+      <c r="M25" s="439" t="n"/>
+      <c r="N25" s="439" t="n"/>
+      <c r="P25" s="441" t="n"/>
+      <c r="Q25" s="441" t="n"/>
+      <c r="R25" s="441" t="n"/>
+      <c r="S25" s="441" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
@@ -19660,56 +19858,56 @@
       <c r="S28" s="15" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="398" t="inlineStr">
+      <c r="A29" s="442" t="inlineStr">
         <is>
           <t>MA21</t>
         </is>
       </c>
-      <c r="B29" s="399" t="n"/>
-      <c r="C29" s="399" t="n"/>
-      <c r="D29" s="399" t="n"/>
-      <c r="F29" s="400" t="inlineStr">
+      <c r="B29" s="443" t="n"/>
+      <c r="C29" s="443" t="n"/>
+      <c r="D29" s="443" t="n"/>
+      <c r="F29" s="444" t="inlineStr">
         <is>
           <t>MA22</t>
         </is>
       </c>
-      <c r="G29" s="401" t="n"/>
-      <c r="H29" s="401" t="n"/>
-      <c r="I29" s="401" t="n"/>
-      <c r="K29" s="402" t="inlineStr">
+      <c r="G29" s="445" t="n"/>
+      <c r="H29" s="445" t="n"/>
+      <c r="I29" s="445" t="n"/>
+      <c r="K29" s="446" t="inlineStr">
         <is>
           <t>MA23</t>
         </is>
       </c>
-      <c r="L29" s="403" t="n"/>
-      <c r="M29" s="403" t="n"/>
-      <c r="N29" s="403" t="n"/>
-      <c r="P29" s="404" t="inlineStr">
+      <c r="L29" s="447" t="n"/>
+      <c r="M29" s="447" t="n"/>
+      <c r="N29" s="447" t="n"/>
+      <c r="P29" s="448" t="inlineStr">
         <is>
           <t>MA24</t>
         </is>
       </c>
-      <c r="Q29" s="405" t="n"/>
-      <c r="R29" s="405" t="n"/>
-      <c r="S29" s="405" t="n"/>
+      <c r="Q29" s="449" t="n"/>
+      <c r="R29" s="449" t="n"/>
+      <c r="S29" s="449" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="399" t="n"/>
-      <c r="B30" s="399" t="n"/>
-      <c r="C30" s="399" t="n"/>
-      <c r="D30" s="399" t="n"/>
-      <c r="F30" s="401" t="n"/>
-      <c r="G30" s="401" t="n"/>
-      <c r="H30" s="401" t="n"/>
-      <c r="I30" s="401" t="n"/>
-      <c r="K30" s="403" t="n"/>
-      <c r="L30" s="403" t="n"/>
-      <c r="M30" s="403" t="n"/>
-      <c r="N30" s="403" t="n"/>
-      <c r="P30" s="405" t="n"/>
-      <c r="Q30" s="405" t="n"/>
-      <c r="R30" s="405" t="n"/>
-      <c r="S30" s="405" t="n"/>
+      <c r="A30" s="443" t="n"/>
+      <c r="B30" s="443" t="n"/>
+      <c r="C30" s="443" t="n"/>
+      <c r="D30" s="443" t="n"/>
+      <c r="F30" s="445" t="n"/>
+      <c r="G30" s="445" t="n"/>
+      <c r="H30" s="445" t="n"/>
+      <c r="I30" s="445" t="n"/>
+      <c r="K30" s="447" t="n"/>
+      <c r="L30" s="447" t="n"/>
+      <c r="M30" s="447" t="n"/>
+      <c r="N30" s="447" t="n"/>
+      <c r="P30" s="449" t="n"/>
+      <c r="Q30" s="449" t="n"/>
+      <c r="R30" s="449" t="n"/>
+      <c r="S30" s="449" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -19814,32 +20012,32 @@
       <c r="S33" s="15" t="n"/>
     </row>
     <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="406" t="inlineStr">
+      <c r="A34" s="450" t="inlineStr">
         <is>
           <t>MA25</t>
         </is>
       </c>
-      <c r="B34" s="407" t="n"/>
-      <c r="C34" s="407" t="n"/>
-      <c r="D34" s="407" t="n"/>
-      <c r="F34" s="408" t="inlineStr">
+      <c r="B34" s="451" t="n"/>
+      <c r="C34" s="451" t="n"/>
+      <c r="D34" s="451" t="n"/>
+      <c r="F34" s="452" t="inlineStr">
         <is>
           <t>MA26</t>
         </is>
       </c>
-      <c r="G34" s="409" t="n"/>
-      <c r="H34" s="409" t="n"/>
-      <c r="I34" s="409" t="n"/>
+      <c r="G34" s="453" t="n"/>
+      <c r="H34" s="453" t="n"/>
+      <c r="I34" s="453" t="n"/>
     </row>
     <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="407" t="n"/>
-      <c r="B35" s="407" t="n"/>
-      <c r="C35" s="407" t="n"/>
-      <c r="D35" s="407" t="n"/>
-      <c r="F35" s="409" t="n"/>
-      <c r="G35" s="409" t="n"/>
-      <c r="H35" s="409" t="n"/>
-      <c r="I35" s="409" t="n"/>
+      <c r="A35" s="451" t="n"/>
+      <c r="B35" s="451" t="n"/>
+      <c r="C35" s="451" t="n"/>
+      <c r="D35" s="451" t="n"/>
+      <c r="F35" s="453" t="n"/>
+      <c r="G35" s="453" t="n"/>
+      <c r="H35" s="453" t="n"/>
+      <c r="I35" s="453" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -20051,56 +20249,56 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="410" t="inlineStr">
+      <c r="A4" s="454" t="inlineStr">
         <is>
           <t>MB1</t>
         </is>
       </c>
-      <c r="B4" s="411" t="n"/>
-      <c r="C4" s="411" t="n"/>
-      <c r="D4" s="411" t="n"/>
-      <c r="F4" s="412" t="inlineStr">
+      <c r="B4" s="455" t="n"/>
+      <c r="C4" s="455" t="n"/>
+      <c r="D4" s="455" t="n"/>
+      <c r="F4" s="456" t="inlineStr">
         <is>
           <t>MB2</t>
         </is>
       </c>
-      <c r="G4" s="413" t="n"/>
-      <c r="H4" s="413" t="n"/>
-      <c r="I4" s="413" t="n"/>
-      <c r="K4" s="414" t="inlineStr">
+      <c r="G4" s="457" t="n"/>
+      <c r="H4" s="457" t="n"/>
+      <c r="I4" s="457" t="n"/>
+      <c r="K4" s="458" t="inlineStr">
         <is>
           <t>MB3</t>
         </is>
       </c>
-      <c r="L4" s="415" t="n"/>
-      <c r="M4" s="415" t="n"/>
-      <c r="N4" s="415" t="n"/>
-      <c r="P4" s="416" t="inlineStr">
+      <c r="L4" s="459" t="n"/>
+      <c r="M4" s="459" t="n"/>
+      <c r="N4" s="459" t="n"/>
+      <c r="P4" s="460" t="inlineStr">
         <is>
           <t>MB4</t>
         </is>
       </c>
-      <c r="Q4" s="417" t="n"/>
-      <c r="R4" s="417" t="n"/>
-      <c r="S4" s="417" t="n"/>
+      <c r="Q4" s="461" t="n"/>
+      <c r="R4" s="461" t="n"/>
+      <c r="S4" s="461" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="411" t="n"/>
-      <c r="B5" s="411" t="n"/>
-      <c r="C5" s="411" t="n"/>
-      <c r="D5" s="411" t="n"/>
-      <c r="F5" s="413" t="n"/>
-      <c r="G5" s="413" t="n"/>
-      <c r="H5" s="413" t="n"/>
-      <c r="I5" s="413" t="n"/>
-      <c r="K5" s="415" t="n"/>
-      <c r="L5" s="415" t="n"/>
-      <c r="M5" s="415" t="n"/>
-      <c r="N5" s="415" t="n"/>
-      <c r="P5" s="417" t="n"/>
-      <c r="Q5" s="417" t="n"/>
-      <c r="R5" s="417" t="n"/>
-      <c r="S5" s="417" t="n"/>
+      <c r="A5" s="455" t="n"/>
+      <c r="B5" s="455" t="n"/>
+      <c r="C5" s="455" t="n"/>
+      <c r="D5" s="455" t="n"/>
+      <c r="F5" s="457" t="n"/>
+      <c r="G5" s="457" t="n"/>
+      <c r="H5" s="457" t="n"/>
+      <c r="I5" s="457" t="n"/>
+      <c r="K5" s="459" t="n"/>
+      <c r="L5" s="459" t="n"/>
+      <c r="M5" s="459" t="n"/>
+      <c r="N5" s="459" t="n"/>
+      <c r="P5" s="461" t="n"/>
+      <c r="Q5" s="461" t="n"/>
+      <c r="R5" s="461" t="n"/>
+      <c r="S5" s="461" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -20205,56 +20403,56 @@
       <c r="S8" s="15" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="418" t="inlineStr">
+      <c r="A9" s="462" t="inlineStr">
         <is>
           <t>MB5</t>
         </is>
       </c>
-      <c r="B9" s="419" t="n"/>
-      <c r="C9" s="419" t="n"/>
-      <c r="D9" s="419" t="n"/>
-      <c r="F9" s="420" t="inlineStr">
+      <c r="B9" s="463" t="n"/>
+      <c r="C9" s="463" t="n"/>
+      <c r="D9" s="463" t="n"/>
+      <c r="F9" s="464" t="inlineStr">
         <is>
           <t>MB6</t>
         </is>
       </c>
-      <c r="G9" s="421" t="n"/>
-      <c r="H9" s="421" t="n"/>
-      <c r="I9" s="421" t="n"/>
-      <c r="K9" s="422" t="inlineStr">
+      <c r="G9" s="465" t="n"/>
+      <c r="H9" s="465" t="n"/>
+      <c r="I9" s="465" t="n"/>
+      <c r="K9" s="466" t="inlineStr">
         <is>
           <t>MB7</t>
         </is>
       </c>
-      <c r="L9" s="423" t="n"/>
-      <c r="M9" s="423" t="n"/>
-      <c r="N9" s="423" t="n"/>
-      <c r="P9" s="424" t="inlineStr">
+      <c r="L9" s="467" t="n"/>
+      <c r="M9" s="467" t="n"/>
+      <c r="N9" s="467" t="n"/>
+      <c r="P9" s="468" t="inlineStr">
         <is>
           <t>MB8</t>
         </is>
       </c>
-      <c r="Q9" s="425" t="n"/>
-      <c r="R9" s="425" t="n"/>
-      <c r="S9" s="425" t="n"/>
+      <c r="Q9" s="469" t="n"/>
+      <c r="R9" s="469" t="n"/>
+      <c r="S9" s="469" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="419" t="n"/>
-      <c r="B10" s="419" t="n"/>
-      <c r="C10" s="419" t="n"/>
-      <c r="D10" s="419" t="n"/>
-      <c r="F10" s="421" t="n"/>
-      <c r="G10" s="421" t="n"/>
-      <c r="H10" s="421" t="n"/>
-      <c r="I10" s="421" t="n"/>
-      <c r="K10" s="423" t="n"/>
-      <c r="L10" s="423" t="n"/>
-      <c r="M10" s="423" t="n"/>
-      <c r="N10" s="423" t="n"/>
-      <c r="P10" s="425" t="n"/>
-      <c r="Q10" s="425" t="n"/>
-      <c r="R10" s="425" t="n"/>
-      <c r="S10" s="425" t="n"/>
+      <c r="A10" s="463" t="n"/>
+      <c r="B10" s="463" t="n"/>
+      <c r="C10" s="463" t="n"/>
+      <c r="D10" s="463" t="n"/>
+      <c r="F10" s="465" t="n"/>
+      <c r="G10" s="465" t="n"/>
+      <c r="H10" s="465" t="n"/>
+      <c r="I10" s="465" t="n"/>
+      <c r="K10" s="467" t="n"/>
+      <c r="L10" s="467" t="n"/>
+      <c r="M10" s="467" t="n"/>
+      <c r="N10" s="467" t="n"/>
+      <c r="P10" s="469" t="n"/>
+      <c r="Q10" s="469" t="n"/>
+      <c r="R10" s="469" t="n"/>
+      <c r="S10" s="469" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -20359,56 +20557,56 @@
       <c r="S13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="426" t="inlineStr">
+      <c r="A14" s="470" t="inlineStr">
         <is>
           <t>MB9</t>
         </is>
       </c>
-      <c r="B14" s="427" t="n"/>
-      <c r="C14" s="427" t="n"/>
-      <c r="D14" s="427" t="n"/>
-      <c r="F14" s="428" t="inlineStr">
+      <c r="B14" s="471" t="n"/>
+      <c r="C14" s="471" t="n"/>
+      <c r="D14" s="471" t="n"/>
+      <c r="F14" s="472" t="inlineStr">
         <is>
           <t>MB10</t>
         </is>
       </c>
-      <c r="G14" s="429" t="n"/>
-      <c r="H14" s="429" t="n"/>
-      <c r="I14" s="429" t="n"/>
-      <c r="K14" s="430" t="inlineStr">
+      <c r="G14" s="473" t="n"/>
+      <c r="H14" s="473" t="n"/>
+      <c r="I14" s="473" t="n"/>
+      <c r="K14" s="474" t="inlineStr">
         <is>
           <t>MB11</t>
         </is>
       </c>
-      <c r="L14" s="431" t="n"/>
-      <c r="M14" s="431" t="n"/>
-      <c r="N14" s="431" t="n"/>
-      <c r="P14" s="432" t="inlineStr">
+      <c r="L14" s="475" t="n"/>
+      <c r="M14" s="475" t="n"/>
+      <c r="N14" s="475" t="n"/>
+      <c r="P14" s="476" t="inlineStr">
         <is>
           <t>MB12</t>
         </is>
       </c>
-      <c r="Q14" s="433" t="n"/>
-      <c r="R14" s="433" t="n"/>
-      <c r="S14" s="433" t="n"/>
+      <c r="Q14" s="477" t="n"/>
+      <c r="R14" s="477" t="n"/>
+      <c r="S14" s="477" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="427" t="n"/>
-      <c r="B15" s="427" t="n"/>
-      <c r="C15" s="427" t="n"/>
-      <c r="D15" s="427" t="n"/>
-      <c r="F15" s="429" t="n"/>
-      <c r="G15" s="429" t="n"/>
-      <c r="H15" s="429" t="n"/>
-      <c r="I15" s="429" t="n"/>
-      <c r="K15" s="431" t="n"/>
-      <c r="L15" s="431" t="n"/>
-      <c r="M15" s="431" t="n"/>
-      <c r="N15" s="431" t="n"/>
-      <c r="P15" s="433" t="n"/>
-      <c r="Q15" s="433" t="n"/>
-      <c r="R15" s="433" t="n"/>
-      <c r="S15" s="433" t="n"/>
+      <c r="A15" s="471" t="n"/>
+      <c r="B15" s="471" t="n"/>
+      <c r="C15" s="471" t="n"/>
+      <c r="D15" s="471" t="n"/>
+      <c r="F15" s="473" t="n"/>
+      <c r="G15" s="473" t="n"/>
+      <c r="H15" s="473" t="n"/>
+      <c r="I15" s="473" t="n"/>
+      <c r="K15" s="475" t="n"/>
+      <c r="L15" s="475" t="n"/>
+      <c r="M15" s="475" t="n"/>
+      <c r="N15" s="475" t="n"/>
+      <c r="P15" s="477" t="n"/>
+      <c r="Q15" s="477" t="n"/>
+      <c r="R15" s="477" t="n"/>
+      <c r="S15" s="477" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -20513,56 +20711,56 @@
       <c r="S18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="434" t="inlineStr">
+      <c r="A19" s="478" t="inlineStr">
         <is>
           <t>MB13</t>
         </is>
       </c>
-      <c r="B19" s="435" t="n"/>
-      <c r="C19" s="435" t="n"/>
-      <c r="D19" s="435" t="n"/>
-      <c r="F19" s="436" t="inlineStr">
+      <c r="B19" s="479" t="n"/>
+      <c r="C19" s="479" t="n"/>
+      <c r="D19" s="479" t="n"/>
+      <c r="F19" s="480" t="inlineStr">
         <is>
           <t>MB14</t>
         </is>
       </c>
-      <c r="G19" s="437" t="n"/>
-      <c r="H19" s="437" t="n"/>
-      <c r="I19" s="437" t="n"/>
-      <c r="K19" s="438" t="inlineStr">
+      <c r="G19" s="481" t="n"/>
+      <c r="H19" s="481" t="n"/>
+      <c r="I19" s="481" t="n"/>
+      <c r="K19" s="482" t="inlineStr">
         <is>
           <t>MB15</t>
         </is>
       </c>
-      <c r="L19" s="439" t="n"/>
-      <c r="M19" s="439" t="n"/>
-      <c r="N19" s="439" t="n"/>
-      <c r="P19" s="440" t="inlineStr">
+      <c r="L19" s="483" t="n"/>
+      <c r="M19" s="483" t="n"/>
+      <c r="N19" s="483" t="n"/>
+      <c r="P19" s="484" t="inlineStr">
         <is>
           <t>MB16</t>
         </is>
       </c>
-      <c r="Q19" s="441" t="n"/>
-      <c r="R19" s="441" t="n"/>
-      <c r="S19" s="441" t="n"/>
+      <c r="Q19" s="485" t="n"/>
+      <c r="R19" s="485" t="n"/>
+      <c r="S19" s="485" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="435" t="n"/>
-      <c r="B20" s="435" t="n"/>
-      <c r="C20" s="435" t="n"/>
-      <c r="D20" s="435" t="n"/>
-      <c r="F20" s="437" t="n"/>
-      <c r="G20" s="437" t="n"/>
-      <c r="H20" s="437" t="n"/>
-      <c r="I20" s="437" t="n"/>
-      <c r="K20" s="439" t="n"/>
-      <c r="L20" s="439" t="n"/>
-      <c r="M20" s="439" t="n"/>
-      <c r="N20" s="439" t="n"/>
-      <c r="P20" s="441" t="n"/>
-      <c r="Q20" s="441" t="n"/>
-      <c r="R20" s="441" t="n"/>
-      <c r="S20" s="441" t="n"/>
+      <c r="A20" s="479" t="n"/>
+      <c r="B20" s="479" t="n"/>
+      <c r="C20" s="479" t="n"/>
+      <c r="D20" s="479" t="n"/>
+      <c r="F20" s="481" t="n"/>
+      <c r="G20" s="481" t="n"/>
+      <c r="H20" s="481" t="n"/>
+      <c r="I20" s="481" t="n"/>
+      <c r="K20" s="483" t="n"/>
+      <c r="L20" s="483" t="n"/>
+      <c r="M20" s="483" t="n"/>
+      <c r="N20" s="483" t="n"/>
+      <c r="P20" s="485" t="n"/>
+      <c r="Q20" s="485" t="n"/>
+      <c r="R20" s="485" t="n"/>
+      <c r="S20" s="485" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -20667,56 +20865,56 @@
       <c r="S23" s="15" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="442" t="inlineStr">
+      <c r="A24" s="486" t="inlineStr">
         <is>
           <t>MB17</t>
         </is>
       </c>
-      <c r="B24" s="443" t="n"/>
-      <c r="C24" s="443" t="n"/>
-      <c r="D24" s="443" t="n"/>
-      <c r="F24" s="444" t="inlineStr">
+      <c r="B24" s="487" t="n"/>
+      <c r="C24" s="487" t="n"/>
+      <c r="D24" s="487" t="n"/>
+      <c r="F24" s="488" t="inlineStr">
         <is>
           <t>MB18</t>
         </is>
       </c>
-      <c r="G24" s="445" t="n"/>
-      <c r="H24" s="445" t="n"/>
-      <c r="I24" s="445" t="n"/>
-      <c r="K24" s="446" t="inlineStr">
+      <c r="G24" s="489" t="n"/>
+      <c r="H24" s="489" t="n"/>
+      <c r="I24" s="489" t="n"/>
+      <c r="K24" s="490" t="inlineStr">
         <is>
           <t>MB19</t>
         </is>
       </c>
-      <c r="L24" s="447" t="n"/>
-      <c r="M24" s="447" t="n"/>
-      <c r="N24" s="447" t="n"/>
-      <c r="P24" s="448" t="inlineStr">
+      <c r="L24" s="491" t="n"/>
+      <c r="M24" s="491" t="n"/>
+      <c r="N24" s="491" t="n"/>
+      <c r="P24" s="492" t="inlineStr">
         <is>
           <t>MB20</t>
         </is>
       </c>
-      <c r="Q24" s="449" t="n"/>
-      <c r="R24" s="449" t="n"/>
-      <c r="S24" s="449" t="n"/>
+      <c r="Q24" s="493" t="n"/>
+      <c r="R24" s="493" t="n"/>
+      <c r="S24" s="493" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="443" t="n"/>
-      <c r="B25" s="443" t="n"/>
-      <c r="C25" s="443" t="n"/>
-      <c r="D25" s="443" t="n"/>
-      <c r="F25" s="445" t="n"/>
-      <c r="G25" s="445" t="n"/>
-      <c r="H25" s="445" t="n"/>
-      <c r="I25" s="445" t="n"/>
-      <c r="K25" s="447" t="n"/>
-      <c r="L25" s="447" t="n"/>
-      <c r="M25" s="447" t="n"/>
-      <c r="N25" s="447" t="n"/>
-      <c r="P25" s="449" t="n"/>
-      <c r="Q25" s="449" t="n"/>
-      <c r="R25" s="449" t="n"/>
-      <c r="S25" s="449" t="n"/>
+      <c r="A25" s="487" t="n"/>
+      <c r="B25" s="487" t="n"/>
+      <c r="C25" s="487" t="n"/>
+      <c r="D25" s="487" t="n"/>
+      <c r="F25" s="489" t="n"/>
+      <c r="G25" s="489" t="n"/>
+      <c r="H25" s="489" t="n"/>
+      <c r="I25" s="489" t="n"/>
+      <c r="K25" s="491" t="n"/>
+      <c r="L25" s="491" t="n"/>
+      <c r="M25" s="491" t="n"/>
+      <c r="N25" s="491" t="n"/>
+      <c r="P25" s="493" t="n"/>
+      <c r="Q25" s="493" t="n"/>
+      <c r="R25" s="493" t="n"/>
+      <c r="S25" s="493" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
@@ -20821,56 +21019,56 @@
       <c r="S28" s="15" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="450" t="inlineStr">
+      <c r="A29" s="494" t="inlineStr">
         <is>
           <t>MB21</t>
         </is>
       </c>
-      <c r="B29" s="451" t="n"/>
-      <c r="C29" s="451" t="n"/>
-      <c r="D29" s="451" t="n"/>
-      <c r="F29" s="452" t="inlineStr">
+      <c r="B29" s="495" t="n"/>
+      <c r="C29" s="495" t="n"/>
+      <c r="D29" s="495" t="n"/>
+      <c r="F29" s="496" t="inlineStr">
         <is>
           <t>MB22</t>
         </is>
       </c>
-      <c r="G29" s="453" t="n"/>
-      <c r="H29" s="453" t="n"/>
-      <c r="I29" s="453" t="n"/>
-      <c r="K29" s="454" t="inlineStr">
+      <c r="G29" s="497" t="n"/>
+      <c r="H29" s="497" t="n"/>
+      <c r="I29" s="497" t="n"/>
+      <c r="K29" s="498" t="inlineStr">
         <is>
           <t>MB23</t>
         </is>
       </c>
-      <c r="L29" s="455" t="n"/>
-      <c r="M29" s="455" t="n"/>
-      <c r="N29" s="455" t="n"/>
-      <c r="P29" s="456" t="inlineStr">
+      <c r="L29" s="499" t="n"/>
+      <c r="M29" s="499" t="n"/>
+      <c r="N29" s="499" t="n"/>
+      <c r="P29" s="500" t="inlineStr">
         <is>
           <t>MB24</t>
         </is>
       </c>
-      <c r="Q29" s="457" t="n"/>
-      <c r="R29" s="457" t="n"/>
-      <c r="S29" s="457" t="n"/>
+      <c r="Q29" s="501" t="n"/>
+      <c r="R29" s="501" t="n"/>
+      <c r="S29" s="501" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="451" t="n"/>
-      <c r="B30" s="451" t="n"/>
-      <c r="C30" s="451" t="n"/>
-      <c r="D30" s="451" t="n"/>
-      <c r="F30" s="453" t="n"/>
-      <c r="G30" s="453" t="n"/>
-      <c r="H30" s="453" t="n"/>
-      <c r="I30" s="453" t="n"/>
-      <c r="K30" s="455" t="n"/>
-      <c r="L30" s="455" t="n"/>
-      <c r="M30" s="455" t="n"/>
-      <c r="N30" s="455" t="n"/>
-      <c r="P30" s="457" t="n"/>
-      <c r="Q30" s="457" t="n"/>
-      <c r="R30" s="457" t="n"/>
-      <c r="S30" s="457" t="n"/>
+      <c r="A30" s="495" t="n"/>
+      <c r="B30" s="495" t="n"/>
+      <c r="C30" s="495" t="n"/>
+      <c r="D30" s="495" t="n"/>
+      <c r="F30" s="497" t="n"/>
+      <c r="G30" s="497" t="n"/>
+      <c r="H30" s="497" t="n"/>
+      <c r="I30" s="497" t="n"/>
+      <c r="K30" s="499" t="n"/>
+      <c r="L30" s="499" t="n"/>
+      <c r="M30" s="499" t="n"/>
+      <c r="N30" s="499" t="n"/>
+      <c r="P30" s="501" t="n"/>
+      <c r="Q30" s="501" t="n"/>
+      <c r="R30" s="501" t="n"/>
+      <c r="S30" s="501" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -20975,56 +21173,56 @@
       <c r="S33" s="15" t="n"/>
     </row>
     <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="458" t="inlineStr">
+      <c r="A34" s="502" t="inlineStr">
         <is>
           <t>MB25</t>
         </is>
       </c>
-      <c r="B34" s="459" t="n"/>
-      <c r="C34" s="459" t="n"/>
-      <c r="D34" s="459" t="n"/>
-      <c r="F34" s="460" t="inlineStr">
+      <c r="B34" s="503" t="n"/>
+      <c r="C34" s="503" t="n"/>
+      <c r="D34" s="503" t="n"/>
+      <c r="F34" s="504" t="inlineStr">
         <is>
           <t>MB26</t>
         </is>
       </c>
-      <c r="G34" s="461" t="n"/>
-      <c r="H34" s="461" t="n"/>
-      <c r="I34" s="461" t="n"/>
-      <c r="K34" s="462" t="inlineStr">
+      <c r="G34" s="505" t="n"/>
+      <c r="H34" s="505" t="n"/>
+      <c r="I34" s="505" t="n"/>
+      <c r="K34" s="506" t="inlineStr">
         <is>
           <t>MB27</t>
         </is>
       </c>
-      <c r="L34" s="463" t="n"/>
-      <c r="M34" s="463" t="n"/>
-      <c r="N34" s="463" t="n"/>
-      <c r="P34" s="464" t="inlineStr">
+      <c r="L34" s="507" t="n"/>
+      <c r="M34" s="507" t="n"/>
+      <c r="N34" s="507" t="n"/>
+      <c r="P34" s="508" t="inlineStr">
         <is>
           <t>MB28</t>
         </is>
       </c>
-      <c r="Q34" s="465" t="n"/>
-      <c r="R34" s="465" t="n"/>
-      <c r="S34" s="465" t="n"/>
+      <c r="Q34" s="509" t="n"/>
+      <c r="R34" s="509" t="n"/>
+      <c r="S34" s="509" t="n"/>
     </row>
     <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="459" t="n"/>
-      <c r="B35" s="459" t="n"/>
-      <c r="C35" s="459" t="n"/>
-      <c r="D35" s="459" t="n"/>
-      <c r="F35" s="461" t="n"/>
-      <c r="G35" s="461" t="n"/>
-      <c r="H35" s="461" t="n"/>
-      <c r="I35" s="461" t="n"/>
-      <c r="K35" s="463" t="n"/>
-      <c r="L35" s="463" t="n"/>
-      <c r="M35" s="463" t="n"/>
-      <c r="N35" s="463" t="n"/>
-      <c r="P35" s="465" t="n"/>
-      <c r="Q35" s="465" t="n"/>
-      <c r="R35" s="465" t="n"/>
-      <c r="S35" s="465" t="n"/>
+      <c r="A35" s="503" t="n"/>
+      <c r="B35" s="503" t="n"/>
+      <c r="C35" s="503" t="n"/>
+      <c r="D35" s="503" t="n"/>
+      <c r="F35" s="505" t="n"/>
+      <c r="G35" s="505" t="n"/>
+      <c r="H35" s="505" t="n"/>
+      <c r="I35" s="505" t="n"/>
+      <c r="K35" s="507" t="n"/>
+      <c r="L35" s="507" t="n"/>
+      <c r="M35" s="507" t="n"/>
+      <c r="N35" s="507" t="n"/>
+      <c r="P35" s="509" t="n"/>
+      <c r="Q35" s="509" t="n"/>
+      <c r="R35" s="509" t="n"/>
+      <c r="S35" s="509" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -21129,56 +21327,56 @@
       <c r="S38" s="15" t="n"/>
     </row>
     <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="466" t="inlineStr">
+      <c r="A39" s="510" t="inlineStr">
         <is>
           <t>MB29</t>
         </is>
       </c>
-      <c r="B39" s="467" t="n"/>
-      <c r="C39" s="467" t="n"/>
-      <c r="D39" s="467" t="n"/>
-      <c r="F39" s="468" t="inlineStr">
+      <c r="B39" s="511" t="n"/>
+      <c r="C39" s="511" t="n"/>
+      <c r="D39" s="511" t="n"/>
+      <c r="F39" s="512" t="inlineStr">
         <is>
           <t>MB30</t>
         </is>
       </c>
-      <c r="G39" s="469" t="n"/>
-      <c r="H39" s="469" t="n"/>
-      <c r="I39" s="469" t="n"/>
-      <c r="K39" s="470" t="inlineStr">
+      <c r="G39" s="513" t="n"/>
+      <c r="H39" s="513" t="n"/>
+      <c r="I39" s="513" t="n"/>
+      <c r="K39" s="514" t="inlineStr">
         <is>
           <t>MB31</t>
         </is>
       </c>
-      <c r="L39" s="471" t="n"/>
-      <c r="M39" s="471" t="n"/>
-      <c r="N39" s="471" t="n"/>
-      <c r="P39" s="472" t="inlineStr">
+      <c r="L39" s="515" t="n"/>
+      <c r="M39" s="515" t="n"/>
+      <c r="N39" s="515" t="n"/>
+      <c r="P39" s="516" t="inlineStr">
         <is>
           <t>MB32</t>
         </is>
       </c>
-      <c r="Q39" s="473" t="n"/>
-      <c r="R39" s="473" t="n"/>
-      <c r="S39" s="473" t="n"/>
+      <c r="Q39" s="517" t="n"/>
+      <c r="R39" s="517" t="n"/>
+      <c r="S39" s="517" t="n"/>
     </row>
     <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="467" t="n"/>
-      <c r="B40" s="467" t="n"/>
-      <c r="C40" s="467" t="n"/>
-      <c r="D40" s="467" t="n"/>
-      <c r="F40" s="469" t="n"/>
-      <c r="G40" s="469" t="n"/>
-      <c r="H40" s="469" t="n"/>
-      <c r="I40" s="469" t="n"/>
-      <c r="K40" s="471" t="n"/>
-      <c r="L40" s="471" t="n"/>
-      <c r="M40" s="471" t="n"/>
-      <c r="N40" s="471" t="n"/>
-      <c r="P40" s="473" t="n"/>
-      <c r="Q40" s="473" t="n"/>
-      <c r="R40" s="473" t="n"/>
-      <c r="S40" s="473" t="n"/>
+      <c r="A40" s="511" t="n"/>
+      <c r="B40" s="511" t="n"/>
+      <c r="C40" s="511" t="n"/>
+      <c r="D40" s="511" t="n"/>
+      <c r="F40" s="513" t="n"/>
+      <c r="G40" s="513" t="n"/>
+      <c r="H40" s="513" t="n"/>
+      <c r="I40" s="513" t="n"/>
+      <c r="K40" s="515" t="n"/>
+      <c r="L40" s="515" t="n"/>
+      <c r="M40" s="515" t="n"/>
+      <c r="N40" s="515" t="n"/>
+      <c r="P40" s="517" t="n"/>
+      <c r="Q40" s="517" t="n"/>
+      <c r="R40" s="517" t="n"/>
+      <c r="S40" s="517" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
@@ -21462,56 +21660,56 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="474" t="inlineStr">
+      <c r="A4" s="518" t="inlineStr">
         <is>
           <t>MC1</t>
         </is>
       </c>
-      <c r="B4" s="475" t="n"/>
-      <c r="C4" s="475" t="n"/>
-      <c r="D4" s="475" t="n"/>
-      <c r="F4" s="476" t="inlineStr">
+      <c r="B4" s="519" t="n"/>
+      <c r="C4" s="519" t="n"/>
+      <c r="D4" s="519" t="n"/>
+      <c r="F4" s="520" t="inlineStr">
         <is>
           <t>MC2</t>
         </is>
       </c>
-      <c r="G4" s="477" t="n"/>
-      <c r="H4" s="477" t="n"/>
-      <c r="I4" s="477" t="n"/>
-      <c r="K4" s="478" t="inlineStr">
+      <c r="G4" s="521" t="n"/>
+      <c r="H4" s="521" t="n"/>
+      <c r="I4" s="521" t="n"/>
+      <c r="K4" s="522" t="inlineStr">
         <is>
           <t>MC3</t>
         </is>
       </c>
-      <c r="L4" s="479" t="n"/>
-      <c r="M4" s="479" t="n"/>
-      <c r="N4" s="479" t="n"/>
-      <c r="P4" s="480" t="inlineStr">
+      <c r="L4" s="523" t="n"/>
+      <c r="M4" s="523" t="n"/>
+      <c r="N4" s="523" t="n"/>
+      <c r="P4" s="524" t="inlineStr">
         <is>
           <t>MC4</t>
         </is>
       </c>
-      <c r="Q4" s="481" t="n"/>
-      <c r="R4" s="481" t="n"/>
-      <c r="S4" s="481" t="n"/>
+      <c r="Q4" s="525" t="n"/>
+      <c r="R4" s="525" t="n"/>
+      <c r="S4" s="525" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="475" t="n"/>
-      <c r="B5" s="475" t="n"/>
-      <c r="C5" s="475" t="n"/>
-      <c r="D5" s="475" t="n"/>
-      <c r="F5" s="477" t="n"/>
-      <c r="G5" s="477" t="n"/>
-      <c r="H5" s="477" t="n"/>
-      <c r="I5" s="477" t="n"/>
-      <c r="K5" s="479" t="n"/>
-      <c r="L5" s="479" t="n"/>
-      <c r="M5" s="479" t="n"/>
-      <c r="N5" s="479" t="n"/>
-      <c r="P5" s="481" t="n"/>
-      <c r="Q5" s="481" t="n"/>
-      <c r="R5" s="481" t="n"/>
-      <c r="S5" s="481" t="n"/>
+      <c r="A5" s="519" t="n"/>
+      <c r="B5" s="519" t="n"/>
+      <c r="C5" s="519" t="n"/>
+      <c r="D5" s="519" t="n"/>
+      <c r="F5" s="521" t="n"/>
+      <c r="G5" s="521" t="n"/>
+      <c r="H5" s="521" t="n"/>
+      <c r="I5" s="521" t="n"/>
+      <c r="K5" s="523" t="n"/>
+      <c r="L5" s="523" t="n"/>
+      <c r="M5" s="523" t="n"/>
+      <c r="N5" s="523" t="n"/>
+      <c r="P5" s="525" t="n"/>
+      <c r="Q5" s="525" t="n"/>
+      <c r="R5" s="525" t="n"/>
+      <c r="S5" s="525" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -21616,56 +21814,56 @@
       <c r="S8" s="15" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="482" t="inlineStr">
+      <c r="A9" s="526" t="inlineStr">
         <is>
           <t>MC5</t>
         </is>
       </c>
-      <c r="B9" s="483" t="n"/>
-      <c r="C9" s="483" t="n"/>
-      <c r="D9" s="483" t="n"/>
-      <c r="F9" s="484" t="inlineStr">
+      <c r="B9" s="527" t="n"/>
+      <c r="C9" s="527" t="n"/>
+      <c r="D9" s="527" t="n"/>
+      <c r="F9" s="528" t="inlineStr">
         <is>
           <t>MC6</t>
         </is>
       </c>
-      <c r="G9" s="485" t="n"/>
-      <c r="H9" s="485" t="n"/>
-      <c r="I9" s="485" t="n"/>
-      <c r="K9" s="486" t="inlineStr">
+      <c r="G9" s="529" t="n"/>
+      <c r="H9" s="529" t="n"/>
+      <c r="I9" s="529" t="n"/>
+      <c r="K9" s="530" t="inlineStr">
         <is>
           <t>MC7</t>
         </is>
       </c>
-      <c r="L9" s="487" t="n"/>
-      <c r="M9" s="487" t="n"/>
-      <c r="N9" s="487" t="n"/>
-      <c r="P9" s="488" t="inlineStr">
+      <c r="L9" s="531" t="n"/>
+      <c r="M9" s="531" t="n"/>
+      <c r="N9" s="531" t="n"/>
+      <c r="P9" s="532" t="inlineStr">
         <is>
           <t>MC8</t>
         </is>
       </c>
-      <c r="Q9" s="489" t="n"/>
-      <c r="R9" s="489" t="n"/>
-      <c r="S9" s="489" t="n"/>
+      <c r="Q9" s="533" t="n"/>
+      <c r="R9" s="533" t="n"/>
+      <c r="S9" s="533" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="483" t="n"/>
-      <c r="B10" s="483" t="n"/>
-      <c r="C10" s="483" t="n"/>
-      <c r="D10" s="483" t="n"/>
-      <c r="F10" s="485" t="n"/>
-      <c r="G10" s="485" t="n"/>
-      <c r="H10" s="485" t="n"/>
-      <c r="I10" s="485" t="n"/>
-      <c r="K10" s="487" t="n"/>
-      <c r="L10" s="487" t="n"/>
-      <c r="M10" s="487" t="n"/>
-      <c r="N10" s="487" t="n"/>
-      <c r="P10" s="489" t="n"/>
-      <c r="Q10" s="489" t="n"/>
-      <c r="R10" s="489" t="n"/>
-      <c r="S10" s="489" t="n"/>
+      <c r="A10" s="527" t="n"/>
+      <c r="B10" s="527" t="n"/>
+      <c r="C10" s="527" t="n"/>
+      <c r="D10" s="527" t="n"/>
+      <c r="F10" s="529" t="n"/>
+      <c r="G10" s="529" t="n"/>
+      <c r="H10" s="529" t="n"/>
+      <c r="I10" s="529" t="n"/>
+      <c r="K10" s="531" t="n"/>
+      <c r="L10" s="531" t="n"/>
+      <c r="M10" s="531" t="n"/>
+      <c r="N10" s="531" t="n"/>
+      <c r="P10" s="533" t="n"/>
+      <c r="Q10" s="533" t="n"/>
+      <c r="R10" s="533" t="n"/>
+      <c r="S10" s="533" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -21770,56 +21968,56 @@
       <c r="S13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="490" t="inlineStr">
+      <c r="A14" s="534" t="inlineStr">
         <is>
           <t>MC9</t>
         </is>
       </c>
-      <c r="B14" s="491" t="n"/>
-      <c r="C14" s="491" t="n"/>
-      <c r="D14" s="491" t="n"/>
-      <c r="F14" s="492" t="inlineStr">
+      <c r="B14" s="535" t="n"/>
+      <c r="C14" s="535" t="n"/>
+      <c r="D14" s="535" t="n"/>
+      <c r="F14" s="536" t="inlineStr">
         <is>
           <t>MC10</t>
         </is>
       </c>
-      <c r="G14" s="493" t="n"/>
-      <c r="H14" s="493" t="n"/>
-      <c r="I14" s="493" t="n"/>
-      <c r="K14" s="494" t="inlineStr">
+      <c r="G14" s="537" t="n"/>
+      <c r="H14" s="537" t="n"/>
+      <c r="I14" s="537" t="n"/>
+      <c r="K14" s="538" t="inlineStr">
         <is>
           <t>MC11</t>
         </is>
       </c>
-      <c r="L14" s="495" t="n"/>
-      <c r="M14" s="495" t="n"/>
-      <c r="N14" s="495" t="n"/>
-      <c r="P14" s="496" t="inlineStr">
+      <c r="L14" s="539" t="n"/>
+      <c r="M14" s="539" t="n"/>
+      <c r="N14" s="539" t="n"/>
+      <c r="P14" s="540" t="inlineStr">
         <is>
           <t>MC12</t>
         </is>
       </c>
-      <c r="Q14" s="497" t="n"/>
-      <c r="R14" s="497" t="n"/>
-      <c r="S14" s="497" t="n"/>
+      <c r="Q14" s="541" t="n"/>
+      <c r="R14" s="541" t="n"/>
+      <c r="S14" s="541" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="491" t="n"/>
-      <c r="B15" s="491" t="n"/>
-      <c r="C15" s="491" t="n"/>
-      <c r="D15" s="491" t="n"/>
-      <c r="F15" s="493" t="n"/>
-      <c r="G15" s="493" t="n"/>
-      <c r="H15" s="493" t="n"/>
-      <c r="I15" s="493" t="n"/>
-      <c r="K15" s="495" t="n"/>
-      <c r="L15" s="495" t="n"/>
-      <c r="M15" s="495" t="n"/>
-      <c r="N15" s="495" t="n"/>
-      <c r="P15" s="497" t="n"/>
-      <c r="Q15" s="497" t="n"/>
-      <c r="R15" s="497" t="n"/>
-      <c r="S15" s="497" t="n"/>
+      <c r="A15" s="535" t="n"/>
+      <c r="B15" s="535" t="n"/>
+      <c r="C15" s="535" t="n"/>
+      <c r="D15" s="535" t="n"/>
+      <c r="F15" s="537" t="n"/>
+      <c r="G15" s="537" t="n"/>
+      <c r="H15" s="537" t="n"/>
+      <c r="I15" s="537" t="n"/>
+      <c r="K15" s="539" t="n"/>
+      <c r="L15" s="539" t="n"/>
+      <c r="M15" s="539" t="n"/>
+      <c r="N15" s="539" t="n"/>
+      <c r="P15" s="541" t="n"/>
+      <c r="Q15" s="541" t="n"/>
+      <c r="R15" s="541" t="n"/>
+      <c r="S15" s="541" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -21924,56 +22122,56 @@
       <c r="S18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="498" t="inlineStr">
+      <c r="A19" s="542" t="inlineStr">
         <is>
           <t>MC13</t>
         </is>
       </c>
-      <c r="B19" s="499" t="n"/>
-      <c r="C19" s="499" t="n"/>
-      <c r="D19" s="499" t="n"/>
-      <c r="F19" s="500" t="inlineStr">
+      <c r="B19" s="543" t="n"/>
+      <c r="C19" s="543" t="n"/>
+      <c r="D19" s="543" t="n"/>
+      <c r="F19" s="544" t="inlineStr">
         <is>
           <t>MC14</t>
         </is>
       </c>
-      <c r="G19" s="501" t="n"/>
-      <c r="H19" s="501" t="n"/>
-      <c r="I19" s="501" t="n"/>
-      <c r="K19" s="502" t="inlineStr">
+      <c r="G19" s="545" t="n"/>
+      <c r="H19" s="545" t="n"/>
+      <c r="I19" s="545" t="n"/>
+      <c r="K19" s="546" t="inlineStr">
         <is>
           <t>MC15</t>
         </is>
       </c>
-      <c r="L19" s="503" t="n"/>
-      <c r="M19" s="503" t="n"/>
-      <c r="N19" s="503" t="n"/>
-      <c r="P19" s="504" t="inlineStr">
+      <c r="L19" s="547" t="n"/>
+      <c r="M19" s="547" t="n"/>
+      <c r="N19" s="547" t="n"/>
+      <c r="P19" s="548" t="inlineStr">
         <is>
           <t>MC16</t>
         </is>
       </c>
-      <c r="Q19" s="505" t="n"/>
-      <c r="R19" s="505" t="n"/>
-      <c r="S19" s="505" t="n"/>
+      <c r="Q19" s="549" t="n"/>
+      <c r="R19" s="549" t="n"/>
+      <c r="S19" s="549" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="499" t="n"/>
-      <c r="B20" s="499" t="n"/>
-      <c r="C20" s="499" t="n"/>
-      <c r="D20" s="499" t="n"/>
-      <c r="F20" s="501" t="n"/>
-      <c r="G20" s="501" t="n"/>
-      <c r="H20" s="501" t="n"/>
-      <c r="I20" s="501" t="n"/>
-      <c r="K20" s="503" t="n"/>
-      <c r="L20" s="503" t="n"/>
-      <c r="M20" s="503" t="n"/>
-      <c r="N20" s="503" t="n"/>
-      <c r="P20" s="505" t="n"/>
-      <c r="Q20" s="505" t="n"/>
-      <c r="R20" s="505" t="n"/>
-      <c r="S20" s="505" t="n"/>
+      <c r="A20" s="543" t="n"/>
+      <c r="B20" s="543" t="n"/>
+      <c r="C20" s="543" t="n"/>
+      <c r="D20" s="543" t="n"/>
+      <c r="F20" s="545" t="n"/>
+      <c r="G20" s="545" t="n"/>
+      <c r="H20" s="545" t="n"/>
+      <c r="I20" s="545" t="n"/>
+      <c r="K20" s="547" t="n"/>
+      <c r="L20" s="547" t="n"/>
+      <c r="M20" s="547" t="n"/>
+      <c r="N20" s="547" t="n"/>
+      <c r="P20" s="549" t="n"/>
+      <c r="Q20" s="549" t="n"/>
+      <c r="R20" s="549" t="n"/>
+      <c r="S20" s="549" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -22078,56 +22276,56 @@
       <c r="S23" s="15" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="506" t="inlineStr">
+      <c r="A24" s="550" t="inlineStr">
         <is>
           <t>MC17</t>
         </is>
       </c>
-      <c r="B24" s="507" t="n"/>
-      <c r="C24" s="507" t="n"/>
-      <c r="D24" s="507" t="n"/>
-      <c r="F24" s="508" t="inlineStr">
+      <c r="B24" s="551" t="n"/>
+      <c r="C24" s="551" t="n"/>
+      <c r="D24" s="551" t="n"/>
+      <c r="F24" s="552" t="inlineStr">
         <is>
           <t>MC18</t>
         </is>
       </c>
-      <c r="G24" s="509" t="n"/>
-      <c r="H24" s="509" t="n"/>
-      <c r="I24" s="509" t="n"/>
-      <c r="K24" s="510" t="inlineStr">
+      <c r="G24" s="553" t="n"/>
+      <c r="H24" s="553" t="n"/>
+      <c r="I24" s="553" t="n"/>
+      <c r="K24" s="554" t="inlineStr">
         <is>
           <t>MC19</t>
         </is>
       </c>
-      <c r="L24" s="511" t="n"/>
-      <c r="M24" s="511" t="n"/>
-      <c r="N24" s="511" t="n"/>
-      <c r="P24" s="512" t="inlineStr">
+      <c r="L24" s="555" t="n"/>
+      <c r="M24" s="555" t="n"/>
+      <c r="N24" s="555" t="n"/>
+      <c r="P24" s="556" t="inlineStr">
         <is>
           <t>MC20</t>
         </is>
       </c>
-      <c r="Q24" s="513" t="n"/>
-      <c r="R24" s="513" t="n"/>
-      <c r="S24" s="513" t="n"/>
+      <c r="Q24" s="557" t="n"/>
+      <c r="R24" s="557" t="n"/>
+      <c r="S24" s="557" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="507" t="n"/>
-      <c r="B25" s="507" t="n"/>
-      <c r="C25" s="507" t="n"/>
-      <c r="D25" s="507" t="n"/>
-      <c r="F25" s="509" t="n"/>
-      <c r="G25" s="509" t="n"/>
-      <c r="H25" s="509" t="n"/>
-      <c r="I25" s="509" t="n"/>
-      <c r="K25" s="511" t="n"/>
-      <c r="L25" s="511" t="n"/>
-      <c r="M25" s="511" t="n"/>
-      <c r="N25" s="511" t="n"/>
-      <c r="P25" s="513" t="n"/>
-      <c r="Q25" s="513" t="n"/>
-      <c r="R25" s="513" t="n"/>
-      <c r="S25" s="513" t="n"/>
+      <c r="A25" s="551" t="n"/>
+      <c r="B25" s="551" t="n"/>
+      <c r="C25" s="551" t="n"/>
+      <c r="D25" s="551" t="n"/>
+      <c r="F25" s="553" t="n"/>
+      <c r="G25" s="553" t="n"/>
+      <c r="H25" s="553" t="n"/>
+      <c r="I25" s="553" t="n"/>
+      <c r="K25" s="555" t="n"/>
+      <c r="L25" s="555" t="n"/>
+      <c r="M25" s="555" t="n"/>
+      <c r="N25" s="555" t="n"/>
+      <c r="P25" s="557" t="n"/>
+      <c r="Q25" s="557" t="n"/>
+      <c r="R25" s="557" t="n"/>
+      <c r="S25" s="557" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
@@ -22232,56 +22430,56 @@
       <c r="S28" s="15" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="514" t="inlineStr">
+      <c r="A29" s="558" t="inlineStr">
         <is>
           <t>MC21</t>
         </is>
       </c>
-      <c r="B29" s="515" t="n"/>
-      <c r="C29" s="515" t="n"/>
-      <c r="D29" s="515" t="n"/>
-      <c r="F29" s="516" t="inlineStr">
+      <c r="B29" s="559" t="n"/>
+      <c r="C29" s="559" t="n"/>
+      <c r="D29" s="559" t="n"/>
+      <c r="F29" s="560" t="inlineStr">
         <is>
           <t>MC22</t>
         </is>
       </c>
-      <c r="G29" s="517" t="n"/>
-      <c r="H29" s="517" t="n"/>
-      <c r="I29" s="517" t="n"/>
-      <c r="K29" s="518" t="inlineStr">
+      <c r="G29" s="561" t="n"/>
+      <c r="H29" s="561" t="n"/>
+      <c r="I29" s="561" t="n"/>
+      <c r="K29" s="562" t="inlineStr">
         <is>
           <t>MC23</t>
         </is>
       </c>
-      <c r="L29" s="519" t="n"/>
-      <c r="M29" s="519" t="n"/>
-      <c r="N29" s="519" t="n"/>
-      <c r="P29" s="520" t="inlineStr">
+      <c r="L29" s="563" t="n"/>
+      <c r="M29" s="563" t="n"/>
+      <c r="N29" s="563" t="n"/>
+      <c r="P29" s="564" t="inlineStr">
         <is>
           <t>MC24</t>
         </is>
       </c>
-      <c r="Q29" s="521" t="n"/>
-      <c r="R29" s="521" t="n"/>
-      <c r="S29" s="521" t="n"/>
+      <c r="Q29" s="565" t="n"/>
+      <c r="R29" s="565" t="n"/>
+      <c r="S29" s="565" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="515" t="n"/>
-      <c r="B30" s="515" t="n"/>
-      <c r="C30" s="515" t="n"/>
-      <c r="D30" s="515" t="n"/>
-      <c r="F30" s="517" t="n"/>
-      <c r="G30" s="517" t="n"/>
-      <c r="H30" s="517" t="n"/>
-      <c r="I30" s="517" t="n"/>
-      <c r="K30" s="519" t="n"/>
-      <c r="L30" s="519" t="n"/>
-      <c r="M30" s="519" t="n"/>
-      <c r="N30" s="519" t="n"/>
-      <c r="P30" s="521" t="n"/>
-      <c r="Q30" s="521" t="n"/>
-      <c r="R30" s="521" t="n"/>
-      <c r="S30" s="521" t="n"/>
+      <c r="A30" s="559" t="n"/>
+      <c r="B30" s="559" t="n"/>
+      <c r="C30" s="559" t="n"/>
+      <c r="D30" s="559" t="n"/>
+      <c r="F30" s="561" t="n"/>
+      <c r="G30" s="561" t="n"/>
+      <c r="H30" s="561" t="n"/>
+      <c r="I30" s="561" t="n"/>
+      <c r="K30" s="563" t="n"/>
+      <c r="L30" s="563" t="n"/>
+      <c r="M30" s="563" t="n"/>
+      <c r="N30" s="563" t="n"/>
+      <c r="P30" s="565" t="n"/>
+      <c r="Q30" s="565" t="n"/>
+      <c r="R30" s="565" t="n"/>
+      <c r="S30" s="565" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -22386,56 +22584,56 @@
       <c r="S33" s="15" t="n"/>
     </row>
     <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="522" t="inlineStr">
+      <c r="A34" s="566" t="inlineStr">
         <is>
           <t>MC25</t>
         </is>
       </c>
-      <c r="B34" s="523" t="n"/>
-      <c r="C34" s="523" t="n"/>
-      <c r="D34" s="523" t="n"/>
-      <c r="F34" s="524" t="inlineStr">
+      <c r="B34" s="567" t="n"/>
+      <c r="C34" s="567" t="n"/>
+      <c r="D34" s="567" t="n"/>
+      <c r="F34" s="568" t="inlineStr">
         <is>
           <t>MC26</t>
         </is>
       </c>
-      <c r="G34" s="525" t="n"/>
-      <c r="H34" s="525" t="n"/>
-      <c r="I34" s="525" t="n"/>
-      <c r="K34" s="526" t="inlineStr">
+      <c r="G34" s="569" t="n"/>
+      <c r="H34" s="569" t="n"/>
+      <c r="I34" s="569" t="n"/>
+      <c r="K34" s="570" t="inlineStr">
         <is>
           <t>MC27</t>
         </is>
       </c>
-      <c r="L34" s="527" t="n"/>
-      <c r="M34" s="527" t="n"/>
-      <c r="N34" s="527" t="n"/>
-      <c r="P34" s="528" t="inlineStr">
+      <c r="L34" s="571" t="n"/>
+      <c r="M34" s="571" t="n"/>
+      <c r="N34" s="571" t="n"/>
+      <c r="P34" s="572" t="inlineStr">
         <is>
           <t>MC28</t>
         </is>
       </c>
-      <c r="Q34" s="529" t="n"/>
-      <c r="R34" s="529" t="n"/>
-      <c r="S34" s="529" t="n"/>
+      <c r="Q34" s="573" t="n"/>
+      <c r="R34" s="573" t="n"/>
+      <c r="S34" s="573" t="n"/>
     </row>
     <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="523" t="n"/>
-      <c r="B35" s="523" t="n"/>
-      <c r="C35" s="523" t="n"/>
-      <c r="D35" s="523" t="n"/>
-      <c r="F35" s="525" t="n"/>
-      <c r="G35" s="525" t="n"/>
-      <c r="H35" s="525" t="n"/>
-      <c r="I35" s="525" t="n"/>
-      <c r="K35" s="527" t="n"/>
-      <c r="L35" s="527" t="n"/>
-      <c r="M35" s="527" t="n"/>
-      <c r="N35" s="527" t="n"/>
-      <c r="P35" s="529" t="n"/>
-      <c r="Q35" s="529" t="n"/>
-      <c r="R35" s="529" t="n"/>
-      <c r="S35" s="529" t="n"/>
+      <c r="A35" s="567" t="n"/>
+      <c r="B35" s="567" t="n"/>
+      <c r="C35" s="567" t="n"/>
+      <c r="D35" s="567" t="n"/>
+      <c r="F35" s="569" t="n"/>
+      <c r="G35" s="569" t="n"/>
+      <c r="H35" s="569" t="n"/>
+      <c r="I35" s="569" t="n"/>
+      <c r="K35" s="571" t="n"/>
+      <c r="L35" s="571" t="n"/>
+      <c r="M35" s="571" t="n"/>
+      <c r="N35" s="571" t="n"/>
+      <c r="P35" s="573" t="n"/>
+      <c r="Q35" s="573" t="n"/>
+      <c r="R35" s="573" t="n"/>
+      <c r="S35" s="573" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -22540,20 +22738,20 @@
       <c r="S38" s="15" t="n"/>
     </row>
     <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="530" t="inlineStr">
+      <c r="A39" s="574" t="inlineStr">
         <is>
           <t>MC29</t>
         </is>
       </c>
-      <c r="B39" s="531" t="n"/>
-      <c r="C39" s="531" t="n"/>
-      <c r="D39" s="531" t="n"/>
+      <c r="B39" s="575" t="n"/>
+      <c r="C39" s="575" t="n"/>
+      <c r="D39" s="575" t="n"/>
     </row>
     <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="531" t="n"/>
-      <c r="B40" s="531" t="n"/>
-      <c r="C40" s="531" t="n"/>
-      <c r="D40" s="531" t="n"/>
+      <c r="A40" s="575" t="n"/>
+      <c r="B40" s="575" t="n"/>
+      <c r="C40" s="575" t="n"/>
+      <c r="D40" s="575" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">

--- a/artkal-c197-m221-418-official/colors.xlsx
+++ b/artkal-c197-m221-418-official/colors.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="信息" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="01_C" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="02_CE" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="03_CG" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="04_CP" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="05_CT" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="06_MA" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="07_MB" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="08_MC" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="09_MD" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="10_ME" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="11_MF" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="12_MG" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="13_MH" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="14_MM" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="信息" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_C" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_CE" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_CG" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_CP" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_CT" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_MA" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_MB" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_MC" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_MD" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_ME" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_MF" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_MG" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_MH" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_MM" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -64,7 +64,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="417">
+  <fills count="418">
     <fill>
       <patternFill/>
     </fill>
@@ -1013,47 +1013,52 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6C6D2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE664A6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6875C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4C764"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF32B195"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF757DD1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB1DC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5688A0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6B849D"/>
+        <fgColor rgb="FFE2E2E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0E0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B1D2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAC3AD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1E3B1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98D8CA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBABEE8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA6D8ED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC3CF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5C1CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -2173,7 +2178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="838">
+  <cellXfs count="836">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2941,12 +2946,9 @@
     <xf numFmtId="0" fontId="5" fillId="190" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="191" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="190" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="191" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="191" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="192" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="191" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="192" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2954,23 +2956,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="193" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="194" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="194" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="195" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="195" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="196" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="196" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="197" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="197" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="198" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="198" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="198" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3026,11 +3019,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="211" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="212" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="212" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="212" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="213" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="213" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="213" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3102,7 +3095,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="230" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="231" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="231" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="231" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3114,11 +3107,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="233" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="234" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="234" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="234" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="235" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="235" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="235" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3126,7 +3119,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="236" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="237" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="237" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="237" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3134,19 +3127,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="238" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="239" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="239" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="239" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="240" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="240" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="240" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="241" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="241" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="241" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="242" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="242" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="242" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3158,7 +3151,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="244" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="245" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="245" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="245" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3170,11 +3163,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="247" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="248" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="248" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="248" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="249" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="249" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="249" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3182,7 +3175,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="250" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="251" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="251" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="251" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3218,7 +3211,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="259" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="260" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="260" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="260" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3242,11 +3235,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="265" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="266" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="266" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="266" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="267" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="267" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="267" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3254,7 +3247,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="268" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="269" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="269" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="269" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3262,7 +3255,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="270" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="271" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="271" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="271" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3270,11 +3263,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="272" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="273" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="273" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="273" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="274" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="274" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="274" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3286,7 +3279,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="276" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="277" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="277" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="277" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3306,11 +3299,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="281" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="282" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="282" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="282" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="283" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="283" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="283" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3318,7 +3311,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="284" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="285" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="285" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="285" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3342,15 +3335,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="290" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="291" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="291" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="291" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="292" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="292" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="292" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="293" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="293" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="293" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3358,11 +3351,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="294" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="295" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="295" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="295" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="296" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="296" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="296" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3370,7 +3363,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="297" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="298" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="298" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="298" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3382,7 +3375,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="300" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="301" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="301" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="301" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3398,7 +3391,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="304" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="305" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="305" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="305" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3410,11 +3403,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="307" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="308" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="308" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="308" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="309" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="309" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="309" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3422,7 +3415,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="310" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="311" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="311" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="311" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3442,7 +3435,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="315" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="316" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="316" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="316" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3454,7 +3447,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="318" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="319" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="319" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="319" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3462,11 +3455,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="320" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="321" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="321" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="321" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="322" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="322" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="322" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3474,11 +3467,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="323" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="324" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="324" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="324" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="325" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="325" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="325" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3510,7 +3503,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="332" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="333" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="333" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="333" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3518,7 +3511,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="334" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="335" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="335" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="335" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3526,7 +3519,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="336" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="337" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="337" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="337" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3554,11 +3547,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="343" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="344" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="344" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="344" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="345" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="345" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="345" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3574,15 +3567,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="348" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="349" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="349" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="349" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="350" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="350" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="350" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="351" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="351" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="351" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3590,7 +3583,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="352" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="353" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="353" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="353" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3598,7 +3591,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="354" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="355" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="355" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="355" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3618,11 +3611,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="359" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="360" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="360" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="360" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="361" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="361" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="361" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3646,7 +3639,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="366" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="367" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="367" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="367" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3654,15 +3647,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="368" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="369" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="369" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="369" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="370" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="370" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="370" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="371" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="371" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="371" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3670,7 +3663,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="372" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="373" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="373" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="373" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3678,7 +3671,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="374" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="375" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="375" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="375" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3686,11 +3679,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="376" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="377" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="377" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="377" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="378" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="378" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="378" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3698,11 +3691,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="379" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="380" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="380" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="380" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="381" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="381" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="381" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3710,7 +3703,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="382" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="383" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="383" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="383" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3722,7 +3715,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="385" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="386" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="386" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="386" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3754,11 +3747,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="393" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="394" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="394" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="394" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="395" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="395" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="395" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3790,7 +3783,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="402" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="403" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="403" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="403" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3798,7 +3791,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="404" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="405" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="405" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="405" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3814,11 +3807,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="408" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="409" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="409" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="409" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="410" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="410" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="410" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3830,22 +3823,26 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="412" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="413" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="413" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="413" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="414" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="414" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="414" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="415" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="415" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="415" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="416" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="416" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="416" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="417" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="417" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4407,56 +4404,56 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="576" t="inlineStr">
+      <c r="A4" s="574" t="inlineStr">
         <is>
           <t>MD1</t>
         </is>
       </c>
-      <c r="B4" s="577" t="n"/>
-      <c r="C4" s="577" t="n"/>
-      <c r="D4" s="577" t="n"/>
-      <c r="F4" s="578" t="inlineStr">
+      <c r="B4" s="575" t="n"/>
+      <c r="C4" s="575" t="n"/>
+      <c r="D4" s="575" t="n"/>
+      <c r="F4" s="576" t="inlineStr">
         <is>
           <t>MD2</t>
         </is>
       </c>
-      <c r="G4" s="579" t="n"/>
-      <c r="H4" s="579" t="n"/>
-      <c r="I4" s="579" t="n"/>
-      <c r="K4" s="580" t="inlineStr">
+      <c r="G4" s="577" t="n"/>
+      <c r="H4" s="577" t="n"/>
+      <c r="I4" s="577" t="n"/>
+      <c r="K4" s="578" t="inlineStr">
         <is>
           <t>MD3</t>
         </is>
       </c>
-      <c r="L4" s="581" t="n"/>
-      <c r="M4" s="581" t="n"/>
-      <c r="N4" s="581" t="n"/>
-      <c r="P4" s="582" t="inlineStr">
+      <c r="L4" s="579" t="n"/>
+      <c r="M4" s="579" t="n"/>
+      <c r="N4" s="579" t="n"/>
+      <c r="P4" s="580" t="inlineStr">
         <is>
           <t>MD4</t>
         </is>
       </c>
-      <c r="Q4" s="583" t="n"/>
-      <c r="R4" s="583" t="n"/>
-      <c r="S4" s="583" t="n"/>
+      <c r="Q4" s="581" t="n"/>
+      <c r="R4" s="581" t="n"/>
+      <c r="S4" s="581" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="577" t="n"/>
-      <c r="B5" s="577" t="n"/>
-      <c r="C5" s="577" t="n"/>
-      <c r="D5" s="577" t="n"/>
-      <c r="F5" s="579" t="n"/>
-      <c r="G5" s="579" t="n"/>
-      <c r="H5" s="579" t="n"/>
-      <c r="I5" s="579" t="n"/>
-      <c r="K5" s="581" t="n"/>
-      <c r="L5" s="581" t="n"/>
-      <c r="M5" s="581" t="n"/>
-      <c r="N5" s="581" t="n"/>
-      <c r="P5" s="583" t="n"/>
-      <c r="Q5" s="583" t="n"/>
-      <c r="R5" s="583" t="n"/>
-      <c r="S5" s="583" t="n"/>
+      <c r="A5" s="575" t="n"/>
+      <c r="B5" s="575" t="n"/>
+      <c r="C5" s="575" t="n"/>
+      <c r="D5" s="575" t="n"/>
+      <c r="F5" s="577" t="n"/>
+      <c r="G5" s="577" t="n"/>
+      <c r="H5" s="577" t="n"/>
+      <c r="I5" s="577" t="n"/>
+      <c r="K5" s="579" t="n"/>
+      <c r="L5" s="579" t="n"/>
+      <c r="M5" s="579" t="n"/>
+      <c r="N5" s="579" t="n"/>
+      <c r="P5" s="581" t="n"/>
+      <c r="Q5" s="581" t="n"/>
+      <c r="R5" s="581" t="n"/>
+      <c r="S5" s="581" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -4561,56 +4558,56 @@
       <c r="S8" s="15" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="584" t="inlineStr">
+      <c r="A9" s="582" t="inlineStr">
         <is>
           <t>MD5</t>
         </is>
       </c>
-      <c r="B9" s="585" t="n"/>
-      <c r="C9" s="585" t="n"/>
-      <c r="D9" s="585" t="n"/>
-      <c r="F9" s="586" t="inlineStr">
+      <c r="B9" s="583" t="n"/>
+      <c r="C9" s="583" t="n"/>
+      <c r="D9" s="583" t="n"/>
+      <c r="F9" s="584" t="inlineStr">
         <is>
           <t>MD6</t>
         </is>
       </c>
-      <c r="G9" s="587" t="n"/>
-      <c r="H9" s="587" t="n"/>
-      <c r="I9" s="587" t="n"/>
-      <c r="K9" s="588" t="inlineStr">
+      <c r="G9" s="585" t="n"/>
+      <c r="H9" s="585" t="n"/>
+      <c r="I9" s="585" t="n"/>
+      <c r="K9" s="586" t="inlineStr">
         <is>
           <t>MD7</t>
         </is>
       </c>
-      <c r="L9" s="589" t="n"/>
-      <c r="M9" s="589" t="n"/>
-      <c r="N9" s="589" t="n"/>
-      <c r="P9" s="590" t="inlineStr">
+      <c r="L9" s="587" t="n"/>
+      <c r="M9" s="587" t="n"/>
+      <c r="N9" s="587" t="n"/>
+      <c r="P9" s="588" t="inlineStr">
         <is>
           <t>MD8</t>
         </is>
       </c>
-      <c r="Q9" s="591" t="n"/>
-      <c r="R9" s="591" t="n"/>
-      <c r="S9" s="591" t="n"/>
+      <c r="Q9" s="589" t="n"/>
+      <c r="R9" s="589" t="n"/>
+      <c r="S9" s="589" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="585" t="n"/>
-      <c r="B10" s="585" t="n"/>
-      <c r="C10" s="585" t="n"/>
-      <c r="D10" s="585" t="n"/>
-      <c r="F10" s="587" t="n"/>
-      <c r="G10" s="587" t="n"/>
-      <c r="H10" s="587" t="n"/>
-      <c r="I10" s="587" t="n"/>
-      <c r="K10" s="589" t="n"/>
-      <c r="L10" s="589" t="n"/>
-      <c r="M10" s="589" t="n"/>
-      <c r="N10" s="589" t="n"/>
-      <c r="P10" s="591" t="n"/>
-      <c r="Q10" s="591" t="n"/>
-      <c r="R10" s="591" t="n"/>
-      <c r="S10" s="591" t="n"/>
+      <c r="A10" s="583" t="n"/>
+      <c r="B10" s="583" t="n"/>
+      <c r="C10" s="583" t="n"/>
+      <c r="D10" s="583" t="n"/>
+      <c r="F10" s="585" t="n"/>
+      <c r="G10" s="585" t="n"/>
+      <c r="H10" s="585" t="n"/>
+      <c r="I10" s="585" t="n"/>
+      <c r="K10" s="587" t="n"/>
+      <c r="L10" s="587" t="n"/>
+      <c r="M10" s="587" t="n"/>
+      <c r="N10" s="587" t="n"/>
+      <c r="P10" s="589" t="n"/>
+      <c r="Q10" s="589" t="n"/>
+      <c r="R10" s="589" t="n"/>
+      <c r="S10" s="589" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -4715,56 +4712,56 @@
       <c r="S13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="592" t="inlineStr">
+      <c r="A14" s="590" t="inlineStr">
         <is>
           <t>MD9</t>
         </is>
       </c>
-      <c r="B14" s="593" t="n"/>
-      <c r="C14" s="593" t="n"/>
-      <c r="D14" s="593" t="n"/>
-      <c r="F14" s="594" t="inlineStr">
+      <c r="B14" s="591" t="n"/>
+      <c r="C14" s="591" t="n"/>
+      <c r="D14" s="591" t="n"/>
+      <c r="F14" s="592" t="inlineStr">
         <is>
           <t>MD10</t>
         </is>
       </c>
-      <c r="G14" s="595" t="n"/>
-      <c r="H14" s="595" t="n"/>
-      <c r="I14" s="595" t="n"/>
-      <c r="K14" s="596" t="inlineStr">
+      <c r="G14" s="593" t="n"/>
+      <c r="H14" s="593" t="n"/>
+      <c r="I14" s="593" t="n"/>
+      <c r="K14" s="594" t="inlineStr">
         <is>
           <t>MD11</t>
         </is>
       </c>
-      <c r="L14" s="597" t="n"/>
-      <c r="M14" s="597" t="n"/>
-      <c r="N14" s="597" t="n"/>
-      <c r="P14" s="598" t="inlineStr">
+      <c r="L14" s="595" t="n"/>
+      <c r="M14" s="595" t="n"/>
+      <c r="N14" s="595" t="n"/>
+      <c r="P14" s="596" t="inlineStr">
         <is>
           <t>MD12</t>
         </is>
       </c>
-      <c r="Q14" s="599" t="n"/>
-      <c r="R14" s="599" t="n"/>
-      <c r="S14" s="599" t="n"/>
+      <c r="Q14" s="597" t="n"/>
+      <c r="R14" s="597" t="n"/>
+      <c r="S14" s="597" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="593" t="n"/>
-      <c r="B15" s="593" t="n"/>
-      <c r="C15" s="593" t="n"/>
-      <c r="D15" s="593" t="n"/>
-      <c r="F15" s="595" t="n"/>
-      <c r="G15" s="595" t="n"/>
-      <c r="H15" s="595" t="n"/>
-      <c r="I15" s="595" t="n"/>
-      <c r="K15" s="597" t="n"/>
-      <c r="L15" s="597" t="n"/>
-      <c r="M15" s="597" t="n"/>
-      <c r="N15" s="597" t="n"/>
-      <c r="P15" s="599" t="n"/>
-      <c r="Q15" s="599" t="n"/>
-      <c r="R15" s="599" t="n"/>
-      <c r="S15" s="599" t="n"/>
+      <c r="A15" s="591" t="n"/>
+      <c r="B15" s="591" t="n"/>
+      <c r="C15" s="591" t="n"/>
+      <c r="D15" s="591" t="n"/>
+      <c r="F15" s="593" t="n"/>
+      <c r="G15" s="593" t="n"/>
+      <c r="H15" s="593" t="n"/>
+      <c r="I15" s="593" t="n"/>
+      <c r="K15" s="595" t="n"/>
+      <c r="L15" s="595" t="n"/>
+      <c r="M15" s="595" t="n"/>
+      <c r="N15" s="595" t="n"/>
+      <c r="P15" s="597" t="n"/>
+      <c r="Q15" s="597" t="n"/>
+      <c r="R15" s="597" t="n"/>
+      <c r="S15" s="597" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -4869,56 +4866,56 @@
       <c r="S18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="600" t="inlineStr">
+      <c r="A19" s="598" t="inlineStr">
         <is>
           <t>MD13</t>
         </is>
       </c>
-      <c r="B19" s="601" t="n"/>
-      <c r="C19" s="601" t="n"/>
-      <c r="D19" s="601" t="n"/>
-      <c r="F19" s="602" t="inlineStr">
+      <c r="B19" s="599" t="n"/>
+      <c r="C19" s="599" t="n"/>
+      <c r="D19" s="599" t="n"/>
+      <c r="F19" s="600" t="inlineStr">
         <is>
           <t>MD14</t>
         </is>
       </c>
-      <c r="G19" s="603" t="n"/>
-      <c r="H19" s="603" t="n"/>
-      <c r="I19" s="603" t="n"/>
-      <c r="K19" s="604" t="inlineStr">
+      <c r="G19" s="601" t="n"/>
+      <c r="H19" s="601" t="n"/>
+      <c r="I19" s="601" t="n"/>
+      <c r="K19" s="602" t="inlineStr">
         <is>
           <t>MD15</t>
         </is>
       </c>
-      <c r="L19" s="605" t="n"/>
-      <c r="M19" s="605" t="n"/>
-      <c r="N19" s="605" t="n"/>
-      <c r="P19" s="606" t="inlineStr">
+      <c r="L19" s="603" t="n"/>
+      <c r="M19" s="603" t="n"/>
+      <c r="N19" s="603" t="n"/>
+      <c r="P19" s="604" t="inlineStr">
         <is>
           <t>MD16</t>
         </is>
       </c>
-      <c r="Q19" s="607" t="n"/>
-      <c r="R19" s="607" t="n"/>
-      <c r="S19" s="607" t="n"/>
+      <c r="Q19" s="605" t="n"/>
+      <c r="R19" s="605" t="n"/>
+      <c r="S19" s="605" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="601" t="n"/>
-      <c r="B20" s="601" t="n"/>
-      <c r="C20" s="601" t="n"/>
-      <c r="D20" s="601" t="n"/>
-      <c r="F20" s="603" t="n"/>
-      <c r="G20" s="603" t="n"/>
-      <c r="H20" s="603" t="n"/>
-      <c r="I20" s="603" t="n"/>
-      <c r="K20" s="605" t="n"/>
-      <c r="L20" s="605" t="n"/>
-      <c r="M20" s="605" t="n"/>
-      <c r="N20" s="605" t="n"/>
-      <c r="P20" s="607" t="n"/>
-      <c r="Q20" s="607" t="n"/>
-      <c r="R20" s="607" t="n"/>
-      <c r="S20" s="607" t="n"/>
+      <c r="A20" s="599" t="n"/>
+      <c r="B20" s="599" t="n"/>
+      <c r="C20" s="599" t="n"/>
+      <c r="D20" s="599" t="n"/>
+      <c r="F20" s="601" t="n"/>
+      <c r="G20" s="601" t="n"/>
+      <c r="H20" s="601" t="n"/>
+      <c r="I20" s="601" t="n"/>
+      <c r="K20" s="603" t="n"/>
+      <c r="L20" s="603" t="n"/>
+      <c r="M20" s="603" t="n"/>
+      <c r="N20" s="603" t="n"/>
+      <c r="P20" s="605" t="n"/>
+      <c r="Q20" s="605" t="n"/>
+      <c r="R20" s="605" t="n"/>
+      <c r="S20" s="605" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -5023,56 +5020,56 @@
       <c r="S23" s="15" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="608" t="inlineStr">
+      <c r="A24" s="606" t="inlineStr">
         <is>
           <t>MD17</t>
         </is>
       </c>
-      <c r="B24" s="609" t="n"/>
-      <c r="C24" s="609" t="n"/>
-      <c r="D24" s="609" t="n"/>
-      <c r="F24" s="610" t="inlineStr">
+      <c r="B24" s="607" t="n"/>
+      <c r="C24" s="607" t="n"/>
+      <c r="D24" s="607" t="n"/>
+      <c r="F24" s="608" t="inlineStr">
         <is>
           <t>MD18</t>
         </is>
       </c>
-      <c r="G24" s="611" t="n"/>
-      <c r="H24" s="611" t="n"/>
-      <c r="I24" s="611" t="n"/>
-      <c r="K24" s="612" t="inlineStr">
+      <c r="G24" s="609" t="n"/>
+      <c r="H24" s="609" t="n"/>
+      <c r="I24" s="609" t="n"/>
+      <c r="K24" s="610" t="inlineStr">
         <is>
           <t>MD19</t>
         </is>
       </c>
-      <c r="L24" s="613" t="n"/>
-      <c r="M24" s="613" t="n"/>
-      <c r="N24" s="613" t="n"/>
-      <c r="P24" s="614" t="inlineStr">
+      <c r="L24" s="611" t="n"/>
+      <c r="M24" s="611" t="n"/>
+      <c r="N24" s="611" t="n"/>
+      <c r="P24" s="612" t="inlineStr">
         <is>
           <t>MD20</t>
         </is>
       </c>
-      <c r="Q24" s="615" t="n"/>
-      <c r="R24" s="615" t="n"/>
-      <c r="S24" s="615" t="n"/>
+      <c r="Q24" s="613" t="n"/>
+      <c r="R24" s="613" t="n"/>
+      <c r="S24" s="613" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="609" t="n"/>
-      <c r="B25" s="609" t="n"/>
-      <c r="C25" s="609" t="n"/>
-      <c r="D25" s="609" t="n"/>
-      <c r="F25" s="611" t="n"/>
-      <c r="G25" s="611" t="n"/>
-      <c r="H25" s="611" t="n"/>
-      <c r="I25" s="611" t="n"/>
-      <c r="K25" s="613" t="n"/>
-      <c r="L25" s="613" t="n"/>
-      <c r="M25" s="613" t="n"/>
-      <c r="N25" s="613" t="n"/>
-      <c r="P25" s="615" t="n"/>
-      <c r="Q25" s="615" t="n"/>
-      <c r="R25" s="615" t="n"/>
-      <c r="S25" s="615" t="n"/>
+      <c r="A25" s="607" t="n"/>
+      <c r="B25" s="607" t="n"/>
+      <c r="C25" s="607" t="n"/>
+      <c r="D25" s="607" t="n"/>
+      <c r="F25" s="609" t="n"/>
+      <c r="G25" s="609" t="n"/>
+      <c r="H25" s="609" t="n"/>
+      <c r="I25" s="609" t="n"/>
+      <c r="K25" s="611" t="n"/>
+      <c r="L25" s="611" t="n"/>
+      <c r="M25" s="611" t="n"/>
+      <c r="N25" s="611" t="n"/>
+      <c r="P25" s="613" t="n"/>
+      <c r="Q25" s="613" t="n"/>
+      <c r="R25" s="613" t="n"/>
+      <c r="S25" s="613" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
@@ -5177,56 +5174,56 @@
       <c r="S28" s="15" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="616" t="inlineStr">
+      <c r="A29" s="614" t="inlineStr">
         <is>
           <t>MD21</t>
         </is>
       </c>
-      <c r="B29" s="617" t="n"/>
-      <c r="C29" s="617" t="n"/>
-      <c r="D29" s="617" t="n"/>
-      <c r="F29" s="618" t="inlineStr">
+      <c r="B29" s="615" t="n"/>
+      <c r="C29" s="615" t="n"/>
+      <c r="D29" s="615" t="n"/>
+      <c r="F29" s="616" t="inlineStr">
         <is>
           <t>MD22</t>
         </is>
       </c>
-      <c r="G29" s="619" t="n"/>
-      <c r="H29" s="619" t="n"/>
-      <c r="I29" s="619" t="n"/>
-      <c r="K29" s="620" t="inlineStr">
+      <c r="G29" s="617" t="n"/>
+      <c r="H29" s="617" t="n"/>
+      <c r="I29" s="617" t="n"/>
+      <c r="K29" s="618" t="inlineStr">
         <is>
           <t>MD23</t>
         </is>
       </c>
-      <c r="L29" s="621" t="n"/>
-      <c r="M29" s="621" t="n"/>
-      <c r="N29" s="621" t="n"/>
-      <c r="P29" s="622" t="inlineStr">
+      <c r="L29" s="619" t="n"/>
+      <c r="M29" s="619" t="n"/>
+      <c r="N29" s="619" t="n"/>
+      <c r="P29" s="620" t="inlineStr">
         <is>
           <t>MD24</t>
         </is>
       </c>
-      <c r="Q29" s="623" t="n"/>
-      <c r="R29" s="623" t="n"/>
-      <c r="S29" s="623" t="n"/>
+      <c r="Q29" s="621" t="n"/>
+      <c r="R29" s="621" t="n"/>
+      <c r="S29" s="621" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="617" t="n"/>
-      <c r="B30" s="617" t="n"/>
-      <c r="C30" s="617" t="n"/>
-      <c r="D30" s="617" t="n"/>
-      <c r="F30" s="619" t="n"/>
-      <c r="G30" s="619" t="n"/>
-      <c r="H30" s="619" t="n"/>
-      <c r="I30" s="619" t="n"/>
-      <c r="K30" s="621" t="n"/>
-      <c r="L30" s="621" t="n"/>
-      <c r="M30" s="621" t="n"/>
-      <c r="N30" s="621" t="n"/>
-      <c r="P30" s="623" t="n"/>
-      <c r="Q30" s="623" t="n"/>
-      <c r="R30" s="623" t="n"/>
-      <c r="S30" s="623" t="n"/>
+      <c r="A30" s="615" t="n"/>
+      <c r="B30" s="615" t="n"/>
+      <c r="C30" s="615" t="n"/>
+      <c r="D30" s="615" t="n"/>
+      <c r="F30" s="617" t="n"/>
+      <c r="G30" s="617" t="n"/>
+      <c r="H30" s="617" t="n"/>
+      <c r="I30" s="617" t="n"/>
+      <c r="K30" s="619" t="n"/>
+      <c r="L30" s="619" t="n"/>
+      <c r="M30" s="619" t="n"/>
+      <c r="N30" s="619" t="n"/>
+      <c r="P30" s="621" t="n"/>
+      <c r="Q30" s="621" t="n"/>
+      <c r="R30" s="621" t="n"/>
+      <c r="S30" s="621" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -5331,32 +5328,32 @@
       <c r="S33" s="15" t="n"/>
     </row>
     <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="624" t="inlineStr">
+      <c r="A34" s="622" t="inlineStr">
         <is>
           <t>MD25</t>
         </is>
       </c>
-      <c r="B34" s="625" t="n"/>
-      <c r="C34" s="625" t="n"/>
-      <c r="D34" s="625" t="n"/>
-      <c r="F34" s="626" t="inlineStr">
+      <c r="B34" s="623" t="n"/>
+      <c r="C34" s="623" t="n"/>
+      <c r="D34" s="623" t="n"/>
+      <c r="F34" s="624" t="inlineStr">
         <is>
           <t>MD26</t>
         </is>
       </c>
-      <c r="G34" s="627" t="n"/>
-      <c r="H34" s="627" t="n"/>
-      <c r="I34" s="627" t="n"/>
+      <c r="G34" s="625" t="n"/>
+      <c r="H34" s="625" t="n"/>
+      <c r="I34" s="625" t="n"/>
     </row>
     <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="625" t="n"/>
-      <c r="B35" s="625" t="n"/>
-      <c r="C35" s="625" t="n"/>
-      <c r="D35" s="625" t="n"/>
-      <c r="F35" s="627" t="n"/>
-      <c r="G35" s="627" t="n"/>
-      <c r="H35" s="627" t="n"/>
-      <c r="I35" s="627" t="n"/>
+      <c r="A35" s="623" t="n"/>
+      <c r="B35" s="623" t="n"/>
+      <c r="C35" s="623" t="n"/>
+      <c r="D35" s="623" t="n"/>
+      <c r="F35" s="625" t="n"/>
+      <c r="G35" s="625" t="n"/>
+      <c r="H35" s="625" t="n"/>
+      <c r="I35" s="625" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -5568,56 +5565,56 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="628" t="inlineStr">
+      <c r="A4" s="626" t="inlineStr">
         <is>
           <t>ME1</t>
         </is>
       </c>
-      <c r="B4" s="629" t="n"/>
-      <c r="C4" s="629" t="n"/>
-      <c r="D4" s="629" t="n"/>
-      <c r="F4" s="630" t="inlineStr">
+      <c r="B4" s="627" t="n"/>
+      <c r="C4" s="627" t="n"/>
+      <c r="D4" s="627" t="n"/>
+      <c r="F4" s="628" t="inlineStr">
         <is>
           <t>ME2</t>
         </is>
       </c>
-      <c r="G4" s="631" t="n"/>
-      <c r="H4" s="631" t="n"/>
-      <c r="I4" s="631" t="n"/>
-      <c r="K4" s="632" t="inlineStr">
+      <c r="G4" s="629" t="n"/>
+      <c r="H4" s="629" t="n"/>
+      <c r="I4" s="629" t="n"/>
+      <c r="K4" s="630" t="inlineStr">
         <is>
           <t>ME3</t>
         </is>
       </c>
-      <c r="L4" s="633" t="n"/>
-      <c r="M4" s="633" t="n"/>
-      <c r="N4" s="633" t="n"/>
-      <c r="P4" s="634" t="inlineStr">
+      <c r="L4" s="631" t="n"/>
+      <c r="M4" s="631" t="n"/>
+      <c r="N4" s="631" t="n"/>
+      <c r="P4" s="632" t="inlineStr">
         <is>
           <t>ME4</t>
         </is>
       </c>
-      <c r="Q4" s="635" t="n"/>
-      <c r="R4" s="635" t="n"/>
-      <c r="S4" s="635" t="n"/>
+      <c r="Q4" s="633" t="n"/>
+      <c r="R4" s="633" t="n"/>
+      <c r="S4" s="633" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="629" t="n"/>
-      <c r="B5" s="629" t="n"/>
-      <c r="C5" s="629" t="n"/>
-      <c r="D5" s="629" t="n"/>
-      <c r="F5" s="631" t="n"/>
-      <c r="G5" s="631" t="n"/>
-      <c r="H5" s="631" t="n"/>
-      <c r="I5" s="631" t="n"/>
-      <c r="K5" s="633" t="n"/>
-      <c r="L5" s="633" t="n"/>
-      <c r="M5" s="633" t="n"/>
-      <c r="N5" s="633" t="n"/>
-      <c r="P5" s="635" t="n"/>
-      <c r="Q5" s="635" t="n"/>
-      <c r="R5" s="635" t="n"/>
-      <c r="S5" s="635" t="n"/>
+      <c r="A5" s="627" t="n"/>
+      <c r="B5" s="627" t="n"/>
+      <c r="C5" s="627" t="n"/>
+      <c r="D5" s="627" t="n"/>
+      <c r="F5" s="629" t="n"/>
+      <c r="G5" s="629" t="n"/>
+      <c r="H5" s="629" t="n"/>
+      <c r="I5" s="629" t="n"/>
+      <c r="K5" s="631" t="n"/>
+      <c r="L5" s="631" t="n"/>
+      <c r="M5" s="631" t="n"/>
+      <c r="N5" s="631" t="n"/>
+      <c r="P5" s="633" t="n"/>
+      <c r="Q5" s="633" t="n"/>
+      <c r="R5" s="633" t="n"/>
+      <c r="S5" s="633" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -5722,56 +5719,56 @@
       <c r="S8" s="15" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="636" t="inlineStr">
+      <c r="A9" s="634" t="inlineStr">
         <is>
           <t>ME5</t>
         </is>
       </c>
-      <c r="B9" s="637" t="n"/>
-      <c r="C9" s="637" t="n"/>
-      <c r="D9" s="637" t="n"/>
-      <c r="F9" s="638" t="inlineStr">
+      <c r="B9" s="635" t="n"/>
+      <c r="C9" s="635" t="n"/>
+      <c r="D9" s="635" t="n"/>
+      <c r="F9" s="636" t="inlineStr">
         <is>
           <t>ME6</t>
         </is>
       </c>
-      <c r="G9" s="639" t="n"/>
-      <c r="H9" s="639" t="n"/>
-      <c r="I9" s="639" t="n"/>
-      <c r="K9" s="640" t="inlineStr">
+      <c r="G9" s="637" t="n"/>
+      <c r="H9" s="637" t="n"/>
+      <c r="I9" s="637" t="n"/>
+      <c r="K9" s="638" t="inlineStr">
         <is>
           <t>ME7</t>
         </is>
       </c>
-      <c r="L9" s="641" t="n"/>
-      <c r="M9" s="641" t="n"/>
-      <c r="N9" s="641" t="n"/>
-      <c r="P9" s="642" t="inlineStr">
+      <c r="L9" s="639" t="n"/>
+      <c r="M9" s="639" t="n"/>
+      <c r="N9" s="639" t="n"/>
+      <c r="P9" s="640" t="inlineStr">
         <is>
           <t>ME8</t>
         </is>
       </c>
-      <c r="Q9" s="643" t="n"/>
-      <c r="R9" s="643" t="n"/>
-      <c r="S9" s="643" t="n"/>
+      <c r="Q9" s="641" t="n"/>
+      <c r="R9" s="641" t="n"/>
+      <c r="S9" s="641" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="637" t="n"/>
-      <c r="B10" s="637" t="n"/>
-      <c r="C10" s="637" t="n"/>
-      <c r="D10" s="637" t="n"/>
-      <c r="F10" s="639" t="n"/>
-      <c r="G10" s="639" t="n"/>
-      <c r="H10" s="639" t="n"/>
-      <c r="I10" s="639" t="n"/>
-      <c r="K10" s="641" t="n"/>
-      <c r="L10" s="641" t="n"/>
-      <c r="M10" s="641" t="n"/>
-      <c r="N10" s="641" t="n"/>
-      <c r="P10" s="643" t="n"/>
-      <c r="Q10" s="643" t="n"/>
-      <c r="R10" s="643" t="n"/>
-      <c r="S10" s="643" t="n"/>
+      <c r="A10" s="635" t="n"/>
+      <c r="B10" s="635" t="n"/>
+      <c r="C10" s="635" t="n"/>
+      <c r="D10" s="635" t="n"/>
+      <c r="F10" s="637" t="n"/>
+      <c r="G10" s="637" t="n"/>
+      <c r="H10" s="637" t="n"/>
+      <c r="I10" s="637" t="n"/>
+      <c r="K10" s="639" t="n"/>
+      <c r="L10" s="639" t="n"/>
+      <c r="M10" s="639" t="n"/>
+      <c r="N10" s="639" t="n"/>
+      <c r="P10" s="641" t="n"/>
+      <c r="Q10" s="641" t="n"/>
+      <c r="R10" s="641" t="n"/>
+      <c r="S10" s="641" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -5876,56 +5873,56 @@
       <c r="S13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="644" t="inlineStr">
+      <c r="A14" s="642" t="inlineStr">
         <is>
           <t>ME9</t>
         </is>
       </c>
-      <c r="B14" s="645" t="n"/>
-      <c r="C14" s="645" t="n"/>
-      <c r="D14" s="645" t="n"/>
-      <c r="F14" s="646" t="inlineStr">
+      <c r="B14" s="643" t="n"/>
+      <c r="C14" s="643" t="n"/>
+      <c r="D14" s="643" t="n"/>
+      <c r="F14" s="644" t="inlineStr">
         <is>
           <t>ME10</t>
         </is>
       </c>
-      <c r="G14" s="647" t="n"/>
-      <c r="H14" s="647" t="n"/>
-      <c r="I14" s="647" t="n"/>
-      <c r="K14" s="648" t="inlineStr">
+      <c r="G14" s="645" t="n"/>
+      <c r="H14" s="645" t="n"/>
+      <c r="I14" s="645" t="n"/>
+      <c r="K14" s="646" t="inlineStr">
         <is>
           <t>ME11</t>
         </is>
       </c>
-      <c r="L14" s="649" t="n"/>
-      <c r="M14" s="649" t="n"/>
-      <c r="N14" s="649" t="n"/>
-      <c r="P14" s="650" t="inlineStr">
+      <c r="L14" s="647" t="n"/>
+      <c r="M14" s="647" t="n"/>
+      <c r="N14" s="647" t="n"/>
+      <c r="P14" s="648" t="inlineStr">
         <is>
           <t>ME12</t>
         </is>
       </c>
-      <c r="Q14" s="651" t="n"/>
-      <c r="R14" s="651" t="n"/>
-      <c r="S14" s="651" t="n"/>
+      <c r="Q14" s="649" t="n"/>
+      <c r="R14" s="649" t="n"/>
+      <c r="S14" s="649" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="645" t="n"/>
-      <c r="B15" s="645" t="n"/>
-      <c r="C15" s="645" t="n"/>
-      <c r="D15" s="645" t="n"/>
-      <c r="F15" s="647" t="n"/>
-      <c r="G15" s="647" t="n"/>
-      <c r="H15" s="647" t="n"/>
-      <c r="I15" s="647" t="n"/>
-      <c r="K15" s="649" t="n"/>
-      <c r="L15" s="649" t="n"/>
-      <c r="M15" s="649" t="n"/>
-      <c r="N15" s="649" t="n"/>
-      <c r="P15" s="651" t="n"/>
-      <c r="Q15" s="651" t="n"/>
-      <c r="R15" s="651" t="n"/>
-      <c r="S15" s="651" t="n"/>
+      <c r="A15" s="643" t="n"/>
+      <c r="B15" s="643" t="n"/>
+      <c r="C15" s="643" t="n"/>
+      <c r="D15" s="643" t="n"/>
+      <c r="F15" s="645" t="n"/>
+      <c r="G15" s="645" t="n"/>
+      <c r="H15" s="645" t="n"/>
+      <c r="I15" s="645" t="n"/>
+      <c r="K15" s="647" t="n"/>
+      <c r="L15" s="647" t="n"/>
+      <c r="M15" s="647" t="n"/>
+      <c r="N15" s="647" t="n"/>
+      <c r="P15" s="649" t="n"/>
+      <c r="Q15" s="649" t="n"/>
+      <c r="R15" s="649" t="n"/>
+      <c r="S15" s="649" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -6030,56 +6027,56 @@
       <c r="S18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="652" t="inlineStr">
+      <c r="A19" s="650" t="inlineStr">
         <is>
           <t>ME13</t>
         </is>
       </c>
-      <c r="B19" s="653" t="n"/>
-      <c r="C19" s="653" t="n"/>
-      <c r="D19" s="653" t="n"/>
-      <c r="F19" s="654" t="inlineStr">
+      <c r="B19" s="651" t="n"/>
+      <c r="C19" s="651" t="n"/>
+      <c r="D19" s="651" t="n"/>
+      <c r="F19" s="652" t="inlineStr">
         <is>
           <t>ME14</t>
         </is>
       </c>
-      <c r="G19" s="655" t="n"/>
-      <c r="H19" s="655" t="n"/>
-      <c r="I19" s="655" t="n"/>
-      <c r="K19" s="656" t="inlineStr">
+      <c r="G19" s="653" t="n"/>
+      <c r="H19" s="653" t="n"/>
+      <c r="I19" s="653" t="n"/>
+      <c r="K19" s="654" t="inlineStr">
         <is>
           <t>ME15</t>
         </is>
       </c>
-      <c r="L19" s="657" t="n"/>
-      <c r="M19" s="657" t="n"/>
-      <c r="N19" s="657" t="n"/>
-      <c r="P19" s="658" t="inlineStr">
+      <c r="L19" s="655" t="n"/>
+      <c r="M19" s="655" t="n"/>
+      <c r="N19" s="655" t="n"/>
+      <c r="P19" s="656" t="inlineStr">
         <is>
           <t>ME16</t>
         </is>
       </c>
-      <c r="Q19" s="659" t="n"/>
-      <c r="R19" s="659" t="n"/>
-      <c r="S19" s="659" t="n"/>
+      <c r="Q19" s="657" t="n"/>
+      <c r="R19" s="657" t="n"/>
+      <c r="S19" s="657" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="653" t="n"/>
-      <c r="B20" s="653" t="n"/>
-      <c r="C20" s="653" t="n"/>
-      <c r="D20" s="653" t="n"/>
-      <c r="F20" s="655" t="n"/>
-      <c r="G20" s="655" t="n"/>
-      <c r="H20" s="655" t="n"/>
-      <c r="I20" s="655" t="n"/>
-      <c r="K20" s="657" t="n"/>
-      <c r="L20" s="657" t="n"/>
-      <c r="M20" s="657" t="n"/>
-      <c r="N20" s="657" t="n"/>
-      <c r="P20" s="659" t="n"/>
-      <c r="Q20" s="659" t="n"/>
-      <c r="R20" s="659" t="n"/>
-      <c r="S20" s="659" t="n"/>
+      <c r="A20" s="651" t="n"/>
+      <c r="B20" s="651" t="n"/>
+      <c r="C20" s="651" t="n"/>
+      <c r="D20" s="651" t="n"/>
+      <c r="F20" s="653" t="n"/>
+      <c r="G20" s="653" t="n"/>
+      <c r="H20" s="653" t="n"/>
+      <c r="I20" s="653" t="n"/>
+      <c r="K20" s="655" t="n"/>
+      <c r="L20" s="655" t="n"/>
+      <c r="M20" s="655" t="n"/>
+      <c r="N20" s="655" t="n"/>
+      <c r="P20" s="657" t="n"/>
+      <c r="Q20" s="657" t="n"/>
+      <c r="R20" s="657" t="n"/>
+      <c r="S20" s="657" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -6184,56 +6181,56 @@
       <c r="S23" s="15" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="660" t="inlineStr">
+      <c r="A24" s="658" t="inlineStr">
         <is>
           <t>ME17</t>
         </is>
       </c>
-      <c r="B24" s="661" t="n"/>
-      <c r="C24" s="661" t="n"/>
-      <c r="D24" s="661" t="n"/>
-      <c r="F24" s="662" t="inlineStr">
+      <c r="B24" s="659" t="n"/>
+      <c r="C24" s="659" t="n"/>
+      <c r="D24" s="659" t="n"/>
+      <c r="F24" s="660" t="inlineStr">
         <is>
           <t>ME18</t>
         </is>
       </c>
-      <c r="G24" s="663" t="n"/>
-      <c r="H24" s="663" t="n"/>
-      <c r="I24" s="663" t="n"/>
-      <c r="K24" s="664" t="inlineStr">
+      <c r="G24" s="661" t="n"/>
+      <c r="H24" s="661" t="n"/>
+      <c r="I24" s="661" t="n"/>
+      <c r="K24" s="662" t="inlineStr">
         <is>
           <t>ME19</t>
         </is>
       </c>
-      <c r="L24" s="665" t="n"/>
-      <c r="M24" s="665" t="n"/>
-      <c r="N24" s="665" t="n"/>
-      <c r="P24" s="666" t="inlineStr">
+      <c r="L24" s="663" t="n"/>
+      <c r="M24" s="663" t="n"/>
+      <c r="N24" s="663" t="n"/>
+      <c r="P24" s="664" t="inlineStr">
         <is>
           <t>ME20</t>
         </is>
       </c>
-      <c r="Q24" s="667" t="n"/>
-      <c r="R24" s="667" t="n"/>
-      <c r="S24" s="667" t="n"/>
+      <c r="Q24" s="665" t="n"/>
+      <c r="R24" s="665" t="n"/>
+      <c r="S24" s="665" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="661" t="n"/>
-      <c r="B25" s="661" t="n"/>
-      <c r="C25" s="661" t="n"/>
-      <c r="D25" s="661" t="n"/>
-      <c r="F25" s="663" t="n"/>
-      <c r="G25" s="663" t="n"/>
-      <c r="H25" s="663" t="n"/>
-      <c r="I25" s="663" t="n"/>
-      <c r="K25" s="665" t="n"/>
-      <c r="L25" s="665" t="n"/>
-      <c r="M25" s="665" t="n"/>
-      <c r="N25" s="665" t="n"/>
-      <c r="P25" s="667" t="n"/>
-      <c r="Q25" s="667" t="n"/>
-      <c r="R25" s="667" t="n"/>
-      <c r="S25" s="667" t="n"/>
+      <c r="A25" s="659" t="n"/>
+      <c r="B25" s="659" t="n"/>
+      <c r="C25" s="659" t="n"/>
+      <c r="D25" s="659" t="n"/>
+      <c r="F25" s="661" t="n"/>
+      <c r="G25" s="661" t="n"/>
+      <c r="H25" s="661" t="n"/>
+      <c r="I25" s="661" t="n"/>
+      <c r="K25" s="663" t="n"/>
+      <c r="L25" s="663" t="n"/>
+      <c r="M25" s="663" t="n"/>
+      <c r="N25" s="663" t="n"/>
+      <c r="P25" s="665" t="n"/>
+      <c r="Q25" s="665" t="n"/>
+      <c r="R25" s="665" t="n"/>
+      <c r="S25" s="665" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
@@ -6338,56 +6335,56 @@
       <c r="S28" s="15" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="668" t="inlineStr">
+      <c r="A29" s="666" t="inlineStr">
         <is>
           <t>ME21</t>
         </is>
       </c>
-      <c r="B29" s="669" t="n"/>
-      <c r="C29" s="669" t="n"/>
-      <c r="D29" s="669" t="n"/>
-      <c r="F29" s="670" t="inlineStr">
+      <c r="B29" s="667" t="n"/>
+      <c r="C29" s="667" t="n"/>
+      <c r="D29" s="667" t="n"/>
+      <c r="F29" s="668" t="inlineStr">
         <is>
           <t>ME22</t>
         </is>
       </c>
-      <c r="G29" s="671" t="n"/>
-      <c r="H29" s="671" t="n"/>
-      <c r="I29" s="671" t="n"/>
-      <c r="K29" s="672" t="inlineStr">
+      <c r="G29" s="669" t="n"/>
+      <c r="H29" s="669" t="n"/>
+      <c r="I29" s="669" t="n"/>
+      <c r="K29" s="670" t="inlineStr">
         <is>
           <t>ME23</t>
         </is>
       </c>
-      <c r="L29" s="673" t="n"/>
-      <c r="M29" s="673" t="n"/>
-      <c r="N29" s="673" t="n"/>
-      <c r="P29" s="674" t="inlineStr">
+      <c r="L29" s="671" t="n"/>
+      <c r="M29" s="671" t="n"/>
+      <c r="N29" s="671" t="n"/>
+      <c r="P29" s="672" t="inlineStr">
         <is>
           <t>ME24</t>
         </is>
       </c>
-      <c r="Q29" s="675" t="n"/>
-      <c r="R29" s="675" t="n"/>
-      <c r="S29" s="675" t="n"/>
+      <c r="Q29" s="673" t="n"/>
+      <c r="R29" s="673" t="n"/>
+      <c r="S29" s="673" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="669" t="n"/>
-      <c r="B30" s="669" t="n"/>
-      <c r="C30" s="669" t="n"/>
-      <c r="D30" s="669" t="n"/>
-      <c r="F30" s="671" t="n"/>
-      <c r="G30" s="671" t="n"/>
-      <c r="H30" s="671" t="n"/>
-      <c r="I30" s="671" t="n"/>
-      <c r="K30" s="673" t="n"/>
-      <c r="L30" s="673" t="n"/>
-      <c r="M30" s="673" t="n"/>
-      <c r="N30" s="673" t="n"/>
-      <c r="P30" s="675" t="n"/>
-      <c r="Q30" s="675" t="n"/>
-      <c r="R30" s="675" t="n"/>
-      <c r="S30" s="675" t="n"/>
+      <c r="A30" s="667" t="n"/>
+      <c r="B30" s="667" t="n"/>
+      <c r="C30" s="667" t="n"/>
+      <c r="D30" s="667" t="n"/>
+      <c r="F30" s="669" t="n"/>
+      <c r="G30" s="669" t="n"/>
+      <c r="H30" s="669" t="n"/>
+      <c r="I30" s="669" t="n"/>
+      <c r="K30" s="671" t="n"/>
+      <c r="L30" s="671" t="n"/>
+      <c r="M30" s="671" t="n"/>
+      <c r="N30" s="671" t="n"/>
+      <c r="P30" s="673" t="n"/>
+      <c r="Q30" s="673" t="n"/>
+      <c r="R30" s="673" t="n"/>
+      <c r="S30" s="673" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -6639,56 +6636,56 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="676" t="inlineStr">
+      <c r="A4" s="674" t="inlineStr">
         <is>
           <t>MF1</t>
         </is>
       </c>
-      <c r="B4" s="677" t="n"/>
-      <c r="C4" s="677" t="n"/>
-      <c r="D4" s="677" t="n"/>
-      <c r="F4" s="678" t="inlineStr">
+      <c r="B4" s="675" t="n"/>
+      <c r="C4" s="675" t="n"/>
+      <c r="D4" s="675" t="n"/>
+      <c r="F4" s="676" t="inlineStr">
         <is>
           <t>MF2</t>
         </is>
       </c>
-      <c r="G4" s="679" t="n"/>
-      <c r="H4" s="679" t="n"/>
-      <c r="I4" s="679" t="n"/>
-      <c r="K4" s="680" t="inlineStr">
+      <c r="G4" s="677" t="n"/>
+      <c r="H4" s="677" t="n"/>
+      <c r="I4" s="677" t="n"/>
+      <c r="K4" s="678" t="inlineStr">
         <is>
           <t>MF3</t>
         </is>
       </c>
-      <c r="L4" s="681" t="n"/>
-      <c r="M4" s="681" t="n"/>
-      <c r="N4" s="681" t="n"/>
-      <c r="P4" s="682" t="inlineStr">
+      <c r="L4" s="679" t="n"/>
+      <c r="M4" s="679" t="n"/>
+      <c r="N4" s="679" t="n"/>
+      <c r="P4" s="680" t="inlineStr">
         <is>
           <t>MF4</t>
         </is>
       </c>
-      <c r="Q4" s="683" t="n"/>
-      <c r="R4" s="683" t="n"/>
-      <c r="S4" s="683" t="n"/>
+      <c r="Q4" s="681" t="n"/>
+      <c r="R4" s="681" t="n"/>
+      <c r="S4" s="681" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="677" t="n"/>
-      <c r="B5" s="677" t="n"/>
-      <c r="C5" s="677" t="n"/>
-      <c r="D5" s="677" t="n"/>
-      <c r="F5" s="679" t="n"/>
-      <c r="G5" s="679" t="n"/>
-      <c r="H5" s="679" t="n"/>
-      <c r="I5" s="679" t="n"/>
-      <c r="K5" s="681" t="n"/>
-      <c r="L5" s="681" t="n"/>
-      <c r="M5" s="681" t="n"/>
-      <c r="N5" s="681" t="n"/>
-      <c r="P5" s="683" t="n"/>
-      <c r="Q5" s="683" t="n"/>
-      <c r="R5" s="683" t="n"/>
-      <c r="S5" s="683" t="n"/>
+      <c r="A5" s="675" t="n"/>
+      <c r="B5" s="675" t="n"/>
+      <c r="C5" s="675" t="n"/>
+      <c r="D5" s="675" t="n"/>
+      <c r="F5" s="677" t="n"/>
+      <c r="G5" s="677" t="n"/>
+      <c r="H5" s="677" t="n"/>
+      <c r="I5" s="677" t="n"/>
+      <c r="K5" s="679" t="n"/>
+      <c r="L5" s="679" t="n"/>
+      <c r="M5" s="679" t="n"/>
+      <c r="N5" s="679" t="n"/>
+      <c r="P5" s="681" t="n"/>
+      <c r="Q5" s="681" t="n"/>
+      <c r="R5" s="681" t="n"/>
+      <c r="S5" s="681" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -6793,56 +6790,56 @@
       <c r="S8" s="15" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="684" t="inlineStr">
+      <c r="A9" s="682" t="inlineStr">
         <is>
           <t>MF5</t>
         </is>
       </c>
-      <c r="B9" s="685" t="n"/>
-      <c r="C9" s="685" t="n"/>
-      <c r="D9" s="685" t="n"/>
-      <c r="F9" s="686" t="inlineStr">
+      <c r="B9" s="683" t="n"/>
+      <c r="C9" s="683" t="n"/>
+      <c r="D9" s="683" t="n"/>
+      <c r="F9" s="684" t="inlineStr">
         <is>
           <t>MF6</t>
         </is>
       </c>
-      <c r="G9" s="687" t="n"/>
-      <c r="H9" s="687" t="n"/>
-      <c r="I9" s="687" t="n"/>
-      <c r="K9" s="688" t="inlineStr">
+      <c r="G9" s="685" t="n"/>
+      <c r="H9" s="685" t="n"/>
+      <c r="I9" s="685" t="n"/>
+      <c r="K9" s="686" t="inlineStr">
         <is>
           <t>MF7</t>
         </is>
       </c>
-      <c r="L9" s="689" t="n"/>
-      <c r="M9" s="689" t="n"/>
-      <c r="N9" s="689" t="n"/>
-      <c r="P9" s="690" t="inlineStr">
+      <c r="L9" s="687" t="n"/>
+      <c r="M9" s="687" t="n"/>
+      <c r="N9" s="687" t="n"/>
+      <c r="P9" s="688" t="inlineStr">
         <is>
           <t>MF8</t>
         </is>
       </c>
-      <c r="Q9" s="691" t="n"/>
-      <c r="R9" s="691" t="n"/>
-      <c r="S9" s="691" t="n"/>
+      <c r="Q9" s="689" t="n"/>
+      <c r="R9" s="689" t="n"/>
+      <c r="S9" s="689" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="685" t="n"/>
-      <c r="B10" s="685" t="n"/>
-      <c r="C10" s="685" t="n"/>
-      <c r="D10" s="685" t="n"/>
-      <c r="F10" s="687" t="n"/>
-      <c r="G10" s="687" t="n"/>
-      <c r="H10" s="687" t="n"/>
-      <c r="I10" s="687" t="n"/>
-      <c r="K10" s="689" t="n"/>
-      <c r="L10" s="689" t="n"/>
-      <c r="M10" s="689" t="n"/>
-      <c r="N10" s="689" t="n"/>
-      <c r="P10" s="691" t="n"/>
-      <c r="Q10" s="691" t="n"/>
-      <c r="R10" s="691" t="n"/>
-      <c r="S10" s="691" t="n"/>
+      <c r="A10" s="683" t="n"/>
+      <c r="B10" s="683" t="n"/>
+      <c r="C10" s="683" t="n"/>
+      <c r="D10" s="683" t="n"/>
+      <c r="F10" s="685" t="n"/>
+      <c r="G10" s="685" t="n"/>
+      <c r="H10" s="685" t="n"/>
+      <c r="I10" s="685" t="n"/>
+      <c r="K10" s="687" t="n"/>
+      <c r="L10" s="687" t="n"/>
+      <c r="M10" s="687" t="n"/>
+      <c r="N10" s="687" t="n"/>
+      <c r="P10" s="689" t="n"/>
+      <c r="Q10" s="689" t="n"/>
+      <c r="R10" s="689" t="n"/>
+      <c r="S10" s="689" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -6947,56 +6944,56 @@
       <c r="S13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="692" t="inlineStr">
+      <c r="A14" s="690" t="inlineStr">
         <is>
           <t>MF9</t>
         </is>
       </c>
-      <c r="B14" s="693" t="n"/>
-      <c r="C14" s="693" t="n"/>
-      <c r="D14" s="693" t="n"/>
-      <c r="F14" s="694" t="inlineStr">
+      <c r="B14" s="691" t="n"/>
+      <c r="C14" s="691" t="n"/>
+      <c r="D14" s="691" t="n"/>
+      <c r="F14" s="692" t="inlineStr">
         <is>
           <t>MF10</t>
         </is>
       </c>
-      <c r="G14" s="695" t="n"/>
-      <c r="H14" s="695" t="n"/>
-      <c r="I14" s="695" t="n"/>
-      <c r="K14" s="696" t="inlineStr">
+      <c r="G14" s="693" t="n"/>
+      <c r="H14" s="693" t="n"/>
+      <c r="I14" s="693" t="n"/>
+      <c r="K14" s="694" t="inlineStr">
         <is>
           <t>MF11</t>
         </is>
       </c>
-      <c r="L14" s="697" t="n"/>
-      <c r="M14" s="697" t="n"/>
-      <c r="N14" s="697" t="n"/>
-      <c r="P14" s="698" t="inlineStr">
+      <c r="L14" s="695" t="n"/>
+      <c r="M14" s="695" t="n"/>
+      <c r="N14" s="695" t="n"/>
+      <c r="P14" s="696" t="inlineStr">
         <is>
           <t>MF12</t>
         </is>
       </c>
-      <c r="Q14" s="699" t="n"/>
-      <c r="R14" s="699" t="n"/>
-      <c r="S14" s="699" t="n"/>
+      <c r="Q14" s="697" t="n"/>
+      <c r="R14" s="697" t="n"/>
+      <c r="S14" s="697" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="693" t="n"/>
-      <c r="B15" s="693" t="n"/>
-      <c r="C15" s="693" t="n"/>
-      <c r="D15" s="693" t="n"/>
-      <c r="F15" s="695" t="n"/>
-      <c r="G15" s="695" t="n"/>
-      <c r="H15" s="695" t="n"/>
-      <c r="I15" s="695" t="n"/>
-      <c r="K15" s="697" t="n"/>
-      <c r="L15" s="697" t="n"/>
-      <c r="M15" s="697" t="n"/>
-      <c r="N15" s="697" t="n"/>
-      <c r="P15" s="699" t="n"/>
-      <c r="Q15" s="699" t="n"/>
-      <c r="R15" s="699" t="n"/>
-      <c r="S15" s="699" t="n"/>
+      <c r="A15" s="691" t="n"/>
+      <c r="B15" s="691" t="n"/>
+      <c r="C15" s="691" t="n"/>
+      <c r="D15" s="691" t="n"/>
+      <c r="F15" s="693" t="n"/>
+      <c r="G15" s="693" t="n"/>
+      <c r="H15" s="693" t="n"/>
+      <c r="I15" s="693" t="n"/>
+      <c r="K15" s="695" t="n"/>
+      <c r="L15" s="695" t="n"/>
+      <c r="M15" s="695" t="n"/>
+      <c r="N15" s="695" t="n"/>
+      <c r="P15" s="697" t="n"/>
+      <c r="Q15" s="697" t="n"/>
+      <c r="R15" s="697" t="n"/>
+      <c r="S15" s="697" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -7101,56 +7098,56 @@
       <c r="S18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="700" t="inlineStr">
+      <c r="A19" s="698" t="inlineStr">
         <is>
           <t>MF13</t>
         </is>
       </c>
-      <c r="B19" s="701" t="n"/>
-      <c r="C19" s="701" t="n"/>
-      <c r="D19" s="701" t="n"/>
-      <c r="F19" s="702" t="inlineStr">
+      <c r="B19" s="699" t="n"/>
+      <c r="C19" s="699" t="n"/>
+      <c r="D19" s="699" t="n"/>
+      <c r="F19" s="700" t="inlineStr">
         <is>
           <t>MF14</t>
         </is>
       </c>
-      <c r="G19" s="703" t="n"/>
-      <c r="H19" s="703" t="n"/>
-      <c r="I19" s="703" t="n"/>
-      <c r="K19" s="704" t="inlineStr">
+      <c r="G19" s="701" t="n"/>
+      <c r="H19" s="701" t="n"/>
+      <c r="I19" s="701" t="n"/>
+      <c r="K19" s="702" t="inlineStr">
         <is>
           <t>MF15</t>
         </is>
       </c>
-      <c r="L19" s="705" t="n"/>
-      <c r="M19" s="705" t="n"/>
-      <c r="N19" s="705" t="n"/>
-      <c r="P19" s="706" t="inlineStr">
+      <c r="L19" s="703" t="n"/>
+      <c r="M19" s="703" t="n"/>
+      <c r="N19" s="703" t="n"/>
+      <c r="P19" s="704" t="inlineStr">
         <is>
           <t>MF16</t>
         </is>
       </c>
-      <c r="Q19" s="707" t="n"/>
-      <c r="R19" s="707" t="n"/>
-      <c r="S19" s="707" t="n"/>
+      <c r="Q19" s="705" t="n"/>
+      <c r="R19" s="705" t="n"/>
+      <c r="S19" s="705" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="701" t="n"/>
-      <c r="B20" s="701" t="n"/>
-      <c r="C20" s="701" t="n"/>
-      <c r="D20" s="701" t="n"/>
-      <c r="F20" s="703" t="n"/>
-      <c r="G20" s="703" t="n"/>
-      <c r="H20" s="703" t="n"/>
-      <c r="I20" s="703" t="n"/>
-      <c r="K20" s="705" t="n"/>
-      <c r="L20" s="705" t="n"/>
-      <c r="M20" s="705" t="n"/>
-      <c r="N20" s="705" t="n"/>
-      <c r="P20" s="707" t="n"/>
-      <c r="Q20" s="707" t="n"/>
-      <c r="R20" s="707" t="n"/>
-      <c r="S20" s="707" t="n"/>
+      <c r="A20" s="699" t="n"/>
+      <c r="B20" s="699" t="n"/>
+      <c r="C20" s="699" t="n"/>
+      <c r="D20" s="699" t="n"/>
+      <c r="F20" s="701" t="n"/>
+      <c r="G20" s="701" t="n"/>
+      <c r="H20" s="701" t="n"/>
+      <c r="I20" s="701" t="n"/>
+      <c r="K20" s="703" t="n"/>
+      <c r="L20" s="703" t="n"/>
+      <c r="M20" s="703" t="n"/>
+      <c r="N20" s="703" t="n"/>
+      <c r="P20" s="705" t="n"/>
+      <c r="Q20" s="705" t="n"/>
+      <c r="R20" s="705" t="n"/>
+      <c r="S20" s="705" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -7255,56 +7252,56 @@
       <c r="S23" s="15" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="708" t="inlineStr">
+      <c r="A24" s="706" t="inlineStr">
         <is>
           <t>MF17</t>
         </is>
       </c>
-      <c r="B24" s="709" t="n"/>
-      <c r="C24" s="709" t="n"/>
-      <c r="D24" s="709" t="n"/>
-      <c r="F24" s="710" t="inlineStr">
+      <c r="B24" s="707" t="n"/>
+      <c r="C24" s="707" t="n"/>
+      <c r="D24" s="707" t="n"/>
+      <c r="F24" s="708" t="inlineStr">
         <is>
           <t>MF18</t>
         </is>
       </c>
-      <c r="G24" s="711" t="n"/>
-      <c r="H24" s="711" t="n"/>
-      <c r="I24" s="711" t="n"/>
-      <c r="K24" s="712" t="inlineStr">
+      <c r="G24" s="709" t="n"/>
+      <c r="H24" s="709" t="n"/>
+      <c r="I24" s="709" t="n"/>
+      <c r="K24" s="710" t="inlineStr">
         <is>
           <t>MF19</t>
         </is>
       </c>
-      <c r="L24" s="713" t="n"/>
-      <c r="M24" s="713" t="n"/>
-      <c r="N24" s="713" t="n"/>
-      <c r="P24" s="714" t="inlineStr">
+      <c r="L24" s="711" t="n"/>
+      <c r="M24" s="711" t="n"/>
+      <c r="N24" s="711" t="n"/>
+      <c r="P24" s="712" t="inlineStr">
         <is>
           <t>MF20</t>
         </is>
       </c>
-      <c r="Q24" s="715" t="n"/>
-      <c r="R24" s="715" t="n"/>
-      <c r="S24" s="715" t="n"/>
+      <c r="Q24" s="713" t="n"/>
+      <c r="R24" s="713" t="n"/>
+      <c r="S24" s="713" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="709" t="n"/>
-      <c r="B25" s="709" t="n"/>
-      <c r="C25" s="709" t="n"/>
-      <c r="D25" s="709" t="n"/>
-      <c r="F25" s="711" t="n"/>
-      <c r="G25" s="711" t="n"/>
-      <c r="H25" s="711" t="n"/>
-      <c r="I25" s="711" t="n"/>
-      <c r="K25" s="713" t="n"/>
-      <c r="L25" s="713" t="n"/>
-      <c r="M25" s="713" t="n"/>
-      <c r="N25" s="713" t="n"/>
-      <c r="P25" s="715" t="n"/>
-      <c r="Q25" s="715" t="n"/>
-      <c r="R25" s="715" t="n"/>
-      <c r="S25" s="715" t="n"/>
+      <c r="A25" s="707" t="n"/>
+      <c r="B25" s="707" t="n"/>
+      <c r="C25" s="707" t="n"/>
+      <c r="D25" s="707" t="n"/>
+      <c r="F25" s="709" t="n"/>
+      <c r="G25" s="709" t="n"/>
+      <c r="H25" s="709" t="n"/>
+      <c r="I25" s="709" t="n"/>
+      <c r="K25" s="711" t="n"/>
+      <c r="L25" s="711" t="n"/>
+      <c r="M25" s="711" t="n"/>
+      <c r="N25" s="711" t="n"/>
+      <c r="P25" s="713" t="n"/>
+      <c r="Q25" s="713" t="n"/>
+      <c r="R25" s="713" t="n"/>
+      <c r="S25" s="713" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
@@ -7409,56 +7406,56 @@
       <c r="S28" s="15" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="716" t="inlineStr">
+      <c r="A29" s="714" t="inlineStr">
         <is>
           <t>MF21</t>
         </is>
       </c>
-      <c r="B29" s="717" t="n"/>
-      <c r="C29" s="717" t="n"/>
-      <c r="D29" s="717" t="n"/>
-      <c r="F29" s="718" t="inlineStr">
+      <c r="B29" s="715" t="n"/>
+      <c r="C29" s="715" t="n"/>
+      <c r="D29" s="715" t="n"/>
+      <c r="F29" s="716" t="inlineStr">
         <is>
           <t>MF22</t>
         </is>
       </c>
-      <c r="G29" s="719" t="n"/>
-      <c r="H29" s="719" t="n"/>
-      <c r="I29" s="719" t="n"/>
-      <c r="K29" s="720" t="inlineStr">
+      <c r="G29" s="717" t="n"/>
+      <c r="H29" s="717" t="n"/>
+      <c r="I29" s="717" t="n"/>
+      <c r="K29" s="718" t="inlineStr">
         <is>
           <t>MF23</t>
         </is>
       </c>
-      <c r="L29" s="721" t="n"/>
-      <c r="M29" s="721" t="n"/>
-      <c r="N29" s="721" t="n"/>
-      <c r="P29" s="722" t="inlineStr">
+      <c r="L29" s="719" t="n"/>
+      <c r="M29" s="719" t="n"/>
+      <c r="N29" s="719" t="n"/>
+      <c r="P29" s="720" t="inlineStr">
         <is>
           <t>MF24</t>
         </is>
       </c>
-      <c r="Q29" s="723" t="n"/>
-      <c r="R29" s="723" t="n"/>
-      <c r="S29" s="723" t="n"/>
+      <c r="Q29" s="721" t="n"/>
+      <c r="R29" s="721" t="n"/>
+      <c r="S29" s="721" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="717" t="n"/>
-      <c r="B30" s="717" t="n"/>
-      <c r="C30" s="717" t="n"/>
-      <c r="D30" s="717" t="n"/>
-      <c r="F30" s="719" t="n"/>
-      <c r="G30" s="719" t="n"/>
-      <c r="H30" s="719" t="n"/>
-      <c r="I30" s="719" t="n"/>
-      <c r="K30" s="721" t="n"/>
-      <c r="L30" s="721" t="n"/>
-      <c r="M30" s="721" t="n"/>
-      <c r="N30" s="721" t="n"/>
-      <c r="P30" s="723" t="n"/>
-      <c r="Q30" s="723" t="n"/>
-      <c r="R30" s="723" t="n"/>
-      <c r="S30" s="723" t="n"/>
+      <c r="A30" s="715" t="n"/>
+      <c r="B30" s="715" t="n"/>
+      <c r="C30" s="715" t="n"/>
+      <c r="D30" s="715" t="n"/>
+      <c r="F30" s="717" t="n"/>
+      <c r="G30" s="717" t="n"/>
+      <c r="H30" s="717" t="n"/>
+      <c r="I30" s="717" t="n"/>
+      <c r="K30" s="719" t="n"/>
+      <c r="L30" s="719" t="n"/>
+      <c r="M30" s="719" t="n"/>
+      <c r="N30" s="719" t="n"/>
+      <c r="P30" s="721" t="n"/>
+      <c r="Q30" s="721" t="n"/>
+      <c r="R30" s="721" t="n"/>
+      <c r="S30" s="721" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -7563,20 +7560,20 @@
       <c r="S33" s="15" t="n"/>
     </row>
     <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="724" t="inlineStr">
+      <c r="A34" s="722" t="inlineStr">
         <is>
           <t>MF25</t>
         </is>
       </c>
-      <c r="B34" s="725" t="n"/>
-      <c r="C34" s="725" t="n"/>
-      <c r="D34" s="725" t="n"/>
+      <c r="B34" s="723" t="n"/>
+      <c r="C34" s="723" t="n"/>
+      <c r="D34" s="723" t="n"/>
     </row>
     <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="725" t="n"/>
-      <c r="B35" s="725" t="n"/>
-      <c r="C35" s="725" t="n"/>
-      <c r="D35" s="725" t="n"/>
+      <c r="A35" s="723" t="n"/>
+      <c r="B35" s="723" t="n"/>
+      <c r="C35" s="723" t="n"/>
+      <c r="D35" s="723" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -7760,56 +7757,56 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="726" t="inlineStr">
+      <c r="A4" s="724" t="inlineStr">
         <is>
           <t>MG1</t>
         </is>
       </c>
-      <c r="B4" s="727" t="n"/>
-      <c r="C4" s="727" t="n"/>
-      <c r="D4" s="727" t="n"/>
-      <c r="F4" s="728" t="inlineStr">
+      <c r="B4" s="725" t="n"/>
+      <c r="C4" s="725" t="n"/>
+      <c r="D4" s="725" t="n"/>
+      <c r="F4" s="726" t="inlineStr">
         <is>
           <t>MG2</t>
         </is>
       </c>
-      <c r="G4" s="729" t="n"/>
-      <c r="H4" s="729" t="n"/>
-      <c r="I4" s="729" t="n"/>
-      <c r="K4" s="730" t="inlineStr">
+      <c r="G4" s="727" t="n"/>
+      <c r="H4" s="727" t="n"/>
+      <c r="I4" s="727" t="n"/>
+      <c r="K4" s="728" t="inlineStr">
         <is>
           <t>MG3</t>
         </is>
       </c>
-      <c r="L4" s="731" t="n"/>
-      <c r="M4" s="731" t="n"/>
-      <c r="N4" s="731" t="n"/>
-      <c r="P4" s="732" t="inlineStr">
+      <c r="L4" s="729" t="n"/>
+      <c r="M4" s="729" t="n"/>
+      <c r="N4" s="729" t="n"/>
+      <c r="P4" s="730" t="inlineStr">
         <is>
           <t>MG4</t>
         </is>
       </c>
-      <c r="Q4" s="733" t="n"/>
-      <c r="R4" s="733" t="n"/>
-      <c r="S4" s="733" t="n"/>
+      <c r="Q4" s="731" t="n"/>
+      <c r="R4" s="731" t="n"/>
+      <c r="S4" s="731" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="727" t="n"/>
-      <c r="B5" s="727" t="n"/>
-      <c r="C5" s="727" t="n"/>
-      <c r="D5" s="727" t="n"/>
-      <c r="F5" s="729" t="n"/>
-      <c r="G5" s="729" t="n"/>
-      <c r="H5" s="729" t="n"/>
-      <c r="I5" s="729" t="n"/>
-      <c r="K5" s="731" t="n"/>
-      <c r="L5" s="731" t="n"/>
-      <c r="M5" s="731" t="n"/>
-      <c r="N5" s="731" t="n"/>
-      <c r="P5" s="733" t="n"/>
-      <c r="Q5" s="733" t="n"/>
-      <c r="R5" s="733" t="n"/>
-      <c r="S5" s="733" t="n"/>
+      <c r="A5" s="725" t="n"/>
+      <c r="B5" s="725" t="n"/>
+      <c r="C5" s="725" t="n"/>
+      <c r="D5" s="725" t="n"/>
+      <c r="F5" s="727" t="n"/>
+      <c r="G5" s="727" t="n"/>
+      <c r="H5" s="727" t="n"/>
+      <c r="I5" s="727" t="n"/>
+      <c r="K5" s="729" t="n"/>
+      <c r="L5" s="729" t="n"/>
+      <c r="M5" s="729" t="n"/>
+      <c r="N5" s="729" t="n"/>
+      <c r="P5" s="731" t="n"/>
+      <c r="Q5" s="731" t="n"/>
+      <c r="R5" s="731" t="n"/>
+      <c r="S5" s="731" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -7914,56 +7911,56 @@
       <c r="S8" s="15" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="734" t="inlineStr">
+      <c r="A9" s="732" t="inlineStr">
         <is>
           <t>MG5</t>
         </is>
       </c>
-      <c r="B9" s="735" t="n"/>
-      <c r="C9" s="735" t="n"/>
-      <c r="D9" s="735" t="n"/>
-      <c r="F9" s="736" t="inlineStr">
+      <c r="B9" s="733" t="n"/>
+      <c r="C9" s="733" t="n"/>
+      <c r="D9" s="733" t="n"/>
+      <c r="F9" s="734" t="inlineStr">
         <is>
           <t>MG6</t>
         </is>
       </c>
-      <c r="G9" s="737" t="n"/>
-      <c r="H9" s="737" t="n"/>
-      <c r="I9" s="737" t="n"/>
-      <c r="K9" s="738" t="inlineStr">
+      <c r="G9" s="735" t="n"/>
+      <c r="H9" s="735" t="n"/>
+      <c r="I9" s="735" t="n"/>
+      <c r="K9" s="736" t="inlineStr">
         <is>
           <t>MG7</t>
         </is>
       </c>
-      <c r="L9" s="739" t="n"/>
-      <c r="M9" s="739" t="n"/>
-      <c r="N9" s="739" t="n"/>
-      <c r="P9" s="740" t="inlineStr">
+      <c r="L9" s="737" t="n"/>
+      <c r="M9" s="737" t="n"/>
+      <c r="N9" s="737" t="n"/>
+      <c r="P9" s="738" t="inlineStr">
         <is>
           <t>MG8</t>
         </is>
       </c>
-      <c r="Q9" s="741" t="n"/>
-      <c r="R9" s="741" t="n"/>
-      <c r="S9" s="741" t="n"/>
+      <c r="Q9" s="739" t="n"/>
+      <c r="R9" s="739" t="n"/>
+      <c r="S9" s="739" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="735" t="n"/>
-      <c r="B10" s="735" t="n"/>
-      <c r="C10" s="735" t="n"/>
-      <c r="D10" s="735" t="n"/>
-      <c r="F10" s="737" t="n"/>
-      <c r="G10" s="737" t="n"/>
-      <c r="H10" s="737" t="n"/>
-      <c r="I10" s="737" t="n"/>
-      <c r="K10" s="739" t="n"/>
-      <c r="L10" s="739" t="n"/>
-      <c r="M10" s="739" t="n"/>
-      <c r="N10" s="739" t="n"/>
-      <c r="P10" s="741" t="n"/>
-      <c r="Q10" s="741" t="n"/>
-      <c r="R10" s="741" t="n"/>
-      <c r="S10" s="741" t="n"/>
+      <c r="A10" s="733" t="n"/>
+      <c r="B10" s="733" t="n"/>
+      <c r="C10" s="733" t="n"/>
+      <c r="D10" s="733" t="n"/>
+      <c r="F10" s="735" t="n"/>
+      <c r="G10" s="735" t="n"/>
+      <c r="H10" s="735" t="n"/>
+      <c r="I10" s="735" t="n"/>
+      <c r="K10" s="737" t="n"/>
+      <c r="L10" s="737" t="n"/>
+      <c r="M10" s="737" t="n"/>
+      <c r="N10" s="737" t="n"/>
+      <c r="P10" s="739" t="n"/>
+      <c r="Q10" s="739" t="n"/>
+      <c r="R10" s="739" t="n"/>
+      <c r="S10" s="739" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -8068,56 +8065,56 @@
       <c r="S13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="742" t="inlineStr">
+      <c r="A14" s="740" t="inlineStr">
         <is>
           <t>MG9</t>
         </is>
       </c>
-      <c r="B14" s="743" t="n"/>
-      <c r="C14" s="743" t="n"/>
-      <c r="D14" s="743" t="n"/>
-      <c r="F14" s="744" t="inlineStr">
+      <c r="B14" s="741" t="n"/>
+      <c r="C14" s="741" t="n"/>
+      <c r="D14" s="741" t="n"/>
+      <c r="F14" s="742" t="inlineStr">
         <is>
           <t>MG10</t>
         </is>
       </c>
-      <c r="G14" s="745" t="n"/>
-      <c r="H14" s="745" t="n"/>
-      <c r="I14" s="745" t="n"/>
-      <c r="K14" s="746" t="inlineStr">
+      <c r="G14" s="743" t="n"/>
+      <c r="H14" s="743" t="n"/>
+      <c r="I14" s="743" t="n"/>
+      <c r="K14" s="744" t="inlineStr">
         <is>
           <t>MG11</t>
         </is>
       </c>
-      <c r="L14" s="747" t="n"/>
-      <c r="M14" s="747" t="n"/>
-      <c r="N14" s="747" t="n"/>
-      <c r="P14" s="748" t="inlineStr">
+      <c r="L14" s="745" t="n"/>
+      <c r="M14" s="745" t="n"/>
+      <c r="N14" s="745" t="n"/>
+      <c r="P14" s="746" t="inlineStr">
         <is>
           <t>MG12</t>
         </is>
       </c>
-      <c r="Q14" s="749" t="n"/>
-      <c r="R14" s="749" t="n"/>
-      <c r="S14" s="749" t="n"/>
+      <c r="Q14" s="747" t="n"/>
+      <c r="R14" s="747" t="n"/>
+      <c r="S14" s="747" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="743" t="n"/>
-      <c r="B15" s="743" t="n"/>
-      <c r="C15" s="743" t="n"/>
-      <c r="D15" s="743" t="n"/>
-      <c r="F15" s="745" t="n"/>
-      <c r="G15" s="745" t="n"/>
-      <c r="H15" s="745" t="n"/>
-      <c r="I15" s="745" t="n"/>
-      <c r="K15" s="747" t="n"/>
-      <c r="L15" s="747" t="n"/>
-      <c r="M15" s="747" t="n"/>
-      <c r="N15" s="747" t="n"/>
-      <c r="P15" s="749" t="n"/>
-      <c r="Q15" s="749" t="n"/>
-      <c r="R15" s="749" t="n"/>
-      <c r="S15" s="749" t="n"/>
+      <c r="A15" s="741" t="n"/>
+      <c r="B15" s="741" t="n"/>
+      <c r="C15" s="741" t="n"/>
+      <c r="D15" s="741" t="n"/>
+      <c r="F15" s="743" t="n"/>
+      <c r="G15" s="743" t="n"/>
+      <c r="H15" s="743" t="n"/>
+      <c r="I15" s="743" t="n"/>
+      <c r="K15" s="745" t="n"/>
+      <c r="L15" s="745" t="n"/>
+      <c r="M15" s="745" t="n"/>
+      <c r="N15" s="745" t="n"/>
+      <c r="P15" s="747" t="n"/>
+      <c r="Q15" s="747" t="n"/>
+      <c r="R15" s="747" t="n"/>
+      <c r="S15" s="747" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -8222,56 +8219,56 @@
       <c r="S18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="750" t="inlineStr">
+      <c r="A19" s="748" t="inlineStr">
         <is>
           <t>MG13</t>
         </is>
       </c>
-      <c r="B19" s="751" t="n"/>
-      <c r="C19" s="751" t="n"/>
-      <c r="D19" s="751" t="n"/>
-      <c r="F19" s="752" t="inlineStr">
+      <c r="B19" s="749" t="n"/>
+      <c r="C19" s="749" t="n"/>
+      <c r="D19" s="749" t="n"/>
+      <c r="F19" s="750" t="inlineStr">
         <is>
           <t>MG14</t>
         </is>
       </c>
-      <c r="G19" s="753" t="n"/>
-      <c r="H19" s="753" t="n"/>
-      <c r="I19" s="753" t="n"/>
-      <c r="K19" s="754" t="inlineStr">
+      <c r="G19" s="751" t="n"/>
+      <c r="H19" s="751" t="n"/>
+      <c r="I19" s="751" t="n"/>
+      <c r="K19" s="752" t="inlineStr">
         <is>
           <t>MG15</t>
         </is>
       </c>
-      <c r="L19" s="755" t="n"/>
-      <c r="M19" s="755" t="n"/>
-      <c r="N19" s="755" t="n"/>
-      <c r="P19" s="756" t="inlineStr">
+      <c r="L19" s="753" t="n"/>
+      <c r="M19" s="753" t="n"/>
+      <c r="N19" s="753" t="n"/>
+      <c r="P19" s="754" t="inlineStr">
         <is>
           <t>MG16</t>
         </is>
       </c>
-      <c r="Q19" s="757" t="n"/>
-      <c r="R19" s="757" t="n"/>
-      <c r="S19" s="757" t="n"/>
+      <c r="Q19" s="755" t="n"/>
+      <c r="R19" s="755" t="n"/>
+      <c r="S19" s="755" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="751" t="n"/>
-      <c r="B20" s="751" t="n"/>
-      <c r="C20" s="751" t="n"/>
-      <c r="D20" s="751" t="n"/>
-      <c r="F20" s="753" t="n"/>
-      <c r="G20" s="753" t="n"/>
-      <c r="H20" s="753" t="n"/>
-      <c r="I20" s="753" t="n"/>
-      <c r="K20" s="755" t="n"/>
-      <c r="L20" s="755" t="n"/>
-      <c r="M20" s="755" t="n"/>
-      <c r="N20" s="755" t="n"/>
-      <c r="P20" s="757" t="n"/>
-      <c r="Q20" s="757" t="n"/>
-      <c r="R20" s="757" t="n"/>
-      <c r="S20" s="757" t="n"/>
+      <c r="A20" s="749" t="n"/>
+      <c r="B20" s="749" t="n"/>
+      <c r="C20" s="749" t="n"/>
+      <c r="D20" s="749" t="n"/>
+      <c r="F20" s="751" t="n"/>
+      <c r="G20" s="751" t="n"/>
+      <c r="H20" s="751" t="n"/>
+      <c r="I20" s="751" t="n"/>
+      <c r="K20" s="753" t="n"/>
+      <c r="L20" s="753" t="n"/>
+      <c r="M20" s="753" t="n"/>
+      <c r="N20" s="753" t="n"/>
+      <c r="P20" s="755" t="n"/>
+      <c r="Q20" s="755" t="n"/>
+      <c r="R20" s="755" t="n"/>
+      <c r="S20" s="755" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -8376,56 +8373,56 @@
       <c r="S23" s="15" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="758" t="inlineStr">
+      <c r="A24" s="756" t="inlineStr">
         <is>
           <t>MG17</t>
         </is>
       </c>
-      <c r="B24" s="759" t="n"/>
-      <c r="C24" s="759" t="n"/>
-      <c r="D24" s="759" t="n"/>
-      <c r="F24" s="760" t="inlineStr">
+      <c r="B24" s="757" t="n"/>
+      <c r="C24" s="757" t="n"/>
+      <c r="D24" s="757" t="n"/>
+      <c r="F24" s="758" t="inlineStr">
         <is>
           <t>MG18</t>
         </is>
       </c>
-      <c r="G24" s="761" t="n"/>
-      <c r="H24" s="761" t="n"/>
-      <c r="I24" s="761" t="n"/>
-      <c r="K24" s="762" t="inlineStr">
+      <c r="G24" s="759" t="n"/>
+      <c r="H24" s="759" t="n"/>
+      <c r="I24" s="759" t="n"/>
+      <c r="K24" s="760" t="inlineStr">
         <is>
           <t>MG19</t>
         </is>
       </c>
-      <c r="L24" s="763" t="n"/>
-      <c r="M24" s="763" t="n"/>
-      <c r="N24" s="763" t="n"/>
-      <c r="P24" s="764" t="inlineStr">
+      <c r="L24" s="761" t="n"/>
+      <c r="M24" s="761" t="n"/>
+      <c r="N24" s="761" t="n"/>
+      <c r="P24" s="762" t="inlineStr">
         <is>
           <t>MG20</t>
         </is>
       </c>
-      <c r="Q24" s="765" t="n"/>
-      <c r="R24" s="765" t="n"/>
-      <c r="S24" s="765" t="n"/>
+      <c r="Q24" s="763" t="n"/>
+      <c r="R24" s="763" t="n"/>
+      <c r="S24" s="763" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="759" t="n"/>
-      <c r="B25" s="759" t="n"/>
-      <c r="C25" s="759" t="n"/>
-      <c r="D25" s="759" t="n"/>
-      <c r="F25" s="761" t="n"/>
-      <c r="G25" s="761" t="n"/>
-      <c r="H25" s="761" t="n"/>
-      <c r="I25" s="761" t="n"/>
-      <c r="K25" s="763" t="n"/>
-      <c r="L25" s="763" t="n"/>
-      <c r="M25" s="763" t="n"/>
-      <c r="N25" s="763" t="n"/>
-      <c r="P25" s="765" t="n"/>
-      <c r="Q25" s="765" t="n"/>
-      <c r="R25" s="765" t="n"/>
-      <c r="S25" s="765" t="n"/>
+      <c r="A25" s="757" t="n"/>
+      <c r="B25" s="757" t="n"/>
+      <c r="C25" s="757" t="n"/>
+      <c r="D25" s="757" t="n"/>
+      <c r="F25" s="759" t="n"/>
+      <c r="G25" s="759" t="n"/>
+      <c r="H25" s="759" t="n"/>
+      <c r="I25" s="759" t="n"/>
+      <c r="K25" s="761" t="n"/>
+      <c r="L25" s="761" t="n"/>
+      <c r="M25" s="761" t="n"/>
+      <c r="N25" s="761" t="n"/>
+      <c r="P25" s="763" t="n"/>
+      <c r="Q25" s="763" t="n"/>
+      <c r="R25" s="763" t="n"/>
+      <c r="S25" s="763" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
@@ -8530,20 +8527,20 @@
       <c r="S28" s="15" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="766" t="inlineStr">
+      <c r="A29" s="764" t="inlineStr">
         <is>
           <t>MG21</t>
         </is>
       </c>
-      <c r="B29" s="767" t="n"/>
-      <c r="C29" s="767" t="n"/>
-      <c r="D29" s="767" t="n"/>
+      <c r="B29" s="765" t="n"/>
+      <c r="C29" s="765" t="n"/>
+      <c r="D29" s="765" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="767" t="n"/>
-      <c r="B30" s="767" t="n"/>
-      <c r="C30" s="767" t="n"/>
-      <c r="D30" s="767" t="n"/>
+      <c r="A30" s="765" t="n"/>
+      <c r="B30" s="765" t="n"/>
+      <c r="C30" s="765" t="n"/>
+      <c r="D30" s="765" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -8716,9 +8713,9 @@
           <t>MH1</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
+      <c r="B4" s="385" t="n"/>
       <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
+      <c r="D4" s="385" t="n"/>
       <c r="F4" s="6" t="inlineStr">
         <is>
           <t>MH2</t>
@@ -8727,45 +8724,45 @@
       <c r="G4" s="7" t="n"/>
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
-      <c r="K4" s="768" t="inlineStr">
+      <c r="K4" s="766" t="inlineStr">
         <is>
           <t>MH3</t>
         </is>
       </c>
-      <c r="L4" s="769" t="n"/>
-      <c r="M4" s="769" t="n"/>
-      <c r="N4" s="769" t="n"/>
-      <c r="P4" s="770" t="inlineStr">
+      <c r="L4" s="767" t="n"/>
+      <c r="M4" s="767" t="n"/>
+      <c r="N4" s="767" t="n"/>
+      <c r="P4" s="768" t="inlineStr">
         <is>
           <t>MH4</t>
         </is>
       </c>
-      <c r="Q4" s="771" t="n"/>
-      <c r="R4" s="771" t="n"/>
-      <c r="S4" s="771" t="n"/>
+      <c r="Q4" s="769" t="n"/>
+      <c r="R4" s="769" t="n"/>
+      <c r="S4" s="769" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="7" t="n"/>
+      <c r="A5" s="385" t="n"/>
       <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
+      <c r="C5" s="385" t="n"/>
       <c r="D5" s="7" t="n"/>
       <c r="F5" s="7" t="n"/>
       <c r="G5" s="7" t="n"/>
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
-      <c r="K5" s="769" t="n"/>
-      <c r="L5" s="769" t="n"/>
-      <c r="M5" s="769" t="n"/>
-      <c r="N5" s="769" t="n"/>
-      <c r="P5" s="771" t="n"/>
-      <c r="Q5" s="771" t="n"/>
-      <c r="R5" s="771" t="n"/>
-      <c r="S5" s="771" t="n"/>
+      <c r="K5" s="767" t="n"/>
+      <c r="L5" s="767" t="n"/>
+      <c r="M5" s="767" t="n"/>
+      <c r="N5" s="767" t="n"/>
+      <c r="P5" s="769" t="n"/>
+      <c r="Q5" s="769" t="n"/>
+      <c r="R5" s="769" t="n"/>
+      <c r="S5" s="769" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>HEX: #FFFFFF</t>
+          <t>HEX: #FFFFFF00</t>
         </is>
       </c>
       <c r="B6" s="15" t="n"/>
@@ -8799,7 +8796,7 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>RGB: 255, 255, 255</t>
+          <t>RGB: 255, 255, 255, 0</t>
         </is>
       </c>
       <c r="B7" s="15" t="n"/>
@@ -8865,22 +8862,22 @@
       <c r="S8" s="15" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="772" t="inlineStr">
+      <c r="A9" s="770" t="inlineStr">
         <is>
           <t>MH5</t>
         </is>
       </c>
-      <c r="B9" s="773" t="n"/>
-      <c r="C9" s="773" t="n"/>
-      <c r="D9" s="773" t="n"/>
-      <c r="F9" s="774" t="inlineStr">
+      <c r="B9" s="771" t="n"/>
+      <c r="C9" s="771" t="n"/>
+      <c r="D9" s="771" t="n"/>
+      <c r="F9" s="772" t="inlineStr">
         <is>
           <t>MH6</t>
         </is>
       </c>
-      <c r="G9" s="775" t="n"/>
-      <c r="H9" s="775" t="n"/>
-      <c r="I9" s="775" t="n"/>
+      <c r="G9" s="773" t="n"/>
+      <c r="H9" s="773" t="n"/>
+      <c r="I9" s="773" t="n"/>
       <c r="K9" s="8" t="inlineStr">
         <is>
           <t>MH7</t>
@@ -8889,32 +8886,32 @@
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
       <c r="N9" s="9" t="n"/>
-      <c r="P9" s="776" t="inlineStr">
+      <c r="P9" s="774" t="inlineStr">
         <is>
           <t>MH8</t>
         </is>
       </c>
-      <c r="Q9" s="777" t="n"/>
-      <c r="R9" s="777" t="n"/>
-      <c r="S9" s="777" t="n"/>
+      <c r="Q9" s="775" t="n"/>
+      <c r="R9" s="775" t="n"/>
+      <c r="S9" s="775" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="773" t="n"/>
-      <c r="B10" s="773" t="n"/>
-      <c r="C10" s="773" t="n"/>
-      <c r="D10" s="773" t="n"/>
-      <c r="F10" s="775" t="n"/>
-      <c r="G10" s="775" t="n"/>
-      <c r="H10" s="775" t="n"/>
-      <c r="I10" s="775" t="n"/>
+      <c r="A10" s="771" t="n"/>
+      <c r="B10" s="771" t="n"/>
+      <c r="C10" s="771" t="n"/>
+      <c r="D10" s="771" t="n"/>
+      <c r="F10" s="773" t="n"/>
+      <c r="G10" s="773" t="n"/>
+      <c r="H10" s="773" t="n"/>
+      <c r="I10" s="773" t="n"/>
       <c r="K10" s="9" t="n"/>
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="9" t="n"/>
       <c r="N10" s="9" t="n"/>
-      <c r="P10" s="777" t="n"/>
-      <c r="Q10" s="777" t="n"/>
-      <c r="R10" s="777" t="n"/>
-      <c r="S10" s="777" t="n"/>
+      <c r="P10" s="775" t="n"/>
+      <c r="Q10" s="775" t="n"/>
+      <c r="R10" s="775" t="n"/>
+      <c r="S10" s="775" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -9019,56 +9016,56 @@
       <c r="S13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="778" t="inlineStr">
+      <c r="A14" s="776" t="inlineStr">
         <is>
           <t>MH9</t>
         </is>
       </c>
-      <c r="B14" s="779" t="n"/>
-      <c r="C14" s="779" t="n"/>
-      <c r="D14" s="779" t="n"/>
-      <c r="F14" s="780" t="inlineStr">
+      <c r="B14" s="777" t="n"/>
+      <c r="C14" s="777" t="n"/>
+      <c r="D14" s="777" t="n"/>
+      <c r="F14" s="778" t="inlineStr">
         <is>
           <t>MH10</t>
         </is>
       </c>
-      <c r="G14" s="781" t="n"/>
-      <c r="H14" s="781" t="n"/>
-      <c r="I14" s="781" t="n"/>
-      <c r="K14" s="782" t="inlineStr">
+      <c r="G14" s="779" t="n"/>
+      <c r="H14" s="779" t="n"/>
+      <c r="I14" s="779" t="n"/>
+      <c r="K14" s="780" t="inlineStr">
         <is>
           <t>MH11</t>
         </is>
       </c>
-      <c r="L14" s="783" t="n"/>
-      <c r="M14" s="783" t="n"/>
-      <c r="N14" s="783" t="n"/>
-      <c r="P14" s="784" t="inlineStr">
+      <c r="L14" s="781" t="n"/>
+      <c r="M14" s="781" t="n"/>
+      <c r="N14" s="781" t="n"/>
+      <c r="P14" s="782" t="inlineStr">
         <is>
           <t>MH12</t>
         </is>
       </c>
-      <c r="Q14" s="785" t="n"/>
-      <c r="R14" s="785" t="n"/>
-      <c r="S14" s="785" t="n"/>
+      <c r="Q14" s="783" t="n"/>
+      <c r="R14" s="783" t="n"/>
+      <c r="S14" s="783" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="779" t="n"/>
-      <c r="B15" s="779" t="n"/>
-      <c r="C15" s="779" t="n"/>
-      <c r="D15" s="779" t="n"/>
-      <c r="F15" s="781" t="n"/>
-      <c r="G15" s="781" t="n"/>
-      <c r="H15" s="781" t="n"/>
-      <c r="I15" s="781" t="n"/>
-      <c r="K15" s="783" t="n"/>
-      <c r="L15" s="783" t="n"/>
-      <c r="M15" s="783" t="n"/>
-      <c r="N15" s="783" t="n"/>
-      <c r="P15" s="785" t="n"/>
-      <c r="Q15" s="785" t="n"/>
-      <c r="R15" s="785" t="n"/>
-      <c r="S15" s="785" t="n"/>
+      <c r="A15" s="777" t="n"/>
+      <c r="B15" s="777" t="n"/>
+      <c r="C15" s="777" t="n"/>
+      <c r="D15" s="777" t="n"/>
+      <c r="F15" s="779" t="n"/>
+      <c r="G15" s="779" t="n"/>
+      <c r="H15" s="779" t="n"/>
+      <c r="I15" s="779" t="n"/>
+      <c r="K15" s="781" t="n"/>
+      <c r="L15" s="781" t="n"/>
+      <c r="M15" s="781" t="n"/>
+      <c r="N15" s="781" t="n"/>
+      <c r="P15" s="783" t="n"/>
+      <c r="Q15" s="783" t="n"/>
+      <c r="R15" s="783" t="n"/>
+      <c r="S15" s="783" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -9173,56 +9170,56 @@
       <c r="S18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="786" t="inlineStr">
+      <c r="A19" s="784" t="inlineStr">
         <is>
           <t>MH13</t>
         </is>
       </c>
-      <c r="B19" s="787" t="n"/>
-      <c r="C19" s="787" t="n"/>
-      <c r="D19" s="787" t="n"/>
-      <c r="F19" s="788" t="inlineStr">
+      <c r="B19" s="785" t="n"/>
+      <c r="C19" s="785" t="n"/>
+      <c r="D19" s="785" t="n"/>
+      <c r="F19" s="786" t="inlineStr">
         <is>
           <t>MH14</t>
         </is>
       </c>
-      <c r="G19" s="789" t="n"/>
-      <c r="H19" s="789" t="n"/>
-      <c r="I19" s="789" t="n"/>
-      <c r="K19" s="790" t="inlineStr">
+      <c r="G19" s="787" t="n"/>
+      <c r="H19" s="787" t="n"/>
+      <c r="I19" s="787" t="n"/>
+      <c r="K19" s="788" t="inlineStr">
         <is>
           <t>MH15</t>
         </is>
       </c>
-      <c r="L19" s="791" t="n"/>
-      <c r="M19" s="791" t="n"/>
-      <c r="N19" s="791" t="n"/>
-      <c r="P19" s="792" t="inlineStr">
+      <c r="L19" s="789" t="n"/>
+      <c r="M19" s="789" t="n"/>
+      <c r="N19" s="789" t="n"/>
+      <c r="P19" s="790" t="inlineStr">
         <is>
           <t>MH16</t>
         </is>
       </c>
-      <c r="Q19" s="793" t="n"/>
-      <c r="R19" s="793" t="n"/>
-      <c r="S19" s="793" t="n"/>
+      <c r="Q19" s="791" t="n"/>
+      <c r="R19" s="791" t="n"/>
+      <c r="S19" s="791" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="787" t="n"/>
-      <c r="B20" s="787" t="n"/>
-      <c r="C20" s="787" t="n"/>
-      <c r="D20" s="787" t="n"/>
-      <c r="F20" s="789" t="n"/>
-      <c r="G20" s="789" t="n"/>
-      <c r="H20" s="789" t="n"/>
-      <c r="I20" s="789" t="n"/>
-      <c r="K20" s="791" t="n"/>
-      <c r="L20" s="791" t="n"/>
-      <c r="M20" s="791" t="n"/>
-      <c r="N20" s="791" t="n"/>
-      <c r="P20" s="793" t="n"/>
-      <c r="Q20" s="793" t="n"/>
-      <c r="R20" s="793" t="n"/>
-      <c r="S20" s="793" t="n"/>
+      <c r="A20" s="785" t="n"/>
+      <c r="B20" s="785" t="n"/>
+      <c r="C20" s="785" t="n"/>
+      <c r="D20" s="785" t="n"/>
+      <c r="F20" s="787" t="n"/>
+      <c r="G20" s="787" t="n"/>
+      <c r="H20" s="787" t="n"/>
+      <c r="I20" s="787" t="n"/>
+      <c r="K20" s="789" t="n"/>
+      <c r="L20" s="789" t="n"/>
+      <c r="M20" s="789" t="n"/>
+      <c r="N20" s="789" t="n"/>
+      <c r="P20" s="791" t="n"/>
+      <c r="Q20" s="791" t="n"/>
+      <c r="R20" s="791" t="n"/>
+      <c r="S20" s="791" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -9327,56 +9324,56 @@
       <c r="S23" s="15" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="794" t="inlineStr">
+      <c r="A24" s="792" t="inlineStr">
         <is>
           <t>MH17</t>
         </is>
       </c>
-      <c r="B24" s="795" t="n"/>
-      <c r="C24" s="795" t="n"/>
-      <c r="D24" s="795" t="n"/>
-      <c r="F24" s="796" t="inlineStr">
+      <c r="B24" s="793" t="n"/>
+      <c r="C24" s="793" t="n"/>
+      <c r="D24" s="793" t="n"/>
+      <c r="F24" s="794" t="inlineStr">
         <is>
           <t>MH18</t>
         </is>
       </c>
-      <c r="G24" s="797" t="n"/>
-      <c r="H24" s="797" t="n"/>
-      <c r="I24" s="797" t="n"/>
-      <c r="K24" s="798" t="inlineStr">
+      <c r="G24" s="795" t="n"/>
+      <c r="H24" s="795" t="n"/>
+      <c r="I24" s="795" t="n"/>
+      <c r="K24" s="796" t="inlineStr">
         <is>
           <t>MH19</t>
         </is>
       </c>
-      <c r="L24" s="799" t="n"/>
-      <c r="M24" s="799" t="n"/>
-      <c r="N24" s="799" t="n"/>
-      <c r="P24" s="800" t="inlineStr">
+      <c r="L24" s="797" t="n"/>
+      <c r="M24" s="797" t="n"/>
+      <c r="N24" s="797" t="n"/>
+      <c r="P24" s="798" t="inlineStr">
         <is>
           <t>MH20</t>
         </is>
       </c>
-      <c r="Q24" s="801" t="n"/>
-      <c r="R24" s="801" t="n"/>
-      <c r="S24" s="801" t="n"/>
+      <c r="Q24" s="799" t="n"/>
+      <c r="R24" s="799" t="n"/>
+      <c r="S24" s="799" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="795" t="n"/>
-      <c r="B25" s="795" t="n"/>
-      <c r="C25" s="795" t="n"/>
-      <c r="D25" s="795" t="n"/>
-      <c r="F25" s="797" t="n"/>
-      <c r="G25" s="797" t="n"/>
-      <c r="H25" s="797" t="n"/>
-      <c r="I25" s="797" t="n"/>
-      <c r="K25" s="799" t="n"/>
-      <c r="L25" s="799" t="n"/>
-      <c r="M25" s="799" t="n"/>
-      <c r="N25" s="799" t="n"/>
-      <c r="P25" s="801" t="n"/>
-      <c r="Q25" s="801" t="n"/>
-      <c r="R25" s="801" t="n"/>
-      <c r="S25" s="801" t="n"/>
+      <c r="A25" s="793" t="n"/>
+      <c r="B25" s="793" t="n"/>
+      <c r="C25" s="793" t="n"/>
+      <c r="D25" s="793" t="n"/>
+      <c r="F25" s="795" t="n"/>
+      <c r="G25" s="795" t="n"/>
+      <c r="H25" s="795" t="n"/>
+      <c r="I25" s="795" t="n"/>
+      <c r="K25" s="797" t="n"/>
+      <c r="L25" s="797" t="n"/>
+      <c r="M25" s="797" t="n"/>
+      <c r="N25" s="797" t="n"/>
+      <c r="P25" s="799" t="n"/>
+      <c r="Q25" s="799" t="n"/>
+      <c r="R25" s="799" t="n"/>
+      <c r="S25" s="799" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
@@ -9481,44 +9478,44 @@
       <c r="S28" s="15" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="802" t="inlineStr">
+      <c r="A29" s="800" t="inlineStr">
         <is>
           <t>MH21</t>
         </is>
       </c>
-      <c r="B29" s="803" t="n"/>
-      <c r="C29" s="803" t="n"/>
-      <c r="D29" s="803" t="n"/>
-      <c r="F29" s="804" t="inlineStr">
+      <c r="B29" s="801" t="n"/>
+      <c r="C29" s="801" t="n"/>
+      <c r="D29" s="801" t="n"/>
+      <c r="F29" s="802" t="inlineStr">
         <is>
           <t>MH22</t>
         </is>
       </c>
-      <c r="G29" s="805" t="n"/>
-      <c r="H29" s="805" t="n"/>
-      <c r="I29" s="805" t="n"/>
-      <c r="K29" s="806" t="inlineStr">
+      <c r="G29" s="803" t="n"/>
+      <c r="H29" s="803" t="n"/>
+      <c r="I29" s="803" t="n"/>
+      <c r="K29" s="804" t="inlineStr">
         <is>
           <t>MH23</t>
         </is>
       </c>
-      <c r="L29" s="807" t="n"/>
-      <c r="M29" s="807" t="n"/>
-      <c r="N29" s="807" t="n"/>
+      <c r="L29" s="805" t="n"/>
+      <c r="M29" s="805" t="n"/>
+      <c r="N29" s="805" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="803" t="n"/>
-      <c r="B30" s="803" t="n"/>
-      <c r="C30" s="803" t="n"/>
-      <c r="D30" s="803" t="n"/>
-      <c r="F30" s="805" t="n"/>
-      <c r="G30" s="805" t="n"/>
-      <c r="H30" s="805" t="n"/>
-      <c r="I30" s="805" t="n"/>
-      <c r="K30" s="807" t="n"/>
-      <c r="L30" s="807" t="n"/>
-      <c r="M30" s="807" t="n"/>
-      <c r="N30" s="807" t="n"/>
+      <c r="A30" s="801" t="n"/>
+      <c r="B30" s="801" t="n"/>
+      <c r="C30" s="801" t="n"/>
+      <c r="D30" s="801" t="n"/>
+      <c r="F30" s="803" t="n"/>
+      <c r="G30" s="803" t="n"/>
+      <c r="H30" s="803" t="n"/>
+      <c r="I30" s="803" t="n"/>
+      <c r="K30" s="805" t="n"/>
+      <c r="L30" s="805" t="n"/>
+      <c r="M30" s="805" t="n"/>
+      <c r="N30" s="805" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -9599,7 +9596,7 @@
       <c r="N33" s="15" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="92">
+  <mergeCells count="91">
     <mergeCell ref="F27:I27"/>
     <mergeCell ref="P18:S18"/>
     <mergeCell ref="P9:S10"/>
@@ -9632,7 +9629,6 @@
     <mergeCell ref="A14:D15"/>
     <mergeCell ref="P19:S20"/>
     <mergeCell ref="K21:N21"/>
-    <mergeCell ref="A4:D5"/>
     <mergeCell ref="K4:N5"/>
     <mergeCell ref="K32:N32"/>
     <mergeCell ref="F33:I33"/>
@@ -9742,56 +9738,56 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="808" t="inlineStr">
+      <c r="A4" s="806" t="inlineStr">
         <is>
           <t>MM1</t>
         </is>
       </c>
-      <c r="B4" s="809" t="n"/>
-      <c r="C4" s="809" t="n"/>
-      <c r="D4" s="809" t="n"/>
-      <c r="F4" s="810" t="inlineStr">
+      <c r="B4" s="807" t="n"/>
+      <c r="C4" s="807" t="n"/>
+      <c r="D4" s="807" t="n"/>
+      <c r="F4" s="808" t="inlineStr">
         <is>
           <t>MM2</t>
         </is>
       </c>
-      <c r="G4" s="811" t="n"/>
-      <c r="H4" s="811" t="n"/>
-      <c r="I4" s="811" t="n"/>
-      <c r="K4" s="812" t="inlineStr">
+      <c r="G4" s="809" t="n"/>
+      <c r="H4" s="809" t="n"/>
+      <c r="I4" s="809" t="n"/>
+      <c r="K4" s="810" t="inlineStr">
         <is>
           <t>MM3</t>
         </is>
       </c>
-      <c r="L4" s="813" t="n"/>
-      <c r="M4" s="813" t="n"/>
-      <c r="N4" s="813" t="n"/>
-      <c r="P4" s="814" t="inlineStr">
+      <c r="L4" s="811" t="n"/>
+      <c r="M4" s="811" t="n"/>
+      <c r="N4" s="811" t="n"/>
+      <c r="P4" s="812" t="inlineStr">
         <is>
           <t>MM4</t>
         </is>
       </c>
-      <c r="Q4" s="815" t="n"/>
-      <c r="R4" s="815" t="n"/>
-      <c r="S4" s="815" t="n"/>
+      <c r="Q4" s="813" t="n"/>
+      <c r="R4" s="813" t="n"/>
+      <c r="S4" s="813" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="809" t="n"/>
-      <c r="B5" s="809" t="n"/>
-      <c r="C5" s="809" t="n"/>
-      <c r="D5" s="809" t="n"/>
-      <c r="F5" s="811" t="n"/>
-      <c r="G5" s="811" t="n"/>
-      <c r="H5" s="811" t="n"/>
-      <c r="I5" s="811" t="n"/>
-      <c r="K5" s="813" t="n"/>
-      <c r="L5" s="813" t="n"/>
-      <c r="M5" s="813" t="n"/>
-      <c r="N5" s="813" t="n"/>
-      <c r="P5" s="815" t="n"/>
-      <c r="Q5" s="815" t="n"/>
-      <c r="R5" s="815" t="n"/>
-      <c r="S5" s="815" t="n"/>
+      <c r="A5" s="807" t="n"/>
+      <c r="B5" s="807" t="n"/>
+      <c r="C5" s="807" t="n"/>
+      <c r="D5" s="807" t="n"/>
+      <c r="F5" s="809" t="n"/>
+      <c r="G5" s="809" t="n"/>
+      <c r="H5" s="809" t="n"/>
+      <c r="I5" s="809" t="n"/>
+      <c r="K5" s="811" t="n"/>
+      <c r="L5" s="811" t="n"/>
+      <c r="M5" s="811" t="n"/>
+      <c r="N5" s="811" t="n"/>
+      <c r="P5" s="813" t="n"/>
+      <c r="Q5" s="813" t="n"/>
+      <c r="R5" s="813" t="n"/>
+      <c r="S5" s="813" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -9896,56 +9892,56 @@
       <c r="S8" s="15" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="816" t="inlineStr">
+      <c r="A9" s="814" t="inlineStr">
         <is>
           <t>MM5</t>
         </is>
       </c>
-      <c r="B9" s="817" t="n"/>
-      <c r="C9" s="817" t="n"/>
-      <c r="D9" s="817" t="n"/>
-      <c r="F9" s="818" t="inlineStr">
+      <c r="B9" s="815" t="n"/>
+      <c r="C9" s="815" t="n"/>
+      <c r="D9" s="815" t="n"/>
+      <c r="F9" s="816" t="inlineStr">
         <is>
           <t>MM6</t>
         </is>
       </c>
-      <c r="G9" s="819" t="n"/>
-      <c r="H9" s="819" t="n"/>
-      <c r="I9" s="819" t="n"/>
-      <c r="K9" s="820" t="inlineStr">
+      <c r="G9" s="817" t="n"/>
+      <c r="H9" s="817" t="n"/>
+      <c r="I9" s="817" t="n"/>
+      <c r="K9" s="818" t="inlineStr">
         <is>
           <t>MM7</t>
         </is>
       </c>
-      <c r="L9" s="821" t="n"/>
-      <c r="M9" s="821" t="n"/>
-      <c r="N9" s="821" t="n"/>
-      <c r="P9" s="822" t="inlineStr">
+      <c r="L9" s="819" t="n"/>
+      <c r="M9" s="819" t="n"/>
+      <c r="N9" s="819" t="n"/>
+      <c r="P9" s="820" t="inlineStr">
         <is>
           <t>MM8</t>
         </is>
       </c>
-      <c r="Q9" s="823" t="n"/>
-      <c r="R9" s="823" t="n"/>
-      <c r="S9" s="823" t="n"/>
+      <c r="Q9" s="821" t="n"/>
+      <c r="R9" s="821" t="n"/>
+      <c r="S9" s="821" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="817" t="n"/>
-      <c r="B10" s="817" t="n"/>
-      <c r="C10" s="817" t="n"/>
-      <c r="D10" s="817" t="n"/>
-      <c r="F10" s="819" t="n"/>
-      <c r="G10" s="819" t="n"/>
-      <c r="H10" s="819" t="n"/>
-      <c r="I10" s="819" t="n"/>
-      <c r="K10" s="821" t="n"/>
-      <c r="L10" s="821" t="n"/>
-      <c r="M10" s="821" t="n"/>
-      <c r="N10" s="821" t="n"/>
-      <c r="P10" s="823" t="n"/>
-      <c r="Q10" s="823" t="n"/>
-      <c r="R10" s="823" t="n"/>
-      <c r="S10" s="823" t="n"/>
+      <c r="A10" s="815" t="n"/>
+      <c r="B10" s="815" t="n"/>
+      <c r="C10" s="815" t="n"/>
+      <c r="D10" s="815" t="n"/>
+      <c r="F10" s="817" t="n"/>
+      <c r="G10" s="817" t="n"/>
+      <c r="H10" s="817" t="n"/>
+      <c r="I10" s="817" t="n"/>
+      <c r="K10" s="819" t="n"/>
+      <c r="L10" s="819" t="n"/>
+      <c r="M10" s="819" t="n"/>
+      <c r="N10" s="819" t="n"/>
+      <c r="P10" s="821" t="n"/>
+      <c r="Q10" s="821" t="n"/>
+      <c r="R10" s="821" t="n"/>
+      <c r="S10" s="821" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -10050,56 +10046,56 @@
       <c r="S13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="824" t="inlineStr">
+      <c r="A14" s="822" t="inlineStr">
         <is>
           <t>MM9</t>
         </is>
       </c>
-      <c r="B14" s="825" t="n"/>
-      <c r="C14" s="825" t="n"/>
-      <c r="D14" s="825" t="n"/>
-      <c r="F14" s="826" t="inlineStr">
+      <c r="B14" s="823" t="n"/>
+      <c r="C14" s="823" t="n"/>
+      <c r="D14" s="823" t="n"/>
+      <c r="F14" s="824" t="inlineStr">
         <is>
           <t>MM10</t>
         </is>
       </c>
-      <c r="G14" s="827" t="n"/>
-      <c r="H14" s="827" t="n"/>
-      <c r="I14" s="827" t="n"/>
-      <c r="K14" s="828" t="inlineStr">
+      <c r="G14" s="825" t="n"/>
+      <c r="H14" s="825" t="n"/>
+      <c r="I14" s="825" t="n"/>
+      <c r="K14" s="826" t="inlineStr">
         <is>
           <t>MM11</t>
         </is>
       </c>
-      <c r="L14" s="829" t="n"/>
-      <c r="M14" s="829" t="n"/>
-      <c r="N14" s="829" t="n"/>
-      <c r="P14" s="830" t="inlineStr">
+      <c r="L14" s="827" t="n"/>
+      <c r="M14" s="827" t="n"/>
+      <c r="N14" s="827" t="n"/>
+      <c r="P14" s="828" t="inlineStr">
         <is>
           <t>MM12</t>
         </is>
       </c>
-      <c r="Q14" s="831" t="n"/>
-      <c r="R14" s="831" t="n"/>
-      <c r="S14" s="831" t="n"/>
+      <c r="Q14" s="829" t="n"/>
+      <c r="R14" s="829" t="n"/>
+      <c r="S14" s="829" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="825" t="n"/>
-      <c r="B15" s="825" t="n"/>
-      <c r="C15" s="825" t="n"/>
-      <c r="D15" s="825" t="n"/>
-      <c r="F15" s="827" t="n"/>
-      <c r="G15" s="827" t="n"/>
-      <c r="H15" s="827" t="n"/>
-      <c r="I15" s="827" t="n"/>
-      <c r="K15" s="829" t="n"/>
-      <c r="L15" s="829" t="n"/>
-      <c r="M15" s="829" t="n"/>
-      <c r="N15" s="829" t="n"/>
-      <c r="P15" s="831" t="n"/>
-      <c r="Q15" s="831" t="n"/>
-      <c r="R15" s="831" t="n"/>
-      <c r="S15" s="831" t="n"/>
+      <c r="A15" s="823" t="n"/>
+      <c r="B15" s="823" t="n"/>
+      <c r="C15" s="823" t="n"/>
+      <c r="D15" s="823" t="n"/>
+      <c r="F15" s="825" t="n"/>
+      <c r="G15" s="825" t="n"/>
+      <c r="H15" s="825" t="n"/>
+      <c r="I15" s="825" t="n"/>
+      <c r="K15" s="827" t="n"/>
+      <c r="L15" s="827" t="n"/>
+      <c r="M15" s="827" t="n"/>
+      <c r="N15" s="827" t="n"/>
+      <c r="P15" s="829" t="n"/>
+      <c r="Q15" s="829" t="n"/>
+      <c r="R15" s="829" t="n"/>
+      <c r="S15" s="829" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -10204,44 +10200,44 @@
       <c r="S18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="832" t="inlineStr">
+      <c r="A19" s="830" t="inlineStr">
         <is>
           <t>MM13</t>
         </is>
       </c>
-      <c r="B19" s="833" t="n"/>
-      <c r="C19" s="833" t="n"/>
-      <c r="D19" s="833" t="n"/>
-      <c r="F19" s="834" t="inlineStr">
+      <c r="B19" s="831" t="n"/>
+      <c r="C19" s="831" t="n"/>
+      <c r="D19" s="831" t="n"/>
+      <c r="F19" s="832" t="inlineStr">
         <is>
           <t>MM14</t>
         </is>
       </c>
-      <c r="G19" s="835" t="n"/>
-      <c r="H19" s="835" t="n"/>
-      <c r="I19" s="835" t="n"/>
-      <c r="K19" s="836" t="inlineStr">
+      <c r="G19" s="833" t="n"/>
+      <c r="H19" s="833" t="n"/>
+      <c r="I19" s="833" t="n"/>
+      <c r="K19" s="834" t="inlineStr">
         <is>
           <t>MM15</t>
         </is>
       </c>
-      <c r="L19" s="837" t="n"/>
-      <c r="M19" s="837" t="n"/>
-      <c r="N19" s="837" t="n"/>
+      <c r="L19" s="835" t="n"/>
+      <c r="M19" s="835" t="n"/>
+      <c r="N19" s="835" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="833" t="n"/>
-      <c r="B20" s="833" t="n"/>
-      <c r="C20" s="833" t="n"/>
-      <c r="D20" s="833" t="n"/>
-      <c r="F20" s="835" t="n"/>
-      <c r="G20" s="835" t="n"/>
-      <c r="H20" s="835" t="n"/>
-      <c r="I20" s="835" t="n"/>
-      <c r="K20" s="837" t="n"/>
-      <c r="L20" s="837" t="n"/>
-      <c r="M20" s="837" t="n"/>
-      <c r="N20" s="837" t="n"/>
+      <c r="A20" s="831" t="n"/>
+      <c r="B20" s="831" t="n"/>
+      <c r="C20" s="831" t="n"/>
+      <c r="D20" s="831" t="n"/>
+      <c r="F20" s="833" t="n"/>
+      <c r="G20" s="833" t="n"/>
+      <c r="H20" s="833" t="n"/>
+      <c r="I20" s="833" t="n"/>
+      <c r="K20" s="835" t="n"/>
+      <c r="L20" s="835" t="n"/>
+      <c r="M20" s="835" t="n"/>
+      <c r="N20" s="835" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -18653,55 +18649,55 @@
         </is>
       </c>
       <c r="B4" s="385" t="n"/>
-      <c r="C4" s="385" t="n"/>
+      <c r="C4" s="386" t="n"/>
       <c r="D4" s="385" t="n"/>
-      <c r="F4" s="386" t="inlineStr">
+      <c r="F4" s="387" t="inlineStr">
         <is>
           <t>CT02</t>
         </is>
       </c>
-      <c r="G4" s="387" t="n"/>
-      <c r="H4" s="387" t="n"/>
-      <c r="I4" s="387" t="n"/>
-      <c r="K4" s="388" t="inlineStr">
+      <c r="G4" s="388" t="n"/>
+      <c r="H4" s="385" t="n"/>
+      <c r="I4" s="388" t="n"/>
+      <c r="K4" s="389" t="inlineStr">
         <is>
           <t>CT03</t>
         </is>
       </c>
-      <c r="L4" s="389" t="n"/>
-      <c r="M4" s="389" t="n"/>
-      <c r="N4" s="389" t="n"/>
-      <c r="P4" s="390" t="inlineStr">
+      <c r="L4" s="385" t="n"/>
+      <c r="M4" s="390" t="n"/>
+      <c r="N4" s="385" t="n"/>
+      <c r="P4" s="387" t="inlineStr">
         <is>
           <t>CT04</t>
         </is>
       </c>
       <c r="Q4" s="391" t="n"/>
-      <c r="R4" s="391" t="n"/>
+      <c r="R4" s="385" t="n"/>
       <c r="S4" s="391" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="385" t="n"/>
-      <c r="B5" s="385" t="n"/>
+      <c r="B5" s="386" t="n"/>
       <c r="C5" s="385" t="n"/>
-      <c r="D5" s="385" t="n"/>
-      <c r="F5" s="387" t="n"/>
-      <c r="G5" s="387" t="n"/>
-      <c r="H5" s="387" t="n"/>
-      <c r="I5" s="387" t="n"/>
-      <c r="K5" s="389" t="n"/>
-      <c r="L5" s="389" t="n"/>
-      <c r="M5" s="389" t="n"/>
-      <c r="N5" s="389" t="n"/>
+      <c r="D5" s="386" t="n"/>
+      <c r="F5" s="388" t="n"/>
+      <c r="G5" s="385" t="n"/>
+      <c r="H5" s="388" t="n"/>
+      <c r="I5" s="385" t="n"/>
+      <c r="K5" s="385" t="n"/>
+      <c r="L5" s="390" t="n"/>
+      <c r="M5" s="385" t="n"/>
+      <c r="N5" s="390" t="n"/>
       <c r="P5" s="391" t="n"/>
-      <c r="Q5" s="391" t="n"/>
+      <c r="Q5" s="385" t="n"/>
       <c r="R5" s="391" t="n"/>
-      <c r="S5" s="391" t="n"/>
+      <c r="S5" s="385" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>HEX: #C6C6D2</t>
+          <t>HEX: #C6C6D280</t>
         </is>
       </c>
       <c r="B6" s="15" t="n"/>
@@ -18709,7 +18705,7 @@
       <c r="D6" s="15" t="n"/>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>HEX: #E664A6</t>
+          <t>HEX: #E664A680</t>
         </is>
       </c>
       <c r="G6" s="15" t="n"/>
@@ -18717,7 +18713,7 @@
       <c r="I6" s="15" t="n"/>
       <c r="K6" s="14" t="inlineStr">
         <is>
-          <t>HEX: #F6875C</t>
+          <t>HEX: #F6875C80</t>
         </is>
       </c>
       <c r="L6" s="15" t="n"/>
@@ -18725,7 +18721,7 @@
       <c r="N6" s="15" t="n"/>
       <c r="P6" s="14" t="inlineStr">
         <is>
-          <t>HEX: #C4C764</t>
+          <t>HEX: #C4C76480</t>
         </is>
       </c>
       <c r="Q6" s="15" t="n"/>
@@ -18735,7 +18731,7 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>RGB: 198, 198, 210</t>
+          <t>RGB: 198, 198, 210, 128</t>
         </is>
       </c>
       <c r="B7" s="15" t="n"/>
@@ -18743,7 +18739,7 @@
       <c r="D7" s="15" t="n"/>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>RGB: 230, 100, 166</t>
+          <t>RGB: 230, 100, 166, 128</t>
         </is>
       </c>
       <c r="G7" s="15" t="n"/>
@@ -18751,7 +18747,7 @@
       <c r="I7" s="15" t="n"/>
       <c r="K7" s="14" t="inlineStr">
         <is>
-          <t>RGB: 246, 135, 92</t>
+          <t>RGB: 246, 135, 92, 128</t>
         </is>
       </c>
       <c r="L7" s="15" t="n"/>
@@ -18759,7 +18755,7 @@
       <c r="N7" s="15" t="n"/>
       <c r="P7" s="14" t="inlineStr">
         <is>
-          <t>RGB: 196, 199, 100</t>
+          <t>RGB: 196, 199, 100, 128</t>
         </is>
       </c>
       <c r="Q7" s="15" t="n"/>
@@ -18801,61 +18797,61 @@
       <c r="S8" s="15" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="392" t="inlineStr">
+      <c r="A9" s="387" t="inlineStr">
         <is>
           <t>CT05</t>
         </is>
       </c>
-      <c r="B9" s="393" t="n"/>
-      <c r="C9" s="393" t="n"/>
-      <c r="D9" s="393" t="n"/>
-      <c r="F9" s="394" t="inlineStr">
+      <c r="B9" s="392" t="n"/>
+      <c r="C9" s="385" t="n"/>
+      <c r="D9" s="392" t="n"/>
+      <c r="F9" s="393" t="inlineStr">
         <is>
           <t>CT06</t>
         </is>
       </c>
-      <c r="G9" s="395" t="n"/>
-      <c r="H9" s="395" t="n"/>
-      <c r="I9" s="395" t="n"/>
-      <c r="K9" s="396" t="inlineStr">
+      <c r="G9" s="385" t="n"/>
+      <c r="H9" s="394" t="n"/>
+      <c r="I9" s="385" t="n"/>
+      <c r="K9" s="387" t="inlineStr">
         <is>
           <t>CT07</t>
         </is>
       </c>
-      <c r="L9" s="397" t="n"/>
-      <c r="M9" s="397" t="n"/>
-      <c r="N9" s="397" t="n"/>
-      <c r="P9" s="398" t="inlineStr">
+      <c r="L9" s="395" t="n"/>
+      <c r="M9" s="385" t="n"/>
+      <c r="N9" s="395" t="n"/>
+      <c r="P9" s="396" t="inlineStr">
         <is>
           <t>CT08</t>
         </is>
       </c>
-      <c r="Q9" s="399" t="n"/>
-      <c r="R9" s="399" t="n"/>
-      <c r="S9" s="399" t="n"/>
+      <c r="Q9" s="385" t="n"/>
+      <c r="R9" s="397" t="n"/>
+      <c r="S9" s="385" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="393" t="n"/>
-      <c r="B10" s="393" t="n"/>
-      <c r="C10" s="393" t="n"/>
-      <c r="D10" s="393" t="n"/>
-      <c r="F10" s="395" t="n"/>
-      <c r="G10" s="395" t="n"/>
-      <c r="H10" s="395" t="n"/>
-      <c r="I10" s="395" t="n"/>
-      <c r="K10" s="397" t="n"/>
-      <c r="L10" s="397" t="n"/>
-      <c r="M10" s="397" t="n"/>
-      <c r="N10" s="397" t="n"/>
-      <c r="P10" s="399" t="n"/>
-      <c r="Q10" s="399" t="n"/>
-      <c r="R10" s="399" t="n"/>
-      <c r="S10" s="399" t="n"/>
+      <c r="A10" s="392" t="n"/>
+      <c r="B10" s="385" t="n"/>
+      <c r="C10" s="392" t="n"/>
+      <c r="D10" s="385" t="n"/>
+      <c r="F10" s="385" t="n"/>
+      <c r="G10" s="394" t="n"/>
+      <c r="H10" s="385" t="n"/>
+      <c r="I10" s="394" t="n"/>
+      <c r="K10" s="395" t="n"/>
+      <c r="L10" s="385" t="n"/>
+      <c r="M10" s="395" t="n"/>
+      <c r="N10" s="385" t="n"/>
+      <c r="P10" s="385" t="n"/>
+      <c r="Q10" s="397" t="n"/>
+      <c r="R10" s="385" t="n"/>
+      <c r="S10" s="397" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>HEX: #32B195</t>
+          <t>HEX: #32B19580</t>
         </is>
       </c>
       <c r="B11" s="15" t="n"/>
@@ -18863,7 +18859,7 @@
       <c r="D11" s="15" t="n"/>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>HEX: #757DD1</t>
+          <t>HEX: #757DD180</t>
         </is>
       </c>
       <c r="G11" s="15" t="n"/>
@@ -18871,7 +18867,7 @@
       <c r="I11" s="15" t="n"/>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>HEX: #4EB1DC</t>
+          <t>HEX: #4EB1DC80</t>
         </is>
       </c>
       <c r="L11" s="15" t="n"/>
@@ -18879,7 +18875,7 @@
       <c r="N11" s="15" t="n"/>
       <c r="P11" s="14" t="inlineStr">
         <is>
-          <t>HEX: #5688A0</t>
+          <t>HEX: #5688A080</t>
         </is>
       </c>
       <c r="Q11" s="15" t="n"/>
@@ -18889,7 +18885,7 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>RGB: 50, 177, 149</t>
+          <t>RGB: 50, 177, 149, 128</t>
         </is>
       </c>
       <c r="B12" s="15" t="n"/>
@@ -18897,7 +18893,7 @@
       <c r="D12" s="15" t="n"/>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>RGB: 117, 125, 209</t>
+          <t>RGB: 117, 125, 209, 128</t>
         </is>
       </c>
       <c r="G12" s="15" t="n"/>
@@ -18905,7 +18901,7 @@
       <c r="I12" s="15" t="n"/>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>RGB: 78, 177, 220</t>
+          <t>RGB: 78, 177, 220, 128</t>
         </is>
       </c>
       <c r="L12" s="15" t="n"/>
@@ -18913,7 +18909,7 @@
       <c r="N12" s="15" t="n"/>
       <c r="P12" s="14" t="inlineStr">
         <is>
-          <t>RGB: 86, 136, 160</t>
+          <t>RGB: 86, 136, 160, 128</t>
         </is>
       </c>
       <c r="Q12" s="15" t="n"/>
@@ -18955,25 +18951,25 @@
       <c r="S13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="400" t="inlineStr">
+      <c r="A14" s="398" t="inlineStr">
         <is>
           <t>CT09</t>
         </is>
       </c>
-      <c r="B14" s="401" t="n"/>
-      <c r="C14" s="401" t="n"/>
-      <c r="D14" s="401" t="n"/>
+      <c r="B14" s="385" t="n"/>
+      <c r="C14" s="399" t="n"/>
+      <c r="D14" s="385" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="401" t="n"/>
-      <c r="B15" s="401" t="n"/>
-      <c r="C15" s="401" t="n"/>
-      <c r="D15" s="401" t="n"/>
+      <c r="A15" s="385" t="n"/>
+      <c r="B15" s="399" t="n"/>
+      <c r="C15" s="385" t="n"/>
+      <c r="D15" s="399" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>HEX: #6B849D</t>
+          <t>HEX: #6B849D80</t>
         </is>
       </c>
       <c r="B16" s="15" t="n"/>
@@ -18983,7 +18979,7 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>RGB: 107, 132, 157</t>
+          <t>RGB: 107, 132, 157, 128</t>
         </is>
       </c>
       <c r="B17" s="15" t="n"/>
@@ -19001,12 +18997,11 @@
       <c r="D18" s="15" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="27">
     <mergeCell ref="F13:I13"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="P13:S13"/>
-    <mergeCell ref="P9:S10"/>
     <mergeCell ref="P12:S12"/>
     <mergeCell ref="K7:N7"/>
     <mergeCell ref="A13:D13"/>
@@ -19015,29 +19010,21 @@
     <mergeCell ref="F11:I11"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="F6:I6"/>
-    <mergeCell ref="A14:D15"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="F7:I7"/>
-    <mergeCell ref="F9:I10"/>
-    <mergeCell ref="A4:D5"/>
     <mergeCell ref="F12:I12"/>
     <mergeCell ref="K11:N11"/>
     <mergeCell ref="A7:D7"/>
-    <mergeCell ref="K4:N5"/>
     <mergeCell ref="P6:S6"/>
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="P8:S8"/>
     <mergeCell ref="P11:S11"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A9:D10"/>
     <mergeCell ref="F8:I8"/>
     <mergeCell ref="A12:D12"/>
-    <mergeCell ref="K9:N10"/>
-    <mergeCell ref="F4:I5"/>
     <mergeCell ref="K12:N12"/>
     <mergeCell ref="P7:S7"/>
     <mergeCell ref="K8:N8"/>
-    <mergeCell ref="P4:S5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19088,56 +19075,56 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="402" t="inlineStr">
+      <c r="A4" s="400" t="inlineStr">
         <is>
           <t>MA1</t>
         </is>
       </c>
-      <c r="B4" s="403" t="n"/>
-      <c r="C4" s="403" t="n"/>
-      <c r="D4" s="403" t="n"/>
-      <c r="F4" s="404" t="inlineStr">
+      <c r="B4" s="401" t="n"/>
+      <c r="C4" s="401" t="n"/>
+      <c r="D4" s="401" t="n"/>
+      <c r="F4" s="402" t="inlineStr">
         <is>
           <t>MA2</t>
         </is>
       </c>
-      <c r="G4" s="405" t="n"/>
-      <c r="H4" s="405" t="n"/>
-      <c r="I4" s="405" t="n"/>
-      <c r="K4" s="406" t="inlineStr">
+      <c r="G4" s="403" t="n"/>
+      <c r="H4" s="403" t="n"/>
+      <c r="I4" s="403" t="n"/>
+      <c r="K4" s="404" t="inlineStr">
         <is>
           <t>MA3</t>
         </is>
       </c>
-      <c r="L4" s="407" t="n"/>
-      <c r="M4" s="407" t="n"/>
-      <c r="N4" s="407" t="n"/>
-      <c r="P4" s="408" t="inlineStr">
+      <c r="L4" s="405" t="n"/>
+      <c r="M4" s="405" t="n"/>
+      <c r="N4" s="405" t="n"/>
+      <c r="P4" s="406" t="inlineStr">
         <is>
           <t>MA4</t>
         </is>
       </c>
-      <c r="Q4" s="409" t="n"/>
-      <c r="R4" s="409" t="n"/>
-      <c r="S4" s="409" t="n"/>
+      <c r="Q4" s="407" t="n"/>
+      <c r="R4" s="407" t="n"/>
+      <c r="S4" s="407" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="403" t="n"/>
-      <c r="B5" s="403" t="n"/>
-      <c r="C5" s="403" t="n"/>
-      <c r="D5" s="403" t="n"/>
-      <c r="F5" s="405" t="n"/>
-      <c r="G5" s="405" t="n"/>
-      <c r="H5" s="405" t="n"/>
-      <c r="I5" s="405" t="n"/>
-      <c r="K5" s="407" t="n"/>
-      <c r="L5" s="407" t="n"/>
-      <c r="M5" s="407" t="n"/>
-      <c r="N5" s="407" t="n"/>
-      <c r="P5" s="409" t="n"/>
-      <c r="Q5" s="409" t="n"/>
-      <c r="R5" s="409" t="n"/>
-      <c r="S5" s="409" t="n"/>
+      <c r="A5" s="401" t="n"/>
+      <c r="B5" s="401" t="n"/>
+      <c r="C5" s="401" t="n"/>
+      <c r="D5" s="401" t="n"/>
+      <c r="F5" s="403" t="n"/>
+      <c r="G5" s="403" t="n"/>
+      <c r="H5" s="403" t="n"/>
+      <c r="I5" s="403" t="n"/>
+      <c r="K5" s="405" t="n"/>
+      <c r="L5" s="405" t="n"/>
+      <c r="M5" s="405" t="n"/>
+      <c r="N5" s="405" t="n"/>
+      <c r="P5" s="407" t="n"/>
+      <c r="Q5" s="407" t="n"/>
+      <c r="R5" s="407" t="n"/>
+      <c r="S5" s="407" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -19242,56 +19229,56 @@
       <c r="S8" s="15" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="410" t="inlineStr">
+      <c r="A9" s="408" t="inlineStr">
         <is>
           <t>MA5</t>
         </is>
       </c>
-      <c r="B9" s="411" t="n"/>
-      <c r="C9" s="411" t="n"/>
-      <c r="D9" s="411" t="n"/>
-      <c r="F9" s="412" t="inlineStr">
+      <c r="B9" s="409" t="n"/>
+      <c r="C9" s="409" t="n"/>
+      <c r="D9" s="409" t="n"/>
+      <c r="F9" s="410" t="inlineStr">
         <is>
           <t>MA6</t>
         </is>
       </c>
-      <c r="G9" s="413" t="n"/>
-      <c r="H9" s="413" t="n"/>
-      <c r="I9" s="413" t="n"/>
-      <c r="K9" s="414" t="inlineStr">
+      <c r="G9" s="411" t="n"/>
+      <c r="H9" s="411" t="n"/>
+      <c r="I9" s="411" t="n"/>
+      <c r="K9" s="412" t="inlineStr">
         <is>
           <t>MA7</t>
         </is>
       </c>
-      <c r="L9" s="415" t="n"/>
-      <c r="M9" s="415" t="n"/>
-      <c r="N9" s="415" t="n"/>
-      <c r="P9" s="416" t="inlineStr">
+      <c r="L9" s="413" t="n"/>
+      <c r="M9" s="413" t="n"/>
+      <c r="N9" s="413" t="n"/>
+      <c r="P9" s="414" t="inlineStr">
         <is>
           <t>MA8</t>
         </is>
       </c>
-      <c r="Q9" s="417" t="n"/>
-      <c r="R9" s="417" t="n"/>
-      <c r="S9" s="417" t="n"/>
+      <c r="Q9" s="415" t="n"/>
+      <c r="R9" s="415" t="n"/>
+      <c r="S9" s="415" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="411" t="n"/>
-      <c r="B10" s="411" t="n"/>
-      <c r="C10" s="411" t="n"/>
-      <c r="D10" s="411" t="n"/>
-      <c r="F10" s="413" t="n"/>
-      <c r="G10" s="413" t="n"/>
-      <c r="H10" s="413" t="n"/>
-      <c r="I10" s="413" t="n"/>
-      <c r="K10" s="415" t="n"/>
-      <c r="L10" s="415" t="n"/>
-      <c r="M10" s="415" t="n"/>
-      <c r="N10" s="415" t="n"/>
-      <c r="P10" s="417" t="n"/>
-      <c r="Q10" s="417" t="n"/>
-      <c r="R10" s="417" t="n"/>
-      <c r="S10" s="417" t="n"/>
+      <c r="A10" s="409" t="n"/>
+      <c r="B10" s="409" t="n"/>
+      <c r="C10" s="409" t="n"/>
+      <c r="D10" s="409" t="n"/>
+      <c r="F10" s="411" t="n"/>
+      <c r="G10" s="411" t="n"/>
+      <c r="H10" s="411" t="n"/>
+      <c r="I10" s="411" t="n"/>
+      <c r="K10" s="413" t="n"/>
+      <c r="L10" s="413" t="n"/>
+      <c r="M10" s="413" t="n"/>
+      <c r="N10" s="413" t="n"/>
+      <c r="P10" s="415" t="n"/>
+      <c r="Q10" s="415" t="n"/>
+      <c r="R10" s="415" t="n"/>
+      <c r="S10" s="415" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -19396,56 +19383,56 @@
       <c r="S13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="418" t="inlineStr">
+      <c r="A14" s="416" t="inlineStr">
         <is>
           <t>MA9</t>
         </is>
       </c>
-      <c r="B14" s="419" t="n"/>
-      <c r="C14" s="419" t="n"/>
-      <c r="D14" s="419" t="n"/>
-      <c r="F14" s="420" t="inlineStr">
+      <c r="B14" s="417" t="n"/>
+      <c r="C14" s="417" t="n"/>
+      <c r="D14" s="417" t="n"/>
+      <c r="F14" s="418" t="inlineStr">
         <is>
           <t>MA10</t>
         </is>
       </c>
-      <c r="G14" s="421" t="n"/>
-      <c r="H14" s="421" t="n"/>
-      <c r="I14" s="421" t="n"/>
-      <c r="K14" s="422" t="inlineStr">
+      <c r="G14" s="419" t="n"/>
+      <c r="H14" s="419" t="n"/>
+      <c r="I14" s="419" t="n"/>
+      <c r="K14" s="420" t="inlineStr">
         <is>
           <t>MA11</t>
         </is>
       </c>
-      <c r="L14" s="423" t="n"/>
-      <c r="M14" s="423" t="n"/>
-      <c r="N14" s="423" t="n"/>
-      <c r="P14" s="424" t="inlineStr">
+      <c r="L14" s="421" t="n"/>
+      <c r="M14" s="421" t="n"/>
+      <c r="N14" s="421" t="n"/>
+      <c r="P14" s="422" t="inlineStr">
         <is>
           <t>MA12</t>
         </is>
       </c>
-      <c r="Q14" s="425" t="n"/>
-      <c r="R14" s="425" t="n"/>
-      <c r="S14" s="425" t="n"/>
+      <c r="Q14" s="423" t="n"/>
+      <c r="R14" s="423" t="n"/>
+      <c r="S14" s="423" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="419" t="n"/>
-      <c r="B15" s="419" t="n"/>
-      <c r="C15" s="419" t="n"/>
-      <c r="D15" s="419" t="n"/>
-      <c r="F15" s="421" t="n"/>
-      <c r="G15" s="421" t="n"/>
-      <c r="H15" s="421" t="n"/>
-      <c r="I15" s="421" t="n"/>
-      <c r="K15" s="423" t="n"/>
-      <c r="L15" s="423" t="n"/>
-      <c r="M15" s="423" t="n"/>
-      <c r="N15" s="423" t="n"/>
-      <c r="P15" s="425" t="n"/>
-      <c r="Q15" s="425" t="n"/>
-      <c r="R15" s="425" t="n"/>
-      <c r="S15" s="425" t="n"/>
+      <c r="A15" s="417" t="n"/>
+      <c r="B15" s="417" t="n"/>
+      <c r="C15" s="417" t="n"/>
+      <c r="D15" s="417" t="n"/>
+      <c r="F15" s="419" t="n"/>
+      <c r="G15" s="419" t="n"/>
+      <c r="H15" s="419" t="n"/>
+      <c r="I15" s="419" t="n"/>
+      <c r="K15" s="421" t="n"/>
+      <c r="L15" s="421" t="n"/>
+      <c r="M15" s="421" t="n"/>
+      <c r="N15" s="421" t="n"/>
+      <c r="P15" s="423" t="n"/>
+      <c r="Q15" s="423" t="n"/>
+      <c r="R15" s="423" t="n"/>
+      <c r="S15" s="423" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -19550,56 +19537,56 @@
       <c r="S18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="426" t="inlineStr">
+      <c r="A19" s="424" t="inlineStr">
         <is>
           <t>MA13</t>
         </is>
       </c>
-      <c r="B19" s="427" t="n"/>
-      <c r="C19" s="427" t="n"/>
-      <c r="D19" s="427" t="n"/>
-      <c r="F19" s="428" t="inlineStr">
+      <c r="B19" s="425" t="n"/>
+      <c r="C19" s="425" t="n"/>
+      <c r="D19" s="425" t="n"/>
+      <c r="F19" s="426" t="inlineStr">
         <is>
           <t>MA14</t>
         </is>
       </c>
-      <c r="G19" s="429" t="n"/>
-      <c r="H19" s="429" t="n"/>
-      <c r="I19" s="429" t="n"/>
-      <c r="K19" s="430" t="inlineStr">
+      <c r="G19" s="427" t="n"/>
+      <c r="H19" s="427" t="n"/>
+      <c r="I19" s="427" t="n"/>
+      <c r="K19" s="428" t="inlineStr">
         <is>
           <t>MA15</t>
         </is>
       </c>
-      <c r="L19" s="431" t="n"/>
-      <c r="M19" s="431" t="n"/>
-      <c r="N19" s="431" t="n"/>
-      <c r="P19" s="432" t="inlineStr">
+      <c r="L19" s="429" t="n"/>
+      <c r="M19" s="429" t="n"/>
+      <c r="N19" s="429" t="n"/>
+      <c r="P19" s="430" t="inlineStr">
         <is>
           <t>MA16</t>
         </is>
       </c>
-      <c r="Q19" s="433" t="n"/>
-      <c r="R19" s="433" t="n"/>
-      <c r="S19" s="433" t="n"/>
+      <c r="Q19" s="431" t="n"/>
+      <c r="R19" s="431" t="n"/>
+      <c r="S19" s="431" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="427" t="n"/>
-      <c r="B20" s="427" t="n"/>
-      <c r="C20" s="427" t="n"/>
-      <c r="D20" s="427" t="n"/>
-      <c r="F20" s="429" t="n"/>
-      <c r="G20" s="429" t="n"/>
-      <c r="H20" s="429" t="n"/>
-      <c r="I20" s="429" t="n"/>
-      <c r="K20" s="431" t="n"/>
-      <c r="L20" s="431" t="n"/>
-      <c r="M20" s="431" t="n"/>
-      <c r="N20" s="431" t="n"/>
-      <c r="P20" s="433" t="n"/>
-      <c r="Q20" s="433" t="n"/>
-      <c r="R20" s="433" t="n"/>
-      <c r="S20" s="433" t="n"/>
+      <c r="A20" s="425" t="n"/>
+      <c r="B20" s="425" t="n"/>
+      <c r="C20" s="425" t="n"/>
+      <c r="D20" s="425" t="n"/>
+      <c r="F20" s="427" t="n"/>
+      <c r="G20" s="427" t="n"/>
+      <c r="H20" s="427" t="n"/>
+      <c r="I20" s="427" t="n"/>
+      <c r="K20" s="429" t="n"/>
+      <c r="L20" s="429" t="n"/>
+      <c r="M20" s="429" t="n"/>
+      <c r="N20" s="429" t="n"/>
+      <c r="P20" s="431" t="n"/>
+      <c r="Q20" s="431" t="n"/>
+      <c r="R20" s="431" t="n"/>
+      <c r="S20" s="431" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -19704,56 +19691,56 @@
       <c r="S23" s="15" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="434" t="inlineStr">
+      <c r="A24" s="432" t="inlineStr">
         <is>
           <t>MA17</t>
         </is>
       </c>
-      <c r="B24" s="435" t="n"/>
-      <c r="C24" s="435" t="n"/>
-      <c r="D24" s="435" t="n"/>
-      <c r="F24" s="436" t="inlineStr">
+      <c r="B24" s="433" t="n"/>
+      <c r="C24" s="433" t="n"/>
+      <c r="D24" s="433" t="n"/>
+      <c r="F24" s="434" t="inlineStr">
         <is>
           <t>MA18</t>
         </is>
       </c>
-      <c r="G24" s="437" t="n"/>
-      <c r="H24" s="437" t="n"/>
-      <c r="I24" s="437" t="n"/>
-      <c r="K24" s="438" t="inlineStr">
+      <c r="G24" s="435" t="n"/>
+      <c r="H24" s="435" t="n"/>
+      <c r="I24" s="435" t="n"/>
+      <c r="K24" s="436" t="inlineStr">
         <is>
           <t>MA19</t>
         </is>
       </c>
-      <c r="L24" s="439" t="n"/>
-      <c r="M24" s="439" t="n"/>
-      <c r="N24" s="439" t="n"/>
-      <c r="P24" s="440" t="inlineStr">
+      <c r="L24" s="437" t="n"/>
+      <c r="M24" s="437" t="n"/>
+      <c r="N24" s="437" t="n"/>
+      <c r="P24" s="438" t="inlineStr">
         <is>
           <t>MA20</t>
         </is>
       </c>
-      <c r="Q24" s="441" t="n"/>
-      <c r="R24" s="441" t="n"/>
-      <c r="S24" s="441" t="n"/>
+      <c r="Q24" s="439" t="n"/>
+      <c r="R24" s="439" t="n"/>
+      <c r="S24" s="439" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="435" t="n"/>
-      <c r="B25" s="435" t="n"/>
-      <c r="C25" s="435" t="n"/>
-      <c r="D25" s="435" t="n"/>
-      <c r="F25" s="437" t="n"/>
-      <c r="G25" s="437" t="n"/>
-      <c r="H25" s="437" t="n"/>
-      <c r="I25" s="437" t="n"/>
-      <c r="K25" s="439" t="n"/>
-      <c r="L25" s="439" t="n"/>
-      <c r="M25" s="439" t="n"/>
-      <c r="N25" s="439" t="n"/>
-      <c r="P25" s="441" t="n"/>
-      <c r="Q25" s="441" t="n"/>
-      <c r="R25" s="441" t="n"/>
-      <c r="S25" s="441" t="n"/>
+      <c r="A25" s="433" t="n"/>
+      <c r="B25" s="433" t="n"/>
+      <c r="C25" s="433" t="n"/>
+      <c r="D25" s="433" t="n"/>
+      <c r="F25" s="435" t="n"/>
+      <c r="G25" s="435" t="n"/>
+      <c r="H25" s="435" t="n"/>
+      <c r="I25" s="435" t="n"/>
+      <c r="K25" s="437" t="n"/>
+      <c r="L25" s="437" t="n"/>
+      <c r="M25" s="437" t="n"/>
+      <c r="N25" s="437" t="n"/>
+      <c r="P25" s="439" t="n"/>
+      <c r="Q25" s="439" t="n"/>
+      <c r="R25" s="439" t="n"/>
+      <c r="S25" s="439" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
@@ -19858,56 +19845,56 @@
       <c r="S28" s="15" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="442" t="inlineStr">
+      <c r="A29" s="440" t="inlineStr">
         <is>
           <t>MA21</t>
         </is>
       </c>
-      <c r="B29" s="443" t="n"/>
-      <c r="C29" s="443" t="n"/>
-      <c r="D29" s="443" t="n"/>
-      <c r="F29" s="444" t="inlineStr">
+      <c r="B29" s="441" t="n"/>
+      <c r="C29" s="441" t="n"/>
+      <c r="D29" s="441" t="n"/>
+      <c r="F29" s="442" t="inlineStr">
         <is>
           <t>MA22</t>
         </is>
       </c>
-      <c r="G29" s="445" t="n"/>
-      <c r="H29" s="445" t="n"/>
-      <c r="I29" s="445" t="n"/>
-      <c r="K29" s="446" t="inlineStr">
+      <c r="G29" s="443" t="n"/>
+      <c r="H29" s="443" t="n"/>
+      <c r="I29" s="443" t="n"/>
+      <c r="K29" s="444" t="inlineStr">
         <is>
           <t>MA23</t>
         </is>
       </c>
-      <c r="L29" s="447" t="n"/>
-      <c r="M29" s="447" t="n"/>
-      <c r="N29" s="447" t="n"/>
-      <c r="P29" s="448" t="inlineStr">
+      <c r="L29" s="445" t="n"/>
+      <c r="M29" s="445" t="n"/>
+      <c r="N29" s="445" t="n"/>
+      <c r="P29" s="446" t="inlineStr">
         <is>
           <t>MA24</t>
         </is>
       </c>
-      <c r="Q29" s="449" t="n"/>
-      <c r="R29" s="449" t="n"/>
-      <c r="S29" s="449" t="n"/>
+      <c r="Q29" s="447" t="n"/>
+      <c r="R29" s="447" t="n"/>
+      <c r="S29" s="447" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="443" t="n"/>
-      <c r="B30" s="443" t="n"/>
-      <c r="C30" s="443" t="n"/>
-      <c r="D30" s="443" t="n"/>
-      <c r="F30" s="445" t="n"/>
-      <c r="G30" s="445" t="n"/>
-      <c r="H30" s="445" t="n"/>
-      <c r="I30" s="445" t="n"/>
-      <c r="K30" s="447" t="n"/>
-      <c r="L30" s="447" t="n"/>
-      <c r="M30" s="447" t="n"/>
-      <c r="N30" s="447" t="n"/>
-      <c r="P30" s="449" t="n"/>
-      <c r="Q30" s="449" t="n"/>
-      <c r="R30" s="449" t="n"/>
-      <c r="S30" s="449" t="n"/>
+      <c r="A30" s="441" t="n"/>
+      <c r="B30" s="441" t="n"/>
+      <c r="C30" s="441" t="n"/>
+      <c r="D30" s="441" t="n"/>
+      <c r="F30" s="443" t="n"/>
+      <c r="G30" s="443" t="n"/>
+      <c r="H30" s="443" t="n"/>
+      <c r="I30" s="443" t="n"/>
+      <c r="K30" s="445" t="n"/>
+      <c r="L30" s="445" t="n"/>
+      <c r="M30" s="445" t="n"/>
+      <c r="N30" s="445" t="n"/>
+      <c r="P30" s="447" t="n"/>
+      <c r="Q30" s="447" t="n"/>
+      <c r="R30" s="447" t="n"/>
+      <c r="S30" s="447" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -20012,32 +19999,32 @@
       <c r="S33" s="15" t="n"/>
     </row>
     <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="450" t="inlineStr">
+      <c r="A34" s="448" t="inlineStr">
         <is>
           <t>MA25</t>
         </is>
       </c>
-      <c r="B34" s="451" t="n"/>
-      <c r="C34" s="451" t="n"/>
-      <c r="D34" s="451" t="n"/>
-      <c r="F34" s="452" t="inlineStr">
+      <c r="B34" s="449" t="n"/>
+      <c r="C34" s="449" t="n"/>
+      <c r="D34" s="449" t="n"/>
+      <c r="F34" s="450" t="inlineStr">
         <is>
           <t>MA26</t>
         </is>
       </c>
-      <c r="G34" s="453" t="n"/>
-      <c r="H34" s="453" t="n"/>
-      <c r="I34" s="453" t="n"/>
+      <c r="G34" s="451" t="n"/>
+      <c r="H34" s="451" t="n"/>
+      <c r="I34" s="451" t="n"/>
     </row>
     <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="451" t="n"/>
-      <c r="B35" s="451" t="n"/>
-      <c r="C35" s="451" t="n"/>
-      <c r="D35" s="451" t="n"/>
-      <c r="F35" s="453" t="n"/>
-      <c r="G35" s="453" t="n"/>
-      <c r="H35" s="453" t="n"/>
-      <c r="I35" s="453" t="n"/>
+      <c r="A35" s="449" t="n"/>
+      <c r="B35" s="449" t="n"/>
+      <c r="C35" s="449" t="n"/>
+      <c r="D35" s="449" t="n"/>
+      <c r="F35" s="451" t="n"/>
+      <c r="G35" s="451" t="n"/>
+      <c r="H35" s="451" t="n"/>
+      <c r="I35" s="451" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -20249,56 +20236,56 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="454" t="inlineStr">
+      <c r="A4" s="452" t="inlineStr">
         <is>
           <t>MB1</t>
         </is>
       </c>
-      <c r="B4" s="455" t="n"/>
-      <c r="C4" s="455" t="n"/>
-      <c r="D4" s="455" t="n"/>
-      <c r="F4" s="456" t="inlineStr">
+      <c r="B4" s="453" t="n"/>
+      <c r="C4" s="453" t="n"/>
+      <c r="D4" s="453" t="n"/>
+      <c r="F4" s="454" t="inlineStr">
         <is>
           <t>MB2</t>
         </is>
       </c>
-      <c r="G4" s="457" t="n"/>
-      <c r="H4" s="457" t="n"/>
-      <c r="I4" s="457" t="n"/>
-      <c r="K4" s="458" t="inlineStr">
+      <c r="G4" s="455" t="n"/>
+      <c r="H4" s="455" t="n"/>
+      <c r="I4" s="455" t="n"/>
+      <c r="K4" s="456" t="inlineStr">
         <is>
           <t>MB3</t>
         </is>
       </c>
-      <c r="L4" s="459" t="n"/>
-      <c r="M4" s="459" t="n"/>
-      <c r="N4" s="459" t="n"/>
-      <c r="P4" s="460" t="inlineStr">
+      <c r="L4" s="457" t="n"/>
+      <c r="M4" s="457" t="n"/>
+      <c r="N4" s="457" t="n"/>
+      <c r="P4" s="458" t="inlineStr">
         <is>
           <t>MB4</t>
         </is>
       </c>
-      <c r="Q4" s="461" t="n"/>
-      <c r="R4" s="461" t="n"/>
-      <c r="S4" s="461" t="n"/>
+      <c r="Q4" s="459" t="n"/>
+      <c r="R4" s="459" t="n"/>
+      <c r="S4" s="459" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="455" t="n"/>
-      <c r="B5" s="455" t="n"/>
-      <c r="C5" s="455" t="n"/>
-      <c r="D5" s="455" t="n"/>
-      <c r="F5" s="457" t="n"/>
-      <c r="G5" s="457" t="n"/>
-      <c r="H5" s="457" t="n"/>
-      <c r="I5" s="457" t="n"/>
-      <c r="K5" s="459" t="n"/>
-      <c r="L5" s="459" t="n"/>
-      <c r="M5" s="459" t="n"/>
-      <c r="N5" s="459" t="n"/>
-      <c r="P5" s="461" t="n"/>
-      <c r="Q5" s="461" t="n"/>
-      <c r="R5" s="461" t="n"/>
-      <c r="S5" s="461" t="n"/>
+      <c r="A5" s="453" t="n"/>
+      <c r="B5" s="453" t="n"/>
+      <c r="C5" s="453" t="n"/>
+      <c r="D5" s="453" t="n"/>
+      <c r="F5" s="455" t="n"/>
+      <c r="G5" s="455" t="n"/>
+      <c r="H5" s="455" t="n"/>
+      <c r="I5" s="455" t="n"/>
+      <c r="K5" s="457" t="n"/>
+      <c r="L5" s="457" t="n"/>
+      <c r="M5" s="457" t="n"/>
+      <c r="N5" s="457" t="n"/>
+      <c r="P5" s="459" t="n"/>
+      <c r="Q5" s="459" t="n"/>
+      <c r="R5" s="459" t="n"/>
+      <c r="S5" s="459" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -20403,56 +20390,56 @@
       <c r="S8" s="15" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="462" t="inlineStr">
+      <c r="A9" s="460" t="inlineStr">
         <is>
           <t>MB5</t>
         </is>
       </c>
-      <c r="B9" s="463" t="n"/>
-      <c r="C9" s="463" t="n"/>
-      <c r="D9" s="463" t="n"/>
-      <c r="F9" s="464" t="inlineStr">
+      <c r="B9" s="461" t="n"/>
+      <c r="C9" s="461" t="n"/>
+      <c r="D9" s="461" t="n"/>
+      <c r="F9" s="462" t="inlineStr">
         <is>
           <t>MB6</t>
         </is>
       </c>
-      <c r="G9" s="465" t="n"/>
-      <c r="H9" s="465" t="n"/>
-      <c r="I9" s="465" t="n"/>
-      <c r="K9" s="466" t="inlineStr">
+      <c r="G9" s="463" t="n"/>
+      <c r="H9" s="463" t="n"/>
+      <c r="I9" s="463" t="n"/>
+      <c r="K9" s="464" t="inlineStr">
         <is>
           <t>MB7</t>
         </is>
       </c>
-      <c r="L9" s="467" t="n"/>
-      <c r="M9" s="467" t="n"/>
-      <c r="N9" s="467" t="n"/>
-      <c r="P9" s="468" t="inlineStr">
+      <c r="L9" s="465" t="n"/>
+      <c r="M9" s="465" t="n"/>
+      <c r="N9" s="465" t="n"/>
+      <c r="P9" s="466" t="inlineStr">
         <is>
           <t>MB8</t>
         </is>
       </c>
-      <c r="Q9" s="469" t="n"/>
-      <c r="R9" s="469" t="n"/>
-      <c r="S9" s="469" t="n"/>
+      <c r="Q9" s="467" t="n"/>
+      <c r="R9" s="467" t="n"/>
+      <c r="S9" s="467" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="463" t="n"/>
-      <c r="B10" s="463" t="n"/>
-      <c r="C10" s="463" t="n"/>
-      <c r="D10" s="463" t="n"/>
-      <c r="F10" s="465" t="n"/>
-      <c r="G10" s="465" t="n"/>
-      <c r="H10" s="465" t="n"/>
-      <c r="I10" s="465" t="n"/>
-      <c r="K10" s="467" t="n"/>
-      <c r="L10" s="467" t="n"/>
-      <c r="M10" s="467" t="n"/>
-      <c r="N10" s="467" t="n"/>
-      <c r="P10" s="469" t="n"/>
-      <c r="Q10" s="469" t="n"/>
-      <c r="R10" s="469" t="n"/>
-      <c r="S10" s="469" t="n"/>
+      <c r="A10" s="461" t="n"/>
+      <c r="B10" s="461" t="n"/>
+      <c r="C10" s="461" t="n"/>
+      <c r="D10" s="461" t="n"/>
+      <c r="F10" s="463" t="n"/>
+      <c r="G10" s="463" t="n"/>
+      <c r="H10" s="463" t="n"/>
+      <c r="I10" s="463" t="n"/>
+      <c r="K10" s="465" t="n"/>
+      <c r="L10" s="465" t="n"/>
+      <c r="M10" s="465" t="n"/>
+      <c r="N10" s="465" t="n"/>
+      <c r="P10" s="467" t="n"/>
+      <c r="Q10" s="467" t="n"/>
+      <c r="R10" s="467" t="n"/>
+      <c r="S10" s="467" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -20557,56 +20544,56 @@
       <c r="S13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="470" t="inlineStr">
+      <c r="A14" s="468" t="inlineStr">
         <is>
           <t>MB9</t>
         </is>
       </c>
-      <c r="B14" s="471" t="n"/>
-      <c r="C14" s="471" t="n"/>
-      <c r="D14" s="471" t="n"/>
-      <c r="F14" s="472" t="inlineStr">
+      <c r="B14" s="469" t="n"/>
+      <c r="C14" s="469" t="n"/>
+      <c r="D14" s="469" t="n"/>
+      <c r="F14" s="470" t="inlineStr">
         <is>
           <t>MB10</t>
         </is>
       </c>
-      <c r="G14" s="473" t="n"/>
-      <c r="H14" s="473" t="n"/>
-      <c r="I14" s="473" t="n"/>
-      <c r="K14" s="474" t="inlineStr">
+      <c r="G14" s="471" t="n"/>
+      <c r="H14" s="471" t="n"/>
+      <c r="I14" s="471" t="n"/>
+      <c r="K14" s="472" t="inlineStr">
         <is>
           <t>MB11</t>
         </is>
       </c>
-      <c r="L14" s="475" t="n"/>
-      <c r="M14" s="475" t="n"/>
-      <c r="N14" s="475" t="n"/>
-      <c r="P14" s="476" t="inlineStr">
+      <c r="L14" s="473" t="n"/>
+      <c r="M14" s="473" t="n"/>
+      <c r="N14" s="473" t="n"/>
+      <c r="P14" s="474" t="inlineStr">
         <is>
           <t>MB12</t>
         </is>
       </c>
-      <c r="Q14" s="477" t="n"/>
-      <c r="R14" s="477" t="n"/>
-      <c r="S14" s="477" t="n"/>
+      <c r="Q14" s="475" t="n"/>
+      <c r="R14" s="475" t="n"/>
+      <c r="S14" s="475" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="471" t="n"/>
-      <c r="B15" s="471" t="n"/>
-      <c r="C15" s="471" t="n"/>
-      <c r="D15" s="471" t="n"/>
-      <c r="F15" s="473" t="n"/>
-      <c r="G15" s="473" t="n"/>
-      <c r="H15" s="473" t="n"/>
-      <c r="I15" s="473" t="n"/>
-      <c r="K15" s="475" t="n"/>
-      <c r="L15" s="475" t="n"/>
-      <c r="M15" s="475" t="n"/>
-      <c r="N15" s="475" t="n"/>
-      <c r="P15" s="477" t="n"/>
-      <c r="Q15" s="477" t="n"/>
-      <c r="R15" s="477" t="n"/>
-      <c r="S15" s="477" t="n"/>
+      <c r="A15" s="469" t="n"/>
+      <c r="B15" s="469" t="n"/>
+      <c r="C15" s="469" t="n"/>
+      <c r="D15" s="469" t="n"/>
+      <c r="F15" s="471" t="n"/>
+      <c r="G15" s="471" t="n"/>
+      <c r="H15" s="471" t="n"/>
+      <c r="I15" s="471" t="n"/>
+      <c r="K15" s="473" t="n"/>
+      <c r="L15" s="473" t="n"/>
+      <c r="M15" s="473" t="n"/>
+      <c r="N15" s="473" t="n"/>
+      <c r="P15" s="475" t="n"/>
+      <c r="Q15" s="475" t="n"/>
+      <c r="R15" s="475" t="n"/>
+      <c r="S15" s="475" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -20711,56 +20698,56 @@
       <c r="S18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="478" t="inlineStr">
+      <c r="A19" s="476" t="inlineStr">
         <is>
           <t>MB13</t>
         </is>
       </c>
-      <c r="B19" s="479" t="n"/>
-      <c r="C19" s="479" t="n"/>
-      <c r="D19" s="479" t="n"/>
-      <c r="F19" s="480" t="inlineStr">
+      <c r="B19" s="477" t="n"/>
+      <c r="C19" s="477" t="n"/>
+      <c r="D19" s="477" t="n"/>
+      <c r="F19" s="478" t="inlineStr">
         <is>
           <t>MB14</t>
         </is>
       </c>
-      <c r="G19" s="481" t="n"/>
-      <c r="H19" s="481" t="n"/>
-      <c r="I19" s="481" t="n"/>
-      <c r="K19" s="482" t="inlineStr">
+      <c r="G19" s="479" t="n"/>
+      <c r="H19" s="479" t="n"/>
+      <c r="I19" s="479" t="n"/>
+      <c r="K19" s="480" t="inlineStr">
         <is>
           <t>MB15</t>
         </is>
       </c>
-      <c r="L19" s="483" t="n"/>
-      <c r="M19" s="483" t="n"/>
-      <c r="N19" s="483" t="n"/>
-      <c r="P19" s="484" t="inlineStr">
+      <c r="L19" s="481" t="n"/>
+      <c r="M19" s="481" t="n"/>
+      <c r="N19" s="481" t="n"/>
+      <c r="P19" s="482" t="inlineStr">
         <is>
           <t>MB16</t>
         </is>
       </c>
-      <c r="Q19" s="485" t="n"/>
-      <c r="R19" s="485" t="n"/>
-      <c r="S19" s="485" t="n"/>
+      <c r="Q19" s="483" t="n"/>
+      <c r="R19" s="483" t="n"/>
+      <c r="S19" s="483" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="479" t="n"/>
-      <c r="B20" s="479" t="n"/>
-      <c r="C20" s="479" t="n"/>
-      <c r="D20" s="479" t="n"/>
-      <c r="F20" s="481" t="n"/>
-      <c r="G20" s="481" t="n"/>
-      <c r="H20" s="481" t="n"/>
-      <c r="I20" s="481" t="n"/>
-      <c r="K20" s="483" t="n"/>
-      <c r="L20" s="483" t="n"/>
-      <c r="M20" s="483" t="n"/>
-      <c r="N20" s="483" t="n"/>
-      <c r="P20" s="485" t="n"/>
-      <c r="Q20" s="485" t="n"/>
-      <c r="R20" s="485" t="n"/>
-      <c r="S20" s="485" t="n"/>
+      <c r="A20" s="477" t="n"/>
+      <c r="B20" s="477" t="n"/>
+      <c r="C20" s="477" t="n"/>
+      <c r="D20" s="477" t="n"/>
+      <c r="F20" s="479" t="n"/>
+      <c r="G20" s="479" t="n"/>
+      <c r="H20" s="479" t="n"/>
+      <c r="I20" s="479" t="n"/>
+      <c r="K20" s="481" t="n"/>
+      <c r="L20" s="481" t="n"/>
+      <c r="M20" s="481" t="n"/>
+      <c r="N20" s="481" t="n"/>
+      <c r="P20" s="483" t="n"/>
+      <c r="Q20" s="483" t="n"/>
+      <c r="R20" s="483" t="n"/>
+      <c r="S20" s="483" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -20865,56 +20852,56 @@
       <c r="S23" s="15" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="486" t="inlineStr">
+      <c r="A24" s="484" t="inlineStr">
         <is>
           <t>MB17</t>
         </is>
       </c>
-      <c r="B24" s="487" t="n"/>
-      <c r="C24" s="487" t="n"/>
-      <c r="D24" s="487" t="n"/>
-      <c r="F24" s="488" t="inlineStr">
+      <c r="B24" s="485" t="n"/>
+      <c r="C24" s="485" t="n"/>
+      <c r="D24" s="485" t="n"/>
+      <c r="F24" s="486" t="inlineStr">
         <is>
           <t>MB18</t>
         </is>
       </c>
-      <c r="G24" s="489" t="n"/>
-      <c r="H24" s="489" t="n"/>
-      <c r="I24" s="489" t="n"/>
-      <c r="K24" s="490" t="inlineStr">
+      <c r="G24" s="487" t="n"/>
+      <c r="H24" s="487" t="n"/>
+      <c r="I24" s="487" t="n"/>
+      <c r="K24" s="488" t="inlineStr">
         <is>
           <t>MB19</t>
         </is>
       </c>
-      <c r="L24" s="491" t="n"/>
-      <c r="M24" s="491" t="n"/>
-      <c r="N24" s="491" t="n"/>
-      <c r="P24" s="492" t="inlineStr">
+      <c r="L24" s="489" t="n"/>
+      <c r="M24" s="489" t="n"/>
+      <c r="N24" s="489" t="n"/>
+      <c r="P24" s="490" t="inlineStr">
         <is>
           <t>MB20</t>
         </is>
       </c>
-      <c r="Q24" s="493" t="n"/>
-      <c r="R24" s="493" t="n"/>
-      <c r="S24" s="493" t="n"/>
+      <c r="Q24" s="491" t="n"/>
+      <c r="R24" s="491" t="n"/>
+      <c r="S24" s="491" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="487" t="n"/>
-      <c r="B25" s="487" t="n"/>
-      <c r="C25" s="487" t="n"/>
-      <c r="D25" s="487" t="n"/>
-      <c r="F25" s="489" t="n"/>
-      <c r="G25" s="489" t="n"/>
-      <c r="H25" s="489" t="n"/>
-      <c r="I25" s="489" t="n"/>
-      <c r="K25" s="491" t="n"/>
-      <c r="L25" s="491" t="n"/>
-      <c r="M25" s="491" t="n"/>
-      <c r="N25" s="491" t="n"/>
-      <c r="P25" s="493" t="n"/>
-      <c r="Q25" s="493" t="n"/>
-      <c r="R25" s="493" t="n"/>
-      <c r="S25" s="493" t="n"/>
+      <c r="A25" s="485" t="n"/>
+      <c r="B25" s="485" t="n"/>
+      <c r="C25" s="485" t="n"/>
+      <c r="D25" s="485" t="n"/>
+      <c r="F25" s="487" t="n"/>
+      <c r="G25" s="487" t="n"/>
+      <c r="H25" s="487" t="n"/>
+      <c r="I25" s="487" t="n"/>
+      <c r="K25" s="489" t="n"/>
+      <c r="L25" s="489" t="n"/>
+      <c r="M25" s="489" t="n"/>
+      <c r="N25" s="489" t="n"/>
+      <c r="P25" s="491" t="n"/>
+      <c r="Q25" s="491" t="n"/>
+      <c r="R25" s="491" t="n"/>
+      <c r="S25" s="491" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
@@ -21019,56 +21006,56 @@
       <c r="S28" s="15" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="494" t="inlineStr">
+      <c r="A29" s="492" t="inlineStr">
         <is>
           <t>MB21</t>
         </is>
       </c>
-      <c r="B29" s="495" t="n"/>
-      <c r="C29" s="495" t="n"/>
-      <c r="D29" s="495" t="n"/>
-      <c r="F29" s="496" t="inlineStr">
+      <c r="B29" s="493" t="n"/>
+      <c r="C29" s="493" t="n"/>
+      <c r="D29" s="493" t="n"/>
+      <c r="F29" s="494" t="inlineStr">
         <is>
           <t>MB22</t>
         </is>
       </c>
-      <c r="G29" s="497" t="n"/>
-      <c r="H29" s="497" t="n"/>
-      <c r="I29" s="497" t="n"/>
-      <c r="K29" s="498" t="inlineStr">
+      <c r="G29" s="495" t="n"/>
+      <c r="H29" s="495" t="n"/>
+      <c r="I29" s="495" t="n"/>
+      <c r="K29" s="496" t="inlineStr">
         <is>
           <t>MB23</t>
         </is>
       </c>
-      <c r="L29" s="499" t="n"/>
-      <c r="M29" s="499" t="n"/>
-      <c r="N29" s="499" t="n"/>
-      <c r="P29" s="500" t="inlineStr">
+      <c r="L29" s="497" t="n"/>
+      <c r="M29" s="497" t="n"/>
+      <c r="N29" s="497" t="n"/>
+      <c r="P29" s="498" t="inlineStr">
         <is>
           <t>MB24</t>
         </is>
       </c>
-      <c r="Q29" s="501" t="n"/>
-      <c r="R29" s="501" t="n"/>
-      <c r="S29" s="501" t="n"/>
+      <c r="Q29" s="499" t="n"/>
+      <c r="R29" s="499" t="n"/>
+      <c r="S29" s="499" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="495" t="n"/>
-      <c r="B30" s="495" t="n"/>
-      <c r="C30" s="495" t="n"/>
-      <c r="D30" s="495" t="n"/>
-      <c r="F30" s="497" t="n"/>
-      <c r="G30" s="497" t="n"/>
-      <c r="H30" s="497" t="n"/>
-      <c r="I30" s="497" t="n"/>
-      <c r="K30" s="499" t="n"/>
-      <c r="L30" s="499" t="n"/>
-      <c r="M30" s="499" t="n"/>
-      <c r="N30" s="499" t="n"/>
-      <c r="P30" s="501" t="n"/>
-      <c r="Q30" s="501" t="n"/>
-      <c r="R30" s="501" t="n"/>
-      <c r="S30" s="501" t="n"/>
+      <c r="A30" s="493" t="n"/>
+      <c r="B30" s="493" t="n"/>
+      <c r="C30" s="493" t="n"/>
+      <c r="D30" s="493" t="n"/>
+      <c r="F30" s="495" t="n"/>
+      <c r="G30" s="495" t="n"/>
+      <c r="H30" s="495" t="n"/>
+      <c r="I30" s="495" t="n"/>
+      <c r="K30" s="497" t="n"/>
+      <c r="L30" s="497" t="n"/>
+      <c r="M30" s="497" t="n"/>
+      <c r="N30" s="497" t="n"/>
+      <c r="P30" s="499" t="n"/>
+      <c r="Q30" s="499" t="n"/>
+      <c r="R30" s="499" t="n"/>
+      <c r="S30" s="499" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -21173,56 +21160,56 @@
       <c r="S33" s="15" t="n"/>
     </row>
     <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="502" t="inlineStr">
+      <c r="A34" s="500" t="inlineStr">
         <is>
           <t>MB25</t>
         </is>
       </c>
-      <c r="B34" s="503" t="n"/>
-      <c r="C34" s="503" t="n"/>
-      <c r="D34" s="503" t="n"/>
-      <c r="F34" s="504" t="inlineStr">
+      <c r="B34" s="501" t="n"/>
+      <c r="C34" s="501" t="n"/>
+      <c r="D34" s="501" t="n"/>
+      <c r="F34" s="502" t="inlineStr">
         <is>
           <t>MB26</t>
         </is>
       </c>
-      <c r="G34" s="505" t="n"/>
-      <c r="H34" s="505" t="n"/>
-      <c r="I34" s="505" t="n"/>
-      <c r="K34" s="506" t="inlineStr">
+      <c r="G34" s="503" t="n"/>
+      <c r="H34" s="503" t="n"/>
+      <c r="I34" s="503" t="n"/>
+      <c r="K34" s="504" t="inlineStr">
         <is>
           <t>MB27</t>
         </is>
       </c>
-      <c r="L34" s="507" t="n"/>
-      <c r="M34" s="507" t="n"/>
-      <c r="N34" s="507" t="n"/>
-      <c r="P34" s="508" t="inlineStr">
+      <c r="L34" s="505" t="n"/>
+      <c r="M34" s="505" t="n"/>
+      <c r="N34" s="505" t="n"/>
+      <c r="P34" s="506" t="inlineStr">
         <is>
           <t>MB28</t>
         </is>
       </c>
-      <c r="Q34" s="509" t="n"/>
-      <c r="R34" s="509" t="n"/>
-      <c r="S34" s="509" t="n"/>
+      <c r="Q34" s="507" t="n"/>
+      <c r="R34" s="507" t="n"/>
+      <c r="S34" s="507" t="n"/>
     </row>
     <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="503" t="n"/>
-      <c r="B35" s="503" t="n"/>
-      <c r="C35" s="503" t="n"/>
-      <c r="D35" s="503" t="n"/>
-      <c r="F35" s="505" t="n"/>
-      <c r="G35" s="505" t="n"/>
-      <c r="H35" s="505" t="n"/>
-      <c r="I35" s="505" t="n"/>
-      <c r="K35" s="507" t="n"/>
-      <c r="L35" s="507" t="n"/>
-      <c r="M35" s="507" t="n"/>
-      <c r="N35" s="507" t="n"/>
-      <c r="P35" s="509" t="n"/>
-      <c r="Q35" s="509" t="n"/>
-      <c r="R35" s="509" t="n"/>
-      <c r="S35" s="509" t="n"/>
+      <c r="A35" s="501" t="n"/>
+      <c r="B35" s="501" t="n"/>
+      <c r="C35" s="501" t="n"/>
+      <c r="D35" s="501" t="n"/>
+      <c r="F35" s="503" t="n"/>
+      <c r="G35" s="503" t="n"/>
+      <c r="H35" s="503" t="n"/>
+      <c r="I35" s="503" t="n"/>
+      <c r="K35" s="505" t="n"/>
+      <c r="L35" s="505" t="n"/>
+      <c r="M35" s="505" t="n"/>
+      <c r="N35" s="505" t="n"/>
+      <c r="P35" s="507" t="n"/>
+      <c r="Q35" s="507" t="n"/>
+      <c r="R35" s="507" t="n"/>
+      <c r="S35" s="507" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -21327,56 +21314,56 @@
       <c r="S38" s="15" t="n"/>
     </row>
     <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="510" t="inlineStr">
+      <c r="A39" s="508" t="inlineStr">
         <is>
           <t>MB29</t>
         </is>
       </c>
-      <c r="B39" s="511" t="n"/>
-      <c r="C39" s="511" t="n"/>
-      <c r="D39" s="511" t="n"/>
-      <c r="F39" s="512" t="inlineStr">
+      <c r="B39" s="509" t="n"/>
+      <c r="C39" s="509" t="n"/>
+      <c r="D39" s="509" t="n"/>
+      <c r="F39" s="510" t="inlineStr">
         <is>
           <t>MB30</t>
         </is>
       </c>
-      <c r="G39" s="513" t="n"/>
-      <c r="H39" s="513" t="n"/>
-      <c r="I39" s="513" t="n"/>
-      <c r="K39" s="514" t="inlineStr">
+      <c r="G39" s="511" t="n"/>
+      <c r="H39" s="511" t="n"/>
+      <c r="I39" s="511" t="n"/>
+      <c r="K39" s="512" t="inlineStr">
         <is>
           <t>MB31</t>
         </is>
       </c>
-      <c r="L39" s="515" t="n"/>
-      <c r="M39" s="515" t="n"/>
-      <c r="N39" s="515" t="n"/>
-      <c r="P39" s="516" t="inlineStr">
+      <c r="L39" s="513" t="n"/>
+      <c r="M39" s="513" t="n"/>
+      <c r="N39" s="513" t="n"/>
+      <c r="P39" s="514" t="inlineStr">
         <is>
           <t>MB32</t>
         </is>
       </c>
-      <c r="Q39" s="517" t="n"/>
-      <c r="R39" s="517" t="n"/>
-      <c r="S39" s="517" t="n"/>
+      <c r="Q39" s="515" t="n"/>
+      <c r="R39" s="515" t="n"/>
+      <c r="S39" s="515" t="n"/>
     </row>
     <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="511" t="n"/>
-      <c r="B40" s="511" t="n"/>
-      <c r="C40" s="511" t="n"/>
-      <c r="D40" s="511" t="n"/>
-      <c r="F40" s="513" t="n"/>
-      <c r="G40" s="513" t="n"/>
-      <c r="H40" s="513" t="n"/>
-      <c r="I40" s="513" t="n"/>
-      <c r="K40" s="515" t="n"/>
-      <c r="L40" s="515" t="n"/>
-      <c r="M40" s="515" t="n"/>
-      <c r="N40" s="515" t="n"/>
-      <c r="P40" s="517" t="n"/>
-      <c r="Q40" s="517" t="n"/>
-      <c r="R40" s="517" t="n"/>
-      <c r="S40" s="517" t="n"/>
+      <c r="A40" s="509" t="n"/>
+      <c r="B40" s="509" t="n"/>
+      <c r="C40" s="509" t="n"/>
+      <c r="D40" s="509" t="n"/>
+      <c r="F40" s="511" t="n"/>
+      <c r="G40" s="511" t="n"/>
+      <c r="H40" s="511" t="n"/>
+      <c r="I40" s="511" t="n"/>
+      <c r="K40" s="513" t="n"/>
+      <c r="L40" s="513" t="n"/>
+      <c r="M40" s="513" t="n"/>
+      <c r="N40" s="513" t="n"/>
+      <c r="P40" s="515" t="n"/>
+      <c r="Q40" s="515" t="n"/>
+      <c r="R40" s="515" t="n"/>
+      <c r="S40" s="515" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
@@ -21660,56 +21647,56 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="518" t="inlineStr">
+      <c r="A4" s="516" t="inlineStr">
         <is>
           <t>MC1</t>
         </is>
       </c>
-      <c r="B4" s="519" t="n"/>
-      <c r="C4" s="519" t="n"/>
-      <c r="D4" s="519" t="n"/>
-      <c r="F4" s="520" t="inlineStr">
+      <c r="B4" s="517" t="n"/>
+      <c r="C4" s="517" t="n"/>
+      <c r="D4" s="517" t="n"/>
+      <c r="F4" s="518" t="inlineStr">
         <is>
           <t>MC2</t>
         </is>
       </c>
-      <c r="G4" s="521" t="n"/>
-      <c r="H4" s="521" t="n"/>
-      <c r="I4" s="521" t="n"/>
-      <c r="K4" s="522" t="inlineStr">
+      <c r="G4" s="519" t="n"/>
+      <c r="H4" s="519" t="n"/>
+      <c r="I4" s="519" t="n"/>
+      <c r="K4" s="520" t="inlineStr">
         <is>
           <t>MC3</t>
         </is>
       </c>
-      <c r="L4" s="523" t="n"/>
-      <c r="M4" s="523" t="n"/>
-      <c r="N4" s="523" t="n"/>
-      <c r="P4" s="524" t="inlineStr">
+      <c r="L4" s="521" t="n"/>
+      <c r="M4" s="521" t="n"/>
+      <c r="N4" s="521" t="n"/>
+      <c r="P4" s="522" t="inlineStr">
         <is>
           <t>MC4</t>
         </is>
       </c>
-      <c r="Q4" s="525" t="n"/>
-      <c r="R4" s="525" t="n"/>
-      <c r="S4" s="525" t="n"/>
+      <c r="Q4" s="523" t="n"/>
+      <c r="R4" s="523" t="n"/>
+      <c r="S4" s="523" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="519" t="n"/>
-      <c r="B5" s="519" t="n"/>
-      <c r="C5" s="519" t="n"/>
-      <c r="D5" s="519" t="n"/>
-      <c r="F5" s="521" t="n"/>
-      <c r="G5" s="521" t="n"/>
-      <c r="H5" s="521" t="n"/>
-      <c r="I5" s="521" t="n"/>
-      <c r="K5" s="523" t="n"/>
-      <c r="L5" s="523" t="n"/>
-      <c r="M5" s="523" t="n"/>
-      <c r="N5" s="523" t="n"/>
-      <c r="P5" s="525" t="n"/>
-      <c r="Q5" s="525" t="n"/>
-      <c r="R5" s="525" t="n"/>
-      <c r="S5" s="525" t="n"/>
+      <c r="A5" s="517" t="n"/>
+      <c r="B5" s="517" t="n"/>
+      <c r="C5" s="517" t="n"/>
+      <c r="D5" s="517" t="n"/>
+      <c r="F5" s="519" t="n"/>
+      <c r="G5" s="519" t="n"/>
+      <c r="H5" s="519" t="n"/>
+      <c r="I5" s="519" t="n"/>
+      <c r="K5" s="521" t="n"/>
+      <c r="L5" s="521" t="n"/>
+      <c r="M5" s="521" t="n"/>
+      <c r="N5" s="521" t="n"/>
+      <c r="P5" s="523" t="n"/>
+      <c r="Q5" s="523" t="n"/>
+      <c r="R5" s="523" t="n"/>
+      <c r="S5" s="523" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -21814,56 +21801,56 @@
       <c r="S8" s="15" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="526" t="inlineStr">
+      <c r="A9" s="524" t="inlineStr">
         <is>
           <t>MC5</t>
         </is>
       </c>
-      <c r="B9" s="527" t="n"/>
-      <c r="C9" s="527" t="n"/>
-      <c r="D9" s="527" t="n"/>
-      <c r="F9" s="528" t="inlineStr">
+      <c r="B9" s="525" t="n"/>
+      <c r="C9" s="525" t="n"/>
+      <c r="D9" s="525" t="n"/>
+      <c r="F9" s="526" t="inlineStr">
         <is>
           <t>MC6</t>
         </is>
       </c>
-      <c r="G9" s="529" t="n"/>
-      <c r="H9" s="529" t="n"/>
-      <c r="I9" s="529" t="n"/>
-      <c r="K9" s="530" t="inlineStr">
+      <c r="G9" s="527" t="n"/>
+      <c r="H9" s="527" t="n"/>
+      <c r="I9" s="527" t="n"/>
+      <c r="K9" s="528" t="inlineStr">
         <is>
           <t>MC7</t>
         </is>
       </c>
-      <c r="L9" s="531" t="n"/>
-      <c r="M9" s="531" t="n"/>
-      <c r="N9" s="531" t="n"/>
-      <c r="P9" s="532" t="inlineStr">
+      <c r="L9" s="529" t="n"/>
+      <c r="M9" s="529" t="n"/>
+      <c r="N9" s="529" t="n"/>
+      <c r="P9" s="530" t="inlineStr">
         <is>
           <t>MC8</t>
         </is>
       </c>
-      <c r="Q9" s="533" t="n"/>
-      <c r="R9" s="533" t="n"/>
-      <c r="S9" s="533" t="n"/>
+      <c r="Q9" s="531" t="n"/>
+      <c r="R9" s="531" t="n"/>
+      <c r="S9" s="531" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="527" t="n"/>
-      <c r="B10" s="527" t="n"/>
-      <c r="C10" s="527" t="n"/>
-      <c r="D10" s="527" t="n"/>
-      <c r="F10" s="529" t="n"/>
-      <c r="G10" s="529" t="n"/>
-      <c r="H10" s="529" t="n"/>
-      <c r="I10" s="529" t="n"/>
-      <c r="K10" s="531" t="n"/>
-      <c r="L10" s="531" t="n"/>
-      <c r="M10" s="531" t="n"/>
-      <c r="N10" s="531" t="n"/>
-      <c r="P10" s="533" t="n"/>
-      <c r="Q10" s="533" t="n"/>
-      <c r="R10" s="533" t="n"/>
-      <c r="S10" s="533" t="n"/>
+      <c r="A10" s="525" t="n"/>
+      <c r="B10" s="525" t="n"/>
+      <c r="C10" s="525" t="n"/>
+      <c r="D10" s="525" t="n"/>
+      <c r="F10" s="527" t="n"/>
+      <c r="G10" s="527" t="n"/>
+      <c r="H10" s="527" t="n"/>
+      <c r="I10" s="527" t="n"/>
+      <c r="K10" s="529" t="n"/>
+      <c r="L10" s="529" t="n"/>
+      <c r="M10" s="529" t="n"/>
+      <c r="N10" s="529" t="n"/>
+      <c r="P10" s="531" t="n"/>
+      <c r="Q10" s="531" t="n"/>
+      <c r="R10" s="531" t="n"/>
+      <c r="S10" s="531" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -21968,56 +21955,56 @@
       <c r="S13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="534" t="inlineStr">
+      <c r="A14" s="532" t="inlineStr">
         <is>
           <t>MC9</t>
         </is>
       </c>
-      <c r="B14" s="535" t="n"/>
-      <c r="C14" s="535" t="n"/>
-      <c r="D14" s="535" t="n"/>
-      <c r="F14" s="536" t="inlineStr">
+      <c r="B14" s="533" t="n"/>
+      <c r="C14" s="533" t="n"/>
+      <c r="D14" s="533" t="n"/>
+      <c r="F14" s="534" t="inlineStr">
         <is>
           <t>MC10</t>
         </is>
       </c>
-      <c r="G14" s="537" t="n"/>
-      <c r="H14" s="537" t="n"/>
-      <c r="I14" s="537" t="n"/>
-      <c r="K14" s="538" t="inlineStr">
+      <c r="G14" s="535" t="n"/>
+      <c r="H14" s="535" t="n"/>
+      <c r="I14" s="535" t="n"/>
+      <c r="K14" s="536" t="inlineStr">
         <is>
           <t>MC11</t>
         </is>
       </c>
-      <c r="L14" s="539" t="n"/>
-      <c r="M14" s="539" t="n"/>
-      <c r="N14" s="539" t="n"/>
-      <c r="P14" s="540" t="inlineStr">
+      <c r="L14" s="537" t="n"/>
+      <c r="M14" s="537" t="n"/>
+      <c r="N14" s="537" t="n"/>
+      <c r="P14" s="538" t="inlineStr">
         <is>
           <t>MC12</t>
         </is>
       </c>
-      <c r="Q14" s="541" t="n"/>
-      <c r="R14" s="541" t="n"/>
-      <c r="S14" s="541" t="n"/>
+      <c r="Q14" s="539" t="n"/>
+      <c r="R14" s="539" t="n"/>
+      <c r="S14" s="539" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="535" t="n"/>
-      <c r="B15" s="535" t="n"/>
-      <c r="C15" s="535" t="n"/>
-      <c r="D15" s="535" t="n"/>
-      <c r="F15" s="537" t="n"/>
-      <c r="G15" s="537" t="n"/>
-      <c r="H15" s="537" t="n"/>
-      <c r="I15" s="537" t="n"/>
-      <c r="K15" s="539" t="n"/>
-      <c r="L15" s="539" t="n"/>
-      <c r="M15" s="539" t="n"/>
-      <c r="N15" s="539" t="n"/>
-      <c r="P15" s="541" t="n"/>
-      <c r="Q15" s="541" t="n"/>
-      <c r="R15" s="541" t="n"/>
-      <c r="S15" s="541" t="n"/>
+      <c r="A15" s="533" t="n"/>
+      <c r="B15" s="533" t="n"/>
+      <c r="C15" s="533" t="n"/>
+      <c r="D15" s="533" t="n"/>
+      <c r="F15" s="535" t="n"/>
+      <c r="G15" s="535" t="n"/>
+      <c r="H15" s="535" t="n"/>
+      <c r="I15" s="535" t="n"/>
+      <c r="K15" s="537" t="n"/>
+      <c r="L15" s="537" t="n"/>
+      <c r="M15" s="537" t="n"/>
+      <c r="N15" s="537" t="n"/>
+      <c r="P15" s="539" t="n"/>
+      <c r="Q15" s="539" t="n"/>
+      <c r="R15" s="539" t="n"/>
+      <c r="S15" s="539" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -22122,56 +22109,56 @@
       <c r="S18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="542" t="inlineStr">
+      <c r="A19" s="540" t="inlineStr">
         <is>
           <t>MC13</t>
         </is>
       </c>
-      <c r="B19" s="543" t="n"/>
-      <c r="C19" s="543" t="n"/>
-      <c r="D19" s="543" t="n"/>
-      <c r="F19" s="544" t="inlineStr">
+      <c r="B19" s="541" t="n"/>
+      <c r="C19" s="541" t="n"/>
+      <c r="D19" s="541" t="n"/>
+      <c r="F19" s="542" t="inlineStr">
         <is>
           <t>MC14</t>
         </is>
       </c>
-      <c r="G19" s="545" t="n"/>
-      <c r="H19" s="545" t="n"/>
-      <c r="I19" s="545" t="n"/>
-      <c r="K19" s="546" t="inlineStr">
+      <c r="G19" s="543" t="n"/>
+      <c r="H19" s="543" t="n"/>
+      <c r="I19" s="543" t="n"/>
+      <c r="K19" s="544" t="inlineStr">
         <is>
           <t>MC15</t>
         </is>
       </c>
-      <c r="L19" s="547" t="n"/>
-      <c r="M19" s="547" t="n"/>
-      <c r="N19" s="547" t="n"/>
-      <c r="P19" s="548" t="inlineStr">
+      <c r="L19" s="545" t="n"/>
+      <c r="M19" s="545" t="n"/>
+      <c r="N19" s="545" t="n"/>
+      <c r="P19" s="546" t="inlineStr">
         <is>
           <t>MC16</t>
         </is>
       </c>
-      <c r="Q19" s="549" t="n"/>
-      <c r="R19" s="549" t="n"/>
-      <c r="S19" s="549" t="n"/>
+      <c r="Q19" s="547" t="n"/>
+      <c r="R19" s="547" t="n"/>
+      <c r="S19" s="547" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="543" t="n"/>
-      <c r="B20" s="543" t="n"/>
-      <c r="C20" s="543" t="n"/>
-      <c r="D20" s="543" t="n"/>
-      <c r="F20" s="545" t="n"/>
-      <c r="G20" s="545" t="n"/>
-      <c r="H20" s="545" t="n"/>
-      <c r="I20" s="545" t="n"/>
-      <c r="K20" s="547" t="n"/>
-      <c r="L20" s="547" t="n"/>
-      <c r="M20" s="547" t="n"/>
-      <c r="N20" s="547" t="n"/>
-      <c r="P20" s="549" t="n"/>
-      <c r="Q20" s="549" t="n"/>
-      <c r="R20" s="549" t="n"/>
-      <c r="S20" s="549" t="n"/>
+      <c r="A20" s="541" t="n"/>
+      <c r="B20" s="541" t="n"/>
+      <c r="C20" s="541" t="n"/>
+      <c r="D20" s="541" t="n"/>
+      <c r="F20" s="543" t="n"/>
+      <c r="G20" s="543" t="n"/>
+      <c r="H20" s="543" t="n"/>
+      <c r="I20" s="543" t="n"/>
+      <c r="K20" s="545" t="n"/>
+      <c r="L20" s="545" t="n"/>
+      <c r="M20" s="545" t="n"/>
+      <c r="N20" s="545" t="n"/>
+      <c r="P20" s="547" t="n"/>
+      <c r="Q20" s="547" t="n"/>
+      <c r="R20" s="547" t="n"/>
+      <c r="S20" s="547" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -22276,56 +22263,56 @@
       <c r="S23" s="15" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="550" t="inlineStr">
+      <c r="A24" s="548" t="inlineStr">
         <is>
           <t>MC17</t>
         </is>
       </c>
-      <c r="B24" s="551" t="n"/>
-      <c r="C24" s="551" t="n"/>
-      <c r="D24" s="551" t="n"/>
-      <c r="F24" s="552" t="inlineStr">
+      <c r="B24" s="549" t="n"/>
+      <c r="C24" s="549" t="n"/>
+      <c r="D24" s="549" t="n"/>
+      <c r="F24" s="550" t="inlineStr">
         <is>
           <t>MC18</t>
         </is>
       </c>
-      <c r="G24" s="553" t="n"/>
-      <c r="H24" s="553" t="n"/>
-      <c r="I24" s="553" t="n"/>
-      <c r="K24" s="554" t="inlineStr">
+      <c r="G24" s="551" t="n"/>
+      <c r="H24" s="551" t="n"/>
+      <c r="I24" s="551" t="n"/>
+      <c r="K24" s="552" t="inlineStr">
         <is>
           <t>MC19</t>
         </is>
       </c>
-      <c r="L24" s="555" t="n"/>
-      <c r="M24" s="555" t="n"/>
-      <c r="N24" s="555" t="n"/>
-      <c r="P24" s="556" t="inlineStr">
+      <c r="L24" s="553" t="n"/>
+      <c r="M24" s="553" t="n"/>
+      <c r="N24" s="553" t="n"/>
+      <c r="P24" s="554" t="inlineStr">
         <is>
           <t>MC20</t>
         </is>
       </c>
-      <c r="Q24" s="557" t="n"/>
-      <c r="R24" s="557" t="n"/>
-      <c r="S24" s="557" t="n"/>
+      <c r="Q24" s="555" t="n"/>
+      <c r="R24" s="555" t="n"/>
+      <c r="S24" s="555" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="551" t="n"/>
-      <c r="B25" s="551" t="n"/>
-      <c r="C25" s="551" t="n"/>
-      <c r="D25" s="551" t="n"/>
-      <c r="F25" s="553" t="n"/>
-      <c r="G25" s="553" t="n"/>
-      <c r="H25" s="553" t="n"/>
-      <c r="I25" s="553" t="n"/>
-      <c r="K25" s="555" t="n"/>
-      <c r="L25" s="555" t="n"/>
-      <c r="M25" s="555" t="n"/>
-      <c r="N25" s="555" t="n"/>
-      <c r="P25" s="557" t="n"/>
-      <c r="Q25" s="557" t="n"/>
-      <c r="R25" s="557" t="n"/>
-      <c r="S25" s="557" t="n"/>
+      <c r="A25" s="549" t="n"/>
+      <c r="B25" s="549" t="n"/>
+      <c r="C25" s="549" t="n"/>
+      <c r="D25" s="549" t="n"/>
+      <c r="F25" s="551" t="n"/>
+      <c r="G25" s="551" t="n"/>
+      <c r="H25" s="551" t="n"/>
+      <c r="I25" s="551" t="n"/>
+      <c r="K25" s="553" t="n"/>
+      <c r="L25" s="553" t="n"/>
+      <c r="M25" s="553" t="n"/>
+      <c r="N25" s="553" t="n"/>
+      <c r="P25" s="555" t="n"/>
+      <c r="Q25" s="555" t="n"/>
+      <c r="R25" s="555" t="n"/>
+      <c r="S25" s="555" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
@@ -22430,56 +22417,56 @@
       <c r="S28" s="15" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="558" t="inlineStr">
+      <c r="A29" s="556" t="inlineStr">
         <is>
           <t>MC21</t>
         </is>
       </c>
-      <c r="B29" s="559" t="n"/>
-      <c r="C29" s="559" t="n"/>
-      <c r="D29" s="559" t="n"/>
-      <c r="F29" s="560" t="inlineStr">
+      <c r="B29" s="557" t="n"/>
+      <c r="C29" s="557" t="n"/>
+      <c r="D29" s="557" t="n"/>
+      <c r="F29" s="558" t="inlineStr">
         <is>
           <t>MC22</t>
         </is>
       </c>
-      <c r="G29" s="561" t="n"/>
-      <c r="H29" s="561" t="n"/>
-      <c r="I29" s="561" t="n"/>
-      <c r="K29" s="562" t="inlineStr">
+      <c r="G29" s="559" t="n"/>
+      <c r="H29" s="559" t="n"/>
+      <c r="I29" s="559" t="n"/>
+      <c r="K29" s="560" t="inlineStr">
         <is>
           <t>MC23</t>
         </is>
       </c>
-      <c r="L29" s="563" t="n"/>
-      <c r="M29" s="563" t="n"/>
-      <c r="N29" s="563" t="n"/>
-      <c r="P29" s="564" t="inlineStr">
+      <c r="L29" s="561" t="n"/>
+      <c r="M29" s="561" t="n"/>
+      <c r="N29" s="561" t="n"/>
+      <c r="P29" s="562" t="inlineStr">
         <is>
           <t>MC24</t>
         </is>
       </c>
-      <c r="Q29" s="565" t="n"/>
-      <c r="R29" s="565" t="n"/>
-      <c r="S29" s="565" t="n"/>
+      <c r="Q29" s="563" t="n"/>
+      <c r="R29" s="563" t="n"/>
+      <c r="S29" s="563" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="559" t="n"/>
-      <c r="B30" s="559" t="n"/>
-      <c r="C30" s="559" t="n"/>
-      <c r="D30" s="559" t="n"/>
-      <c r="F30" s="561" t="n"/>
-      <c r="G30" s="561" t="n"/>
-      <c r="H30" s="561" t="n"/>
-      <c r="I30" s="561" t="n"/>
-      <c r="K30" s="563" t="n"/>
-      <c r="L30" s="563" t="n"/>
-      <c r="M30" s="563" t="n"/>
-      <c r="N30" s="563" t="n"/>
-      <c r="P30" s="565" t="n"/>
-      <c r="Q30" s="565" t="n"/>
-      <c r="R30" s="565" t="n"/>
-      <c r="S30" s="565" t="n"/>
+      <c r="A30" s="557" t="n"/>
+      <c r="B30" s="557" t="n"/>
+      <c r="C30" s="557" t="n"/>
+      <c r="D30" s="557" t="n"/>
+      <c r="F30" s="559" t="n"/>
+      <c r="G30" s="559" t="n"/>
+      <c r="H30" s="559" t="n"/>
+      <c r="I30" s="559" t="n"/>
+      <c r="K30" s="561" t="n"/>
+      <c r="L30" s="561" t="n"/>
+      <c r="M30" s="561" t="n"/>
+      <c r="N30" s="561" t="n"/>
+      <c r="P30" s="563" t="n"/>
+      <c r="Q30" s="563" t="n"/>
+      <c r="R30" s="563" t="n"/>
+      <c r="S30" s="563" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -22584,56 +22571,56 @@
       <c r="S33" s="15" t="n"/>
     </row>
     <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="566" t="inlineStr">
+      <c r="A34" s="564" t="inlineStr">
         <is>
           <t>MC25</t>
         </is>
       </c>
-      <c r="B34" s="567" t="n"/>
-      <c r="C34" s="567" t="n"/>
-      <c r="D34" s="567" t="n"/>
-      <c r="F34" s="568" t="inlineStr">
+      <c r="B34" s="565" t="n"/>
+      <c r="C34" s="565" t="n"/>
+      <c r="D34" s="565" t="n"/>
+      <c r="F34" s="566" t="inlineStr">
         <is>
           <t>MC26</t>
         </is>
       </c>
-      <c r="G34" s="569" t="n"/>
-      <c r="H34" s="569" t="n"/>
-      <c r="I34" s="569" t="n"/>
-      <c r="K34" s="570" t="inlineStr">
+      <c r="G34" s="567" t="n"/>
+      <c r="H34" s="567" t="n"/>
+      <c r="I34" s="567" t="n"/>
+      <c r="K34" s="568" t="inlineStr">
         <is>
           <t>MC27</t>
         </is>
       </c>
-      <c r="L34" s="571" t="n"/>
-      <c r="M34" s="571" t="n"/>
-      <c r="N34" s="571" t="n"/>
-      <c r="P34" s="572" t="inlineStr">
+      <c r="L34" s="569" t="n"/>
+      <c r="M34" s="569" t="n"/>
+      <c r="N34" s="569" t="n"/>
+      <c r="P34" s="570" t="inlineStr">
         <is>
           <t>MC28</t>
         </is>
       </c>
-      <c r="Q34" s="573" t="n"/>
-      <c r="R34" s="573" t="n"/>
-      <c r="S34" s="573" t="n"/>
+      <c r="Q34" s="571" t="n"/>
+      <c r="R34" s="571" t="n"/>
+      <c r="S34" s="571" t="n"/>
     </row>
     <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="567" t="n"/>
-      <c r="B35" s="567" t="n"/>
-      <c r="C35" s="567" t="n"/>
-      <c r="D35" s="567" t="n"/>
-      <c r="F35" s="569" t="n"/>
-      <c r="G35" s="569" t="n"/>
-      <c r="H35" s="569" t="n"/>
-      <c r="I35" s="569" t="n"/>
-      <c r="K35" s="571" t="n"/>
-      <c r="L35" s="571" t="n"/>
-      <c r="M35" s="571" t="n"/>
-      <c r="N35" s="571" t="n"/>
-      <c r="P35" s="573" t="n"/>
-      <c r="Q35" s="573" t="n"/>
-      <c r="R35" s="573" t="n"/>
-      <c r="S35" s="573" t="n"/>
+      <c r="A35" s="565" t="n"/>
+      <c r="B35" s="565" t="n"/>
+      <c r="C35" s="565" t="n"/>
+      <c r="D35" s="565" t="n"/>
+      <c r="F35" s="567" t="n"/>
+      <c r="G35" s="567" t="n"/>
+      <c r="H35" s="567" t="n"/>
+      <c r="I35" s="567" t="n"/>
+      <c r="K35" s="569" t="n"/>
+      <c r="L35" s="569" t="n"/>
+      <c r="M35" s="569" t="n"/>
+      <c r="N35" s="569" t="n"/>
+      <c r="P35" s="571" t="n"/>
+      <c r="Q35" s="571" t="n"/>
+      <c r="R35" s="571" t="n"/>
+      <c r="S35" s="571" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -22738,20 +22725,20 @@
       <c r="S38" s="15" t="n"/>
     </row>
     <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="574" t="inlineStr">
+      <c r="A39" s="572" t="inlineStr">
         <is>
           <t>MC29</t>
         </is>
       </c>
-      <c r="B39" s="575" t="n"/>
-      <c r="C39" s="575" t="n"/>
-      <c r="D39" s="575" t="n"/>
+      <c r="B39" s="573" t="n"/>
+      <c r="C39" s="573" t="n"/>
+      <c r="D39" s="573" t="n"/>
     </row>
     <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="575" t="n"/>
-      <c r="B40" s="575" t="n"/>
-      <c r="C40" s="575" t="n"/>
-      <c r="D40" s="575" t="n"/>
+      <c r="A40" s="573" t="n"/>
+      <c r="B40" s="573" t="n"/>
+      <c r="C40" s="573" t="n"/>
+      <c r="D40" s="573" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
